--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -512,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H111"/>
+  <dimension ref="A1:H108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -666,15 +666,15 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>63</v>
-      </c>
-      <c r="B8" s="7" t="n"/>
+        <v>62</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D8" s="7" t="n"/>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="7" t="n"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>James Cook III</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C9" s="7" t="n"/>
@@ -698,13 +698,13 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Puka Nacua</t>
         </is>
       </c>
       <c r="E10" s="7" t="n"/>
@@ -714,13 +714,13 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -730,15 +730,15 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="B12" s="7" t="n"/>
+        <v>59</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D12" s="7" t="n"/>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="n"/>
@@ -746,15 +746,15 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>56</v>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
@@ -762,15 +762,15 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
@@ -778,11 +778,11 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="C15" s="7" t="n"/>
@@ -794,7 +794,7 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
@@ -810,15 +810,15 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
@@ -826,15 +826,15 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="B18" s="7" t="n"/>
+        <v>45</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
@@ -874,11 +874,11 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>De'Von Achane</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C21" s="7" t="n"/>
@@ -894,7 +894,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>De'Von Achane</t>
         </is>
       </c>
       <c r="C22" s="7" t="n"/>
@@ -906,15 +906,15 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="B23" s="7" t="n"/>
+        <v>37</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
@@ -922,47 +922,47 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="n"/>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="B26" s="7" t="n"/>
+        <v>35</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
@@ -970,13 +970,13 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Nico Collins</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E27" s="7" t="n"/>
@@ -986,11 +986,11 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C28" s="7" t="n"/>
@@ -1002,31 +1002,31 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D29" s="7" t="n"/>
       <c r="E29" s="7" t="n"/>
-      <c r="F29" s="7" t="n"/>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G29" s="7" t="n"/>
       <c r="H29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="n"/>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E30" s="7" t="n"/>
       <c r="F30" s="7" t="n"/>
       <c r="G30" s="7" t="n"/>
@@ -1034,13 +1034,13 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>Nico Collins</t>
         </is>
       </c>
       <c r="E31" s="7" t="n"/>
@@ -1050,15 +1050,15 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
@@ -1066,29 +1066,29 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="B33" s="7" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C33" s="7" t="n"/>
       <c r="D33" s="7" t="n"/>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E34" s="7" t="n"/>
@@ -1098,45 +1098,45 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D35" s="7" t="n"/>
       <c r="E35" s="7" t="n"/>
-      <c r="F35" s="7" t="n"/>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G35" s="7" t="n"/>
       <c r="H35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D36" s="7" t="n"/>
       <c r="E36" s="7" t="n"/>
       <c r="F36" s="7" t="n"/>
       <c r="G36" s="7" t="n"/>
-      <c r="H36" s="7" t="n"/>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E37" s="7" t="n"/>
@@ -1146,13 +1146,13 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E38" s="7" t="n"/>
@@ -1162,13 +1162,13 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E39" s="7" t="n"/>
@@ -1178,29 +1178,29 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="n"/>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E40" s="7" t="n"/>
-      <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
       <c r="H40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E41" s="7" t="n"/>
@@ -1210,31 +1210,31 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B42" s="7" t="n"/>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="n"/>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="7" t="n"/>
-      <c r="H42" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B43" s="7" t="n"/>
       <c r="C43" s="7" t="n"/>
-      <c r="D43" s="7" t="n"/>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E43" s="7" t="n"/>
       <c r="F43" s="7" t="n"/>
       <c r="G43" s="7" t="n"/>
@@ -1242,11 +1242,11 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Jadarian Price</t>
         </is>
       </c>
       <c r="C44" s="7" t="n"/>
@@ -1260,13 +1260,13 @@
       <c r="A45" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B45" s="7" t="n"/>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D45" s="7" t="n"/>
       <c r="E45" s="7" t="n"/>
       <c r="F45" s="7" t="n"/>
       <c r="G45" s="7" t="n"/>
@@ -1552,7 +1552,7 @@
       <c r="C63" s="7" t="n"/>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E63" s="7" t="n"/>
@@ -1568,7 +1568,7 @@
       <c r="C64" s="7" t="n"/>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E64" s="7" t="n"/>
@@ -1582,13 +1582,13 @@
       </c>
       <c r="B65" s="7" t="n"/>
       <c r="C65" s="7" t="n"/>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D65" s="7" t="n"/>
       <c r="E65" s="7" t="n"/>
-      <c r="F65" s="7" t="n"/>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G65" s="7" t="n"/>
       <c r="H65" s="7" t="n"/>
     </row>
@@ -1600,7 +1600,7 @@
       <c r="C66" s="7" t="n"/>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E66" s="7" t="n"/>
@@ -1610,15 +1610,15 @@
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B67" s="7" t="n"/>
       <c r="C67" s="7" t="n"/>
-      <c r="D67" s="7" t="n"/>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E67" s="7" t="n"/>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
@@ -1628,13 +1628,13 @@
       <c r="A68" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B68" s="7" t="n"/>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C68" s="7" t="n"/>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>De'Zhaun Stribling</t>
-        </is>
-      </c>
+      <c r="D68" s="7" t="n"/>
       <c r="E68" s="7" t="n"/>
       <c r="F68" s="7" t="n"/>
       <c r="G68" s="7" t="n"/>
@@ -1646,43 +1646,43 @@
       </c>
       <c r="B69" s="7" t="n"/>
       <c r="C69" s="7" t="n"/>
-      <c r="D69" s="7" t="n"/>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>De'Zhaun Stribling</t>
+        </is>
+      </c>
       <c r="E69" s="7" t="n"/>
       <c r="F69" s="7" t="n"/>
       <c r="G69" s="7" t="n"/>
-      <c r="H69" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B70" s="7" t="n"/>
       <c r="C70" s="7" t="n"/>
       <c r="D70" s="7" t="n"/>
       <c r="E70" s="7" t="n"/>
       <c r="F70" s="7" t="n"/>
       <c r="G70" s="7" t="n"/>
-      <c r="H70" s="7" t="n"/>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B71" s="7" t="n"/>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C71" s="7" t="n"/>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D71" s="7" t="n"/>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
@@ -1696,7 +1696,7 @@
       <c r="C72" s="7" t="n"/>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E72" s="7" t="n"/>
@@ -1706,15 +1706,15 @@
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B73" s="7" t="n"/>
       <c r="C73" s="7" t="n"/>
-      <c r="D73" s="7" t="n"/>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Carnell Tate</t>
+        </is>
+      </c>
       <c r="E73" s="7" t="n"/>
       <c r="F73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C74" s="7" t="n"/>
@@ -1740,13 +1740,13 @@
       <c r="A75" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B75" s="7" t="n"/>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C75" s="7" t="n"/>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D75" s="7" t="n"/>
       <c r="E75" s="7" t="n"/>
       <c r="F75" s="7" t="n"/>
       <c r="G75" s="7" t="n"/>
@@ -1760,7 +1760,7 @@
       <c r="C76" s="7" t="n"/>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E76" s="7" t="n"/>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="77">
       <c r="A77" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B77" s="7" t="n"/>
       <c r="C77" s="7" t="n"/>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E77" s="7" t="n"/>
@@ -1792,7 +1792,7 @@
       <c r="C78" s="7" t="n"/>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E78" s="7" t="n"/>
@@ -1808,7 +1808,7 @@
       <c r="C79" s="7" t="n"/>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E79" s="7" t="n"/>
@@ -1824,7 +1824,7 @@
       <c r="C80" s="7" t="n"/>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E80" s="7" t="n"/>
@@ -1838,13 +1838,13 @@
       </c>
       <c r="B81" s="7" t="n"/>
       <c r="C81" s="7" t="n"/>
-      <c r="D81" s="7" t="n"/>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>Quentin Johnston</t>
+        </is>
+      </c>
       <c r="E81" s="7" t="n"/>
-      <c r="F81" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F81" s="7" t="n"/>
       <c r="G81" s="7" t="n"/>
       <c r="H81" s="7" t="n"/>
     </row>
@@ -2016,7 +2016,7 @@
       <c r="C92" s="7" t="n"/>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>Makai Lemon</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E92" s="7" t="n"/>
@@ -2030,13 +2030,13 @@
       </c>
       <c r="B93" s="7" t="n"/>
       <c r="C93" s="7" t="n"/>
-      <c r="D93" s="7" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
+      <c r="D93" s="7" t="n"/>
       <c r="E93" s="7" t="n"/>
-      <c r="F93" s="7" t="n"/>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G93" s="7" t="n"/>
       <c r="H93" s="7" t="n"/>
     </row>
@@ -2048,13 +2048,13 @@
       <c r="C94" s="7" t="n"/>
       <c r="D94" s="7" t="n"/>
       <c r="E94" s="7" t="n"/>
-      <c r="F94" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F94" s="7" t="n"/>
       <c r="G94" s="7" t="n"/>
-      <c r="H94" s="7" t="n"/>
+      <c r="H94" s="7" t="inlineStr">
+        <is>
+          <t>Jalen Hurts</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
@@ -2068,7 +2068,7 @@
       <c r="G95" s="7" t="n"/>
       <c r="H95" s="7" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       <c r="G96" s="7" t="n"/>
       <c r="H96" s="7" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
     </row>
@@ -2190,13 +2190,13 @@
       </c>
       <c r="B103" s="7" t="n"/>
       <c r="C103" s="7" t="n"/>
-      <c r="D103" s="7" t="inlineStr">
-        <is>
-          <t>Jordan Addison</t>
-        </is>
-      </c>
+      <c r="D103" s="7" t="n"/>
       <c r="E103" s="7" t="n"/>
-      <c r="F103" s="7" t="n"/>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G103" s="7" t="n"/>
       <c r="H103" s="7" t="n"/>
     </row>
@@ -2208,59 +2208,59 @@
       <c r="C104" s="7" t="n"/>
       <c r="D104" s="7" t="n"/>
       <c r="E104" s="7" t="n"/>
-      <c r="F104" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F104" s="7" t="n"/>
       <c r="G104" s="7" t="n"/>
-      <c r="H104" s="7" t="n"/>
+      <c r="H104" s="7" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B105" s="7" t="n"/>
       <c r="C105" s="7" t="n"/>
       <c r="D105" s="7" t="n"/>
       <c r="E105" s="7" t="n"/>
-      <c r="F105" s="7" t="n"/>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G105" s="7" t="n"/>
-      <c r="H105" s="7" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H105" s="7" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B106" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C106" s="7" t="n"/>
       <c r="D106" s="7" t="n"/>
       <c r="E106" s="7" t="n"/>
       <c r="F106" s="7" t="n"/>
       <c r="G106" s="7" t="n"/>
-      <c r="H106" s="7" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H106" s="7" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B107" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>Kenny Gainwell</t>
+        </is>
+      </c>
       <c r="C107" s="7" t="n"/>
       <c r="D107" s="7" t="n"/>
       <c r="E107" s="7" t="n"/>
-      <c r="F107" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F107" s="7" t="n"/>
       <c r="G107" s="7" t="n"/>
       <c r="H107" s="7" t="n"/>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Rachaad White</t>
         </is>
       </c>
       <c r="C108" s="7" t="n"/>
@@ -2279,54 +2279,6 @@
       <c r="F108" s="7" t="n"/>
       <c r="G108" s="7" t="n"/>
       <c r="H108" s="7" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B109" s="7" t="inlineStr">
-        <is>
-          <t>Kenny Gainwell</t>
-        </is>
-      </c>
-      <c r="C109" s="7" t="n"/>
-      <c r="D109" s="7" t="n"/>
-      <c r="E109" s="7" t="n"/>
-      <c r="F109" s="7" t="n"/>
-      <c r="G109" s="7" t="n"/>
-      <c r="H109" s="7" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B110" s="7" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
-      <c r="C110" s="7" t="n"/>
-      <c r="D110" s="7" t="n"/>
-      <c r="E110" s="7" t="n"/>
-      <c r="F110" s="7" t="n"/>
-      <c r="G110" s="7" t="n"/>
-      <c r="H110" s="7" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B111" s="7" t="n"/>
-      <c r="C111" s="7" t="n"/>
-      <c r="D111" s="7" t="inlineStr">
-        <is>
-          <t>Wan'Dale Robinson</t>
-        </is>
-      </c>
-      <c r="E111" s="7" t="n"/>
-      <c r="F111" s="7" t="n"/>
-      <c r="G111" s="7" t="n"/>
-      <c r="H111" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2359,7 +2311,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 108 players, top value 70.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 105 players, top value 70.</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2370,7 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.9, WR 3.4, TE 3.8, QB 0.0.</t>
+          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.9, WR 3.3, TE 4.0, QB 0.0.</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2397,7 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Chris Olave 32-&gt;26, Trey McBride 25-&gt;19, DeVonta Smith 27-&gt;22, Rashee Rice 26-&gt;21, Garrett Wilson 23-&gt;18, Malik Nabers 20-&gt;15, CeeDee Lamb 47-&gt;43, De'Von Achane 41-&gt;37</t>
+          <t>Largest moves vs. the baseline in this file: Chris Olave 41-&gt;36, Malik Nabers 30-&gt;25, Trey McBride 30-&gt;25, DeVonta Smith 27-&gt;22, Rashee Rice 26-&gt;21, Garrett Wilson 23-&gt;18, Derrick Henry 55-&gt;59, CeeDee Lamb 47-&gt;43</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -602,11 +602,11 @@
     </row>
     <row r="4">
       <c r="A4" s="6" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Bijan Robinson</t>
+          <t>Jahmyr Gibbs</t>
         </is>
       </c>
       <c r="C4" s="7" t="n"/>
@@ -618,11 +618,11 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Jahmyr Gibbs</t>
+          <t>Bijan Robinson</t>
         </is>
       </c>
       <c r="C5" s="7" t="n"/>
@@ -636,13 +636,13 @@
       <c r="A6" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+      <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="7" t="n"/>
       <c r="G6" s="7" t="n"/>
@@ -650,11 +650,11 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C7" s="7" t="n"/>
@@ -666,11 +666,11 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>James Cook III</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C8" s="7" t="n"/>
@@ -682,11 +682,11 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C9" s="7" t="n"/>
@@ -698,7 +698,7 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
@@ -714,15 +714,15 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>61</v>
-      </c>
-      <c r="B11" s="7" t="n"/>
+        <v>60</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D11" s="7" t="n"/>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
@@ -730,15 +730,15 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="n"/>
@@ -746,13 +746,13 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E13" s="7" t="n"/>
@@ -762,15 +762,15 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="B14" s="7" t="n"/>
+        <v>57</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D14" s="7" t="n"/>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
@@ -778,11 +778,11 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Saquon Barkley</t>
+          <t>Ashton Jeanty</t>
         </is>
       </c>
       <c r="C15" s="7" t="n"/>
@@ -794,15 +794,15 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>56</v>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
@@ -810,15 +810,15 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="B17" s="7" t="n"/>
+        <v>48</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D17" s="7" t="n"/>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
@@ -826,7 +826,7 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
@@ -842,15 +842,15 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>43</v>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
@@ -858,31 +858,31 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
@@ -890,7 +890,7 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
@@ -906,11 +906,11 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C23" s="7" t="n"/>
@@ -922,7 +922,7 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
@@ -938,15 +938,15 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="B25" s="7" t="n"/>
+        <v>34</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
@@ -954,11 +954,11 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C26" s="7" t="n"/>
@@ -970,15 +970,15 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="B27" s="7" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D27" s="7" t="n"/>
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
@@ -986,15 +986,15 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="7" t="n"/>
@@ -1002,23 +1002,23 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E29" s="7" t="n"/>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F29" s="7" t="n"/>
       <c r="G29" s="7" t="n"/>
       <c r="H29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
@@ -1034,15 +1034,15 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B31" s="7" t="n"/>
+        <v>29</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D31" s="7" t="n"/>
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="7" t="n"/>
       <c r="G31" s="7" t="n"/>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
@@ -1068,13 +1068,13 @@
       <c r="A33" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+      <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="n"/>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
@@ -1082,13 +1082,13 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E34" s="7" t="n"/>
@@ -1098,17 +1098,17 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
-      <c r="D35" s="7" t="n"/>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E35" s="7" t="n"/>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F35" s="7" t="n"/>
       <c r="G35" s="7" t="n"/>
       <c r="H35" s="7" t="n"/>
     </row>
@@ -1130,29 +1130,29 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D37" s="7" t="n"/>
       <c r="E37" s="7" t="n"/>
-      <c r="F37" s="7" t="n"/>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G37" s="7" t="n"/>
       <c r="H37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E38" s="7" t="n"/>
@@ -1162,13 +1162,13 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E39" s="7" t="n"/>
@@ -1178,15 +1178,15 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="B40" s="7" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D40" s="7" t="n"/>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
@@ -1194,15 +1194,15 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="B41" s="7" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D41" s="7" t="n"/>
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="7" t="n"/>
@@ -1210,15 +1210,15 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="B42" s="7" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D42" s="7" t="n"/>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="7" t="n"/>
@@ -1226,15 +1226,15 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B43" s="7" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C43" s="7" t="n"/>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D43" s="7" t="n"/>
       <c r="E43" s="7" t="n"/>
       <c r="F43" s="7" t="n"/>
       <c r="G43" s="7" t="n"/>
@@ -1258,15 +1258,15 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B45" s="7" t="n"/>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="n"/>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E45" s="7" t="n"/>
       <c r="F45" s="7" t="n"/>
       <c r="G45" s="7" t="n"/>
@@ -1274,15 +1274,15 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="n"/>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="7" t="n"/>
@@ -1290,15 +1290,15 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="n"/>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E47" s="7" t="n"/>
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="7" t="n"/>
@@ -1306,13 +1306,13 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B48" s="7" t="n"/>
       <c r="C48" s="7" t="n"/>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E48" s="7" t="n"/>
@@ -1322,15 +1322,15 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B49" s="7" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D49" s="7" t="n"/>
       <c r="E49" s="7" t="n"/>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n"/>
@@ -1338,31 +1338,31 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B50" s="7" t="n"/>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="n"/>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E50" s="7" t="n"/>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F50" s="7" t="n"/>
       <c r="G50" s="7" t="n"/>
       <c r="H50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B51" s="7" t="n"/>
       <c r="C51" s="7" t="n"/>
-      <c r="D51" s="7" t="n"/>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E51" s="7" t="n"/>
       <c r="F51" s="7" t="n"/>
       <c r="G51" s="7" t="n"/>
@@ -1370,15 +1370,15 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B52" s="7" t="n"/>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="7" t="n"/>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="7" t="n"/>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C53" s="7" t="n"/>
@@ -1408,7 +1408,7 @@
       <c r="C54" s="7" t="n"/>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E54" s="7" t="n"/>
@@ -1434,59 +1434,59 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B56" s="7" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C56" s="7" t="n"/>
       <c r="D56" s="7" t="n"/>
       <c r="E56" s="7" t="n"/>
-      <c r="F56" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="n"/>
       <c r="H56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B57" s="7" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C57" s="7" t="n"/>
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
       <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
-      <c r="H57" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B58" s="7" t="n"/>
       <c r="C58" s="7" t="n"/>
       <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
-      <c r="F58" s="7" t="n"/>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C59" s="7" t="n"/>
@@ -1498,63 +1498,63 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B60" s="7" t="n"/>
       <c r="C60" s="7" t="n"/>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D60" s="7" t="n"/>
       <c r="E60" s="7" t="n"/>
-      <c r="F60" s="7" t="n"/>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G60" s="7" t="n"/>
       <c r="H60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
       <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
-      <c r="H61" s="7" t="n"/>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B62" s="7" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C62" s="7" t="n"/>
       <c r="D62" s="7" t="n"/>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="7" t="n"/>
-      <c r="H62" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B63" s="7" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C63" s="7" t="n"/>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D63" s="7" t="n"/>
       <c r="E63" s="7" t="n"/>
       <c r="F63" s="7" t="n"/>
       <c r="G63" s="7" t="n"/>
@@ -1562,13 +1562,13 @@
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B64" s="7" t="n"/>
       <c r="C64" s="7" t="n"/>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="E64" s="7" t="n"/>
@@ -1578,17 +1578,17 @@
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B65" s="7" t="n"/>
       <c r="C65" s="7" t="n"/>
-      <c r="D65" s="7" t="n"/>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E65" s="7" t="n"/>
-      <c r="F65" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F65" s="7" t="n"/>
       <c r="G65" s="7" t="n"/>
       <c r="H65" s="7" t="n"/>
     </row>
@@ -1600,7 +1600,7 @@
       <c r="C66" s="7" t="n"/>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E66" s="7" t="n"/>
@@ -1614,13 +1614,13 @@
       </c>
       <c r="B67" s="7" t="n"/>
       <c r="C67" s="7" t="n"/>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>Jameson Williams</t>
-        </is>
-      </c>
+      <c r="D67" s="7" t="n"/>
       <c r="E67" s="7" t="n"/>
-      <c r="F67" s="7" t="n"/>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G67" s="7" t="n"/>
       <c r="H67" s="7" t="n"/>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C68" s="7" t="n"/>
@@ -1644,13 +1644,13 @@
       <c r="A69" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B69" s="7" t="n"/>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C69" s="7" t="n"/>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>De'Zhaun Stribling</t>
-        </is>
-      </c>
+      <c r="D69" s="7" t="n"/>
       <c r="E69" s="7" t="n"/>
       <c r="F69" s="7" t="n"/>
       <c r="G69" s="7" t="n"/>
@@ -1662,27 +1662,27 @@
       </c>
       <c r="B70" s="7" t="n"/>
       <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="n"/>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E70" s="7" t="n"/>
       <c r="F70" s="7" t="n"/>
       <c r="G70" s="7" t="n"/>
-      <c r="H70" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B71" s="7" t="n"/>
       <c r="C71" s="7" t="n"/>
-      <c r="D71" s="7" t="n"/>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>Terry McLaurin</t>
+        </is>
+      </c>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
@@ -1690,13 +1690,13 @@
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B72" s="7" t="n"/>
       <c r="C72" s="7" t="n"/>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E72" s="7" t="n"/>
@@ -1706,95 +1706,95 @@
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B73" s="7" t="n"/>
       <c r="C73" s="7" t="n"/>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>Carnell Tate</t>
-        </is>
-      </c>
+      <c r="D73" s="7" t="n"/>
       <c r="E73" s="7" t="n"/>
-      <c r="F73" s="7" t="n"/>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G73" s="7" t="n"/>
       <c r="H73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B74" s="7" t="n"/>
       <c r="C74" s="7" t="n"/>
       <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
       <c r="F74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
-      <c r="H74" s="7" t="n"/>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B75" s="7" t="n"/>
       <c r="C75" s="7" t="n"/>
       <c r="D75" s="7" t="n"/>
       <c r="E75" s="7" t="n"/>
       <c r="F75" s="7" t="n"/>
       <c r="G75" s="7" t="n"/>
-      <c r="H75" s="7" t="n"/>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B76" s="7" t="n"/>
       <c r="C76" s="7" t="n"/>
-      <c r="D76" s="7" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D76" s="7" t="n"/>
       <c r="E76" s="7" t="n"/>
-      <c r="F76" s="7" t="n"/>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G76" s="7" t="n"/>
       <c r="H76" s="7" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B77" s="7" t="n"/>
       <c r="C77" s="7" t="n"/>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>Brian Thomas Jr.</t>
-        </is>
-      </c>
+      <c r="D77" s="7" t="n"/>
       <c r="E77" s="7" t="n"/>
       <c r="F77" s="7" t="n"/>
       <c r="G77" s="7" t="n"/>
-      <c r="H77" s="7" t="n"/>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>Jalen Hurts</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B78" s="7" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
       <c r="C78" s="7" t="n"/>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>KC Concepcion</t>
-        </is>
-      </c>
+      <c r="D78" s="7" t="n"/>
       <c r="E78" s="7" t="n"/>
       <c r="F78" s="7" t="n"/>
       <c r="G78" s="7" t="n"/>
@@ -1802,13 +1802,13 @@
     </row>
     <row r="79">
       <c r="A79" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B79" s="7" t="n"/>
       <c r="C79" s="7" t="n"/>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E79" s="7" t="n"/>
@@ -1818,13 +1818,13 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B80" s="7" t="n"/>
       <c r="C80" s="7" t="n"/>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E80" s="7" t="n"/>
@@ -1834,27 +1834,27 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B81" s="7" t="n"/>
       <c r="C81" s="7" t="n"/>
-      <c r="D81" s="7" t="inlineStr">
-        <is>
-          <t>Quentin Johnston</t>
-        </is>
-      </c>
+      <c r="D81" s="7" t="n"/>
       <c r="E81" s="7" t="n"/>
       <c r="F81" s="7" t="n"/>
       <c r="G81" s="7" t="n"/>
-      <c r="H81" s="7" t="n"/>
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C82" s="7" t="n"/>
@@ -1866,15 +1866,15 @@
     </row>
     <row r="83">
       <c r="A83" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B83" s="7" t="n"/>
       <c r="C83" s="7" t="n"/>
-      <c r="D83" s="7" t="n"/>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E83" s="7" t="n"/>
       <c r="F83" s="7" t="n"/>
       <c r="G83" s="7" t="n"/>
@@ -1882,15 +1882,15 @@
     </row>
     <row r="84">
       <c r="A84" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>Jonathon Brooks</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B84" s="7" t="n"/>
       <c r="C84" s="7" t="n"/>
-      <c r="D84" s="7" t="n"/>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>KC Concepcion</t>
+        </is>
+      </c>
       <c r="E84" s="7" t="n"/>
       <c r="F84" s="7" t="n"/>
       <c r="G84" s="7" t="n"/>
@@ -1898,15 +1898,15 @@
     </row>
     <row r="85">
       <c r="A85" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>Mike Washington Jr.</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B85" s="7" t="n"/>
       <c r="C85" s="7" t="n"/>
-      <c r="D85" s="7" t="n"/>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E85" s="7" t="n"/>
       <c r="F85" s="7" t="n"/>
       <c r="G85" s="7" t="n"/>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C86" s="7" t="n"/>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>Blake Corum</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C87" s="7" t="n"/>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C88" s="7" t="n"/>
@@ -1964,13 +1964,13 @@
       <c r="A89" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B89" s="7" t="n"/>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>Rico Dowdle</t>
+        </is>
+      </c>
       <c r="C89" s="7" t="n"/>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>Chris Godwin Jr.</t>
-        </is>
-      </c>
+      <c r="D89" s="7" t="n"/>
       <c r="E89" s="7" t="n"/>
       <c r="F89" s="7" t="n"/>
       <c r="G89" s="7" t="n"/>
@@ -1980,13 +1980,13 @@
       <c r="A90" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B90" s="7" t="n"/>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C90" s="7" t="n"/>
-      <c r="D90" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Reed</t>
-        </is>
-      </c>
+      <c r="D90" s="7" t="n"/>
       <c r="E90" s="7" t="n"/>
       <c r="F90" s="7" t="n"/>
       <c r="G90" s="7" t="n"/>
@@ -1996,13 +1996,13 @@
       <c r="A91" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B91" s="7" t="n"/>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C91" s="7" t="n"/>
-      <c r="D91" s="7" t="inlineStr">
-        <is>
-          <t>Jordyn Tyson</t>
-        </is>
-      </c>
+      <c r="D91" s="7" t="n"/>
       <c r="E91" s="7" t="n"/>
       <c r="F91" s="7" t="n"/>
       <c r="G91" s="7" t="n"/>
@@ -2016,7 +2016,7 @@
       <c r="C92" s="7" t="n"/>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E92" s="7" t="n"/>
@@ -2030,13 +2030,13 @@
       </c>
       <c r="B93" s="7" t="n"/>
       <c r="C93" s="7" t="n"/>
-      <c r="D93" s="7" t="n"/>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>Quentin Johnston</t>
+        </is>
+      </c>
       <c r="E93" s="7" t="n"/>
-      <c r="F93" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F93" s="7" t="n"/>
       <c r="G93" s="7" t="n"/>
       <c r="H93" s="7" t="n"/>
     </row>
@@ -2046,15 +2046,15 @@
       </c>
       <c r="B94" s="7" t="n"/>
       <c r="C94" s="7" t="n"/>
-      <c r="D94" s="7" t="n"/>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>Chris Godwin Jr.</t>
+        </is>
+      </c>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="7" t="n"/>
       <c r="G94" s="7" t="n"/>
-      <c r="H94" s="7" t="inlineStr">
-        <is>
-          <t>Jalen Hurts</t>
-        </is>
-      </c>
+      <c r="H94" s="7" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
@@ -2062,15 +2062,15 @@
       </c>
       <c r="B95" s="7" t="n"/>
       <c r="C95" s="7" t="n"/>
-      <c r="D95" s="7" t="n"/>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Reed</t>
+        </is>
+      </c>
       <c r="E95" s="7" t="n"/>
       <c r="F95" s="7" t="n"/>
       <c r="G95" s="7" t="n"/>
-      <c r="H95" s="7" t="inlineStr">
-        <is>
-          <t>Justin Herbert</t>
-        </is>
-      </c>
+      <c r="H95" s="7" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
@@ -2078,15 +2078,15 @@
       </c>
       <c r="B96" s="7" t="n"/>
       <c r="C96" s="7" t="n"/>
-      <c r="D96" s="7" t="n"/>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>Jordyn Tyson</t>
+        </is>
+      </c>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="7" t="n"/>
       <c r="G96" s="7" t="n"/>
-      <c r="H96" s="7" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H96" s="7" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
@@ -2094,27 +2094,27 @@
       </c>
       <c r="B97" s="7" t="n"/>
       <c r="C97" s="7" t="n"/>
-      <c r="D97" s="7" t="n"/>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="7" t="n"/>
       <c r="G97" s="7" t="n"/>
-      <c r="H97" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H97" s="7" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B98" s="7" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B98" s="7" t="n"/>
       <c r="C98" s="7" t="n"/>
-      <c r="D98" s="7" t="n"/>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E98" s="7" t="n"/>
       <c r="F98" s="7" t="n"/>
       <c r="G98" s="7" t="n"/>
@@ -2122,63 +2122,63 @@
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B99" s="7" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B99" s="7" t="n"/>
       <c r="C99" s="7" t="n"/>
       <c r="D99" s="7" t="n"/>
       <c r="E99" s="7" t="n"/>
-      <c r="F99" s="7" t="n"/>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G99" s="7" t="n"/>
       <c r="H99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B100" s="7" t="n"/>
       <c r="C100" s="7" t="n"/>
-      <c r="D100" s="7" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D100" s="7" t="n"/>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="7" t="n"/>
       <c r="G100" s="7" t="n"/>
-      <c r="H100" s="7" t="n"/>
+      <c r="H100" s="7" t="inlineStr">
+        <is>
+          <t>Justin Herbert</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B101" s="7" t="n"/>
       <c r="C101" s="7" t="n"/>
-      <c r="D101" s="7" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D101" s="7" t="n"/>
       <c r="E101" s="7" t="n"/>
       <c r="F101" s="7" t="n"/>
       <c r="G101" s="7" t="n"/>
-      <c r="H101" s="7" t="n"/>
+      <c r="H101" s="7" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B102" s="7" t="n"/>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C102" s="7" t="n"/>
-      <c r="D102" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
+      <c r="D102" s="7" t="n"/>
       <c r="E102" s="7" t="n"/>
       <c r="F102" s="7" t="n"/>
       <c r="G102" s="7" t="n"/>
@@ -2188,15 +2188,15 @@
       <c r="A103" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B103" s="7" t="n"/>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C103" s="7" t="n"/>
       <c r="D103" s="7" t="n"/>
       <c r="E103" s="7" t="n"/>
-      <c r="F103" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F103" s="7" t="n"/>
       <c r="G103" s="7" t="n"/>
       <c r="H103" s="7" t="n"/>
     </row>
@@ -2206,43 +2206,43 @@
       </c>
       <c r="B104" s="7" t="n"/>
       <c r="C104" s="7" t="n"/>
-      <c r="D104" s="7" t="n"/>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E104" s="7" t="n"/>
       <c r="F104" s="7" t="n"/>
       <c r="G104" s="7" t="n"/>
-      <c r="H104" s="7" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H104" s="7" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B105" s="7" t="n"/>
       <c r="C105" s="7" t="n"/>
       <c r="D105" s="7" t="n"/>
       <c r="E105" s="7" t="n"/>
-      <c r="F105" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F105" s="7" t="n"/>
       <c r="G105" s="7" t="n"/>
-      <c r="H105" s="7" t="n"/>
+      <c r="H105" s="7" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B106" s="7" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B106" s="7" t="n"/>
       <c r="C106" s="7" t="n"/>
-      <c r="D106" s="7" t="n"/>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>Marvin Harrison Jr.</t>
+        </is>
+      </c>
       <c r="E106" s="7" t="n"/>
       <c r="F106" s="7" t="n"/>
       <c r="G106" s="7" t="n"/>
@@ -2292,7 +2292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -2311,14 +2311,14 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 105 players, top value 70.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 105 players, top value 75.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>Derived in two steps (plain numbers; one row per player, sorted by value). Generated by scripts/trade-values/build_trade_values.py.</t>
+          <t>Derived in the steps below (plain numbers; one row per player, sorted by value). Generated by scripts/trade-values/build_trade_values.py.</t>
         </is>
       </c>
     </row>
@@ -2328,76 +2328,114 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>1) Scoring (zero-sum). Players with a real receiving role gain value in Full PPR and lose the same amount in Standard,</t>
+          <t>0) Weekly re-seed. The sheet values were first moved toward the 2026 week 3 Half PPR medians</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   relative to Half PPR; the total of those moves is taken back evenly (equal amount per player) from everyone else,</t>
+          <t xml:space="preserve">   (Projections page snapshot 3): implied = average of the sheet value at the player's projection-rank slot</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   so the pool's total trade value is unchanged. No player drops below 1.</t>
+          <t xml:space="preserve">   within the position and the player's share of the position's points-above-replacement on the position's value budget;</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   receiver move = 2.5 x delta x (receptions/game - replacement receptions/game at the position), delta = -0.5 for this file.</t>
+          <t xml:space="preserve">   new = sheet + 0.4 x (implied - sheet), then rescaled so the total equals the sheet total. 71 players moved.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   A receiving role = receptions/game at least 0.5 above the position's replacement level.</t>
+          <t xml:space="preserve">   No projection this week (value kept): Puka Nacua, Nico Collins, Jadarian Price, Rome Odunze, Josh Jacobs, De'Zhaun Stribling, Jayden Daniels, Jordan Mason, Alec Pierce, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Kenny Gainwell, Jaxson Dart, Ja'Kobi Lane.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   receptions/game = BettingPros consensus receptions line from the 2026 week 1 props; players with no line use the mean line of position peers within 10 value points.</t>
-        </is>
-      </c>
+      <c r="A11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.9, WR 3.3, TE 4.0, QB 0.0.</t>
+          <t>1) Scoring (zero-sum). Players with a real receiving role gain value in Full PPR and lose the same amount in Standard,</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr"/>
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   relative to Half PPR; the total of those moves is taken back evenly (equal amount per player) from everyone else,</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>2) League size. Bigger leagues widen the gap between stars and depth; smaller leagues compress it.</t>
+          <t xml:space="preserve">   so the pool's total trade value is unchanged. No player drops below 1.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   final = top x (value / baseline top) ^ exponent, with top = 75 and exponent = 1.15 for this file (8 teams 65/0.87, 10 teams 70/1.0, 12 teams 75/1.15).</t>
+          <t xml:space="preserve">   receiver move = 2.5 x delta x (receptions/game - replacement receptions/game at the position), delta = -0.5 for this file.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr"/>
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   A receiving role = receptions/game at least 0.5 above the position's replacement level.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Chris Olave 41-&gt;36, Malik Nabers 30-&gt;25, Trey McBride 30-&gt;25, DeVonta Smith 27-&gt;22, Rashee Rice 26-&gt;21, Garrett Wilson 23-&gt;18, Derrick Henry 55-&gt;59, CeeDee Lamb 47-&gt;43</t>
+          <t xml:space="preserve">   receptions/game = BettingPros consensus receptions line from the 2026 week 1 props; players with no line use the mean line of position peers within 10 value points.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.8, WR 3.3, TE 4.5, QB 0.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>2) League size. Bigger leagues widen the gap between stars and depth; smaller leagues compress it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   final = top x (value / baseline top) ^ exponent, with top = 75 and exponent = 1.15 for this file (8 teams 65/0.87, 10 teams 70/1.0, 12 teams 75/1.15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>Largest moves vs. the baseline in this file: Malik Nabers 21-&gt;16, DeVonta Smith 32-&gt;27, Rashee Rice 19-&gt;14, Garrett Wilson 27-&gt;22, Derrick Henry 56-&gt;60, De'Von Achane 42-&gt;38, Chris Olave 45-&gt;41, Drake London 34-&gt;30</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -602,7 +602,7 @@
     </row>
     <row r="4">
       <c r="A4" s="6" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
@@ -634,15 +634,15 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="B6" s="7" t="n"/>
+        <v>67</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="7" t="n"/>
       <c r="G6" s="7" t="n"/>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
@@ -668,13 +668,13 @@
       <c r="A8" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+      <c r="B8" s="7" t="n"/>
       <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="7" t="n"/>
@@ -682,7 +682,7 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
@@ -746,7 +746,7 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
@@ -778,7 +778,7 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
@@ -810,7 +810,7 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
@@ -858,33 +858,33 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n"/>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G21" s="7" t="n"/>
       <c r="H21" s="7" t="n"/>
     </row>
@@ -938,7 +938,7 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
@@ -954,15 +954,15 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
@@ -972,13 +972,13 @@
       <c r="A27" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+      <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
@@ -986,15 +986,15 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B28" s="7" t="n"/>
+        <v>31</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D28" s="7" t="n"/>
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="7" t="n"/>
@@ -1002,15 +1002,15 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="B29" s="7" t="n"/>
+        <v>29</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D29" s="7" t="n"/>
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="7" t="n"/>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
@@ -1034,15 +1034,15 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="7" t="n"/>
       <c r="G31" s="7" t="n"/>
@@ -1050,13 +1050,13 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E32" s="7" t="n"/>
@@ -1066,13 +1066,13 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E33" s="7" t="n"/>
@@ -1082,15 +1082,15 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="B34" s="7" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D34" s="7" t="n"/>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="7" t="n"/>
@@ -1098,13 +1098,13 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E35" s="7" t="n"/>
@@ -1130,17 +1130,17 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7" t="n"/>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E37" s="7" t="n"/>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F37" s="7" t="n"/>
       <c r="G37" s="7" t="n"/>
       <c r="H37" s="7" t="n"/>
     </row>
@@ -1150,19 +1150,19 @@
       </c>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D38" s="7" t="n"/>
       <c r="E38" s="7" t="n"/>
-      <c r="F38" s="7" t="n"/>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G38" s="7" t="n"/>
       <c r="H38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
@@ -1178,11 +1178,11 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C40" s="7" t="n"/>
@@ -1194,11 +1194,11 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C41" s="7" t="n"/>
@@ -1210,11 +1210,11 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="C42" s="7" t="n"/>
@@ -1226,11 +1226,11 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="C43" s="7" t="n"/>
@@ -1242,15 +1242,15 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="n"/>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="7" t="n"/>
@@ -1258,13 +1258,13 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B45" s="7" t="n"/>
       <c r="C45" s="7" t="n"/>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E45" s="7" t="n"/>
@@ -1276,13 +1276,13 @@
       <c r="A46" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B46" s="7" t="n"/>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D46" s="7" t="n"/>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="7" t="n"/>
@@ -1296,7 +1296,7 @@
       <c r="C47" s="7" t="n"/>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E47" s="7" t="n"/>
@@ -1312,7 +1312,7 @@
       <c r="C48" s="7" t="n"/>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E48" s="7" t="n"/>
@@ -1322,15 +1322,15 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B49" s="7" t="n"/>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="n"/>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E49" s="7" t="n"/>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n"/>
@@ -1344,7 +1344,7 @@
       <c r="C50" s="7" t="n"/>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E50" s="7" t="n"/>
@@ -1372,13 +1372,13 @@
       <c r="A52" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B52" s="7" t="n"/>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D52" s="7" t="n"/>
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="7" t="n"/>
@@ -1386,15 +1386,15 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B53" s="7" t="n"/>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="7" t="n"/>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E53" s="7" t="n"/>
       <c r="F53" s="7" t="n"/>
       <c r="G53" s="7" t="n"/>
@@ -1404,13 +1404,13 @@
       <c r="A54" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B54" s="7" t="n"/>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C54" s="7" t="n"/>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D54" s="7" t="n"/>
       <c r="E54" s="7" t="n"/>
       <c r="F54" s="7" t="n"/>
       <c r="G54" s="7" t="n"/>
@@ -1434,11 +1434,11 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C56" s="7" t="n"/>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="C57" s="7" t="n"/>
@@ -1484,15 +1484,15 @@
       <c r="A59" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+      <c r="B59" s="7" t="n"/>
       <c r="C59" s="7" t="n"/>
       <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
-      <c r="F59" s="7" t="n"/>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G59" s="7" t="n"/>
       <c r="H59" s="7" t="n"/>
     </row>
@@ -1504,41 +1504,41 @@
       <c r="C60" s="7" t="n"/>
       <c r="D60" s="7" t="n"/>
       <c r="E60" s="7" t="n"/>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F60" s="7" t="n"/>
       <c r="G60" s="7" t="n"/>
-      <c r="H60" s="7" t="n"/>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B61" s="7" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C61" s="7" t="n"/>
       <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
       <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B62" s="7" t="n"/>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="n"/>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="7" t="n"/>
@@ -1548,29 +1548,29 @@
       <c r="A63" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+      <c r="B63" s="7" t="n"/>
       <c r="C63" s="7" t="n"/>
       <c r="D63" s="7" t="n"/>
       <c r="E63" s="7" t="n"/>
-      <c r="F63" s="7" t="n"/>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G63" s="7" t="n"/>
       <c r="H63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B64" s="7" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C64" s="7" t="n"/>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D64" s="7" t="n"/>
       <c r="E64" s="7" t="n"/>
       <c r="F64" s="7" t="n"/>
       <c r="G64" s="7" t="n"/>
@@ -1578,15 +1578,15 @@
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B65" s="7" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C65" s="7" t="n"/>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>Jameson Williams</t>
-        </is>
-      </c>
+      <c r="D65" s="7" t="n"/>
       <c r="E65" s="7" t="n"/>
       <c r="F65" s="7" t="n"/>
       <c r="G65" s="7" t="n"/>
@@ -1594,13 +1594,13 @@
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B66" s="7" t="n"/>
       <c r="C66" s="7" t="n"/>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E66" s="7" t="n"/>
@@ -1610,17 +1610,17 @@
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B67" s="7" t="n"/>
       <c r="C67" s="7" t="n"/>
-      <c r="D67" s="7" t="n"/>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>Terry McLaurin</t>
+        </is>
+      </c>
       <c r="E67" s="7" t="n"/>
-      <c r="F67" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
       <c r="H67" s="7" t="n"/>
     </row>
@@ -1628,13 +1628,13 @@
       <c r="A68" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+      <c r="B68" s="7" t="n"/>
       <c r="C68" s="7" t="n"/>
-      <c r="D68" s="7" t="n"/>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E68" s="7" t="n"/>
       <c r="F68" s="7" t="n"/>
       <c r="G68" s="7" t="n"/>
@@ -1644,13 +1644,13 @@
       <c r="A69" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B69" s="7" t="n"/>
       <c r="C69" s="7" t="n"/>
-      <c r="D69" s="7" t="n"/>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>De'Zhaun Stribling</t>
+        </is>
+      </c>
       <c r="E69" s="7" t="n"/>
       <c r="F69" s="7" t="n"/>
       <c r="G69" s="7" t="n"/>
@@ -1664,7 +1664,7 @@
       <c r="C70" s="7" t="n"/>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E70" s="7" t="n"/>
@@ -1678,13 +1678,13 @@
       </c>
       <c r="B71" s="7" t="n"/>
       <c r="C71" s="7" t="n"/>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D71" s="7" t="n"/>
       <c r="E71" s="7" t="n"/>
-      <c r="F71" s="7" t="n"/>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G71" s="7" t="n"/>
       <c r="H71" s="7" t="n"/>
     </row>
@@ -1694,15 +1694,15 @@
       </c>
       <c r="B72" s="7" t="n"/>
       <c r="C72" s="7" t="n"/>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>De'Zhaun Stribling</t>
-        </is>
-      </c>
+      <c r="D72" s="7" t="n"/>
       <c r="E72" s="7" t="n"/>
       <c r="F72" s="7" t="n"/>
       <c r="G72" s="7" t="n"/>
-      <c r="H72" s="7" t="n"/>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
@@ -1712,45 +1712,45 @@
       <c r="C73" s="7" t="n"/>
       <c r="D73" s="7" t="n"/>
       <c r="E73" s="7" t="n"/>
-      <c r="F73" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
-      <c r="H73" s="7" t="n"/>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B74" s="7" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C74" s="7" t="n"/>
       <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
       <c r="F74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
-      <c r="H74" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H74" s="7" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B75" s="7" t="n"/>
       <c r="C75" s="7" t="n"/>
       <c r="D75" s="7" t="n"/>
       <c r="E75" s="7" t="n"/>
-      <c r="F75" s="7" t="n"/>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G75" s="7" t="n"/>
-      <c r="H75" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H75" s="7" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n">
@@ -1760,29 +1760,29 @@
       <c r="C76" s="7" t="n"/>
       <c r="D76" s="7" t="n"/>
       <c r="E76" s="7" t="n"/>
-      <c r="F76" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F76" s="7" t="n"/>
       <c r="G76" s="7" t="n"/>
-      <c r="H76" s="7" t="n"/>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>Jalen Hurts</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B77" s="7" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
       <c r="C77" s="7" t="n"/>
       <c r="D77" s="7" t="n"/>
       <c r="E77" s="7" t="n"/>
       <c r="F77" s="7" t="n"/>
       <c r="G77" s="7" t="n"/>
-      <c r="H77" s="7" t="inlineStr">
-        <is>
-          <t>Jalen Hurts</t>
-        </is>
-      </c>
+      <c r="H77" s="7" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="n">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C78" s="7" t="n"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C82" s="7" t="n"/>
@@ -1980,13 +1980,13 @@
       <c r="A90" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B90" s="7" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+      <c r="B90" s="7" t="n"/>
       <c r="C90" s="7" t="n"/>
-      <c r="D90" s="7" t="n"/>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E90" s="7" t="n"/>
       <c r="F90" s="7" t="n"/>
       <c r="G90" s="7" t="n"/>
@@ -1996,13 +1996,13 @@
       <c r="A91" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B91" s="7" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+      <c r="B91" s="7" t="n"/>
       <c r="C91" s="7" t="n"/>
-      <c r="D91" s="7" t="n"/>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>Quentin Johnston</t>
+        </is>
+      </c>
       <c r="E91" s="7" t="n"/>
       <c r="F91" s="7" t="n"/>
       <c r="G91" s="7" t="n"/>
@@ -2016,7 +2016,7 @@
       <c r="C92" s="7" t="n"/>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E92" s="7" t="n"/>
@@ -2032,7 +2032,7 @@
       <c r="C93" s="7" t="n"/>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E93" s="7" t="n"/>
@@ -2048,7 +2048,7 @@
       <c r="C94" s="7" t="n"/>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr.</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E94" s="7" t="n"/>
@@ -2064,7 +2064,7 @@
       <c r="C95" s="7" t="n"/>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E95" s="7" t="n"/>
@@ -2080,7 +2080,7 @@
       <c r="C96" s="7" t="n"/>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E96" s="7" t="n"/>
@@ -2094,27 +2094,27 @@
       </c>
       <c r="B97" s="7" t="n"/>
       <c r="C97" s="7" t="n"/>
-      <c r="D97" s="7" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
+      <c r="D97" s="7" t="n"/>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="7" t="n"/>
       <c r="G97" s="7" t="n"/>
-      <c r="H97" s="7" t="n"/>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B98" s="7" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C98" s="7" t="n"/>
-      <c r="D98" s="7" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D98" s="7" t="n"/>
       <c r="E98" s="7" t="n"/>
       <c r="F98" s="7" t="n"/>
       <c r="G98" s="7" t="n"/>
@@ -2122,63 +2122,63 @@
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B99" s="7" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C99" s="7" t="n"/>
       <c r="D99" s="7" t="n"/>
       <c r="E99" s="7" t="n"/>
-      <c r="F99" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F99" s="7" t="n"/>
       <c r="G99" s="7" t="n"/>
       <c r="H99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B100" s="7" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C100" s="7" t="n"/>
       <c r="D100" s="7" t="n"/>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="7" t="n"/>
       <c r="G100" s="7" t="n"/>
-      <c r="H100" s="7" t="inlineStr">
-        <is>
-          <t>Justin Herbert</t>
-        </is>
-      </c>
+      <c r="H100" s="7" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B101" s="7" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C101" s="7" t="n"/>
       <c r="D101" s="7" t="n"/>
       <c r="E101" s="7" t="n"/>
       <c r="F101" s="7" t="n"/>
       <c r="G101" s="7" t="n"/>
-      <c r="H101" s="7" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H101" s="7" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B102" s="7" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+      <c r="B102" s="7" t="n"/>
       <c r="C102" s="7" t="n"/>
-      <c r="D102" s="7" t="n"/>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E102" s="7" t="n"/>
       <c r="F102" s="7" t="n"/>
       <c r="G102" s="7" t="n"/>
@@ -2188,15 +2188,15 @@
       <c r="A103" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B103" s="7" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+      <c r="B103" s="7" t="n"/>
       <c r="C103" s="7" t="n"/>
       <c r="D103" s="7" t="n"/>
       <c r="E103" s="7" t="n"/>
-      <c r="F103" s="7" t="n"/>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G103" s="7" t="n"/>
       <c r="H103" s="7" t="n"/>
     </row>
@@ -2206,15 +2206,15 @@
       </c>
       <c r="B104" s="7" t="n"/>
       <c r="C104" s="7" t="n"/>
-      <c r="D104" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
+      <c r="D104" s="7" t="n"/>
       <c r="E104" s="7" t="n"/>
       <c r="F104" s="7" t="n"/>
       <c r="G104" s="7" t="n"/>
-      <c r="H104" s="7" t="n"/>
+      <c r="H104" s="7" t="inlineStr">
+        <is>
+          <t>Justin Herbert</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="n">
@@ -2311,7 +2311,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 105 players, top value 75.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 105 players, top value 76.</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 3): implied = average of the sheet value at the player's projection-rank slot</t>
+          <t xml:space="preserve">   (Projections page snapshot 4): implied = average of the sheet value at the player's projection-rank slot</t>
         </is>
       </c>
     </row>
@@ -2349,14 +2349,14 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.4 x (implied - sheet), then rescaled so the total equals the sheet total. 71 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.4 x (implied - sheet), then rescaled so the total equals the sheet total. 76 players moved.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   No projection this week (value kept): Puka Nacua, Nico Collins, Jadarian Price, Rome Odunze, Josh Jacobs, De'Zhaun Stribling, Jayden Daniels, Jordan Mason, Alec Pierce, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Kenny Gainwell, Jaxson Dart, Ja'Kobi Lane.</t>
+          <t xml:space="preserve">   No projection this week (value kept): Puka Nacua, Nico Collins, Rome Odunze, Josh Jacobs, De'Zhaun Stribling, Jayden Daniels, Jordan Mason, Alec Pierce, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Jaxson Dart, Ja'Kobi Lane.</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2435,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Malik Nabers 21-&gt;16, DeVonta Smith 32-&gt;27, Rashee Rice 19-&gt;14, Garrett Wilson 27-&gt;22, Derrick Henry 56-&gt;60, De'Von Achane 42-&gt;38, Chris Olave 45-&gt;41, Drake London 34-&gt;30</t>
+          <t>Largest moves vs. the baseline in this file: Malik Nabers 21-&gt;16, DeVonta Smith 32-&gt;27, Rashee Rice 19-&gt;14, Garrett Wilson 29-&gt;24, Derrick Henry 57-&gt;61, De'Von Achane 42-&gt;38, Chris Olave 47-&gt;43, Drake London 33-&gt;29</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -602,7 +602,7 @@
     </row>
     <row r="4">
       <c r="A4" s="6" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
@@ -666,15 +666,15 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>65</v>
-      </c>
-      <c r="B8" s="7" t="n"/>
+        <v>64</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Jonathan Taylor</t>
+        </is>
+      </c>
       <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D8" s="7" t="n"/>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="7" t="n"/>
@@ -684,13 +684,13 @@
       <c r="A9" s="6" t="n">
         <v>64</v>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Jonathan Taylor</t>
-        </is>
-      </c>
+      <c r="B9" s="7" t="n"/>
       <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="7" t="n"/>
@@ -730,13 +730,13 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E12" s="7" t="n"/>
@@ -746,15 +746,15 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="B13" s="7" t="n"/>
+        <v>57</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D13" s="7" t="n"/>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
@@ -764,13 +764,13 @@
       <c r="A14" s="6" t="n">
         <v>57</v>
       </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+      <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
@@ -794,7 +794,7 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
@@ -810,7 +810,7 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
@@ -842,13 +842,13 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Justin Jefferson</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E19" s="7" t="n"/>
@@ -858,13 +858,13 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>Justin Jefferson</t>
         </is>
       </c>
       <c r="E20" s="7" t="n"/>
@@ -890,15 +890,15 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>De'Von Achane</t>
-        </is>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
@@ -906,11 +906,11 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>De'Von Achane</t>
         </is>
       </c>
       <c r="C23" s="7" t="n"/>
@@ -924,21 +924,21 @@
       <c r="A24" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="B24" s="7" t="n"/>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
@@ -954,19 +954,19 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="n"/>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
@@ -976,7 +976,7 @@
       <c r="C27" s="7" t="n"/>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Nico Collins</t>
         </is>
       </c>
       <c r="E27" s="7" t="n"/>
@@ -1040,7 +1040,7 @@
       <c r="C31" s="7" t="n"/>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E31" s="7" t="n"/>
@@ -1050,13 +1050,13 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E32" s="7" t="n"/>
@@ -1066,13 +1066,13 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E33" s="7" t="n"/>
@@ -1082,15 +1082,15 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="n"/>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="7" t="n"/>
@@ -1098,45 +1098,45 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D35" s="7" t="n"/>
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="7" t="n"/>
-      <c r="H35" s="7" t="n"/>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="B36" s="7" t="n"/>
+        <v>24</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="7" t="n"/>
       <c r="E36" s="7" t="n"/>
       <c r="F36" s="7" t="n"/>
       <c r="G36" s="7" t="n"/>
-      <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E37" s="7" t="n"/>
@@ -1146,17 +1146,17 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="B38" s="7" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C38" s="7" t="n"/>
       <c r="D38" s="7" t="n"/>
       <c r="E38" s="7" t="n"/>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F38" s="7" t="n"/>
       <c r="G38" s="7" t="n"/>
       <c r="H38" s="7" t="n"/>
     </row>
@@ -1178,17 +1178,17 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
       <c r="D40" s="7" t="n"/>
       <c r="E40" s="7" t="n"/>
-      <c r="F40" s="7" t="n"/>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G40" s="7" t="n"/>
       <c r="H40" s="7" t="n"/>
     </row>
@@ -1242,7 +1242,7 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="n"/>
@@ -1260,13 +1260,13 @@
       <c r="A45" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B45" s="7" t="n"/>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D45" s="7" t="n"/>
       <c r="E45" s="7" t="n"/>
       <c r="F45" s="7" t="n"/>
       <c r="G45" s="7" t="n"/>
@@ -1274,15 +1274,15 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="n"/>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="7" t="n"/>
@@ -1344,7 +1344,7 @@
       <c r="C50" s="7" t="n"/>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E50" s="7" t="n"/>
@@ -1360,7 +1360,7 @@
       <c r="C51" s="7" t="n"/>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E51" s="7" t="n"/>
@@ -1370,15 +1370,15 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B52" s="7" t="n"/>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="7" t="n"/>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="7" t="n"/>
@@ -1386,15 +1386,15 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B53" s="7" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D53" s="7" t="n"/>
       <c r="E53" s="7" t="n"/>
       <c r="F53" s="7" t="n"/>
       <c r="G53" s="7" t="n"/>
@@ -1404,29 +1404,29 @@
       <c r="A54" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
       <c r="D54" s="7" t="n"/>
       <c r="E54" s="7" t="n"/>
-      <c r="F54" s="7" t="n"/>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G54" s="7" t="n"/>
       <c r="H54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B55" s="7" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C55" s="7" t="n"/>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
       <c r="F55" s="7" t="n"/>
       <c r="G55" s="7" t="n"/>
@@ -1434,7 +1434,7 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
@@ -1452,31 +1452,31 @@
       <c r="A57" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B57" s="7" t="n"/>
       <c r="C57" s="7" t="n"/>
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
       <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
-      <c r="H57" s="7" t="n"/>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B58" s="7" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C58" s="7" t="n"/>
       <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
     </row>
@@ -1498,31 +1498,31 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B60" s="7" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C60" s="7" t="n"/>
       <c r="D60" s="7" t="n"/>
       <c r="E60" s="7" t="n"/>
       <c r="F60" s="7" t="n"/>
       <c r="G60" s="7" t="n"/>
-      <c r="H60" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+      <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="n"/>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E61" s="7" t="n"/>
       <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
@@ -1536,7 +1536,7 @@
       <c r="C62" s="7" t="n"/>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E62" s="7" t="n"/>
@@ -1562,19 +1562,19 @@
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B64" s="7" t="n"/>
       <c r="C64" s="7" t="n"/>
       <c r="D64" s="7" t="n"/>
       <c r="E64" s="7" t="n"/>
       <c r="F64" s="7" t="n"/>
       <c r="G64" s="7" t="n"/>
-      <c r="H64" s="7" t="n"/>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C65" s="7" t="n"/>
@@ -1596,13 +1596,13 @@
       <c r="A66" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B66" s="7" t="n"/>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C66" s="7" t="n"/>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D66" s="7" t="n"/>
       <c r="E66" s="7" t="n"/>
       <c r="F66" s="7" t="n"/>
       <c r="G66" s="7" t="n"/>
@@ -1616,7 +1616,7 @@
       <c r="C67" s="7" t="n"/>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E67" s="7" t="n"/>
@@ -1632,7 +1632,7 @@
       <c r="C68" s="7" t="n"/>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E68" s="7" t="n"/>
@@ -1648,7 +1648,7 @@
       <c r="C69" s="7" t="n"/>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E69" s="7" t="n"/>
@@ -1664,7 +1664,7 @@
       <c r="C70" s="7" t="n"/>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E70" s="7" t="n"/>
@@ -1678,13 +1678,13 @@
       </c>
       <c r="B71" s="7" t="n"/>
       <c r="C71" s="7" t="n"/>
-      <c r="D71" s="7" t="n"/>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E71" s="7" t="n"/>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
       <c r="H71" s="7" t="n"/>
     </row>
@@ -1700,39 +1700,39 @@
       <c r="G72" s="7" t="n"/>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>Joe Burrow</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B73" s="7" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C73" s="7" t="n"/>
       <c r="D73" s="7" t="n"/>
       <c r="E73" s="7" t="n"/>
       <c r="F73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
-      <c r="H73" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B74" s="7" t="n"/>
       <c r="C74" s="7" t="n"/>
       <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
-      <c r="F74" s="7" t="n"/>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G74" s="7" t="n"/>
       <c r="H74" s="7" t="n"/>
     </row>
@@ -1746,7 +1746,7 @@
       <c r="E75" s="7" t="n"/>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>Isaiah Likely</t>
+          <t>Tucker Kraft</t>
         </is>
       </c>
       <c r="G75" s="7" t="n"/>
@@ -1834,31 +1834,31 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B81" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C81" s="7" t="n"/>
       <c r="D81" s="7" t="n"/>
       <c r="E81" s="7" t="n"/>
       <c r="F81" s="7" t="n"/>
       <c r="G81" s="7" t="n"/>
-      <c r="H81" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H81" s="7" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+      <c r="B82" s="7" t="n"/>
       <c r="C82" s="7" t="n"/>
-      <c r="D82" s="7" t="n"/>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E82" s="7" t="n"/>
       <c r="F82" s="7" t="n"/>
       <c r="G82" s="7" t="n"/>
@@ -1872,7 +1872,7 @@
       <c r="C83" s="7" t="n"/>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E83" s="7" t="n"/>
@@ -1888,7 +1888,7 @@
       <c r="C84" s="7" t="n"/>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E84" s="7" t="n"/>
@@ -1902,15 +1902,15 @@
       </c>
       <c r="B85" s="7" t="n"/>
       <c r="C85" s="7" t="n"/>
-      <c r="D85" s="7" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D85" s="7" t="n"/>
       <c r="E85" s="7" t="n"/>
       <c r="F85" s="7" t="n"/>
       <c r="G85" s="7" t="n"/>
-      <c r="H85" s="7" t="n"/>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="n">
@@ -2064,7 +2064,7 @@
       <c r="C95" s="7" t="n"/>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E95" s="7" t="n"/>
@@ -2078,13 +2078,13 @@
       </c>
       <c r="B96" s="7" t="n"/>
       <c r="C96" s="7" t="n"/>
-      <c r="D96" s="7" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D96" s="7" t="n"/>
       <c r="E96" s="7" t="n"/>
-      <c r="F96" s="7" t="n"/>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G96" s="7" t="n"/>
       <c r="H96" s="7" t="n"/>
     </row>
@@ -2176,7 +2176,7 @@
       <c r="C102" s="7" t="n"/>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E102" s="7" t="n"/>
@@ -2190,13 +2190,13 @@
       </c>
       <c r="B103" s="7" t="n"/>
       <c r="C103" s="7" t="n"/>
-      <c r="D103" s="7" t="n"/>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E103" s="7" t="n"/>
-      <c r="F103" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F103" s="7" t="n"/>
       <c r="G103" s="7" t="n"/>
       <c r="H103" s="7" t="n"/>
     </row>
@@ -2311,7 +2311,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 105 players, top value 76.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 105 players, top value 78.</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 4): implied = average of the sheet value at the player's projection-rank slot</t>
+          <t xml:space="preserve">   (Projections page snapshot 5): implied = average of the sheet value at the player's projection-rank slot</t>
         </is>
       </c>
     </row>
@@ -2349,14 +2349,14 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.4 x (implied - sheet), then rescaled so the total equals the sheet total. 76 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.4 x (implied - sheet), then rescaled so the total equals the sheet total. 78 players moved.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   No projection this week (value kept): Puka Nacua, Nico Collins, Rome Odunze, Josh Jacobs, De'Zhaun Stribling, Jayden Daniels, Jordan Mason, Alec Pierce, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Jaxson Dart, Ja'Kobi Lane.</t>
+          <t xml:space="preserve">   No projection this week (value kept): Puka Nacua, Nico Collins, Josh Jacobs, De'Zhaun Stribling, Jayden Daniels, Jordan Mason, Alec Pierce, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Jaxson Dart, Ja'Kobi Lane.</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2435,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Malik Nabers 21-&gt;16, DeVonta Smith 32-&gt;27, Rashee Rice 19-&gt;14, Garrett Wilson 29-&gt;24, Derrick Henry 57-&gt;61, De'Von Achane 42-&gt;38, Chris Olave 47-&gt;43, Drake London 33-&gt;29</t>
+          <t>Largest moves vs. the baseline in this file: Chris Olave 44-&gt;39, Malik Nabers 21-&gt;16, DeVonta Smith 31-&gt;26, Rashee Rice 20-&gt;15, Garrett Wilson 31-&gt;26, Derrick Henry 57-&gt;61, De'Von Achane 42-&gt;38, Drake London 33-&gt;29</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -602,7 +602,7 @@
     </row>
     <row r="4">
       <c r="A4" s="6" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
@@ -666,15 +666,15 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>64</v>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Jonathan Taylor</t>
-        </is>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="B8" s="7" t="n"/>
       <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="7" t="n"/>
@@ -684,13 +684,13 @@
       <c r="A9" s="6" t="n">
         <v>64</v>
       </c>
-      <c r="B9" s="7" t="n"/>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Jonathan Taylor</t>
+        </is>
+      </c>
       <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D9" s="7" t="n"/>
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="7" t="n"/>
@@ -746,15 +746,15 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
@@ -764,13 +764,13 @@
       <c r="A14" s="6" t="n">
         <v>57</v>
       </c>
-      <c r="B14" s="7" t="n"/>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D14" s="7" t="n"/>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
@@ -794,7 +794,7 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
@@ -810,7 +810,7 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
@@ -826,15 +826,15 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
@@ -842,17 +842,17 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G19" s="7" t="n"/>
       <c r="H19" s="7" t="n"/>
     </row>
@@ -860,13 +860,13 @@
       <c r="A20" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="B20" s="7" t="n"/>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
@@ -878,27 +878,27 @@
       </c>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
       <c r="H21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="B22" s="7" t="n"/>
+        <v>38</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>De'Von Achane</t>
+        </is>
+      </c>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
@@ -906,23 +906,23 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>De'Von Achane</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
       <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
@@ -954,31 +954,31 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B27" s="7" t="n"/>
+        <v>31</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D27" s="7" t="n"/>
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
@@ -986,15 +986,15 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="7" t="n"/>
@@ -1002,15 +1002,15 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="7" t="n"/>
@@ -1020,13 +1020,13 @@
       <c r="A30" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="7" t="n"/>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D30" s="7" t="n"/>
       <c r="E30" s="7" t="n"/>
       <c r="F30" s="7" t="n"/>
       <c r="G30" s="7" t="n"/>
@@ -1034,13 +1034,13 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E31" s="7" t="n"/>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
@@ -1066,13 +1066,13 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E33" s="7" t="n"/>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
@@ -1132,13 +1132,13 @@
       <c r="A37" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="B37" s="7" t="n"/>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D37" s="7" t="n"/>
       <c r="E37" s="7" t="n"/>
       <c r="F37" s="7" t="n"/>
       <c r="G37" s="7" t="n"/>
@@ -1146,15 +1146,15 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="n"/>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E38" s="7" t="n"/>
       <c r="F38" s="7" t="n"/>
       <c r="G38" s="7" t="n"/>
@@ -1164,13 +1164,13 @@
       <c r="A39" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="B39" s="7" t="n"/>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C39" s="7" t="n"/>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D39" s="7" t="n"/>
       <c r="E39" s="7" t="n"/>
       <c r="F39" s="7" t="n"/>
       <c r="G39" s="7" t="n"/>
@@ -1182,39 +1182,39 @@
       </c>
       <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="n"/>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E40" s="7" t="n"/>
-      <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
       <c r="H40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
       <c r="D41" s="7" t="n"/>
       <c r="E41" s="7" t="n"/>
-      <c r="F41" s="7" t="n"/>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G41" s="7" t="n"/>
       <c r="H41" s="7" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="C42" s="7" t="n"/>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="C43" s="7" t="n"/>
@@ -1242,15 +1242,15 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B44" s="7" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D44" s="7" t="n"/>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="7" t="n"/>
@@ -1260,13 +1260,13 @@
       <c r="A45" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+      <c r="B45" s="7" t="n"/>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="n"/>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E45" s="7" t="n"/>
       <c r="F45" s="7" t="n"/>
       <c r="G45" s="7" t="n"/>
@@ -1274,13 +1274,13 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E46" s="7" t="n"/>
@@ -1296,7 +1296,7 @@
       <c r="C47" s="7" t="n"/>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E47" s="7" t="n"/>
@@ -1312,7 +1312,7 @@
       <c r="C48" s="7" t="n"/>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E48" s="7" t="n"/>
@@ -1322,13 +1322,13 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B49" s="7" t="n"/>
       <c r="C49" s="7" t="n"/>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E49" s="7" t="n"/>
@@ -1344,7 +1344,7 @@
       <c r="C50" s="7" t="n"/>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E50" s="7" t="n"/>
@@ -1360,7 +1360,7 @@
       <c r="C51" s="7" t="n"/>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E51" s="7" t="n"/>
@@ -1370,13 +1370,13 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B52" s="7" t="n"/>
       <c r="C52" s="7" t="n"/>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E52" s="7" t="n"/>
@@ -1388,13 +1388,13 @@
       <c r="A53" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B53" s="7" t="n"/>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="7" t="n"/>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E53" s="7" t="n"/>
       <c r="F53" s="7" t="n"/>
       <c r="G53" s="7" t="n"/>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C55" s="7" t="n"/>
@@ -1434,11 +1434,11 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Jadarian Price</t>
         </is>
       </c>
       <c r="C56" s="7" t="n"/>
@@ -1450,19 +1450,19 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B57" s="7" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C57" s="7" t="n"/>
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
       <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
-      <c r="H57" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
@@ -1498,31 +1498,31 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B60" s="7" t="n"/>
       <c r="C60" s="7" t="n"/>
       <c r="D60" s="7" t="n"/>
       <c r="E60" s="7" t="n"/>
       <c r="F60" s="7" t="n"/>
       <c r="G60" s="7" t="n"/>
-      <c r="H60" s="7" t="n"/>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B61" s="7" t="n"/>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
       <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
@@ -1536,7 +1536,7 @@
       <c r="C62" s="7" t="n"/>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="E62" s="7" t="n"/>
@@ -1546,35 +1546,35 @@
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B63" s="7" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C63" s="7" t="n"/>
       <c r="D63" s="7" t="n"/>
       <c r="E63" s="7" t="n"/>
-      <c r="F63" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F63" s="7" t="n"/>
       <c r="G63" s="7" t="n"/>
       <c r="H63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B64" s="7" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C64" s="7" t="n"/>
       <c r="D64" s="7" t="n"/>
       <c r="E64" s="7" t="n"/>
       <c r="F64" s="7" t="n"/>
       <c r="G64" s="7" t="n"/>
-      <c r="H64" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C65" s="7" t="n"/>
@@ -1596,13 +1596,13 @@
       <c r="A66" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B66" s="7" t="n"/>
       <c r="C66" s="7" t="n"/>
-      <c r="D66" s="7" t="n"/>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E66" s="7" t="n"/>
       <c r="F66" s="7" t="n"/>
       <c r="G66" s="7" t="n"/>
@@ -1616,7 +1616,7 @@
       <c r="C67" s="7" t="n"/>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E67" s="7" t="n"/>
@@ -1632,7 +1632,7 @@
       <c r="C68" s="7" t="n"/>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E68" s="7" t="n"/>
@@ -1648,7 +1648,7 @@
       <c r="C69" s="7" t="n"/>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E69" s="7" t="n"/>
@@ -1664,7 +1664,7 @@
       <c r="C70" s="7" t="n"/>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E70" s="7" t="n"/>
@@ -1678,13 +1678,13 @@
       </c>
       <c r="B71" s="7" t="n"/>
       <c r="C71" s="7" t="n"/>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D71" s="7" t="n"/>
       <c r="E71" s="7" t="n"/>
-      <c r="F71" s="7" t="n"/>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G71" s="7" t="n"/>
       <c r="H71" s="7" t="n"/>
     </row>
@@ -1700,39 +1700,39 @@
       <c r="G72" s="7" t="n"/>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Joe Burrow</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B73" s="7" t="n"/>
       <c r="C73" s="7" t="n"/>
       <c r="D73" s="7" t="n"/>
       <c r="E73" s="7" t="n"/>
       <c r="F73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
-      <c r="H73" s="7" t="n"/>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B74" s="7" t="n"/>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C74" s="7" t="n"/>
       <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
-      <c r="F74" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
       <c r="H74" s="7" t="n"/>
     </row>
@@ -1746,7 +1746,7 @@
       <c r="E75" s="7" t="n"/>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G75" s="7" t="n"/>
@@ -1760,29 +1760,29 @@
       <c r="C76" s="7" t="n"/>
       <c r="D76" s="7" t="n"/>
       <c r="E76" s="7" t="n"/>
-      <c r="F76" s="7" t="n"/>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G76" s="7" t="n"/>
-      <c r="H76" s="7" t="inlineStr">
-        <is>
-          <t>Jalen Hurts</t>
-        </is>
-      </c>
+      <c r="H76" s="7" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B77" s="7" t="n"/>
       <c r="C77" s="7" t="n"/>
       <c r="D77" s="7" t="n"/>
       <c r="E77" s="7" t="n"/>
       <c r="F77" s="7" t="n"/>
       <c r="G77" s="7" t="n"/>
-      <c r="H77" s="7" t="n"/>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>Jalen Hurts</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="n">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C78" s="7" t="n"/>
@@ -1804,13 +1804,13 @@
       <c r="A79" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B79" s="7" t="n"/>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
       <c r="C79" s="7" t="n"/>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>Carnell Tate</t>
-        </is>
-      </c>
+      <c r="D79" s="7" t="n"/>
       <c r="E79" s="7" t="n"/>
       <c r="F79" s="7" t="n"/>
       <c r="G79" s="7" t="n"/>
@@ -1824,7 +1824,7 @@
       <c r="C80" s="7" t="n"/>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E80" s="7" t="n"/>
@@ -1834,15 +1834,15 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B81" s="7" t="n"/>
       <c r="C81" s="7" t="n"/>
-      <c r="D81" s="7" t="n"/>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E81" s="7" t="n"/>
       <c r="F81" s="7" t="n"/>
       <c r="G81" s="7" t="n"/>
@@ -1850,19 +1850,19 @@
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B82" s="7" t="n"/>
       <c r="C82" s="7" t="n"/>
-      <c r="D82" s="7" t="inlineStr">
-        <is>
-          <t>Brian Thomas Jr.</t>
-        </is>
-      </c>
+      <c r="D82" s="7" t="n"/>
       <c r="E82" s="7" t="n"/>
       <c r="F82" s="7" t="n"/>
       <c r="G82" s="7" t="n"/>
-      <c r="H82" s="7" t="n"/>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="n">
@@ -1872,7 +1872,7 @@
       <c r="C83" s="7" t="n"/>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E83" s="7" t="n"/>
@@ -1888,7 +1888,7 @@
       <c r="C84" s="7" t="n"/>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E84" s="7" t="n"/>
@@ -1902,15 +1902,15 @@
       </c>
       <c r="B85" s="7" t="n"/>
       <c r="C85" s="7" t="n"/>
-      <c r="D85" s="7" t="n"/>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E85" s="7" t="n"/>
       <c r="F85" s="7" t="n"/>
       <c r="G85" s="7" t="n"/>
-      <c r="H85" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H85" s="7" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="n">
@@ -2080,29 +2080,29 @@
       <c r="C96" s="7" t="n"/>
       <c r="D96" s="7" t="n"/>
       <c r="E96" s="7" t="n"/>
-      <c r="F96" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F96" s="7" t="n"/>
       <c r="G96" s="7" t="n"/>
-      <c r="H96" s="7" t="n"/>
+      <c r="H96" s="7" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B97" s="7" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C97" s="7" t="n"/>
       <c r="D97" s="7" t="n"/>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="7" t="n"/>
       <c r="G97" s="7" t="n"/>
-      <c r="H97" s="7" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H97" s="7" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="C98" s="7" t="n"/>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>Blake Corum</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="C99" s="7" t="n"/>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="C100" s="7" t="n"/>
@@ -2156,13 +2156,13 @@
       <c r="A101" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B101" s="7" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+      <c r="B101" s="7" t="n"/>
       <c r="C101" s="7" t="n"/>
-      <c r="D101" s="7" t="n"/>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
       <c r="E101" s="7" t="n"/>
       <c r="F101" s="7" t="n"/>
       <c r="G101" s="7" t="n"/>
@@ -2176,7 +2176,7 @@
       <c r="C102" s="7" t="n"/>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Ja'Kobi Lane</t>
         </is>
       </c>
       <c r="E102" s="7" t="n"/>
@@ -2190,13 +2190,13 @@
       </c>
       <c r="B103" s="7" t="n"/>
       <c r="C103" s="7" t="n"/>
-      <c r="D103" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
+      <c r="D103" s="7" t="n"/>
       <c r="E103" s="7" t="n"/>
-      <c r="F103" s="7" t="n"/>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G103" s="7" t="n"/>
       <c r="H103" s="7" t="n"/>
     </row>
@@ -2311,7 +2311,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 105 players, top value 78.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 105 players, top value 77.</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 5): implied = average of the sheet value at the player's projection-rank slot</t>
+          <t xml:space="preserve">   (Projections page snapshot 6): implied = average of the sheet value at the player's projection-rank slot</t>
         </is>
       </c>
     </row>
@@ -2349,14 +2349,14 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.4 x (implied - sheet), then rescaled so the total equals the sheet total. 78 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.4 x (implied - sheet), then rescaled so the total equals the sheet total. 77 players moved.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   No projection this week (value kept): Puka Nacua, Nico Collins, Josh Jacobs, De'Zhaun Stribling, Jayden Daniels, Jordan Mason, Alec Pierce, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Jaxson Dart, Ja'Kobi Lane.</t>
+          <t xml:space="preserve">   No projection this week (value kept): Puka Nacua, Nico Collins, Rome Odunze, Josh Jacobs, De'Zhaun Stribling, Jayden Daniels, Jordan Mason, Alec Pierce, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Jaxson Dart, Ja'Kobi Lane.</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2435,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Chris Olave 44-&gt;39, Malik Nabers 21-&gt;16, DeVonta Smith 31-&gt;26, Rashee Rice 20-&gt;15, Garrett Wilson 31-&gt;26, Derrick Henry 57-&gt;61, De'Von Achane 42-&gt;38, Drake London 33-&gt;29</t>
+          <t>Largest moves vs. the baseline in this file: Malik Nabers 21-&gt;16, DeVonta Smith 32-&gt;27, Rashee Rice 19-&gt;14, Derrick Henry 57-&gt;61, De'Von Achane 42-&gt;38, Chris Olave 47-&gt;43, Drake London 33-&gt;29, Nico Collins 36-&gt;32</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -666,15 +666,15 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="B8" s="7" t="n"/>
+        <v>64</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Jonathan Taylor</t>
+        </is>
+      </c>
       <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D8" s="7" t="n"/>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="7" t="n"/>
@@ -684,13 +684,13 @@
       <c r="A9" s="6" t="n">
         <v>64</v>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Jonathan Taylor</t>
-        </is>
-      </c>
+      <c r="B9" s="7" t="n"/>
       <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="7" t="n"/>
@@ -714,15 +714,15 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>61</v>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
@@ -730,15 +730,15 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="B12" s="7" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D12" s="7" t="n"/>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="n"/>
@@ -794,7 +794,7 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
@@ -842,39 +842,39 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="B19" s="7" t="n"/>
+        <v>44</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C19" s="7" t="n"/>
       <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
       <c r="H19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
       <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
@@ -926,7 +926,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C24" s="7" t="n"/>
@@ -938,11 +938,11 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C25" s="7" t="n"/>
@@ -956,13 +956,13 @@
       <c r="A26" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="B26" s="7" t="n"/>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
@@ -970,15 +970,15 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
@@ -992,7 +992,7 @@
       <c r="C28" s="7" t="n"/>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E28" s="7" t="n"/>
@@ -1002,13 +1002,13 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E29" s="7" t="n"/>
@@ -1020,13 +1020,13 @@
       <c r="A30" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+      <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="n"/>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E30" s="7" t="n"/>
       <c r="F30" s="7" t="n"/>
       <c r="G30" s="7" t="n"/>
@@ -1040,7 +1040,7 @@
       <c r="C31" s="7" t="n"/>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E31" s="7" t="n"/>
@@ -1050,15 +1050,15 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="B32" s="7" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
@@ -1072,7 +1072,7 @@
       <c r="C33" s="7" t="n"/>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E33" s="7" t="n"/>
@@ -1088,7 +1088,7 @@
       <c r="C34" s="7" t="n"/>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E34" s="7" t="n"/>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
@@ -1162,17 +1162,17 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
       <c r="D39" s="7" t="n"/>
       <c r="E39" s="7" t="n"/>
-      <c r="F39" s="7" t="n"/>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G39" s="7" t="n"/>
       <c r="H39" s="7" t="n"/>
     </row>
@@ -1180,13 +1180,13 @@
       <c r="A40" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="B40" s="7" t="n"/>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D40" s="7" t="n"/>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
@@ -1198,13 +1198,13 @@
       </c>
       <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="n"/>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E41" s="7" t="n"/>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F41" s="7" t="n"/>
       <c r="G41" s="7" t="n"/>
       <c r="H41" s="7" t="n"/>
     </row>
@@ -1274,13 +1274,13 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E46" s="7" t="n"/>
@@ -1290,13 +1290,13 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="n"/>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E47" s="7" t="n"/>
@@ -1312,7 +1312,7 @@
       <c r="C48" s="7" t="n"/>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E48" s="7" t="n"/>
@@ -1328,7 +1328,7 @@
       <c r="C49" s="7" t="n"/>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E49" s="7" t="n"/>
@@ -1388,13 +1388,13 @@
       <c r="A53" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B53" s="7" t="n"/>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D53" s="7" t="n"/>
       <c r="E53" s="7" t="n"/>
       <c r="F53" s="7" t="n"/>
       <c r="G53" s="7" t="n"/>
@@ -1406,29 +1406,29 @@
       </c>
       <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
-      <c r="D54" s="7" t="n"/>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E54" s="7" t="n"/>
-      <c r="F54" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F54" s="7" t="n"/>
       <c r="G54" s="7" t="n"/>
       <c r="H54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B55" s="7" t="n"/>
       <c r="C55" s="7" t="n"/>
       <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7" t="n"/>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G55" s="7" t="n"/>
       <c r="H55" s="7" t="n"/>
     </row>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
@@ -1546,15 +1546,15 @@
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B63" s="7" t="n"/>
       <c r="C63" s="7" t="n"/>
-      <c r="D63" s="7" t="n"/>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E63" s="7" t="n"/>
       <c r="F63" s="7" t="n"/>
       <c r="G63" s="7" t="n"/>
@@ -1562,17 +1562,17 @@
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B64" s="7" t="n"/>
       <c r="C64" s="7" t="n"/>
       <c r="D64" s="7" t="n"/>
       <c r="E64" s="7" t="n"/>
-      <c r="F64" s="7" t="n"/>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G64" s="7" t="n"/>
       <c r="H64" s="7" t="n"/>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C65" s="7" t="n"/>
@@ -1596,13 +1596,13 @@
       <c r="A66" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B66" s="7" t="n"/>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C66" s="7" t="n"/>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D66" s="7" t="n"/>
       <c r="E66" s="7" t="n"/>
       <c r="F66" s="7" t="n"/>
       <c r="G66" s="7" t="n"/>
@@ -1612,13 +1612,13 @@
       <c r="A67" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B67" s="7" t="n"/>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C67" s="7" t="n"/>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D67" s="7" t="n"/>
       <c r="E67" s="7" t="n"/>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
@@ -1632,7 +1632,7 @@
       <c r="C68" s="7" t="n"/>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E68" s="7" t="n"/>
@@ -1648,7 +1648,7 @@
       <c r="C69" s="7" t="n"/>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E69" s="7" t="n"/>
@@ -1664,7 +1664,7 @@
       <c r="C70" s="7" t="n"/>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E70" s="7" t="n"/>
@@ -1678,13 +1678,13 @@
       </c>
       <c r="B71" s="7" t="n"/>
       <c r="C71" s="7" t="n"/>
-      <c r="D71" s="7" t="n"/>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E71" s="7" t="n"/>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
       <c r="H71" s="7" t="n"/>
     </row>
@@ -1696,13 +1696,13 @@
       <c r="C72" s="7" t="n"/>
       <c r="D72" s="7" t="n"/>
       <c r="E72" s="7" t="n"/>
-      <c r="F72" s="7" t="n"/>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G72" s="7" t="n"/>
-      <c r="H72" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H72" s="7" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
@@ -1716,39 +1716,39 @@
       <c r="G73" s="7" t="n"/>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Joe Burrow</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B74" s="7" t="n"/>
       <c r="C74" s="7" t="n"/>
       <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
       <c r="F74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
-      <c r="H74" s="7" t="n"/>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B75" s="7" t="n"/>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C75" s="7" t="n"/>
       <c r="D75" s="7" t="n"/>
       <c r="E75" s="7" t="n"/>
-      <c r="F75" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F75" s="7" t="n"/>
       <c r="G75" s="7" t="n"/>
       <c r="H75" s="7" t="n"/>
     </row>
@@ -1762,7 +1762,7 @@
       <c r="E76" s="7" t="n"/>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G76" s="7" t="n"/>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C78" s="7" t="n"/>
@@ -1804,13 +1804,13 @@
       <c r="A79" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+      <c r="B79" s="7" t="n"/>
       <c r="C79" s="7" t="n"/>
-      <c r="D79" s="7" t="n"/>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>Carnell Tate</t>
+        </is>
+      </c>
       <c r="E79" s="7" t="n"/>
       <c r="F79" s="7" t="n"/>
       <c r="G79" s="7" t="n"/>
@@ -1824,7 +1824,7 @@
       <c r="C80" s="7" t="n"/>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E80" s="7" t="n"/>
@@ -1838,31 +1838,31 @@
       </c>
       <c r="B81" s="7" t="n"/>
       <c r="C81" s="7" t="n"/>
-      <c r="D81" s="7" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D81" s="7" t="n"/>
       <c r="E81" s="7" t="n"/>
       <c r="F81" s="7" t="n"/>
       <c r="G81" s="7" t="n"/>
-      <c r="H81" s="7" t="n"/>
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B82" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C82" s="7" t="n"/>
       <c r="D82" s="7" t="n"/>
       <c r="E82" s="7" t="n"/>
       <c r="F82" s="7" t="n"/>
       <c r="G82" s="7" t="n"/>
-      <c r="H82" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H82" s="7" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="n">
@@ -2064,7 +2064,7 @@
       <c r="C95" s="7" t="n"/>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E95" s="7" t="n"/>
@@ -2078,31 +2078,31 @@
       </c>
       <c r="B96" s="7" t="n"/>
       <c r="C96" s="7" t="n"/>
-      <c r="D96" s="7" t="n"/>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="7" t="n"/>
       <c r="G96" s="7" t="n"/>
-      <c r="H96" s="7" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H96" s="7" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B97" s="7" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B97" s="7" t="n"/>
       <c r="C97" s="7" t="n"/>
       <c r="D97" s="7" t="n"/>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="7" t="n"/>
       <c r="G97" s="7" t="n"/>
-      <c r="H97" s="7" t="n"/>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>Blake Corum</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="C98" s="7" t="n"/>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="C99" s="7" t="n"/>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>Woody Marks</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="C100" s="7" t="n"/>
@@ -2156,13 +2156,13 @@
       <c r="A101" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B101" s="7" t="n"/>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C101" s="7" t="n"/>
-      <c r="D101" s="7" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
+      <c r="D101" s="7" t="n"/>
       <c r="E101" s="7" t="n"/>
       <c r="F101" s="7" t="n"/>
       <c r="G101" s="7" t="n"/>
@@ -2335,7 +2335,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 6): implied = average of the sheet value at the player's projection-rank slot</t>
+          <t xml:space="preserve">   (Projections page snapshot 7): implied = average of the sheet value at the player's projection-rank slot</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.4 x (implied - sheet), then rescaled so the total equals the sheet total. 77 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.4 x (implied - sheet), then rescaled so the total equals the sheet total. 76 players moved.</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2435,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Malik Nabers 21-&gt;16, DeVonta Smith 32-&gt;27, Rashee Rice 19-&gt;14, Derrick Henry 57-&gt;61, De'Von Achane 42-&gt;38, Chris Olave 47-&gt;43, Drake London 33-&gt;29, Nico Collins 36-&gt;32</t>
+          <t>Largest moves vs. the baseline in this file: Malik Nabers 20-&gt;15, DeVonta Smith 31-&gt;26, Rashee Rice 19-&gt;14, Derrick Henry 57-&gt;61, De'Von Achane 42-&gt;38, Chris Olave 46-&gt;42, Drake London 33-&gt;29, Nico Collins 36-&gt;32</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -602,7 +602,7 @@
     </row>
     <row r="4">
       <c r="A4" s="6" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C6" s="7" t="n"/>
@@ -650,11 +650,11 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C7" s="7" t="n"/>
@@ -778,7 +778,7 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
@@ -810,7 +810,7 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
@@ -842,7 +842,7 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
@@ -890,7 +890,7 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
@@ -906,35 +906,35 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="B23" s="7" t="n"/>
+        <v>37</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C23" s="7" t="n"/>
       <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="n"/>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
@@ -956,13 +956,13 @@
       <c r="A26" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+      <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
@@ -970,15 +970,15 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B27" s="7" t="n"/>
+        <v>31</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D27" s="7" t="n"/>
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
@@ -992,7 +992,7 @@
       <c r="C28" s="7" t="n"/>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E28" s="7" t="n"/>
@@ -1002,13 +1002,13 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E29" s="7" t="n"/>
@@ -1018,13 +1018,13 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E30" s="7" t="n"/>
@@ -1034,15 +1034,15 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" s="7" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D31" s="7" t="n"/>
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="7" t="n"/>
       <c r="G31" s="7" t="n"/>
@@ -1050,15 +1050,15 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
@@ -1086,59 +1086,59 @@
       </c>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D34" s="7" t="n"/>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="n"/>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="B35" s="7" t="n"/>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C35" s="7" t="n"/>
       <c r="D35" s="7" t="n"/>
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="7" t="n"/>
-      <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="7" t="n"/>
       <c r="E36" s="7" t="n"/>
-      <c r="F36" s="7" t="n"/>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G36" s="7" t="n"/>
       <c r="H36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7" t="n"/>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E37" s="7" t="n"/>
       <c r="F37" s="7" t="n"/>
       <c r="G37" s="7" t="n"/>
@@ -1146,13 +1146,13 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E38" s="7" t="n"/>
@@ -1162,27 +1162,27 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
-      <c r="D39" s="7" t="n"/>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E39" s="7" t="n"/>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F39" s="7" t="n"/>
       <c r="G39" s="7" t="n"/>
       <c r="H39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C40" s="7" t="n"/>
@@ -1194,15 +1194,15 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="B41" s="7" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D41" s="7" t="n"/>
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="7" t="n"/>
@@ -1210,15 +1210,15 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B42" s="7" t="n"/>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="n"/>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="7" t="n"/>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C43" s="7" t="n"/>
@@ -1242,11 +1242,11 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="C44" s="7" t="n"/>
@@ -1258,13 +1258,13 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B45" s="7" t="n"/>
       <c r="C45" s="7" t="n"/>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E45" s="7" t="n"/>
@@ -1276,13 +1276,13 @@
       <c r="A46" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B46" s="7" t="n"/>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D46" s="7" t="n"/>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="7" t="n"/>
@@ -1290,13 +1290,13 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="n"/>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E47" s="7" t="n"/>
@@ -1322,13 +1322,13 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B49" s="7" t="n"/>
       <c r="C49" s="7" t="n"/>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E49" s="7" t="n"/>
@@ -1340,13 +1340,13 @@
       <c r="A50" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B50" s="7" t="n"/>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
       <c r="F50" s="7" t="n"/>
       <c r="G50" s="7" t="n"/>
@@ -1388,13 +1388,13 @@
       <c r="A53" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B53" s="7" t="n"/>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="7" t="n"/>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E53" s="7" t="n"/>
       <c r="F53" s="7" t="n"/>
       <c r="G53" s="7" t="n"/>
@@ -1418,27 +1418,27 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B55" s="7" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C55" s="7" t="n"/>
       <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F55" s="7" t="n"/>
       <c r="G55" s="7" t="n"/>
       <c r="H55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C56" s="7" t="n"/>
@@ -1450,23 +1450,23 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B57" s="7" t="n"/>
       <c r="C57" s="7" t="n"/>
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
-      <c r="F57" s="7" t="n"/>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G57" s="7" t="n"/>
       <c r="H57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
@@ -1486,13 +1486,13 @@
       </c>
       <c r="B59" s="7" t="n"/>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="7" t="n"/>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E59" s="7" t="n"/>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F59" s="7" t="n"/>
       <c r="G59" s="7" t="n"/>
       <c r="H59" s="7" t="n"/>
     </row>
@@ -1502,59 +1502,59 @@
       </c>
       <c r="B60" s="7" t="n"/>
       <c r="C60" s="7" t="n"/>
-      <c r="D60" s="7" t="n"/>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E60" s="7" t="n"/>
       <c r="F60" s="7" t="n"/>
       <c r="G60" s="7" t="n"/>
-      <c r="H60" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
       <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
-      <c r="F61" s="7" t="n"/>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G61" s="7" t="n"/>
       <c r="H61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B62" s="7" t="n"/>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D62" s="7" t="n"/>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="7" t="n"/>
-      <c r="H62" s="7" t="n"/>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B63" s="7" t="n"/>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C63" s="7" t="n"/>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>Jameson Williams</t>
-        </is>
-      </c>
+      <c r="D63" s="7" t="n"/>
       <c r="E63" s="7" t="n"/>
       <c r="F63" s="7" t="n"/>
       <c r="G63" s="7" t="n"/>
@@ -1566,13 +1566,13 @@
       </c>
       <c r="B64" s="7" t="n"/>
       <c r="C64" s="7" t="n"/>
-      <c r="D64" s="7" t="n"/>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E64" s="7" t="n"/>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F64" s="7" t="n"/>
       <c r="G64" s="7" t="n"/>
       <c r="H64" s="7" t="n"/>
     </row>
@@ -1612,13 +1612,13 @@
       <c r="A67" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+      <c r="B67" s="7" t="n"/>
       <c r="C67" s="7" t="n"/>
-      <c r="D67" s="7" t="n"/>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E67" s="7" t="n"/>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
@@ -1632,7 +1632,7 @@
       <c r="C68" s="7" t="n"/>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E68" s="7" t="n"/>
@@ -1648,7 +1648,7 @@
       <c r="C69" s="7" t="n"/>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E69" s="7" t="n"/>
@@ -1662,13 +1662,13 @@
       </c>
       <c r="B70" s="7" t="n"/>
       <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="inlineStr">
-        <is>
-          <t>De'Zhaun Stribling</t>
-        </is>
-      </c>
+      <c r="D70" s="7" t="n"/>
       <c r="E70" s="7" t="n"/>
-      <c r="F70" s="7" t="n"/>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G70" s="7" t="n"/>
       <c r="H70" s="7" t="n"/>
     </row>
@@ -1678,15 +1678,15 @@
       </c>
       <c r="B71" s="7" t="n"/>
       <c r="C71" s="7" t="n"/>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D71" s="7" t="n"/>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
-      <c r="H71" s="7" t="n"/>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
@@ -1696,59 +1696,59 @@
       <c r="C72" s="7" t="n"/>
       <c r="D72" s="7" t="n"/>
       <c r="E72" s="7" t="n"/>
-      <c r="F72" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F72" s="7" t="n"/>
       <c r="G72" s="7" t="n"/>
-      <c r="H72" s="7" t="n"/>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B73" s="7" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C73" s="7" t="n"/>
       <c r="D73" s="7" t="n"/>
       <c r="E73" s="7" t="n"/>
       <c r="F73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
-      <c r="H73" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B74" s="7" t="n"/>
       <c r="C74" s="7" t="n"/>
       <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
-      <c r="F74" s="7" t="n"/>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G74" s="7" t="n"/>
-      <c r="H74" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H74" s="7" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B75" s="7" t="n"/>
       <c r="C75" s="7" t="n"/>
       <c r="D75" s="7" t="n"/>
       <c r="E75" s="7" t="n"/>
-      <c r="F75" s="7" t="n"/>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G75" s="7" t="n"/>
       <c r="H75" s="7" t="n"/>
     </row>
@@ -1760,29 +1760,29 @@
       <c r="C76" s="7" t="n"/>
       <c r="D76" s="7" t="n"/>
       <c r="E76" s="7" t="n"/>
-      <c r="F76" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F76" s="7" t="n"/>
       <c r="G76" s="7" t="n"/>
-      <c r="H76" s="7" t="n"/>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>Jalen Hurts</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B77" s="7" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
       <c r="C77" s="7" t="n"/>
       <c r="D77" s="7" t="n"/>
       <c r="E77" s="7" t="n"/>
       <c r="F77" s="7" t="n"/>
       <c r="G77" s="7" t="n"/>
-      <c r="H77" s="7" t="inlineStr">
-        <is>
-          <t>Jalen Hurts</t>
-        </is>
-      </c>
+      <c r="H77" s="7" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="n">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C78" s="7" t="n"/>
@@ -1914,15 +1914,15 @@
     </row>
     <row r="86">
       <c r="A86" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B86" s="7" t="n"/>
       <c r="C86" s="7" t="n"/>
-      <c r="D86" s="7" t="n"/>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E86" s="7" t="n"/>
       <c r="F86" s="7" t="n"/>
       <c r="G86" s="7" t="n"/>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C87" s="7" t="n"/>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C88" s="7" t="n"/>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C89" s="7" t="n"/>
@@ -1980,13 +1980,13 @@
       <c r="A90" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B90" s="7" t="n"/>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>Rico Dowdle</t>
+        </is>
+      </c>
       <c r="C90" s="7" t="n"/>
-      <c r="D90" s="7" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D90" s="7" t="n"/>
       <c r="E90" s="7" t="n"/>
       <c r="F90" s="7" t="n"/>
       <c r="G90" s="7" t="n"/>
@@ -2000,7 +2000,7 @@
       <c r="C91" s="7" t="n"/>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E91" s="7" t="n"/>
@@ -2016,7 +2016,7 @@
       <c r="C92" s="7" t="n"/>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr.</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E92" s="7" t="n"/>
@@ -2032,7 +2032,7 @@
       <c r="C93" s="7" t="n"/>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E93" s="7" t="n"/>
@@ -2048,7 +2048,7 @@
       <c r="C94" s="7" t="n"/>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E94" s="7" t="n"/>
@@ -2064,7 +2064,7 @@
       <c r="C95" s="7" t="n"/>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E95" s="7" t="n"/>
@@ -2080,7 +2080,7 @@
       <c r="C96" s="7" t="n"/>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E96" s="7" t="n"/>
@@ -2311,7 +2311,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 105 players, top value 77.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 105 players, top value 78.</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 7): implied = average of the sheet value at the player's projection-rank slot</t>
+          <t xml:space="preserve">   (Projections page snapshot 8): implied = average of the sheet value at the player's projection-rank slot</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2435,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Malik Nabers 20-&gt;15, DeVonta Smith 31-&gt;26, Rashee Rice 19-&gt;14, Derrick Henry 57-&gt;61, De'Von Achane 42-&gt;38, Chris Olave 46-&gt;42, Drake London 33-&gt;29, Nico Collins 36-&gt;32</t>
+          <t>Largest moves vs. the baseline in this file: Malik Nabers 21-&gt;16, DeVonta Smith 32-&gt;27, Rashee Rice 19-&gt;14, Derrick Henry 57-&gt;61, De'Von Achane 43-&gt;39, Chris Olave 46-&gt;42, Drake London 34-&gt;30, Nico Collins 36-&gt;32</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -602,7 +602,7 @@
     </row>
     <row r="4">
       <c r="A4" s="6" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
@@ -956,13 +956,13 @@
       <c r="A26" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="B26" s="7" t="n"/>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
@@ -970,15 +970,15 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
@@ -986,15 +986,15 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="B28" s="7" t="n"/>
+        <v>31</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D28" s="7" t="n"/>
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="7" t="n"/>
@@ -1008,7 +1008,7 @@
       <c r="C29" s="7" t="n"/>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E29" s="7" t="n"/>
@@ -1024,7 +1024,7 @@
       <c r="C30" s="7" t="n"/>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E30" s="7" t="n"/>
@@ -1034,15 +1034,15 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="7" t="n"/>
       <c r="G31" s="7" t="n"/>
@@ -1050,15 +1050,15 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="B32" s="7" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
@@ -1086,31 +1086,31 @@
       </c>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="n"/>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
       <c r="D35" s="7" t="n"/>
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="7" t="n"/>
-      <c r="H35" s="7" t="n"/>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
@@ -1196,13 +1196,13 @@
       <c r="A41" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+      <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="n"/>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="7" t="n"/>
@@ -1210,15 +1210,15 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="B42" s="7" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D42" s="7" t="n"/>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="7" t="n"/>
@@ -1228,13 +1228,13 @@
       <c r="A43" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B43" s="7" t="n"/>
       <c r="C43" s="7" t="n"/>
-      <c r="D43" s="7" t="n"/>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E43" s="7" t="n"/>
       <c r="F43" s="7" t="n"/>
       <c r="G43" s="7" t="n"/>
@@ -1242,11 +1242,11 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C44" s="7" t="n"/>
@@ -1258,15 +1258,15 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B45" s="7" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D45" s="7" t="n"/>
       <c r="E45" s="7" t="n"/>
       <c r="F45" s="7" t="n"/>
       <c r="G45" s="7" t="n"/>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C46" s="7" t="n"/>
@@ -2311,7 +2311,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 105 players, top value 78.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 105 players, top value 77.</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 8): implied = average of the sheet value at the player's projection-rank slot</t>
+          <t xml:space="preserve">   (Projections page snapshot 9): implied = average of the sheet value at the player's projection-rank slot</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2435,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Malik Nabers 21-&gt;16, DeVonta Smith 32-&gt;27, Rashee Rice 19-&gt;14, Derrick Henry 57-&gt;61, De'Von Achane 43-&gt;39, Chris Olave 46-&gt;42, Drake London 34-&gt;30, Nico Collins 36-&gt;32</t>
+          <t>Largest moves vs. the baseline in this file: Malik Nabers 21-&gt;16, DeVonta Smith 31-&gt;26, Rashee Rice 19-&gt;14, Derrick Henry 57-&gt;61, De'Von Achane 43-&gt;39, Chris Olave 46-&gt;42, Drake London 34-&gt;30, Nico Collins 36-&gt;32</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -618,7 +618,7 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C6" s="7" t="n"/>
@@ -650,11 +650,11 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C7" s="7" t="n"/>
@@ -746,7 +746,7 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
@@ -778,7 +778,7 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
@@ -796,13 +796,13 @@
       <c r="A16" s="6" t="n">
         <v>49</v>
       </c>
-      <c r="B16" s="7" t="n"/>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D16" s="7" t="n"/>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
@@ -810,15 +810,15 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
@@ -938,15 +938,15 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E25" s="7" t="n"/>
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
@@ -954,11 +954,11 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C26" s="7" t="n"/>
@@ -972,13 +972,13 @@
       <c r="A27" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="B27" s="7" t="n"/>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D27" s="7" t="n"/>
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
@@ -986,15 +986,15 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="7" t="n"/>
@@ -1002,15 +1002,15 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="B29" s="7" t="n"/>
+        <v>31</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D29" s="7" t="n"/>
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="7" t="n"/>
@@ -1050,15 +1050,15 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
@@ -1066,15 +1066,15 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="B33" s="7" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D33" s="7" t="n"/>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
@@ -1180,13 +1180,13 @@
       <c r="A40" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+      <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="n"/>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
@@ -1194,15 +1194,15 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="B41" s="7" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D41" s="7" t="n"/>
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="7" t="n"/>
@@ -1226,15 +1226,15 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B43" s="7" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C43" s="7" t="n"/>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D43" s="7" t="n"/>
       <c r="E43" s="7" t="n"/>
       <c r="F43" s="7" t="n"/>
       <c r="G43" s="7" t="n"/>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C44" s="7" t="n"/>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C45" s="7" t="n"/>
@@ -1276,13 +1276,13 @@
       <c r="A46" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+      <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="n"/>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="7" t="n"/>
@@ -1290,13 +1290,13 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="n"/>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E47" s="7" t="n"/>
@@ -1312,7 +1312,7 @@
       <c r="C48" s="7" t="n"/>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E48" s="7" t="n"/>
@@ -1322,15 +1322,15 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B49" s="7" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D49" s="7" t="n"/>
       <c r="E49" s="7" t="n"/>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n"/>
@@ -1340,13 +1340,13 @@
       <c r="A50" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+      <c r="B50" s="7" t="n"/>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="n"/>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E50" s="7" t="n"/>
       <c r="F50" s="7" t="n"/>
       <c r="G50" s="7" t="n"/>
@@ -1360,7 +1360,7 @@
       <c r="C51" s="7" t="n"/>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E51" s="7" t="n"/>
@@ -1370,13 +1370,13 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B52" s="7" t="n"/>
       <c r="C52" s="7" t="n"/>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E52" s="7" t="n"/>
@@ -2328,14 +2328,14 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>0) Weekly re-seed. The sheet values were first moved toward the 2026 week 3 Half PPR medians</t>
+          <t>0) Weekly re-seed. The sheet values were first moved toward the 2026 week 4 Half PPR medians</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 9): implied = average of the sheet value at the player's projection-rank slot</t>
+          <t xml:space="preserve">   (Projections page snapshot 0): implied = average of the sheet value at the player's projection-rank slot</t>
         </is>
       </c>
     </row>
@@ -2349,14 +2349,14 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.4 x (implied - sheet), then rescaled so the total equals the sheet total. 76 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.4 x (implied - sheet), then rescaled so the total equals the sheet total. 75 players moved.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   No projection this week (value kept): Puka Nacua, Nico Collins, Rome Odunze, Josh Jacobs, De'Zhaun Stribling, Jayden Daniels, Jordan Mason, Alec Pierce, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Jaxson Dart, Ja'Kobi Lane.</t>
+          <t xml:space="preserve">   No projection this week (value kept): Puka Nacua, A.J. Brown, Nico Collins, Rome Odunze, Josh Jacobs, De'Zhaun Stribling, Jayden Daniels, Jordan Mason, Alec Pierce, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Jaxson Dart, Ja'Kobi Lane.</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2435,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Malik Nabers 21-&gt;16, DeVonta Smith 31-&gt;26, Rashee Rice 19-&gt;14, Derrick Henry 57-&gt;61, De'Von Achane 43-&gt;39, Chris Olave 46-&gt;42, Drake London 34-&gt;30, Nico Collins 36-&gt;32</t>
+          <t>Largest moves vs. the baseline in this file: Malik Nabers 21-&gt;16, DeVonta Smith 31-&gt;26, Rashee Rice 20-&gt;15, Derrick Henry 57-&gt;61, De'Von Achane 43-&gt;39, Chris Olave 46-&gt;42, Drake London 33-&gt;29, Nico Collins 36-&gt;32</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -602,11 +602,11 @@
     </row>
     <row r="4">
       <c r="A4" s="6" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Jahmyr Gibbs</t>
+          <t>Bijan Robinson</t>
         </is>
       </c>
       <c r="C4" s="7" t="n"/>
@@ -618,11 +618,11 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Bijan Robinson</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C5" s="7" t="n"/>
@@ -634,15 +634,15 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>67</v>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="7" t="n"/>
       <c r="G6" s="7" t="n"/>
@@ -650,11 +650,11 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Jahmyr Gibbs</t>
         </is>
       </c>
       <c r="C7" s="7" t="n"/>
@@ -666,11 +666,11 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="C8" s="7" t="n"/>
@@ -682,15 +682,15 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>64</v>
-      </c>
-      <c r="B9" s="7" t="n"/>
+        <v>56</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D9" s="7" t="n"/>
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="7" t="n"/>
@@ -698,15 +698,15 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>63</v>
-      </c>
-      <c r="B10" s="7" t="n"/>
+        <v>56</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="n"/>
@@ -714,15 +714,15 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>62</v>
-      </c>
-      <c r="B11" s="7" t="n"/>
+        <v>54</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D11" s="7" t="n"/>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
@@ -730,11 +730,11 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C12" s="7" t="n"/>
@@ -746,13 +746,13 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="E13" s="7" t="n"/>
@@ -762,15 +762,15 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
@@ -778,15 +778,15 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B15" s="7" t="n"/>
       <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E15" s="7" t="n"/>
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="7" t="n"/>
@@ -798,7 +798,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Saquon Barkley</t>
+          <t>James Cook III</t>
         </is>
       </c>
       <c r="C16" s="7" t="n"/>
@@ -816,7 +816,7 @@
       <c r="C17" s="7" t="n"/>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>CeeDee Lamb</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E17" s="7" t="n"/>
@@ -826,15 +826,15 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="B18" s="7" t="n"/>
+        <v>39</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
@@ -842,15 +842,15 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
@@ -858,31 +858,31 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="B20" s="7" t="n"/>
+        <v>37</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>De'Von Achane</t>
+        </is>
+      </c>
       <c r="C20" s="7" t="n"/>
       <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="B21" s="7" t="n"/>
+        <v>37</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
@@ -890,31 +890,31 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>De'Von Achane</t>
-        </is>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
       <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="n"/>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
@@ -922,19 +922,19 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="B24" s="7" t="n"/>
+        <v>35</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
@@ -954,27 +954,27 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
       <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C27" s="7" t="n"/>
@@ -986,13 +986,13 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Nico Collins</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E28" s="7" t="n"/>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C29" s="7" t="n"/>
@@ -1020,13 +1020,13 @@
       <c r="A30" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="B30" s="7" t="n"/>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D30" s="7" t="n"/>
       <c r="E30" s="7" t="n"/>
       <c r="F30" s="7" t="n"/>
       <c r="G30" s="7" t="n"/>
@@ -1034,13 +1034,13 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Nico Collins</t>
         </is>
       </c>
       <c r="E31" s="7" t="n"/>
@@ -1050,13 +1050,13 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E32" s="7" t="n"/>
@@ -1066,11 +1066,11 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C33" s="7" t="n"/>
@@ -1082,39 +1082,39 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D34" s="7" t="n"/>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="n"/>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
-      <c r="D35" s="7" t="n"/>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="7" t="n"/>
-      <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
@@ -1122,7 +1122,7 @@
       <c r="E36" s="7" t="n"/>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>Brock Bowers</t>
+          <t>Trey McBride</t>
         </is>
       </c>
       <c r="G36" s="7" t="n"/>
@@ -1130,13 +1130,13 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E37" s="7" t="n"/>
@@ -1152,7 +1152,7 @@
       <c r="C38" s="7" t="n"/>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E38" s="7" t="n"/>
@@ -1162,13 +1162,13 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E39" s="7" t="n"/>
@@ -1178,13 +1178,13 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E40" s="7" t="n"/>
@@ -1194,11 +1194,11 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C41" s="7" t="n"/>
@@ -1210,15 +1210,15 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B42" s="7" t="n"/>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="n"/>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="7" t="n"/>
@@ -1226,11 +1226,11 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="C43" s="7" t="n"/>
@@ -1242,11 +1242,11 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C44" s="7" t="n"/>
@@ -1258,7 +1258,7 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
@@ -1290,13 +1290,13 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="n"/>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E47" s="7" t="n"/>
@@ -1306,15 +1306,15 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B48" s="7" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D48" s="7" t="n"/>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
@@ -1322,11 +1322,11 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C49" s="7" t="n"/>
@@ -1338,13 +1338,13 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B50" s="7" t="n"/>
       <c r="C50" s="7" t="n"/>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E50" s="7" t="n"/>
@@ -1354,15 +1354,15 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B51" s="7" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C51" s="7" t="n"/>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
       <c r="F51" s="7" t="n"/>
       <c r="G51" s="7" t="n"/>
@@ -1370,15 +1370,15 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B52" s="7" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D52" s="7" t="n"/>
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="7" t="n"/>
@@ -1386,13 +1386,13 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B53" s="7" t="n"/>
       <c r="C53" s="7" t="n"/>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E53" s="7" t="n"/>
@@ -1402,13 +1402,13 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E54" s="7" t="n"/>
@@ -1418,11 +1418,11 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C55" s="7" t="n"/>
@@ -1434,11 +1434,11 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C56" s="7" t="n"/>
@@ -1450,47 +1450,47 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B57" s="7" t="n"/>
       <c r="C57" s="7" t="n"/>
-      <c r="D57" s="7" t="n"/>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E57" s="7" t="n"/>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
       <c r="H57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B58" s="7" t="n"/>
       <c r="C58" s="7" t="n"/>
       <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
-      <c r="F58" s="7" t="n"/>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B59" s="7" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>Jameson Williams</t>
-        </is>
-      </c>
+      <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
       <c r="F59" s="7" t="n"/>
       <c r="G59" s="7" t="n"/>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B60" s="7" t="n"/>
       <c r="C60" s="7" t="n"/>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E60" s="7" t="n"/>
@@ -1514,23 +1514,23 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="n"/>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E61" s="7" t="n"/>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
       <c r="H61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B62" s="7" t="n"/>
       <c r="C62" s="7" t="n"/>
@@ -1540,21 +1540,21 @@
       <c r="G62" s="7" t="n"/>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>Drake Maye</t>
+          <t>Joe Burrow</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B63" s="7" t="n"/>
       <c r="C63" s="7" t="n"/>
-      <c r="D63" s="7" t="n"/>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Terry McLaurin</t>
+        </is>
+      </c>
       <c r="E63" s="7" t="n"/>
       <c r="F63" s="7" t="n"/>
       <c r="G63" s="7" t="n"/>
@@ -1562,23 +1562,23 @@
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B64" s="7" t="n"/>
       <c r="C64" s="7" t="n"/>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D64" s="7" t="n"/>
       <c r="E64" s="7" t="n"/>
       <c r="F64" s="7" t="n"/>
       <c r="G64" s="7" t="n"/>
-      <c r="H64" s="7" t="n"/>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
@@ -1594,15 +1594,15 @@
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B66" s="7" t="n"/>
       <c r="C66" s="7" t="n"/>
-      <c r="D66" s="7" t="n"/>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E66" s="7" t="n"/>
       <c r="F66" s="7" t="n"/>
       <c r="G66" s="7" t="n"/>
@@ -1610,13 +1610,13 @@
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B67" s="7" t="n"/>
       <c r="C67" s="7" t="n"/>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E67" s="7" t="n"/>
@@ -1626,39 +1626,39 @@
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B68" s="7" t="n"/>
       <c r="C68" s="7" t="n"/>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D68" s="7" t="n"/>
       <c r="E68" s="7" t="n"/>
-      <c r="F68" s="7" t="n"/>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G68" s="7" t="n"/>
       <c r="H68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B69" s="7" t="n"/>
       <c r="C69" s="7" t="n"/>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>De'Zhaun Stribling</t>
-        </is>
-      </c>
+      <c r="D69" s="7" t="n"/>
       <c r="E69" s="7" t="n"/>
-      <c r="F69" s="7" t="n"/>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G69" s="7" t="n"/>
       <c r="H69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B70" s="7" t="n"/>
       <c r="C70" s="7" t="n"/>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B71" s="7" t="n"/>
       <c r="C71" s="7" t="n"/>
@@ -1684,37 +1684,37 @@
       <c r="G71" s="7" t="n"/>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>Joe Burrow</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B72" s="7" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C72" s="7" t="n"/>
       <c r="D72" s="7" t="n"/>
       <c r="E72" s="7" t="n"/>
       <c r="F72" s="7" t="n"/>
       <c r="G72" s="7" t="n"/>
-      <c r="H72" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H72" s="7" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B73" s="7" t="n"/>
       <c r="C73" s="7" t="n"/>
-      <c r="D73" s="7" t="n"/>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E73" s="7" t="n"/>
       <c r="F73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
@@ -1722,63 +1722,63 @@
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B74" s="7" t="n"/>
       <c r="C74" s="7" t="n"/>
-      <c r="D74" s="7" t="n"/>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E74" s="7" t="n"/>
-      <c r="F74" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
       <c r="H74" s="7" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B75" s="7" t="n"/>
       <c r="C75" s="7" t="n"/>
-      <c r="D75" s="7" t="n"/>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E75" s="7" t="n"/>
-      <c r="F75" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F75" s="7" t="n"/>
       <c r="G75" s="7" t="n"/>
       <c r="H75" s="7" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B76" s="7" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C76" s="7" t="n"/>
       <c r="D76" s="7" t="n"/>
       <c r="E76" s="7" t="n"/>
       <c r="F76" s="7" t="n"/>
       <c r="G76" s="7" t="n"/>
-      <c r="H76" s="7" t="inlineStr">
-        <is>
-          <t>Jalen Hurts</t>
-        </is>
-      </c>
+      <c r="H76" s="7" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B77" s="7" t="n"/>
       <c r="C77" s="7" t="n"/>
-      <c r="D77" s="7" t="n"/>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>De'Zhaun Stribling</t>
+        </is>
+      </c>
       <c r="E77" s="7" t="n"/>
       <c r="F77" s="7" t="n"/>
       <c r="G77" s="7" t="n"/>
@@ -1786,31 +1786,31 @@
     </row>
     <row r="78">
       <c r="A78" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B78" s="7" t="n"/>
       <c r="C78" s="7" t="n"/>
       <c r="D78" s="7" t="n"/>
       <c r="E78" s="7" t="n"/>
       <c r="F78" s="7" t="n"/>
       <c r="G78" s="7" t="n"/>
-      <c r="H78" s="7" t="n"/>
+      <c r="H78" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B79" s="7" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C79" s="7" t="n"/>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>Carnell Tate</t>
-        </is>
-      </c>
+      <c r="D79" s="7" t="n"/>
       <c r="E79" s="7" t="n"/>
       <c r="F79" s="7" t="n"/>
       <c r="G79" s="7" t="n"/>
@@ -1818,13 +1818,13 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B80" s="7" t="n"/>
       <c r="C80" s="7" t="n"/>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E80" s="7" t="n"/>
@@ -1834,7 +1834,7 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B81" s="7" t="n"/>
       <c r="C81" s="7" t="n"/>
@@ -1844,17 +1844,17 @@
       <c r="G81" s="7" t="n"/>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C82" s="7" t="n"/>
@@ -1866,13 +1866,13 @@
     </row>
     <row r="83">
       <c r="A83" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B83" s="7" t="n"/>
       <c r="C83" s="7" t="n"/>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E83" s="7" t="n"/>
@@ -1882,13 +1882,13 @@
     </row>
     <row r="84">
       <c r="A84" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B84" s="7" t="n"/>
       <c r="C84" s="7" t="n"/>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E84" s="7" t="n"/>
@@ -1900,13 +1900,13 @@
       <c r="A85" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B85" s="7" t="n"/>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C85" s="7" t="n"/>
-      <c r="D85" s="7" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D85" s="7" t="n"/>
       <c r="E85" s="7" t="n"/>
       <c r="F85" s="7" t="n"/>
       <c r="G85" s="7" t="n"/>
@@ -1920,7 +1920,7 @@
       <c r="C86" s="7" t="n"/>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E86" s="7" t="n"/>
@@ -1930,15 +1930,15 @@
     </row>
     <row r="87">
       <c r="A87" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B87" s="7" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B87" s="7" t="n"/>
       <c r="C87" s="7" t="n"/>
-      <c r="D87" s="7" t="n"/>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>KC Concepcion</t>
+        </is>
+      </c>
       <c r="E87" s="7" t="n"/>
       <c r="F87" s="7" t="n"/>
       <c r="G87" s="7" t="n"/>
@@ -1946,15 +1946,15 @@
     </row>
     <row r="88">
       <c r="A88" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B88" s="7" t="inlineStr">
-        <is>
-          <t>Jonathon Brooks</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B88" s="7" t="n"/>
       <c r="C88" s="7" t="n"/>
-      <c r="D88" s="7" t="n"/>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>Quentin Johnston</t>
+        </is>
+      </c>
       <c r="E88" s="7" t="n"/>
       <c r="F88" s="7" t="n"/>
       <c r="G88" s="7" t="n"/>
@@ -1962,15 +1962,15 @@
     </row>
     <row r="89">
       <c r="A89" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B89" s="7" t="inlineStr">
-        <is>
-          <t>Mike Washington Jr.</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B89" s="7" t="n"/>
       <c r="C89" s="7" t="n"/>
-      <c r="D89" s="7" t="n"/>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
       <c r="E89" s="7" t="n"/>
       <c r="F89" s="7" t="n"/>
       <c r="G89" s="7" t="n"/>
@@ -1978,33 +1978,33 @@
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B90" s="7" t="inlineStr">
-        <is>
-          <t>Rico Dowdle</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B90" s="7" t="n"/>
       <c r="C90" s="7" t="n"/>
       <c r="D90" s="7" t="n"/>
       <c r="E90" s="7" t="n"/>
-      <c r="F90" s="7" t="n"/>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G90" s="7" t="n"/>
       <c r="H90" s="7" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B91" s="7" t="n"/>
       <c r="C91" s="7" t="n"/>
-      <c r="D91" s="7" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D91" s="7" t="n"/>
       <c r="E91" s="7" t="n"/>
-      <c r="F91" s="7" t="n"/>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G91" s="7" t="n"/>
       <c r="H91" s="7" t="n"/>
     </row>
@@ -2012,13 +2012,13 @@
       <c r="A92" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B92" s="7" t="n"/>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>J.K. Dobbins</t>
+        </is>
+      </c>
       <c r="C92" s="7" t="n"/>
-      <c r="D92" s="7" t="inlineStr">
-        <is>
-          <t>Quentin Johnston</t>
-        </is>
-      </c>
+      <c r="D92" s="7" t="n"/>
       <c r="E92" s="7" t="n"/>
       <c r="F92" s="7" t="n"/>
       <c r="G92" s="7" t="n"/>
@@ -2028,13 +2028,13 @@
       <c r="A93" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B93" s="7" t="n"/>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>Jonathon Brooks</t>
+        </is>
+      </c>
       <c r="C93" s="7" t="n"/>
-      <c r="D93" s="7" t="inlineStr">
-        <is>
-          <t>Chris Godwin Jr.</t>
-        </is>
-      </c>
+      <c r="D93" s="7" t="n"/>
       <c r="E93" s="7" t="n"/>
       <c r="F93" s="7" t="n"/>
       <c r="G93" s="7" t="n"/>
@@ -2044,13 +2044,13 @@
       <c r="A94" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B94" s="7" t="n"/>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>Mike Washington Jr.</t>
+        </is>
+      </c>
       <c r="C94" s="7" t="n"/>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Reed</t>
-        </is>
-      </c>
+      <c r="D94" s="7" t="n"/>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="7" t="n"/>
       <c r="G94" s="7" t="n"/>
@@ -2060,13 +2060,13 @@
       <c r="A95" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B95" s="7" t="n"/>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>Rico Dowdle</t>
+        </is>
+      </c>
       <c r="C95" s="7" t="n"/>
-      <c r="D95" s="7" t="inlineStr">
-        <is>
-          <t>Jordyn Tyson</t>
-        </is>
-      </c>
+      <c r="D95" s="7" t="n"/>
       <c r="E95" s="7" t="n"/>
       <c r="F95" s="7" t="n"/>
       <c r="G95" s="7" t="n"/>
@@ -2080,7 +2080,7 @@
       <c r="C96" s="7" t="n"/>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E96" s="7" t="n"/>
@@ -2094,27 +2094,27 @@
       </c>
       <c r="B97" s="7" t="n"/>
       <c r="C97" s="7" t="n"/>
-      <c r="D97" s="7" t="n"/>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Reed</t>
+        </is>
+      </c>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="7" t="n"/>
       <c r="G97" s="7" t="n"/>
-      <c r="H97" s="7" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H97" s="7" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B98" s="7" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B98" s="7" t="n"/>
       <c r="C98" s="7" t="n"/>
-      <c r="D98" s="7" t="n"/>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>Jordyn Tyson</t>
+        </is>
+      </c>
       <c r="E98" s="7" t="n"/>
       <c r="F98" s="7" t="n"/>
       <c r="G98" s="7" t="n"/>
@@ -2122,19 +2122,19 @@
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B99" s="7" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B99" s="7" t="n"/>
       <c r="C99" s="7" t="n"/>
       <c r="D99" s="7" t="n"/>
       <c r="E99" s="7" t="n"/>
       <c r="F99" s="7" t="n"/>
       <c r="G99" s="7" t="n"/>
-      <c r="H99" s="7" t="n"/>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="C100" s="7" t="n"/>
@@ -2176,7 +2176,7 @@
       <c r="C102" s="7" t="n"/>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E102" s="7" t="n"/>
@@ -2190,13 +2190,13 @@
       </c>
       <c r="B103" s="7" t="n"/>
       <c r="C103" s="7" t="n"/>
-      <c r="D103" s="7" t="n"/>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E103" s="7" t="n"/>
-      <c r="F103" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F103" s="7" t="n"/>
       <c r="G103" s="7" t="n"/>
       <c r="H103" s="7" t="n"/>
     </row>
@@ -2212,7 +2212,7 @@
       <c r="G104" s="7" t="n"/>
       <c r="H104" s="7" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 105 players, top value 77.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 105 players, top value 70.</t>
         </is>
       </c>
     </row>
@@ -2349,14 +2349,14 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.4 x (implied - sheet), then rescaled so the total equals the sheet total. 75 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.4 x (implied - sheet), then rescaled so the total equals the sheet total. 55 players moved.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   No projection this week (value kept): Puka Nacua, A.J. Brown, Nico Collins, Rome Odunze, Josh Jacobs, De'Zhaun Stribling, Jayden Daniels, Jordan Mason, Alec Pierce, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Jaxson Dart, Ja'Kobi Lane.</t>
+          <t xml:space="preserve">   No projection this week (value kept): Bijan Robinson, Puka Nacua, Kenneth Walker III, Saquon Barkley, Ashton Jeanty, Derrick Henry, Justin Jefferson, De'Von Achane, Chris Olave, A.J. Brown, Breece Hall, Drake London, Brock Bowers, Kyren Williams, Josh Allen, Rashee Rice, Zay Flowers, Lamar Jackson, Travis Etienne Jr., Jadarian Price, MarShawn Lloyd, Mike Evans, Joe Burrow, Drake Maye, Luther Burden III, Josh Jacobs, De'Zhaun Stribling, Jayden Daniels, Jordan Mason, Alec Pierce, J.K. Dobbins, Chris Godwin Jr., Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Trevor Lawrence, Rico Dowdle, Dak Prescott, Blake Corum, Kenny Gainwell, Jaxson Dart, Rachaad White, Ja'Kobi Lane, Woody Marks.</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2435,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Malik Nabers 21-&gt;16, DeVonta Smith 31-&gt;26, Rashee Rice 20-&gt;15, Derrick Henry 57-&gt;61, De'Von Achane 43-&gt;39, Chris Olave 46-&gt;42, Drake London 33-&gt;29, Nico Collins 36-&gt;32</t>
+          <t>Largest moves vs. the baseline in this file: CeeDee Lamb 44-&gt;39, Chris Olave 41-&gt;36, Nico Collins 32-&gt;27, Malik Nabers 24-&gt;19, Trey McBride 28-&gt;23, DeVonta Smith 27-&gt;22, Rashee Rice 26-&gt;21, Garrett Wilson 28-&gt;23</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -650,11 +650,11 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Jahmyr Gibbs</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="C7" s="7" t="n"/>
@@ -666,11 +666,11 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Jahmyr Gibbs</t>
         </is>
       </c>
       <c r="C8" s="7" t="n"/>
@@ -730,11 +730,11 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>James Cook III</t>
         </is>
       </c>
       <c r="C12" s="7" t="n"/>
@@ -748,13 +748,13 @@
       <c r="A13" s="6" t="n">
         <v>53</v>
       </c>
-      <c r="B13" s="7" t="n"/>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Jonathan Taylor</t>
+        </is>
+      </c>
       <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D13" s="7" t="n"/>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
@@ -762,7 +762,7 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
@@ -784,7 +784,7 @@
       <c r="C15" s="7" t="n"/>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Justin Jefferson</t>
+          <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="E15" s="7" t="n"/>
@@ -794,15 +794,15 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>49</v>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
@@ -810,7 +810,7 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="n"/>
@@ -826,15 +826,15 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
@@ -844,13 +844,13 @@
       <c r="A19" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="B19" s="7" t="n"/>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
@@ -858,11 +858,11 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>De'Von Achane</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="C20" s="7" t="n"/>
@@ -874,35 +874,35 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
       <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="B22" s="7" t="n"/>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>De'Von Achane</t>
+        </is>
+      </c>
       <c r="C22" s="7" t="n"/>
       <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
@@ -970,11 +970,11 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="C27" s="7" t="n"/>
@@ -988,13 +988,13 @@
       <c r="A28" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="B28" s="7" t="n"/>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D28" s="7" t="n"/>
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="7" t="n"/>
@@ -1002,15 +1002,15 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="7" t="n"/>
@@ -1018,11 +1018,11 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C30" s="7" t="n"/>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
@@ -1050,19 +1050,19 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
-      <c r="H32" s="7" t="n"/>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
@@ -1086,15 +1086,15 @@
       </c>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="n"/>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
@@ -1114,17 +1114,17 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
-      <c r="D36" s="7" t="n"/>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E36" s="7" t="n"/>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F36" s="7" t="n"/>
       <c r="G36" s="7" t="n"/>
       <c r="H36" s="7" t="n"/>
     </row>
@@ -1134,13 +1134,13 @@
       </c>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D37" s="7" t="n"/>
       <c r="E37" s="7" t="n"/>
-      <c r="F37" s="7" t="n"/>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G37" s="7" t="n"/>
       <c r="H37" s="7" t="n"/>
     </row>
@@ -1178,15 +1178,15 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="B40" s="7" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D40" s="7" t="n"/>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
@@ -1196,13 +1196,13 @@
       <c r="A41" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="n"/>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="7" t="n"/>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B42" s="7" t="n"/>
       <c r="C42" s="7" t="n"/>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="C44" s="7" t="n"/>
@@ -1260,13 +1260,13 @@
       <c r="A45" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+      <c r="B45" s="7" t="n"/>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="n"/>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E45" s="7" t="n"/>
       <c r="F45" s="7" t="n"/>
       <c r="G45" s="7" t="n"/>
@@ -1280,7 +1280,7 @@
       <c r="C46" s="7" t="n"/>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E46" s="7" t="n"/>
@@ -1290,15 +1290,15 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B47" s="7" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D47" s="7" t="n"/>
       <c r="E47" s="7" t="n"/>
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="7" t="n"/>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten</t>
+          <t>Jadarian Price</t>
         </is>
       </c>
       <c r="C48" s="7" t="n"/>
@@ -1322,15 +1322,15 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B49" s="7" t="n"/>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="n"/>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E49" s="7" t="n"/>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n"/>
@@ -1338,13 +1338,13 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B50" s="7" t="n"/>
       <c r="C50" s="7" t="n"/>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E50" s="7" t="n"/>
@@ -1354,11 +1354,11 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C51" s="7" t="n"/>
@@ -1370,11 +1370,11 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C52" s="7" t="n"/>
@@ -1386,13 +1386,13 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B53" s="7" t="n"/>
       <c r="C53" s="7" t="n"/>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E53" s="7" t="n"/>
@@ -1402,15 +1402,15 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B54" s="7" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C54" s="7" t="n"/>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D54" s="7" t="n"/>
       <c r="E54" s="7" t="n"/>
       <c r="F54" s="7" t="n"/>
       <c r="G54" s="7" t="n"/>
@@ -1418,11 +1418,11 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C55" s="7" t="n"/>
@@ -1436,29 +1436,29 @@
       <c r="A56" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+      <c r="B56" s="7" t="n"/>
       <c r="C56" s="7" t="n"/>
       <c r="D56" s="7" t="n"/>
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="n"/>
-      <c r="H56" s="7" t="n"/>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B57" s="7" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C57" s="7" t="n"/>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
       <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
@@ -1466,31 +1466,31 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B58" s="7" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C58" s="7" t="n"/>
       <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B59" s="7" t="n"/>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="7" t="n"/>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E59" s="7" t="n"/>
       <c r="F59" s="7" t="n"/>
       <c r="G59" s="7" t="n"/>
@@ -1498,31 +1498,31 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B60" s="7" t="n"/>
       <c r="C60" s="7" t="n"/>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D60" s="7" t="n"/>
       <c r="E60" s="7" t="n"/>
       <c r="F60" s="7" t="n"/>
       <c r="G60" s="7" t="n"/>
-      <c r="H60" s="7" t="n"/>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B61" s="7" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
       <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
@@ -1530,33 +1530,33 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B62" s="7" t="n"/>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="n"/>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="7" t="n"/>
-      <c r="H62" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B63" s="7" t="n"/>
       <c r="C63" s="7" t="n"/>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D63" s="7" t="n"/>
       <c r="E63" s="7" t="n"/>
-      <c r="F63" s="7" t="n"/>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G63" s="7" t="n"/>
       <c r="H63" s="7" t="n"/>
     </row>
@@ -1568,75 +1568,75 @@
       <c r="C64" s="7" t="n"/>
       <c r="D64" s="7" t="n"/>
       <c r="E64" s="7" t="n"/>
-      <c r="F64" s="7" t="n"/>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G64" s="7" t="n"/>
-      <c r="H64" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B65" s="7" t="n"/>
       <c r="C65" s="7" t="n"/>
       <c r="D65" s="7" t="n"/>
       <c r="E65" s="7" t="n"/>
-      <c r="F65" s="7" t="n"/>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G65" s="7" t="n"/>
       <c r="H65" s="7" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B66" s="7" t="n"/>
       <c r="C66" s="7" t="n"/>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D66" s="7" t="n"/>
       <c r="E66" s="7" t="n"/>
-      <c r="F66" s="7" t="n"/>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G66" s="7" t="n"/>
       <c r="H66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B67" s="7" t="n"/>
       <c r="C67" s="7" t="n"/>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D67" s="7" t="n"/>
       <c r="E67" s="7" t="n"/>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
-      <c r="H67" s="7" t="n"/>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>Jalen Hurts</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B68" s="7" t="n"/>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C68" s="7" t="n"/>
       <c r="D68" s="7" t="n"/>
       <c r="E68" s="7" t="n"/>
-      <c r="F68" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F68" s="7" t="n"/>
       <c r="G68" s="7" t="n"/>
       <c r="H68" s="7" t="n"/>
     </row>
@@ -1646,13 +1646,13 @@
       </c>
       <c r="B69" s="7" t="n"/>
       <c r="C69" s="7" t="n"/>
-      <c r="D69" s="7" t="n"/>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E69" s="7" t="n"/>
-      <c r="F69" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F69" s="7" t="n"/>
       <c r="G69" s="7" t="n"/>
       <c r="H69" s="7" t="n"/>
     </row>
@@ -1662,13 +1662,13 @@
       </c>
       <c r="B70" s="7" t="n"/>
       <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="n"/>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E70" s="7" t="n"/>
-      <c r="F70" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F70" s="7" t="n"/>
       <c r="G70" s="7" t="n"/>
       <c r="H70" s="7" t="n"/>
     </row>
@@ -1678,15 +1678,15 @@
       </c>
       <c r="B71" s="7" t="n"/>
       <c r="C71" s="7" t="n"/>
-      <c r="D71" s="7" t="n"/>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
-      <c r="H71" s="7" t="inlineStr">
-        <is>
-          <t>Jalen Hurts</t>
-        </is>
-      </c>
+      <c r="H71" s="7" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C72" s="7" t="n"/>
@@ -1710,27 +1710,27 @@
       </c>
       <c r="B73" s="7" t="n"/>
       <c r="C73" s="7" t="n"/>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D73" s="7" t="n"/>
       <c r="E73" s="7" t="n"/>
       <c r="F73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
-      <c r="H73" s="7" t="n"/>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B74" s="7" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C74" s="7" t="n"/>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>Jameson Williams</t>
-        </is>
-      </c>
+      <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
       <c r="F74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
@@ -1738,13 +1738,13 @@
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B75" s="7" t="n"/>
       <c r="C75" s="7" t="n"/>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E75" s="7" t="n"/>
@@ -1756,29 +1756,29 @@
       <c r="A76" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B76" s="7" t="n"/>
       <c r="C76" s="7" t="n"/>
       <c r="D76" s="7" t="n"/>
       <c r="E76" s="7" t="n"/>
       <c r="F76" s="7" t="n"/>
       <c r="G76" s="7" t="n"/>
-      <c r="H76" s="7" t="n"/>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>Justin Herbert</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B77" s="7" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
       <c r="C77" s="7" t="n"/>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>De'Zhaun Stribling</t>
-        </is>
-      </c>
+      <c r="D77" s="7" t="n"/>
       <c r="E77" s="7" t="n"/>
       <c r="F77" s="7" t="n"/>
       <c r="G77" s="7" t="n"/>
@@ -1786,31 +1786,31 @@
     </row>
     <row r="78">
       <c r="A78" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B78" s="7" t="n"/>
       <c r="C78" s="7" t="n"/>
-      <c r="D78" s="7" t="n"/>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E78" s="7" t="n"/>
       <c r="F78" s="7" t="n"/>
       <c r="G78" s="7" t="n"/>
-      <c r="H78" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H78" s="7" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+      <c r="B79" s="7" t="n"/>
       <c r="C79" s="7" t="n"/>
-      <c r="D79" s="7" t="n"/>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>Marvin Harrison Jr.</t>
+        </is>
+      </c>
       <c r="E79" s="7" t="n"/>
       <c r="F79" s="7" t="n"/>
       <c r="G79" s="7" t="n"/>
@@ -1824,7 +1824,7 @@
       <c r="C80" s="7" t="n"/>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E80" s="7" t="n"/>
@@ -1840,27 +1840,27 @@
       <c r="C81" s="7" t="n"/>
       <c r="D81" s="7" t="n"/>
       <c r="E81" s="7" t="n"/>
-      <c r="F81" s="7" t="n"/>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G81" s="7" t="n"/>
-      <c r="H81" s="7" t="inlineStr">
-        <is>
-          <t>Justin Herbert</t>
-        </is>
-      </c>
+      <c r="H81" s="7" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B82" s="7" t="n"/>
       <c r="C82" s="7" t="n"/>
       <c r="D82" s="7" t="n"/>
       <c r="E82" s="7" t="n"/>
-      <c r="F82" s="7" t="n"/>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G82" s="7" t="n"/>
       <c r="H82" s="7" t="n"/>
     </row>
@@ -1868,13 +1868,13 @@
       <c r="A83" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B83" s="7" t="n"/>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>J.K. Dobbins</t>
+        </is>
+      </c>
       <c r="C83" s="7" t="n"/>
-      <c r="D83" s="7" t="inlineStr">
-        <is>
-          <t>Carnell Tate</t>
-        </is>
-      </c>
+      <c r="D83" s="7" t="n"/>
       <c r="E83" s="7" t="n"/>
       <c r="F83" s="7" t="n"/>
       <c r="G83" s="7" t="n"/>
@@ -1884,13 +1884,13 @@
       <c r="A84" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B84" s="7" t="n"/>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>Jonathon Brooks</t>
+        </is>
+      </c>
       <c r="C84" s="7" t="n"/>
-      <c r="D84" s="7" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D84" s="7" t="n"/>
       <c r="E84" s="7" t="n"/>
       <c r="F84" s="7" t="n"/>
       <c r="G84" s="7" t="n"/>
@@ -1898,11 +1898,11 @@
     </row>
     <row r="85">
       <c r="A85" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C85" s="7" t="n"/>
@@ -1914,15 +1914,15 @@
     </row>
     <row r="86">
       <c r="A86" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B86" s="7" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>Rico Dowdle</t>
+        </is>
+      </c>
       <c r="C86" s="7" t="n"/>
-      <c r="D86" s="7" t="inlineStr">
-        <is>
-          <t>Brian Thomas Jr.</t>
-        </is>
-      </c>
+      <c r="D86" s="7" t="n"/>
       <c r="E86" s="7" t="n"/>
       <c r="F86" s="7" t="n"/>
       <c r="G86" s="7" t="n"/>
@@ -1930,13 +1930,13 @@
     </row>
     <row r="87">
       <c r="A87" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B87" s="7" t="n"/>
       <c r="C87" s="7" t="n"/>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E87" s="7" t="n"/>
@@ -1946,13 +1946,13 @@
     </row>
     <row r="88">
       <c r="A88" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B88" s="7" t="n"/>
       <c r="C88" s="7" t="n"/>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E88" s="7" t="n"/>
@@ -1962,13 +1962,13 @@
     </row>
     <row r="89">
       <c r="A89" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B89" s="7" t="n"/>
       <c r="C89" s="7" t="n"/>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E89" s="7" t="n"/>
@@ -1978,59 +1978,59 @@
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B90" s="7" t="n"/>
       <c r="C90" s="7" t="n"/>
-      <c r="D90" s="7" t="n"/>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>De'Zhaun Stribling</t>
+        </is>
+      </c>
       <c r="E90" s="7" t="n"/>
-      <c r="F90" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F90" s="7" t="n"/>
       <c r="G90" s="7" t="n"/>
       <c r="H90" s="7" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B91" s="7" t="n"/>
       <c r="C91" s="7" t="n"/>
-      <c r="D91" s="7" t="n"/>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>Chris Godwin Jr.</t>
+        </is>
+      </c>
       <c r="E91" s="7" t="n"/>
-      <c r="F91" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F91" s="7" t="n"/>
       <c r="G91" s="7" t="n"/>
       <c r="H91" s="7" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B92" s="7" t="n"/>
       <c r="C92" s="7" t="n"/>
       <c r="D92" s="7" t="n"/>
       <c r="E92" s="7" t="n"/>
       <c r="F92" s="7" t="n"/>
       <c r="G92" s="7" t="n"/>
-      <c r="H92" s="7" t="n"/>
+      <c r="H92" s="7" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="C93" s="7" t="n"/>
@@ -2042,11 +2042,11 @@
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="C94" s="7" t="n"/>
@@ -2058,15 +2058,15 @@
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B95" s="7" t="inlineStr">
-        <is>
-          <t>Rico Dowdle</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B95" s="7" t="n"/>
       <c r="C95" s="7" t="n"/>
-      <c r="D95" s="7" t="n"/>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E95" s="7" t="n"/>
       <c r="F95" s="7" t="n"/>
       <c r="G95" s="7" t="n"/>
@@ -2074,31 +2074,31 @@
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B96" s="7" t="n"/>
       <c r="C96" s="7" t="n"/>
-      <c r="D96" s="7" t="inlineStr">
-        <is>
-          <t>Chris Godwin Jr.</t>
-        </is>
-      </c>
+      <c r="D96" s="7" t="n"/>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="7" t="n"/>
       <c r="G96" s="7" t="n"/>
-      <c r="H96" s="7" t="n"/>
+      <c r="H96" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B97" s="7" t="n"/>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C97" s="7" t="n"/>
-      <c r="D97" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Reed</t>
-        </is>
-      </c>
+      <c r="D97" s="7" t="n"/>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="7" t="n"/>
       <c r="G97" s="7" t="n"/>
@@ -2112,7 +2112,7 @@
       <c r="C98" s="7" t="n"/>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E98" s="7" t="n"/>
@@ -2126,43 +2126,43 @@
       </c>
       <c r="B99" s="7" t="n"/>
       <c r="C99" s="7" t="n"/>
-      <c r="D99" s="7" t="n"/>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E99" s="7" t="n"/>
       <c r="F99" s="7" t="n"/>
       <c r="G99" s="7" t="n"/>
-      <c r="H99" s="7" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B100" s="7" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B100" s="7" t="n"/>
       <c r="C100" s="7" t="n"/>
       <c r="D100" s="7" t="n"/>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="7" t="n"/>
       <c r="G100" s="7" t="n"/>
-      <c r="H100" s="7" t="n"/>
+      <c r="H100" s="7" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B101" s="7" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+      <c r="B101" s="7" t="n"/>
       <c r="C101" s="7" t="n"/>
-      <c r="D101" s="7" t="n"/>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>Carnell Tate</t>
+        </is>
+      </c>
       <c r="E101" s="7" t="n"/>
       <c r="F101" s="7" t="n"/>
       <c r="G101" s="7" t="n"/>
@@ -2176,7 +2176,7 @@
       <c r="C102" s="7" t="n"/>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E102" s="7" t="n"/>
@@ -2186,13 +2186,13 @@
     </row>
     <row r="103">
       <c r="A103" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B103" s="7" t="n"/>
       <c r="C103" s="7" t="n"/>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E103" s="7" t="n"/>
@@ -2202,47 +2202,47 @@
     </row>
     <row r="104">
       <c r="A104" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B104" s="7" t="n"/>
       <c r="C104" s="7" t="n"/>
-      <c r="D104" s="7" t="n"/>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Reed</t>
+        </is>
+      </c>
       <c r="E104" s="7" t="n"/>
       <c r="F104" s="7" t="n"/>
       <c r="G104" s="7" t="n"/>
-      <c r="H104" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H104" s="7" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B105" s="7" t="n"/>
       <c r="C105" s="7" t="n"/>
-      <c r="D105" s="7" t="n"/>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>Jordyn Tyson</t>
+        </is>
+      </c>
       <c r="E105" s="7" t="n"/>
       <c r="F105" s="7" t="n"/>
       <c r="G105" s="7" t="n"/>
-      <c r="H105" s="7" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H105" s="7" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B106" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>Kenny Gainwell</t>
+        </is>
+      </c>
       <c r="C106" s="7" t="n"/>
-      <c r="D106" s="7" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D106" s="7" t="n"/>
       <c r="E106" s="7" t="n"/>
       <c r="F106" s="7" t="n"/>
       <c r="G106" s="7" t="n"/>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>Kenny Gainwell</t>
+          <t>Rachaad White</t>
         </is>
       </c>
       <c r="C107" s="7" t="n"/>
@@ -2268,13 +2268,13 @@
       <c r="A108" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B108" s="7" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
+      <c r="B108" s="7" t="n"/>
       <c r="C108" s="7" t="n"/>
-      <c r="D108" s="7" t="n"/>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E108" s="7" t="n"/>
       <c r="F108" s="7" t="n"/>
       <c r="G108" s="7" t="n"/>
@@ -2401,14 +2401,14 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   receptions/game = BettingPros consensus receptions line from the 2026 week 1 props; players with no line use the mean line of position peers within 10 value points.</t>
+          <t xml:space="preserve">   receptions/game = BettingPros consensus receptions line from the 2026 week 4 props; players with no line use the mean line of position peers within 10 value points.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.8, WR 3.3, TE 4.5, QB 0.0.</t>
+          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.8, WR 2.9, TE 4.5, QB 0.0.</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2435,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: CeeDee Lamb 44-&gt;39, Chris Olave 41-&gt;36, Nico Collins 32-&gt;27, Malik Nabers 24-&gt;19, Trey McBride 28-&gt;23, DeVonta Smith 27-&gt;22, Rashee Rice 26-&gt;21, Garrett Wilson 28-&gt;23</t>
+          <t>Largest moves vs. the baseline in this file: Derrick Henry 55-&gt;61, Trey McBride 28-&gt;22, Jaxon Smith-Njigba 56-&gt;51, James Cook III 49-&gt;54, Chris Olave 41-&gt;36, Drake London 37-&gt;32, DeVonta Smith 27-&gt;22, Rashee Rice 26-&gt;21</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -602,11 +602,11 @@
     </row>
     <row r="4">
       <c r="A4" s="6" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Bijan Robinson</t>
+          <t>Jahmyr Gibbs</t>
         </is>
       </c>
       <c r="C4" s="7" t="n"/>
@@ -618,11 +618,11 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Bijan Robinson</t>
         </is>
       </c>
       <c r="C5" s="7" t="n"/>
@@ -654,7 +654,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Jahmyr Gibbs</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C7" s="7" t="n"/>
@@ -670,7 +670,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C8" s="7" t="n"/>
@@ -682,11 +682,11 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Saquon Barkley</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="C9" s="7" t="n"/>
@@ -698,11 +698,11 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C10" s="7" t="n"/>
@@ -714,15 +714,15 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
@@ -730,11 +730,11 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="C12" s="7" t="n"/>
@@ -746,13 +746,13 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E13" s="7" t="n"/>
@@ -762,13 +762,13 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E14" s="7" t="n"/>
@@ -780,13 +780,13 @@
       <c r="A15" s="6" t="n">
         <v>51</v>
       </c>
-      <c r="B15" s="7" t="n"/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D15" s="7" t="n"/>
       <c r="E15" s="7" t="n"/>
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="7" t="n"/>
@@ -794,15 +794,15 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>49</v>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
@@ -812,13 +812,13 @@
       <c r="A17" s="6" t="n">
         <v>49</v>
       </c>
-      <c r="B17" s="7" t="n"/>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D17" s="7" t="n"/>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
@@ -826,7 +826,7 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
@@ -842,13 +842,13 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>CeeDee Lamb</t>
+          <t>Chris Olave</t>
         </is>
       </c>
       <c r="E19" s="7" t="n"/>
@@ -858,15 +858,15 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>De'Von Achane</t>
-        </is>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
@@ -878,7 +878,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>De'Von Achane</t>
         </is>
       </c>
       <c r="C21" s="7" t="n"/>
@@ -892,17 +892,17 @@
       <c r="A22" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="B22" s="7" t="n"/>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C22" s="7" t="n"/>
       <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
@@ -910,15 +910,15 @@
       </c>
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
@@ -954,17 +954,17 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="B26" s="7" t="n"/>
+        <v>33</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C26" s="7" t="n"/>
       <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="7" t="n"/>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C27" s="7" t="n"/>
@@ -986,13 +986,13 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>Nico Collins</t>
         </is>
       </c>
       <c r="E28" s="7" t="n"/>
@@ -1002,31 +1002,31 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
       <c r="D29" s="7" t="n"/>
       <c r="E29" s="7" t="n"/>
-      <c r="F29" s="7" t="n"/>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G29" s="7" t="n"/>
       <c r="H29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="n"/>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E30" s="7" t="n"/>
       <c r="F30" s="7" t="n"/>
       <c r="G30" s="7" t="n"/>
@@ -1034,31 +1034,31 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D31" s="7" t="n"/>
       <c r="E31" s="7" t="n"/>
-      <c r="F31" s="7" t="n"/>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G31" s="7" t="n"/>
       <c r="H31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="B32" s="7" t="n"/>
+        <v>27</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
@@ -1066,15 +1066,15 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="n"/>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
@@ -1082,55 +1082,55 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="B34" s="7" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C34" s="7" t="n"/>
       <c r="D34" s="7" t="n"/>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D35" s="7" t="n"/>
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="7" t="n"/>
-      <c r="H35" s="7" t="n"/>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
-      <c r="D36" s="7" t="n"/>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E36" s="7" t="n"/>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F36" s="7" t="n"/>
       <c r="G36" s="7" t="n"/>
       <c r="H36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
@@ -1146,13 +1146,13 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E38" s="7" t="n"/>
@@ -1184,7 +1184,7 @@
       <c r="C40" s="7" t="n"/>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E40" s="7" t="n"/>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C41" s="7" t="n"/>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B42" s="7" t="n"/>
       <c r="C42" s="7" t="n"/>
@@ -1226,11 +1226,11 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C43" s="7" t="n"/>
@@ -1242,15 +1242,15 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="n"/>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="7" t="n"/>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="C45" s="7" t="n"/>
@@ -1280,7 +1280,7 @@
       <c r="C46" s="7" t="n"/>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E46" s="7" t="n"/>
@@ -1290,15 +1290,15 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B47" s="7" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D47" s="7" t="n"/>
       <c r="E47" s="7" t="n"/>
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="7" t="n"/>
@@ -1308,13 +1308,13 @@
       <c r="A48" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B48" s="7" t="n"/>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="n"/>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
@@ -1322,15 +1322,15 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B49" s="7" t="n"/>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="n"/>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E49" s="7" t="n"/>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n"/>
@@ -1338,13 +1338,13 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B50" s="7" t="n"/>
       <c r="C50" s="7" t="n"/>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E50" s="7" t="n"/>
@@ -1354,11 +1354,11 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="C51" s="7" t="n"/>
@@ -1370,31 +1370,31 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B52" s="7" t="n"/>
       <c r="C52" s="7" t="n"/>
       <c r="D52" s="7" t="n"/>
       <c r="E52" s="7" t="n"/>
-      <c r="F52" s="7" t="n"/>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G52" s="7" t="n"/>
       <c r="H52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B53" s="7" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D53" s="7" t="n"/>
       <c r="E53" s="7" t="n"/>
       <c r="F53" s="7" t="n"/>
       <c r="G53" s="7" t="n"/>
@@ -1402,15 +1402,15 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B54" s="7" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C54" s="7" t="n"/>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D54" s="7" t="n"/>
       <c r="E54" s="7" t="n"/>
       <c r="F54" s="7" t="n"/>
       <c r="G54" s="7" t="n"/>
@@ -1418,11 +1418,11 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="C55" s="7" t="n"/>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C56" s="7" t="n"/>
@@ -1450,15 +1450,15 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B57" s="7" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C57" s="7" t="n"/>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
       <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
@@ -1466,17 +1466,17 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B58" s="7" t="n"/>
       <c r="C58" s="7" t="n"/>
-      <c r="D58" s="7" t="n"/>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E58" s="7" t="n"/>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
     </row>
@@ -1484,29 +1484,29 @@
       <c r="A59" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B59" s="7" t="n"/>
       <c r="C59" s="7" t="n"/>
       <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
       <c r="F59" s="7" t="n"/>
       <c r="G59" s="7" t="n"/>
-      <c r="H59" s="7" t="n"/>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B60" s="7" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C60" s="7" t="n"/>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D60" s="7" t="n"/>
       <c r="E60" s="7" t="n"/>
       <c r="F60" s="7" t="n"/>
       <c r="G60" s="7" t="n"/>
@@ -1514,13 +1514,13 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E61" s="7" t="n"/>
@@ -1530,29 +1530,29 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B62" s="7" t="n"/>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="n"/>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Terry McLaurin</t>
+        </is>
+      </c>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="7" t="n"/>
-      <c r="H62" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B63" s="7" t="n"/>
       <c r="C63" s="7" t="n"/>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E63" s="7" t="n"/>
@@ -1562,47 +1562,47 @@
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B64" s="7" t="n"/>
       <c r="C64" s="7" t="n"/>
       <c r="D64" s="7" t="n"/>
       <c r="E64" s="7" t="n"/>
-      <c r="F64" s="7" t="n"/>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G64" s="7" t="n"/>
-      <c r="H64" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+      <c r="B65" s="7" t="n"/>
       <c r="C65" s="7" t="n"/>
       <c r="D65" s="7" t="n"/>
       <c r="E65" s="7" t="n"/>
       <c r="F65" s="7" t="n"/>
       <c r="G65" s="7" t="n"/>
-      <c r="H65" s="7" t="n"/>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B66" s="7" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C66" s="7" t="n"/>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D66" s="7" t="n"/>
       <c r="E66" s="7" t="n"/>
       <c r="F66" s="7" t="n"/>
       <c r="G66" s="7" t="n"/>
@@ -1610,13 +1610,13 @@
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B67" s="7" t="n"/>
       <c r="C67" s="7" t="n"/>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="E67" s="7" t="n"/>
@@ -1626,23 +1626,23 @@
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B68" s="7" t="n"/>
       <c r="C68" s="7" t="n"/>
-      <c r="D68" s="7" t="n"/>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E68" s="7" t="n"/>
-      <c r="F68" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F68" s="7" t="n"/>
       <c r="G68" s="7" t="n"/>
       <c r="H68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B69" s="7" t="n"/>
       <c r="C69" s="7" t="n"/>
@@ -1658,7 +1658,7 @@
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B70" s="7" t="n"/>
       <c r="C70" s="7" t="n"/>
@@ -1674,23 +1674,23 @@
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B71" s="7" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C71" s="7" t="n"/>
       <c r="D71" s="7" t="n"/>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
-      <c r="H71" s="7" t="inlineStr">
-        <is>
-          <t>Jalen Hurts</t>
-        </is>
-      </c>
+      <c r="H71" s="7" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
@@ -1706,15 +1706,15 @@
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B73" s="7" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>J.K. Dobbins</t>
+        </is>
+      </c>
       <c r="C73" s="7" t="n"/>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D73" s="7" t="n"/>
       <c r="E73" s="7" t="n"/>
       <c r="F73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
@@ -1722,13 +1722,13 @@
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B74" s="7" t="n"/>
       <c r="C74" s="7" t="n"/>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E74" s="7" t="n"/>
@@ -1738,13 +1738,13 @@
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B75" s="7" t="n"/>
       <c r="C75" s="7" t="n"/>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E75" s="7" t="n"/>
@@ -1756,13 +1756,13 @@
       <c r="A76" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B76" s="7" t="n"/>
       <c r="C76" s="7" t="n"/>
-      <c r="D76" s="7" t="n"/>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>De'Zhaun Stribling</t>
+        </is>
+      </c>
       <c r="E76" s="7" t="n"/>
       <c r="F76" s="7" t="n"/>
       <c r="G76" s="7" t="n"/>
@@ -1776,7 +1776,7 @@
       <c r="C77" s="7" t="n"/>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E77" s="7" t="n"/>
@@ -1802,19 +1802,19 @@
     </row>
     <row r="79">
       <c r="A79" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B79" s="7" t="n"/>
       <c r="C79" s="7" t="n"/>
       <c r="D79" s="7" t="n"/>
       <c r="E79" s="7" t="n"/>
       <c r="F79" s="7" t="n"/>
       <c r="G79" s="7" t="n"/>
-      <c r="H79" s="7" t="n"/>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
@@ -1834,19 +1834,19 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B81" s="7" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
       <c r="C81" s="7" t="n"/>
       <c r="D81" s="7" t="n"/>
       <c r="E81" s="7" t="n"/>
       <c r="F81" s="7" t="n"/>
       <c r="G81" s="7" t="n"/>
-      <c r="H81" s="7" t="inlineStr">
-        <is>
-          <t>Justin Herbert</t>
-        </is>
-      </c>
+      <c r="H81" s="7" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="C82" s="7" t="n"/>
@@ -1900,13 +1900,13 @@
       <c r="A85" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+      <c r="B85" s="7" t="n"/>
       <c r="C85" s="7" t="n"/>
-      <c r="D85" s="7" t="n"/>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E85" s="7" t="n"/>
       <c r="F85" s="7" t="n"/>
       <c r="G85" s="7" t="n"/>
@@ -1920,7 +1920,7 @@
       <c r="C86" s="7" t="n"/>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E86" s="7" t="n"/>
@@ -1936,7 +1936,7 @@
       <c r="C87" s="7" t="n"/>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E87" s="7" t="n"/>
@@ -1952,7 +1952,7 @@
       <c r="C88" s="7" t="n"/>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E88" s="7" t="n"/>
@@ -1966,45 +1966,45 @@
       </c>
       <c r="B89" s="7" t="n"/>
       <c r="C89" s="7" t="n"/>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
+      <c r="D89" s="7" t="n"/>
       <c r="E89" s="7" t="n"/>
       <c r="F89" s="7" t="n"/>
       <c r="G89" s="7" t="n"/>
-      <c r="H89" s="7" t="n"/>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>Jalen Hurts</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B90" s="7" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C90" s="7" t="n"/>
       <c r="D90" s="7" t="n"/>
       <c r="E90" s="7" t="n"/>
-      <c r="F90" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F90" s="7" t="n"/>
       <c r="G90" s="7" t="n"/>
       <c r="H90" s="7" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B91" s="7" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>Jonathon Brooks</t>
+        </is>
+      </c>
       <c r="C91" s="7" t="n"/>
       <c r="D91" s="7" t="n"/>
       <c r="E91" s="7" t="n"/>
-      <c r="F91" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F91" s="7" t="n"/>
       <c r="G91" s="7" t="n"/>
       <c r="H91" s="7" t="n"/>
     </row>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C92" s="7" t="n"/>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C93" s="7" t="n"/>
@@ -2044,13 +2044,13 @@
       <c r="A94" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>Mike Washington Jr.</t>
-        </is>
-      </c>
+      <c r="B94" s="7" t="n"/>
       <c r="C94" s="7" t="n"/>
-      <c r="D94" s="7" t="n"/>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>Chris Godwin Jr.</t>
+        </is>
+      </c>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="7" t="n"/>
       <c r="G94" s="7" t="n"/>
@@ -2060,13 +2060,13 @@
       <c r="A95" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B95" s="7" t="inlineStr">
-        <is>
-          <t>Rico Dowdle</t>
-        </is>
-      </c>
+      <c r="B95" s="7" t="n"/>
       <c r="C95" s="7" t="n"/>
-      <c r="D95" s="7" t="n"/>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Reed</t>
+        </is>
+      </c>
       <c r="E95" s="7" t="n"/>
       <c r="F95" s="7" t="n"/>
       <c r="G95" s="7" t="n"/>
@@ -2080,7 +2080,7 @@
       <c r="C96" s="7" t="n"/>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr.</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E96" s="7" t="n"/>
@@ -2094,13 +2094,13 @@
       </c>
       <c r="B97" s="7" t="n"/>
       <c r="C97" s="7" t="n"/>
-      <c r="D97" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Reed</t>
-        </is>
-      </c>
+      <c r="D97" s="7" t="n"/>
       <c r="E97" s="7" t="n"/>
-      <c r="F97" s="7" t="n"/>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G97" s="7" t="n"/>
       <c r="H97" s="7" t="n"/>
     </row>
@@ -2110,13 +2110,13 @@
       </c>
       <c r="B98" s="7" t="n"/>
       <c r="C98" s="7" t="n"/>
-      <c r="D98" s="7" t="inlineStr">
-        <is>
-          <t>Jordyn Tyson</t>
-        </is>
-      </c>
+      <c r="D98" s="7" t="n"/>
       <c r="E98" s="7" t="n"/>
-      <c r="F98" s="7" t="n"/>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G98" s="7" t="n"/>
       <c r="H98" s="7" t="n"/>
     </row>
@@ -2132,25 +2132,25 @@
       <c r="G99" s="7" t="n"/>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B100" s="7" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B100" s="7" t="n"/>
       <c r="C100" s="7" t="n"/>
       <c r="D100" s="7" t="n"/>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="7" t="n"/>
       <c r="G100" s="7" t="n"/>
-      <c r="H100" s="7" t="n"/>
+      <c r="H100" s="7" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>Woody Marks</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="C101" s="7" t="n"/>
@@ -2172,13 +2172,13 @@
       <c r="A102" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B102" s="7" t="n"/>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C102" s="7" t="n"/>
-      <c r="D102" s="7" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D102" s="7" t="n"/>
       <c r="E102" s="7" t="n"/>
       <c r="F102" s="7" t="n"/>
       <c r="G102" s="7" t="n"/>
@@ -2192,7 +2192,7 @@
       <c r="C103" s="7" t="n"/>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E103" s="7" t="n"/>
@@ -2206,15 +2206,15 @@
       </c>
       <c r="B104" s="7" t="n"/>
       <c r="C104" s="7" t="n"/>
-      <c r="D104" s="7" t="n"/>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E104" s="7" t="n"/>
       <c r="F104" s="7" t="n"/>
       <c r="G104" s="7" t="n"/>
-      <c r="H104" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H104" s="7" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="6" t="n">
@@ -2311,7 +2311,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 105 players, top value 70.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 105 players, top value 68.</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 0): implied = average of the sheet value at the player's projection-rank slot</t>
+          <t xml:space="preserve">   (Projections page snapshot 1): implied = average of the sheet value at the player's projection-rank slot</t>
         </is>
       </c>
     </row>
@@ -2349,14 +2349,14 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.4 x (implied - sheet), then rescaled so the total equals the sheet total. 55 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.4 x (implied - sheet), then rescaled so the total equals the sheet total. 66 players moved.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   No projection this week (value kept): Bijan Robinson, Puka Nacua, Kenneth Walker III, Saquon Barkley, Ashton Jeanty, Derrick Henry, Justin Jefferson, De'Von Achane, Chris Olave, A.J. Brown, Breece Hall, Drake London, Brock Bowers, Kyren Williams, Josh Allen, Rashee Rice, Zay Flowers, Lamar Jackson, Travis Etienne Jr., Jadarian Price, MarShawn Lloyd, Mike Evans, Joe Burrow, Drake Maye, Luther Burden III, Josh Jacobs, De'Zhaun Stribling, Jayden Daniels, Jordan Mason, Alec Pierce, J.K. Dobbins, Chris Godwin Jr., Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Trevor Lawrence, Rico Dowdle, Dak Prescott, Blake Corum, Kenny Gainwell, Jaxson Dart, Rachaad White, Ja'Kobi Lane, Woody Marks.</t>
+          <t xml:space="preserve">   No projection this week (value kept): Puka Nacua, Saquon Barkley, Derrick Henry, Justin Jefferson, De'Von Achane, A.J. Brown, Breece Hall, Kyren Williams, Zay Flowers, Lamar Jackson, Travis Etienne Jr., MarShawn Lloyd, Mike Evans, Joe Burrow, Luther Burden III, Josh Jacobs, De'Zhaun Stribling, Jayden Daniels, Jordan Mason, Alec Pierce, Chris Godwin Jr., Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Trevor Lawrence, Rico Dowdle, Blake Corum, Kenny Gainwell, Jaxson Dart, Rachaad White, Ja'Kobi Lane.</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2408,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.8, WR 3.3, TE 4.5, QB 0.0.</t>
+          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.9, WR 3.3, TE 4.5, QB 0.0.</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2435,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: CeeDee Lamb 44-&gt;39, Chris Olave 41-&gt;36, Nico Collins 32-&gt;27, Malik Nabers 24-&gt;19, Trey McBride 28-&gt;23, DeVonta Smith 27-&gt;22, Rashee Rice 26-&gt;21, Garrett Wilson 28-&gt;23</t>
+          <t>Largest moves vs. the baseline in this file: CeeDee Lamb 44-&gt;39, Drake London 32-&gt;27, Malik Nabers 25-&gt;20, DeVonta Smith 28-&gt;23, Rashee Rice 21-&gt;16, Garrett Wilson 29-&gt;24, Ja'Marr Chase 59-&gt;55, Derrick Henry 55-&gt;59</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -602,11 +602,11 @@
     </row>
     <row r="4">
       <c r="A4" s="6" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Bijan Robinson</t>
+          <t>Jahmyr Gibbs</t>
         </is>
       </c>
       <c r="C4" s="7" t="n"/>
@@ -618,15 +618,15 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>62</v>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="B5" s="7" t="n"/>
       <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E5" s="7" t="n"/>
       <c r="F5" s="7" t="n"/>
       <c r="G5" s="7" t="n"/>
@@ -634,15 +634,15 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>62</v>
-      </c>
-      <c r="B6" s="7" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Bijan Robinson</t>
+        </is>
+      </c>
       <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="7" t="n"/>
       <c r="G6" s="7" t="n"/>
@@ -650,11 +650,11 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C7" s="7" t="n"/>
@@ -666,11 +666,11 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Jahmyr Gibbs</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C8" s="7" t="n"/>
@@ -682,11 +682,11 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Saquon Barkley</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C9" s="7" t="n"/>
@@ -698,15 +698,15 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>56</v>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="n"/>
@@ -714,15 +714,15 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
@@ -730,11 +730,11 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>James Cook III</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="C12" s="7" t="n"/>
@@ -746,15 +746,15 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Jonathan Taylor</t>
-        </is>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
@@ -762,15 +762,15 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>52</v>
-      </c>
-      <c r="B14" s="7" t="n"/>
+        <v>46</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D14" s="7" t="n"/>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
@@ -778,15 +778,15 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="B15" s="7" t="n"/>
+        <v>43</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D15" s="7" t="n"/>
       <c r="E15" s="7" t="n"/>
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="7" t="n"/>
@@ -794,13 +794,13 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Justin Jefferson</t>
+          <t>Chris Olave</t>
         </is>
       </c>
       <c r="E16" s="7" t="n"/>
@@ -810,13 +810,13 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="n"/>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="E17" s="7" t="n"/>
@@ -826,15 +826,15 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="B18" s="7" t="n"/>
+        <v>39</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
@@ -842,15 +842,15 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
@@ -858,23 +858,23 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
       <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
@@ -890,15 +890,15 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>De'Von Achane</t>
-        </is>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
@@ -906,13 +906,13 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E23" s="7" t="n"/>
@@ -922,11 +922,11 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>De'Von Achane</t>
         </is>
       </c>
       <c r="C24" s="7" t="n"/>
@@ -938,15 +938,15 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="B25" s="7" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
@@ -954,27 +954,27 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="B26" s="7" t="n"/>
+        <v>27</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C26" s="7" t="n"/>
       <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C27" s="7" t="n"/>
@@ -986,11 +986,11 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C28" s="7" t="n"/>
@@ -1002,13 +1002,13 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>Nico Collins</t>
         </is>
       </c>
       <c r="E29" s="7" t="n"/>
@@ -1018,11 +1018,11 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C30" s="7" t="n"/>
@@ -1034,15 +1034,15 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" s="7" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D31" s="7" t="n"/>
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="7" t="n"/>
       <c r="G31" s="7" t="n"/>
@@ -1050,47 +1050,47 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+      <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
       <c r="D33" s="7" t="n"/>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
-      <c r="H33" s="7" t="n"/>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="B34" s="7" t="n"/>
+        <v>23</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D34" s="7" t="n"/>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="7" t="n"/>
@@ -1098,15 +1098,15 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="B35" s="7" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C35" s="7" t="n"/>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D35" s="7" t="n"/>
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="7" t="n"/>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
@@ -1130,29 +1130,29 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7" t="n"/>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E37" s="7" t="n"/>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F37" s="7" t="n"/>
       <c r="G37" s="7" t="n"/>
       <c r="H37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E38" s="7" t="n"/>
@@ -1162,31 +1162,31 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D39" s="7" t="n"/>
       <c r="E39" s="7" t="n"/>
-      <c r="F39" s="7" t="n"/>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G39" s="7" t="n"/>
       <c r="H39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="n"/>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
@@ -1194,15 +1194,15 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="B41" s="7" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D41" s="7" t="n"/>
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="7" t="n"/>
@@ -1210,15 +1210,15 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="B42" s="7" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D42" s="7" t="n"/>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="7" t="n"/>
@@ -1226,15 +1226,15 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B43" s="7" t="n"/>
       <c r="C43" s="7" t="n"/>
-      <c r="D43" s="7" t="n"/>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E43" s="7" t="n"/>
       <c r="F43" s="7" t="n"/>
       <c r="G43" s="7" t="n"/>
@@ -1242,15 +1242,15 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="n"/>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="7" t="n"/>
@@ -1258,13 +1258,13 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B45" s="7" t="n"/>
       <c r="C45" s="7" t="n"/>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E45" s="7" t="n"/>
@@ -1274,15 +1274,15 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B46" s="7" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D46" s="7" t="n"/>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="7" t="n"/>
@@ -1290,15 +1290,15 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="n"/>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E47" s="7" t="n"/>
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="7" t="n"/>
@@ -1306,11 +1306,11 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="C48" s="7" t="n"/>
@@ -1322,13 +1322,13 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B49" s="7" t="n"/>
       <c r="C49" s="7" t="n"/>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E49" s="7" t="n"/>
@@ -1338,23 +1338,23 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B50" s="7" t="n"/>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
-      <c r="F50" s="7" t="n"/>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G50" s="7" t="n"/>
       <c r="H50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
@@ -1370,11 +1370,11 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="C52" s="7" t="n"/>
@@ -1386,27 +1386,27 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B53" s="7" t="n"/>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D53" s="7" t="n"/>
       <c r="E53" s="7" t="n"/>
-      <c r="F53" s="7" t="n"/>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G53" s="7" t="n"/>
       <c r="H53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C54" s="7" t="n"/>
@@ -1418,15 +1418,15 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B55" s="7" t="n"/>
       <c r="C55" s="7" t="n"/>
-      <c r="D55" s="7" t="n"/>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E55" s="7" t="n"/>
       <c r="F55" s="7" t="n"/>
       <c r="G55" s="7" t="n"/>
@@ -1434,63 +1434,63 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B56" s="7" t="n"/>
       <c r="C56" s="7" t="n"/>
-      <c r="D56" s="7" t="n"/>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="n"/>
-      <c r="H56" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B57" s="7" t="n"/>
       <c r="C57" s="7" t="n"/>
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
       <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
-      <c r="H57" s="7" t="n"/>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B58" s="7" t="n"/>
       <c r="C58" s="7" t="n"/>
       <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
       <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n"/>
-      <c r="H58" s="7" t="n"/>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B59" s="7" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
       <c r="F59" s="7" t="n"/>
       <c r="G59" s="7" t="n"/>
@@ -1498,31 +1498,31 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B60" s="7" t="n"/>
       <c r="C60" s="7" t="n"/>
-      <c r="D60" s="7" t="n"/>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E60" s="7" t="n"/>
       <c r="F60" s="7" t="n"/>
       <c r="G60" s="7" t="n"/>
-      <c r="H60" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="n"/>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E61" s="7" t="n"/>
       <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
@@ -1530,13 +1530,13 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B62" s="7" t="n"/>
       <c r="C62" s="7" t="n"/>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E62" s="7" t="n"/>
@@ -1546,95 +1546,95 @@
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B63" s="7" t="n"/>
       <c r="C63" s="7" t="n"/>
       <c r="D63" s="7" t="n"/>
       <c r="E63" s="7" t="n"/>
-      <c r="F63" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F63" s="7" t="n"/>
       <c r="G63" s="7" t="n"/>
-      <c r="H63" s="7" t="n"/>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B64" s="7" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C64" s="7" t="n"/>
       <c r="D64" s="7" t="n"/>
       <c r="E64" s="7" t="n"/>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F64" s="7" t="n"/>
       <c r="G64" s="7" t="n"/>
       <c r="H64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B65" s="7" t="n"/>
       <c r="C65" s="7" t="n"/>
-      <c r="D65" s="7" t="n"/>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E65" s="7" t="n"/>
-      <c r="F65" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F65" s="7" t="n"/>
       <c r="G65" s="7" t="n"/>
       <c r="H65" s="7" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B66" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
       <c r="C66" s="7" t="n"/>
       <c r="D66" s="7" t="n"/>
       <c r="E66" s="7" t="n"/>
-      <c r="F66" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F66" s="7" t="n"/>
       <c r="G66" s="7" t="n"/>
       <c r="H66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B67" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C67" s="7" t="n"/>
       <c r="D67" s="7" t="n"/>
       <c r="E67" s="7" t="n"/>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
-      <c r="H67" s="7" t="inlineStr">
-        <is>
-          <t>Jalen Hurts</t>
-        </is>
-      </c>
+      <c r="H67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B68" s="7" t="n"/>
       <c r="C68" s="7" t="n"/>
-      <c r="D68" s="7" t="n"/>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E68" s="7" t="n"/>
       <c r="F68" s="7" t="n"/>
       <c r="G68" s="7" t="n"/>
@@ -1642,13 +1642,13 @@
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B69" s="7" t="n"/>
       <c r="C69" s="7" t="n"/>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E69" s="7" t="n"/>
@@ -1658,15 +1658,15 @@
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B70" s="7" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D70" s="7" t="n"/>
       <c r="E70" s="7" t="n"/>
       <c r="F70" s="7" t="n"/>
       <c r="G70" s="7" t="n"/>
@@ -1674,15 +1674,15 @@
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B71" s="7" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C71" s="7" t="n"/>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D71" s="7" t="n"/>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
@@ -1690,11 +1690,11 @@
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C72" s="7" t="n"/>
@@ -1706,27 +1706,27 @@
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B73" s="7" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>Mike Washington Jr.</t>
+        </is>
+      </c>
       <c r="C73" s="7" t="n"/>
       <c r="D73" s="7" t="n"/>
       <c r="E73" s="7" t="n"/>
       <c r="F73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
-      <c r="H73" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C74" s="7" t="n"/>
@@ -1738,13 +1738,13 @@
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B75" s="7" t="n"/>
       <c r="C75" s="7" t="n"/>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E75" s="7" t="n"/>
@@ -1754,31 +1754,31 @@
     </row>
     <row r="76">
       <c r="A76" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B76" s="7" t="n"/>
       <c r="C76" s="7" t="n"/>
-      <c r="D76" s="7" t="n"/>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E76" s="7" t="n"/>
       <c r="F76" s="7" t="n"/>
       <c r="G76" s="7" t="n"/>
-      <c r="H76" s="7" t="inlineStr">
-        <is>
-          <t>Justin Herbert</t>
-        </is>
-      </c>
+      <c r="H76" s="7" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B77" s="7" t="n"/>
       <c r="C77" s="7" t="n"/>
-      <c r="D77" s="7" t="n"/>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>Terry McLaurin</t>
+        </is>
+      </c>
       <c r="E77" s="7" t="n"/>
       <c r="F77" s="7" t="n"/>
       <c r="G77" s="7" t="n"/>
@@ -1786,13 +1786,13 @@
     </row>
     <row r="78">
       <c r="A78" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B78" s="7" t="n"/>
       <c r="C78" s="7" t="n"/>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E78" s="7" t="n"/>
@@ -1802,13 +1802,13 @@
     </row>
     <row r="79">
       <c r="A79" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B79" s="7" t="n"/>
       <c r="C79" s="7" t="n"/>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E79" s="7" t="n"/>
@@ -1818,13 +1818,13 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B80" s="7" t="n"/>
       <c r="C80" s="7" t="n"/>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E80" s="7" t="n"/>
@@ -1834,7 +1834,7 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B81" s="7" t="n"/>
       <c r="C81" s="7" t="n"/>
@@ -1842,7 +1842,7 @@
       <c r="E81" s="7" t="n"/>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>Colston Loveland</t>
         </is>
       </c>
       <c r="G81" s="7" t="n"/>
@@ -1850,43 +1850,43 @@
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B82" s="7" t="n"/>
       <c r="C82" s="7" t="n"/>
       <c r="D82" s="7" t="n"/>
       <c r="E82" s="7" t="n"/>
-      <c r="F82" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F82" s="7" t="n"/>
       <c r="G82" s="7" t="n"/>
-      <c r="H82" s="7" t="n"/>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B83" s="7" t="n"/>
       <c r="C83" s="7" t="n"/>
       <c r="D83" s="7" t="n"/>
       <c r="E83" s="7" t="n"/>
       <c r="F83" s="7" t="n"/>
       <c r="G83" s="7" t="n"/>
-      <c r="H83" s="7" t="n"/>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="C84" s="7" t="n"/>
@@ -1898,11 +1898,11 @@
     </row>
     <row r="85">
       <c r="A85" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C85" s="7" t="n"/>
@@ -1914,11 +1914,11 @@
     </row>
     <row r="86">
       <c r="A86" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="C86" s="7" t="n"/>
@@ -1930,15 +1930,15 @@
     </row>
     <row r="87">
       <c r="A87" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B87" s="7" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C87" s="7" t="n"/>
-      <c r="D87" s="7" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D87" s="7" t="n"/>
       <c r="E87" s="7" t="n"/>
       <c r="F87" s="7" t="n"/>
       <c r="G87" s="7" t="n"/>
@@ -1946,13 +1946,13 @@
     </row>
     <row r="88">
       <c r="A88" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B88" s="7" t="n"/>
       <c r="C88" s="7" t="n"/>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E88" s="7" t="n"/>
@@ -1962,13 +1962,13 @@
     </row>
     <row r="89">
       <c r="A89" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B89" s="7" t="n"/>
       <c r="C89" s="7" t="n"/>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E89" s="7" t="n"/>
@@ -1978,13 +1978,13 @@
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B90" s="7" t="n"/>
       <c r="C90" s="7" t="n"/>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E90" s="7" t="n"/>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B91" s="7" t="n"/>
       <c r="C91" s="7" t="n"/>
@@ -2010,31 +2010,31 @@
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B92" s="7" t="n"/>
       <c r="C92" s="7" t="n"/>
-      <c r="D92" s="7" t="n"/>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E92" s="7" t="n"/>
       <c r="F92" s="7" t="n"/>
       <c r="G92" s="7" t="n"/>
-      <c r="H92" s="7" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B93" s="7" t="n"/>
       <c r="C93" s="7" t="n"/>
-      <c r="D93" s="7" t="n"/>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E93" s="7" t="n"/>
       <c r="F93" s="7" t="n"/>
       <c r="G93" s="7" t="n"/>
@@ -2042,15 +2042,15 @@
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B94" s="7" t="n"/>
       <c r="C94" s="7" t="n"/>
-      <c r="D94" s="7" t="n"/>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="7" t="n"/>
       <c r="G94" s="7" t="n"/>
@@ -2058,109 +2058,109 @@
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B95" s="7" t="n"/>
       <c r="C95" s="7" t="n"/>
-      <c r="D95" s="7" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D95" s="7" t="n"/>
       <c r="E95" s="7" t="n"/>
-      <c r="F95" s="7" t="n"/>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G95" s="7" t="n"/>
       <c r="H95" s="7" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B96" s="7" t="n"/>
       <c r="C96" s="7" t="n"/>
       <c r="D96" s="7" t="n"/>
       <c r="E96" s="7" t="n"/>
-      <c r="F96" s="7" t="n"/>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G96" s="7" t="n"/>
-      <c r="H96" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H96" s="7" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B97" s="7" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B97" s="7" t="n"/>
       <c r="C97" s="7" t="n"/>
       <c r="D97" s="7" t="n"/>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="7" t="n"/>
       <c r="G97" s="7" t="n"/>
-      <c r="H97" s="7" t="n"/>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>Jalen Hurts</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B98" s="7" t="n"/>
       <c r="C98" s="7" t="n"/>
-      <c r="D98" s="7" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D98" s="7" t="n"/>
       <c r="E98" s="7" t="n"/>
       <c r="F98" s="7" t="n"/>
       <c r="G98" s="7" t="n"/>
-      <c r="H98" s="7" t="n"/>
+      <c r="H98" s="7" t="inlineStr">
+        <is>
+          <t>Justin Herbert</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B99" s="7" t="n"/>
       <c r="C99" s="7" t="n"/>
-      <c r="D99" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
+      <c r="D99" s="7" t="n"/>
       <c r="E99" s="7" t="n"/>
       <c r="F99" s="7" t="n"/>
       <c r="G99" s="7" t="n"/>
-      <c r="H99" s="7" t="n"/>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B100" s="7" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C100" s="7" t="n"/>
       <c r="D100" s="7" t="n"/>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="7" t="n"/>
       <c r="G100" s="7" t="n"/>
-      <c r="H100" s="7" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H100" s="7" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B101" s="7" t="n"/>
       <c r="C101" s="7" t="n"/>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E101" s="7" t="n"/>
@@ -2170,15 +2170,15 @@
     </row>
     <row r="102">
       <c r="A102" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B102" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C102" s="7" t="n"/>
-      <c r="D102" s="7" t="inlineStr">
-        <is>
-          <t>KC Concepcion</t>
-        </is>
-      </c>
+      <c r="D102" s="7" t="n"/>
       <c r="E102" s="7" t="n"/>
       <c r="F102" s="7" t="n"/>
       <c r="G102" s="7" t="n"/>
@@ -2186,15 +2186,15 @@
     </row>
     <row r="103">
       <c r="A103" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B103" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>Kenny Gainwell</t>
+        </is>
+      </c>
       <c r="C103" s="7" t="n"/>
-      <c r="D103" s="7" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
+      <c r="D103" s="7" t="n"/>
       <c r="E103" s="7" t="n"/>
       <c r="F103" s="7" t="n"/>
       <c r="G103" s="7" t="n"/>
@@ -2202,15 +2202,15 @@
     </row>
     <row r="104">
       <c r="A104" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B104" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>Rachaad White</t>
+        </is>
+      </c>
       <c r="C104" s="7" t="n"/>
-      <c r="D104" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Reed</t>
-        </is>
-      </c>
+      <c r="D104" s="7" t="n"/>
       <c r="E104" s="7" t="n"/>
       <c r="F104" s="7" t="n"/>
       <c r="G104" s="7" t="n"/>
@@ -2218,13 +2218,13 @@
     </row>
     <row r="105">
       <c r="A105" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B105" s="7" t="n"/>
       <c r="C105" s="7" t="n"/>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E105" s="7" t="n"/>
@@ -2236,13 +2236,13 @@
       <c r="A106" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B106" s="7" t="inlineStr">
-        <is>
-          <t>Kenny Gainwell</t>
-        </is>
-      </c>
+      <c r="B106" s="7" t="n"/>
       <c r="C106" s="7" t="n"/>
-      <c r="D106" s="7" t="n"/>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>Carnell Tate</t>
+        </is>
+      </c>
       <c r="E106" s="7" t="n"/>
       <c r="F106" s="7" t="n"/>
       <c r="G106" s="7" t="n"/>
@@ -2252,13 +2252,13 @@
       <c r="A107" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B107" s="7" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
+      <c r="B107" s="7" t="n"/>
       <c r="C107" s="7" t="n"/>
-      <c r="D107" s="7" t="n"/>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
       <c r="E107" s="7" t="n"/>
       <c r="F107" s="7" t="n"/>
       <c r="G107" s="7" t="n"/>
@@ -2270,13 +2270,13 @@
       </c>
       <c r="B108" s="7" t="n"/>
       <c r="C108" s="7" t="n"/>
-      <c r="D108" s="7" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D108" s="7" t="n"/>
       <c r="E108" s="7" t="n"/>
-      <c r="F108" s="7" t="n"/>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G108" s="7" t="n"/>
       <c r="H108" s="7" t="n"/>
     </row>
@@ -2311,7 +2311,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 105 players, top value 70.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 105 players, top value 85.</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 0): implied = average of the sheet value at the player's projection-rank slot</t>
+          <t xml:space="preserve">   (Projections page snapshot 0; 32 players used week 3 medians): implied = average of the seed value at the player's projection-rank slot among the projected players at the position</t>
         </is>
       </c>
     </row>
@@ -2349,14 +2349,14 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.4 x (implied - sheet), then rescaled so the total equals the sheet total. 55 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.8 x (implied - sheet), then rescaled so the total equals the sheet total. 80 players moved.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   No projection this week (value kept): Bijan Robinson, Puka Nacua, Kenneth Walker III, Saquon Barkley, Ashton Jeanty, Derrick Henry, Justin Jefferson, De'Von Achane, Chris Olave, A.J. Brown, Breece Hall, Drake London, Brock Bowers, Kyren Williams, Josh Allen, Rashee Rice, Zay Flowers, Lamar Jackson, Travis Etienne Jr., Jadarian Price, MarShawn Lloyd, Mike Evans, Joe Burrow, Drake Maye, Luther Burden III, Josh Jacobs, De'Zhaun Stribling, Jayden Daniels, Jordan Mason, Alec Pierce, J.K. Dobbins, Chris Godwin Jr., Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Trevor Lawrence, Rico Dowdle, Dak Prescott, Blake Corum, Kenny Gainwell, Jaxson Dart, Rachaad White, Ja'Kobi Lane, Woody Marks.</t>
+          <t xml:space="preserve">   No projection this week (value kept): Puka Nacua, Josh Jacobs, De'Zhaun Stribling, Jayden Daniels, Jordan Mason, Alec Pierce, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Jaxson Dart, Ja'Kobi Lane.</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2408,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.8, WR 2.9, TE 4.5, QB 0.0.</t>
+          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.9, WR 3.2, TE 3.5, QB 0.0.</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2435,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Derrick Henry 55-&gt;61, Trey McBride 28-&gt;22, Jaxon Smith-Njigba 56-&gt;51, James Cook III 49-&gt;54, Chris Olave 41-&gt;36, Drake London 37-&gt;32, DeVonta Smith 27-&gt;22, Rashee Rice 26-&gt;21</t>
+          <t>Largest moves vs. the baseline in this file: Puka Nacua 65-&gt;50, Jaxon Smith-Njigba 82-&gt;67, Ja'Marr Chase 67-&gt;53, Amon-Ra St. Brown 66-&gt;52, Chris Olave 56-&gt;42, Trey McBride 47-&gt;33, Bijan Robinson 74-&gt;61, Jahmyr Gibbs 85-&gt;72</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -620,13 +620,13 @@
       <c r="A5" s="6" t="n">
         <v>67</v>
       </c>
-      <c r="B5" s="7" t="n"/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Bijan Robinson</t>
+        </is>
+      </c>
       <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D5" s="7" t="n"/>
       <c r="E5" s="7" t="n"/>
       <c r="F5" s="7" t="n"/>
       <c r="G5" s="7" t="n"/>
@@ -634,11 +634,11 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Bijan Robinson</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C6" s="7" t="n"/>
@@ -650,15 +650,15 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>56</v>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B7" s="7" t="n"/>
       <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="7" t="n"/>
@@ -666,7 +666,7 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
@@ -682,11 +682,11 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C9" s="7" t="n"/>
@@ -698,13 +698,13 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Chris Olave</t>
         </is>
       </c>
       <c r="E10" s="7" t="n"/>
@@ -714,13 +714,13 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -732,13 +732,13 @@
       <c r="A12" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+      <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="n"/>
@@ -746,15 +746,15 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="B13" s="7" t="n"/>
+        <v>49</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D13" s="7" t="n"/>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
@@ -762,15 +762,15 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
@@ -778,7 +778,7 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
@@ -794,15 +794,15 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="B16" s="7" t="n"/>
+        <v>38</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D16" s="7" t="n"/>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
@@ -810,23 +810,23 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D17" s="7" t="n"/>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="n"/>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
@@ -842,15 +842,15 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="B19" s="7" t="n"/>
+        <v>33</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
@@ -862,31 +862,31 @@
       </c>
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
@@ -896,7 +896,7 @@
       <c r="C22" s="7" t="n"/>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E22" s="7" t="n"/>
@@ -906,15 +906,15 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B23" s="7" t="n"/>
+        <v>31</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
@@ -922,15 +922,15 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>De'Von Achane</t>
-        </is>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
@@ -938,11 +938,11 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C25" s="7" t="n"/>
@@ -954,11 +954,11 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>De'Von Achane</t>
         </is>
       </c>
       <c r="C26" s="7" t="n"/>
@@ -974,7 +974,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C27" s="7" t="n"/>
@@ -988,13 +988,13 @@
       <c r="A28" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+      <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="7" t="n"/>
@@ -1002,27 +1002,27 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D29" s="7" t="n"/>
       <c r="E29" s="7" t="n"/>
-      <c r="F29" s="7" t="n"/>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G29" s="7" t="n"/>
       <c r="H29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C30" s="7" t="n"/>
@@ -1034,15 +1034,15 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="7" t="n"/>
       <c r="G31" s="7" t="n"/>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
@@ -1066,39 +1066,39 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="n"/>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
       <c r="D34" s="7" t="n"/>
       <c r="E34" s="7" t="n"/>
-      <c r="F34" s="7" t="n"/>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G34" s="7" t="n"/>
       <c r="H34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
@@ -1118,27 +1118,27 @@
       </c>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D36" s="7" t="n"/>
       <c r="E36" s="7" t="n"/>
       <c r="F36" s="7" t="n"/>
       <c r="G36" s="7" t="n"/>
-      <c r="H36" s="7" t="n"/>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="B37" s="7" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D37" s="7" t="n"/>
       <c r="E37" s="7" t="n"/>
       <c r="F37" s="7" t="n"/>
       <c r="G37" s="7" t="n"/>
@@ -1146,13 +1146,13 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E38" s="7" t="n"/>
@@ -1162,29 +1162,29 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="B39" s="7" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C39" s="7" t="n"/>
       <c r="D39" s="7" t="n"/>
       <c r="E39" s="7" t="n"/>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F39" s="7" t="n"/>
       <c r="G39" s="7" t="n"/>
       <c r="H39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E40" s="7" t="n"/>
@@ -1196,13 +1196,13 @@
       <c r="A41" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+      <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="n"/>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="7" t="n"/>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C42" s="7" t="n"/>
@@ -1226,13 +1226,13 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B43" s="7" t="n"/>
       <c r="C43" s="7" t="n"/>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E43" s="7" t="n"/>
@@ -1244,13 +1244,13 @@
       <c r="A44" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B44" s="7" t="n"/>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D44" s="7" t="n"/>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="7" t="n"/>
@@ -1258,13 +1258,13 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B45" s="7" t="n"/>
       <c r="C45" s="7" t="n"/>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E45" s="7" t="n"/>
@@ -1274,31 +1274,31 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
       <c r="D46" s="7" t="n"/>
       <c r="E46" s="7" t="n"/>
-      <c r="F46" s="7" t="n"/>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G46" s="7" t="n"/>
       <c r="H46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B47" s="7" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D47" s="7" t="n"/>
       <c r="E47" s="7" t="n"/>
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="7" t="n"/>
@@ -1306,15 +1306,15 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B48" s="7" t="n"/>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="n"/>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
@@ -1322,15 +1322,15 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B49" s="7" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D49" s="7" t="n"/>
       <c r="E49" s="7" t="n"/>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n"/>
@@ -1338,7 +1338,7 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B50" s="7" t="n"/>
       <c r="C50" s="7" t="n"/>
@@ -1354,11 +1354,11 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="C51" s="7" t="n"/>
@@ -1370,11 +1370,11 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C52" s="7" t="n"/>
@@ -1386,17 +1386,17 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B53" s="7" t="n"/>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="7" t="n"/>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E53" s="7" t="n"/>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F53" s="7" t="n"/>
       <c r="G53" s="7" t="n"/>
       <c r="H53" s="7" t="n"/>
     </row>
@@ -1404,13 +1404,13 @@
       <c r="A54" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+      <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
-      <c r="D54" s="7" t="n"/>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E54" s="7" t="n"/>
       <c r="F54" s="7" t="n"/>
       <c r="G54" s="7" t="n"/>
@@ -1418,15 +1418,15 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B55" s="7" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C55" s="7" t="n"/>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
       <c r="F55" s="7" t="n"/>
       <c r="G55" s="7" t="n"/>
@@ -1434,13 +1434,13 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B56" s="7" t="n"/>
       <c r="C56" s="7" t="n"/>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E56" s="7" t="n"/>
@@ -1450,23 +1450,23 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B57" s="7" t="n"/>
       <c r="C57" s="7" t="n"/>
-      <c r="D57" s="7" t="n"/>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>De'Zhaun Stribling</t>
+        </is>
+      </c>
       <c r="E57" s="7" t="n"/>
       <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
-      <c r="H57" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B58" s="7" t="n"/>
       <c r="C58" s="7" t="n"/>
@@ -1476,7 +1476,7 @@
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Drake Maye</t>
         </is>
       </c>
     </row>
@@ -1484,17 +1484,17 @@
       <c r="A59" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B59" s="7" t="n"/>
       <c r="C59" s="7" t="n"/>
       <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
       <c r="F59" s="7" t="n"/>
       <c r="G59" s="7" t="n"/>
-      <c r="H59" s="7" t="n"/>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
@@ -1502,25 +1502,25 @@
       </c>
       <c r="B60" s="7" t="n"/>
       <c r="C60" s="7" t="n"/>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D60" s="7" t="n"/>
       <c r="E60" s="7" t="n"/>
       <c r="F60" s="7" t="n"/>
       <c r="G60" s="7" t="n"/>
-      <c r="H60" s="7" t="n"/>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E61" s="7" t="n"/>
@@ -1530,13 +1530,13 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B62" s="7" t="n"/>
       <c r="C62" s="7" t="n"/>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E62" s="7" t="n"/>
@@ -1546,27 +1546,27 @@
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B63" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
       <c r="C63" s="7" t="n"/>
       <c r="D63" s="7" t="n"/>
       <c r="E63" s="7" t="n"/>
       <c r="F63" s="7" t="n"/>
       <c r="G63" s="7" t="n"/>
-      <c r="H63" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C64" s="7" t="n"/>
@@ -1578,15 +1578,15 @@
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B65" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C65" s="7" t="n"/>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D65" s="7" t="n"/>
       <c r="E65" s="7" t="n"/>
       <c r="F65" s="7" t="n"/>
       <c r="G65" s="7" t="n"/>
@@ -1596,13 +1596,13 @@
       <c r="A66" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+      <c r="B66" s="7" t="n"/>
       <c r="C66" s="7" t="n"/>
-      <c r="D66" s="7" t="n"/>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E66" s="7" t="n"/>
       <c r="F66" s="7" t="n"/>
       <c r="G66" s="7" t="n"/>
@@ -1612,13 +1612,13 @@
       <c r="A67" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+      <c r="B67" s="7" t="n"/>
       <c r="C67" s="7" t="n"/>
-      <c r="D67" s="7" t="n"/>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E67" s="7" t="n"/>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
@@ -1632,7 +1632,7 @@
       <c r="C68" s="7" t="n"/>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E68" s="7" t="n"/>
@@ -1648,7 +1648,7 @@
       <c r="C69" s="7" t="n"/>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E69" s="7" t="n"/>
@@ -1658,15 +1658,15 @@
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B70" s="7" t="n"/>
       <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="n"/>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E70" s="7" t="n"/>
       <c r="F70" s="7" t="n"/>
       <c r="G70" s="7" t="n"/>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C71" s="7" t="n"/>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Jadarian Price</t>
         </is>
       </c>
       <c r="C72" s="7" t="n"/>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C73" s="7" t="n"/>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C74" s="7" t="n"/>
@@ -1740,13 +1740,13 @@
       <c r="A75" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B75" s="7" t="n"/>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C75" s="7" t="n"/>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D75" s="7" t="n"/>
       <c r="E75" s="7" t="n"/>
       <c r="F75" s="7" t="n"/>
       <c r="G75" s="7" t="n"/>
@@ -1756,13 +1756,13 @@
       <c r="A76" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B76" s="7" t="n"/>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>Jonathon Brooks</t>
+        </is>
+      </c>
       <c r="C76" s="7" t="n"/>
-      <c r="D76" s="7" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D76" s="7" t="n"/>
       <c r="E76" s="7" t="n"/>
       <c r="F76" s="7" t="n"/>
       <c r="G76" s="7" t="n"/>
@@ -1772,13 +1772,13 @@
       <c r="A77" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B77" s="7" t="n"/>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Mike Washington Jr.</t>
+        </is>
+      </c>
       <c r="C77" s="7" t="n"/>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D77" s="7" t="n"/>
       <c r="E77" s="7" t="n"/>
       <c r="F77" s="7" t="n"/>
       <c r="G77" s="7" t="n"/>
@@ -1788,13 +1788,13 @@
       <c r="A78" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B78" s="7" t="n"/>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>Rico Dowdle</t>
+        </is>
+      </c>
       <c r="C78" s="7" t="n"/>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D78" s="7" t="n"/>
       <c r="E78" s="7" t="n"/>
       <c r="F78" s="7" t="n"/>
       <c r="G78" s="7" t="n"/>
@@ -1808,7 +1808,7 @@
       <c r="C79" s="7" t="n"/>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E79" s="7" t="n"/>
@@ -1824,7 +1824,7 @@
       <c r="C80" s="7" t="n"/>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E80" s="7" t="n"/>
@@ -1838,13 +1838,13 @@
       </c>
       <c r="B81" s="7" t="n"/>
       <c r="C81" s="7" t="n"/>
-      <c r="D81" s="7" t="n"/>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Reed</t>
+        </is>
+      </c>
       <c r="E81" s="7" t="n"/>
-      <c r="F81" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F81" s="7" t="n"/>
       <c r="G81" s="7" t="n"/>
       <c r="H81" s="7" t="n"/>
     </row>
@@ -1854,15 +1854,15 @@
       </c>
       <c r="B82" s="7" t="n"/>
       <c r="C82" s="7" t="n"/>
-      <c r="D82" s="7" t="n"/>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>Jordyn Tyson</t>
+        </is>
+      </c>
       <c r="E82" s="7" t="n"/>
       <c r="F82" s="7" t="n"/>
       <c r="G82" s="7" t="n"/>
-      <c r="H82" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H82" s="7" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="n">
@@ -1872,45 +1872,45 @@
       <c r="C83" s="7" t="n"/>
       <c r="D83" s="7" t="n"/>
       <c r="E83" s="7" t="n"/>
-      <c r="F83" s="7" t="n"/>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G83" s="7" t="n"/>
-      <c r="H83" s="7" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H83" s="7" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B84" s="7" t="n"/>
       <c r="C84" s="7" t="n"/>
       <c r="D84" s="7" t="n"/>
       <c r="E84" s="7" t="n"/>
       <c r="F84" s="7" t="n"/>
       <c r="G84" s="7" t="n"/>
-      <c r="H84" s="7" t="n"/>
+      <c r="H84" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B85" s="7" t="n"/>
       <c r="C85" s="7" t="n"/>
       <c r="D85" s="7" t="n"/>
       <c r="E85" s="7" t="n"/>
       <c r="F85" s="7" t="n"/>
       <c r="G85" s="7" t="n"/>
-      <c r="H85" s="7" t="n"/>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="n">
@@ -1952,7 +1952,7 @@
       <c r="C88" s="7" t="n"/>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E88" s="7" t="n"/>
@@ -1968,7 +1968,7 @@
       <c r="C89" s="7" t="n"/>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E89" s="7" t="n"/>
@@ -1984,7 +1984,7 @@
       <c r="C90" s="7" t="n"/>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E90" s="7" t="n"/>
@@ -2000,7 +2000,7 @@
       <c r="C91" s="7" t="n"/>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr.</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E91" s="7" t="n"/>
@@ -2016,7 +2016,7 @@
       <c r="C92" s="7" t="n"/>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E92" s="7" t="n"/>
@@ -2032,7 +2032,7 @@
       <c r="C93" s="7" t="n"/>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E93" s="7" t="n"/>
@@ -2048,7 +2048,7 @@
       <c r="C94" s="7" t="n"/>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E94" s="7" t="n"/>
@@ -2062,13 +2062,13 @@
       </c>
       <c r="B95" s="7" t="n"/>
       <c r="C95" s="7" t="n"/>
-      <c r="D95" s="7" t="n"/>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E95" s="7" t="n"/>
-      <c r="F95" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F95" s="7" t="n"/>
       <c r="G95" s="7" t="n"/>
       <c r="H95" s="7" t="n"/>
     </row>
@@ -2160,7 +2160,7 @@
       <c r="C101" s="7" t="n"/>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E101" s="7" t="n"/>
@@ -2170,33 +2170,33 @@
     </row>
     <row r="102">
       <c r="A102" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B102" s="7" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B102" s="7" t="n"/>
       <c r="C102" s="7" t="n"/>
       <c r="D102" s="7" t="n"/>
       <c r="E102" s="7" t="n"/>
-      <c r="F102" s="7" t="n"/>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G102" s="7" t="n"/>
       <c r="H102" s="7" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B103" s="7" t="inlineStr">
-        <is>
-          <t>Kenny Gainwell</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B103" s="7" t="n"/>
       <c r="C103" s="7" t="n"/>
       <c r="D103" s="7" t="n"/>
       <c r="E103" s="7" t="n"/>
-      <c r="F103" s="7" t="n"/>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G103" s="7" t="n"/>
       <c r="H103" s="7" t="n"/>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>Rachaad White</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="C104" s="7" t="n"/>
@@ -2220,13 +2220,13 @@
       <c r="A105" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B105" s="7" t="n"/>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>Kenny Gainwell</t>
+        </is>
+      </c>
       <c r="C105" s="7" t="n"/>
-      <c r="D105" s="7" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D105" s="7" t="n"/>
       <c r="E105" s="7" t="n"/>
       <c r="F105" s="7" t="n"/>
       <c r="G105" s="7" t="n"/>
@@ -2236,13 +2236,13 @@
       <c r="A106" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B106" s="7" t="n"/>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>Rachaad White</t>
+        </is>
+      </c>
       <c r="C106" s="7" t="n"/>
-      <c r="D106" s="7" t="inlineStr">
-        <is>
-          <t>Carnell Tate</t>
-        </is>
-      </c>
+      <c r="D106" s="7" t="n"/>
       <c r="E106" s="7" t="n"/>
       <c r="F106" s="7" t="n"/>
       <c r="G106" s="7" t="n"/>
@@ -2256,7 +2256,7 @@
       <c r="C107" s="7" t="n"/>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E107" s="7" t="n"/>
@@ -2270,13 +2270,13 @@
       </c>
       <c r="B108" s="7" t="n"/>
       <c r="C108" s="7" t="n"/>
-      <c r="D108" s="7" t="n"/>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
       <c r="E108" s="7" t="n"/>
-      <c r="F108" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F108" s="7" t="n"/>
       <c r="G108" s="7" t="n"/>
       <c r="H108" s="7" t="n"/>
     </row>
@@ -2311,7 +2311,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 105 players, top value 85.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 105 players, top value 88.</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 0; 32 players used week 3 medians): implied = average of the seed value at the player's projection-rank slot among the projected players at the position</t>
+          <t xml:space="preserve">   (Projections page snapshot 1; 13 players used week 3 medians): implied = average of the seed value at the player's projection-rank slot among the projected players at the position</t>
         </is>
       </c>
     </row>
@@ -2349,14 +2349,14 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.8 x (implied - sheet), then rescaled so the total equals the sheet total. 80 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.8 x (implied - sheet), then rescaled so the total equals the sheet total. 88 players moved.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   No projection this week (value kept): Puka Nacua, Josh Jacobs, De'Zhaun Stribling, Jayden Daniels, Jordan Mason, Alec Pierce, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Jaxson Dart, Ja'Kobi Lane.</t>
+          <t xml:space="preserve">   No projection this week (value kept): Josh Jacobs, De'Zhaun Stribling, Jayden Daniels, Jordan Mason, Alec Pierce, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Jaxson Dart, Ja'Kobi Lane.</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2408,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.9, WR 3.2, TE 3.5, QB 0.0.</t>
+          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 2.0, WR 3.0, TE 3.8, QB 0.0.</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2435,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Puka Nacua 65-&gt;50, Jaxon Smith-Njigba 82-&gt;67, Ja'Marr Chase 67-&gt;53, Amon-Ra St. Brown 66-&gt;52, Chris Olave 56-&gt;42, Trey McBride 47-&gt;33, Bijan Robinson 74-&gt;61, Jahmyr Gibbs 85-&gt;72</t>
+          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 75-&gt;57, Puka Nacua 58-&gt;41, Bijan Robinson 83-&gt;67, Jahmyr Gibbs 88-&gt;72, Ja'Marr Chase 66-&gt;50, Amon-Ra St. Brown 66-&gt;50, Chris Olave 67-&gt;51, Christian McCaffrey 67-&gt;52</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -602,7 +602,7 @@
     </row>
     <row r="4">
       <c r="A4" s="6" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
@@ -618,15 +618,15 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>67</v>
-      </c>
-      <c r="B5" s="7" t="n"/>
+        <v>66</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Bijan Robinson</t>
+        </is>
+      </c>
       <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D5" s="7" t="n"/>
       <c r="E5" s="7" t="n"/>
       <c r="F5" s="7" t="n"/>
       <c r="G5" s="7" t="n"/>
@@ -634,15 +634,15 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>61</v>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Bijan Robinson</t>
-        </is>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="7" t="n"/>
       <c r="G6" s="7" t="n"/>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
@@ -698,15 +698,15 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="B10" s="7" t="n"/>
+        <v>56</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="n"/>
@@ -714,13 +714,13 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Puka Nacua</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -730,15 +730,15 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="n"/>
@@ -746,13 +746,13 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Puka Nacua</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E13" s="7" t="n"/>
@@ -762,7 +762,7 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
@@ -794,15 +794,15 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="B16" s="7" t="n"/>
+        <v>44</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D16" s="7" t="n"/>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
@@ -810,7 +810,7 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="n"/>
@@ -826,15 +826,15 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
@@ -842,7 +842,7 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
@@ -858,47 +858,47 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
       <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="n"/>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="B21" s="7" t="n"/>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>De'Von Achane</t>
+        </is>
+      </c>
       <c r="C21" s="7" t="n"/>
       <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="B22" s="7" t="n"/>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
@@ -906,15 +906,15 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B23" s="7" t="n"/>
+        <v>31</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
@@ -922,11 +922,11 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>De'Von Achane</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C24" s="7" t="n"/>
@@ -938,27 +938,27 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C26" s="7" t="n"/>
@@ -970,15 +970,15 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
@@ -986,15 +986,15 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="7" t="n"/>
@@ -1008,7 +1008,7 @@
       <c r="C29" s="7" t="n"/>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Nico Collins</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E29" s="7" t="n"/>
@@ -1036,29 +1036,29 @@
       <c r="A31" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+      <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
       <c r="D31" s="7" t="n"/>
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="7" t="n"/>
       <c r="G31" s="7" t="n"/>
-      <c r="H31" s="7" t="n"/>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="B32" s="7" t="n"/>
+        <v>23</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
@@ -1066,27 +1066,27 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="n"/>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Saquon Barkley</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C34" s="7" t="n"/>
@@ -1100,13 +1100,13 @@
       <c r="A35" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+      <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
-      <c r="D35" s="7" t="n"/>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="7" t="n"/>
@@ -1114,13 +1114,13 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E36" s="7" t="n"/>
@@ -1130,13 +1130,13 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E37" s="7" t="n"/>
@@ -1146,15 +1146,15 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="B38" s="7" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D38" s="7" t="n"/>
       <c r="E38" s="7" t="n"/>
       <c r="F38" s="7" t="n"/>
       <c r="G38" s="7" t="n"/>
@@ -1162,29 +1162,29 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="B39" s="7" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C39" s="7" t="n"/>
       <c r="D39" s="7" t="n"/>
       <c r="E39" s="7" t="n"/>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F39" s="7" t="n"/>
       <c r="G39" s="7" t="n"/>
       <c r="H39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E40" s="7" t="n"/>
@@ -1194,15 +1194,15 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="n"/>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="7" t="n"/>
@@ -1210,11 +1210,11 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C42" s="7" t="n"/>
@@ -1226,15 +1226,15 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B43" s="7" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C43" s="7" t="n"/>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D43" s="7" t="n"/>
       <c r="E43" s="7" t="n"/>
       <c r="F43" s="7" t="n"/>
       <c r="G43" s="7" t="n"/>
@@ -1242,13 +1242,13 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="n"/>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E44" s="7" t="n"/>
@@ -1258,31 +1258,31 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B45" s="7" t="n"/>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D45" s="7" t="n"/>
       <c r="E45" s="7" t="n"/>
-      <c r="F45" s="7" t="n"/>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G45" s="7" t="n"/>
       <c r="H45" s="7" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="n"/>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="7" t="n"/>
@@ -1290,23 +1290,23 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D47" s="7" t="n"/>
       <c r="E47" s="7" t="n"/>
-      <c r="F47" s="7" t="n"/>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G47" s="7" t="n"/>
       <c r="H47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
@@ -1322,13 +1322,13 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B49" s="7" t="n"/>
       <c r="C49" s="7" t="n"/>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E49" s="7" t="n"/>
@@ -1338,31 +1338,31 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B50" s="7" t="n"/>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="n"/>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E50" s="7" t="n"/>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F50" s="7" t="n"/>
       <c r="G50" s="7" t="n"/>
       <c r="H50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B51" s="7" t="n"/>
       <c r="C51" s="7" t="n"/>
-      <c r="D51" s="7" t="n"/>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E51" s="7" t="n"/>
       <c r="F51" s="7" t="n"/>
       <c r="G51" s="7" t="n"/>
@@ -1370,15 +1370,15 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B52" s="7" t="n"/>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="7" t="n"/>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="7" t="n"/>
@@ -1386,7 +1386,7 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B53" s="7" t="n"/>
       <c r="C53" s="7" t="n"/>
@@ -1394,7 +1394,7 @@
       <c r="E53" s="7" t="n"/>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>Brock Bowers</t>
+          <t>Tyler Warren</t>
         </is>
       </c>
       <c r="G53" s="7" t="n"/>
@@ -1402,11 +1402,11 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="C54" s="7" t="n"/>
@@ -1418,15 +1418,15 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B55" s="7" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C55" s="7" t="n"/>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
       <c r="F55" s="7" t="n"/>
       <c r="G55" s="7" t="n"/>
@@ -1434,15 +1434,15 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B56" s="7" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C56" s="7" t="n"/>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D56" s="7" t="n"/>
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="n"/>
@@ -1450,47 +1450,47 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B57" s="7" t="n"/>
       <c r="C57" s="7" t="n"/>
-      <c r="D57" s="7" t="n"/>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E57" s="7" t="n"/>
       <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
-      <c r="H57" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B58" s="7" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C58" s="7" t="n"/>
       <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
       <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n"/>
-      <c r="H58" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B59" s="7" t="n"/>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="7" t="n"/>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E59" s="7" t="n"/>
       <c r="F59" s="7" t="n"/>
       <c r="G59" s="7" t="n"/>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B60" s="7" t="n"/>
       <c r="C60" s="7" t="n"/>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E60" s="7" t="n"/>
@@ -1514,13 +1514,13 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E61" s="7" t="n"/>
@@ -1530,43 +1530,43 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B62" s="7" t="n"/>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>De'Zhaun Stribling</t>
-        </is>
-      </c>
+      <c r="D62" s="7" t="n"/>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="7" t="n"/>
-      <c r="H62" s="7" t="n"/>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B63" s="7" t="n"/>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C63" s="7" t="n"/>
       <c r="D63" s="7" t="n"/>
       <c r="E63" s="7" t="n"/>
       <c r="F63" s="7" t="n"/>
       <c r="G63" s="7" t="n"/>
-      <c r="H63" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C64" s="7" t="n"/>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B65" s="7" t="n"/>
       <c r="C65" s="7" t="n"/>
@@ -1594,15 +1594,15 @@
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B66" s="7" t="n"/>
       <c r="C66" s="7" t="n"/>
-      <c r="D66" s="7" t="n"/>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E66" s="7" t="n"/>
       <c r="F66" s="7" t="n"/>
       <c r="G66" s="7" t="n"/>
@@ -1610,15 +1610,15 @@
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B67" s="7" t="n"/>
       <c r="C67" s="7" t="n"/>
-      <c r="D67" s="7" t="n"/>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>De'Zhaun Stribling</t>
+        </is>
+      </c>
       <c r="E67" s="7" t="n"/>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
@@ -1626,13 +1626,13 @@
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B68" s="7" t="n"/>
       <c r="C68" s="7" t="n"/>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E68" s="7" t="n"/>
@@ -1642,91 +1642,91 @@
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B69" s="7" t="n"/>
       <c r="C69" s="7" t="n"/>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D69" s="7" t="n"/>
       <c r="E69" s="7" t="n"/>
-      <c r="F69" s="7" t="n"/>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G69" s="7" t="n"/>
       <c r="H69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B70" s="7" t="n"/>
       <c r="C70" s="7" t="n"/>
       <c r="D70" s="7" t="n"/>
       <c r="E70" s="7" t="n"/>
-      <c r="F70" s="7" t="n"/>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G70" s="7" t="n"/>
       <c r="H70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B71" s="7" t="n"/>
       <c r="C71" s="7" t="n"/>
       <c r="D71" s="7" t="n"/>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
-      <c r="H71" s="7" t="n"/>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>Jonathon Brooks</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B72" s="7" t="n"/>
       <c r="C72" s="7" t="n"/>
       <c r="D72" s="7" t="n"/>
       <c r="E72" s="7" t="n"/>
       <c r="F72" s="7" t="n"/>
       <c r="G72" s="7" t="n"/>
-      <c r="H72" s="7" t="n"/>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>Mike Washington Jr.</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B73" s="7" t="n"/>
       <c r="C73" s="7" t="n"/>
       <c r="D73" s="7" t="n"/>
       <c r="E73" s="7" t="n"/>
       <c r="F73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
-      <c r="H73" s="7" t="n"/>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C74" s="7" t="n"/>
@@ -1738,15 +1738,15 @@
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B75" s="7" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C75" s="7" t="n"/>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D75" s="7" t="n"/>
       <c r="E75" s="7" t="n"/>
       <c r="F75" s="7" t="n"/>
       <c r="G75" s="7" t="n"/>
@@ -1754,15 +1754,15 @@
     </row>
     <row r="76">
       <c r="A76" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B76" s="7" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
       <c r="C76" s="7" t="n"/>
-      <c r="D76" s="7" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D76" s="7" t="n"/>
       <c r="E76" s="7" t="n"/>
       <c r="F76" s="7" t="n"/>
       <c r="G76" s="7" t="n"/>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="77">
       <c r="A77" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B77" s="7" t="n"/>
       <c r="C77" s="7" t="n"/>
@@ -1786,13 +1786,13 @@
     </row>
     <row r="78">
       <c r="A78" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B78" s="7" t="n"/>
       <c r="C78" s="7" t="n"/>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E78" s="7" t="n"/>
@@ -1804,13 +1804,13 @@
       <c r="A79" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B79" s="7" t="n"/>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C79" s="7" t="n"/>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Reed</t>
-        </is>
-      </c>
+      <c r="D79" s="7" t="n"/>
       <c r="E79" s="7" t="n"/>
       <c r="F79" s="7" t="n"/>
       <c r="G79" s="7" t="n"/>
@@ -1820,13 +1820,13 @@
       <c r="A80" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B80" s="7" t="n"/>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>Jonathon Brooks</t>
+        </is>
+      </c>
       <c r="C80" s="7" t="n"/>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>Jordyn Tyson</t>
-        </is>
-      </c>
+      <c r="D80" s="7" t="n"/>
       <c r="E80" s="7" t="n"/>
       <c r="F80" s="7" t="n"/>
       <c r="G80" s="7" t="n"/>
@@ -1836,15 +1836,15 @@
       <c r="A81" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B81" s="7" t="n"/>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>Mike Washington Jr.</t>
+        </is>
+      </c>
       <c r="C81" s="7" t="n"/>
       <c r="D81" s="7" t="n"/>
       <c r="E81" s="7" t="n"/>
-      <c r="F81" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F81" s="7" t="n"/>
       <c r="G81" s="7" t="n"/>
       <c r="H81" s="7" t="n"/>
     </row>
@@ -1852,45 +1852,45 @@
       <c r="A82" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B82" s="7" t="n"/>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>Rico Dowdle</t>
+        </is>
+      </c>
       <c r="C82" s="7" t="n"/>
       <c r="D82" s="7" t="n"/>
       <c r="E82" s="7" t="n"/>
       <c r="F82" s="7" t="n"/>
       <c r="G82" s="7" t="n"/>
-      <c r="H82" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H82" s="7" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B83" s="7" t="n"/>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C83" s="7" t="n"/>
       <c r="D83" s="7" t="n"/>
       <c r="E83" s="7" t="n"/>
       <c r="F83" s="7" t="n"/>
       <c r="G83" s="7" t="n"/>
-      <c r="H83" s="7" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H83" s="7" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B84" s="7" t="n"/>
       <c r="C84" s="7" t="n"/>
-      <c r="D84" s="7" t="n"/>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>Marvin Harrison Jr.</t>
+        </is>
+      </c>
       <c r="E84" s="7" t="n"/>
       <c r="F84" s="7" t="n"/>
       <c r="G84" s="7" t="n"/>
@@ -1898,15 +1898,15 @@
     </row>
     <row r="85">
       <c r="A85" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B85" s="7" t="n"/>
       <c r="C85" s="7" t="n"/>
-      <c r="D85" s="7" t="n"/>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>KC Concepcion</t>
+        </is>
+      </c>
       <c r="E85" s="7" t="n"/>
       <c r="F85" s="7" t="n"/>
       <c r="G85" s="7" t="n"/>
@@ -1914,15 +1914,15 @@
     </row>
     <row r="86">
       <c r="A86" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B86" s="7" t="n"/>
       <c r="C86" s="7" t="n"/>
-      <c r="D86" s="7" t="n"/>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>Quentin Johnston</t>
+        </is>
+      </c>
       <c r="E86" s="7" t="n"/>
       <c r="F86" s="7" t="n"/>
       <c r="G86" s="7" t="n"/>
@@ -1930,15 +1930,15 @@
     </row>
     <row r="87">
       <c r="A87" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B87" s="7" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B87" s="7" t="n"/>
       <c r="C87" s="7" t="n"/>
-      <c r="D87" s="7" t="n"/>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>Chris Godwin Jr.</t>
+        </is>
+      </c>
       <c r="E87" s="7" t="n"/>
       <c r="F87" s="7" t="n"/>
       <c r="G87" s="7" t="n"/>
@@ -1946,13 +1946,13 @@
     </row>
     <row r="88">
       <c r="A88" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B88" s="7" t="n"/>
       <c r="C88" s="7" t="n"/>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E88" s="7" t="n"/>
@@ -1962,13 +1962,13 @@
     </row>
     <row r="89">
       <c r="A89" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B89" s="7" t="n"/>
       <c r="C89" s="7" t="n"/>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E89" s="7" t="n"/>
@@ -1978,63 +1978,63 @@
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B90" s="7" t="n"/>
       <c r="C90" s="7" t="n"/>
-      <c r="D90" s="7" t="inlineStr">
-        <is>
-          <t>Quentin Johnston</t>
-        </is>
-      </c>
+      <c r="D90" s="7" t="n"/>
       <c r="E90" s="7" t="n"/>
-      <c r="F90" s="7" t="n"/>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G90" s="7" t="n"/>
       <c r="H90" s="7" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B91" s="7" t="n"/>
       <c r="C91" s="7" t="n"/>
-      <c r="D91" s="7" t="inlineStr">
-        <is>
-          <t>Chris Godwin Jr.</t>
-        </is>
-      </c>
+      <c r="D91" s="7" t="n"/>
       <c r="E91" s="7" t="n"/>
-      <c r="F91" s="7" t="n"/>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G91" s="7" t="n"/>
       <c r="H91" s="7" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B92" s="7" t="n"/>
       <c r="C92" s="7" t="n"/>
-      <c r="D92" s="7" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D92" s="7" t="n"/>
       <c r="E92" s="7" t="n"/>
       <c r="F92" s="7" t="n"/>
       <c r="G92" s="7" t="n"/>
-      <c r="H92" s="7" t="n"/>
+      <c r="H92" s="7" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B93" s="7" t="n"/>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>J.K. Dobbins</t>
+        </is>
+      </c>
       <c r="C93" s="7" t="n"/>
-      <c r="D93" s="7" t="inlineStr">
-        <is>
-          <t>Brian Thomas Jr.</t>
-        </is>
-      </c>
+      <c r="D93" s="7" t="n"/>
       <c r="E93" s="7" t="n"/>
       <c r="F93" s="7" t="n"/>
       <c r="G93" s="7" t="n"/>
@@ -2044,13 +2044,13 @@
       <c r="A94" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B94" s="7" t="n"/>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C94" s="7" t="n"/>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
+      <c r="D94" s="7" t="n"/>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="7" t="n"/>
       <c r="G94" s="7" t="n"/>
@@ -2060,15 +2060,15 @@
       <c r="A95" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B95" s="7" t="n"/>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C95" s="7" t="n"/>
       <c r="D95" s="7" t="n"/>
       <c r="E95" s="7" t="n"/>
-      <c r="F95" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F95" s="7" t="n"/>
       <c r="G95" s="7" t="n"/>
       <c r="H95" s="7" t="n"/>
     </row>
@@ -2078,13 +2078,13 @@
       </c>
       <c r="B96" s="7" t="n"/>
       <c r="C96" s="7" t="n"/>
-      <c r="D96" s="7" t="n"/>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E96" s="7" t="n"/>
-      <c r="F96" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F96" s="7" t="n"/>
       <c r="G96" s="7" t="n"/>
       <c r="H96" s="7" t="n"/>
     </row>
@@ -2094,15 +2094,15 @@
       </c>
       <c r="B97" s="7" t="n"/>
       <c r="C97" s="7" t="n"/>
-      <c r="D97" s="7" t="n"/>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="7" t="n"/>
       <c r="G97" s="7" t="n"/>
-      <c r="H97" s="7" t="inlineStr">
-        <is>
-          <t>Jalen Hurts</t>
-        </is>
-      </c>
+      <c r="H97" s="7" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
@@ -2110,15 +2110,15 @@
       </c>
       <c r="B98" s="7" t="n"/>
       <c r="C98" s="7" t="n"/>
-      <c r="D98" s="7" t="n"/>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E98" s="7" t="n"/>
       <c r="F98" s="7" t="n"/>
       <c r="G98" s="7" t="n"/>
-      <c r="H98" s="7" t="inlineStr">
-        <is>
-          <t>Justin Herbert</t>
-        </is>
-      </c>
+      <c r="H98" s="7" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
@@ -2126,27 +2126,27 @@
       </c>
       <c r="B99" s="7" t="n"/>
       <c r="C99" s="7" t="n"/>
-      <c r="D99" s="7" t="n"/>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E99" s="7" t="n"/>
       <c r="F99" s="7" t="n"/>
       <c r="G99" s="7" t="n"/>
-      <c r="H99" s="7" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B100" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B100" s="7" t="n"/>
       <c r="C100" s="7" t="n"/>
-      <c r="D100" s="7" t="n"/>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="7" t="n"/>
       <c r="G100" s="7" t="n"/>
@@ -2154,59 +2154,59 @@
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B101" s="7" t="n"/>
       <c r="C101" s="7" t="n"/>
-      <c r="D101" s="7" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D101" s="7" t="n"/>
       <c r="E101" s="7" t="n"/>
       <c r="F101" s="7" t="n"/>
       <c r="G101" s="7" t="n"/>
-      <c r="H101" s="7" t="n"/>
+      <c r="H101" s="7" t="inlineStr">
+        <is>
+          <t>Jalen Hurts</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B102" s="7" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B102" s="7" t="n"/>
       <c r="C102" s="7" t="n"/>
       <c r="D102" s="7" t="n"/>
       <c r="E102" s="7" t="n"/>
       <c r="F102" s="7" t="n"/>
       <c r="G102" s="7" t="n"/>
-      <c r="H102" s="7" t="n"/>
+      <c r="H102" s="7" t="inlineStr">
+        <is>
+          <t>Justin Herbert</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B103" s="7" t="inlineStr">
-        <is>
-          <t>Kenny Gainwell</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B103" s="7" t="n"/>
       <c r="C103" s="7" t="n"/>
       <c r="D103" s="7" t="n"/>
       <c r="E103" s="7" t="n"/>
       <c r="F103" s="7" t="n"/>
       <c r="G103" s="7" t="n"/>
-      <c r="H103" s="7" t="n"/>
+      <c r="H103" s="7" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>Rachaad White</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="C104" s="7" t="n"/>
@@ -2218,13 +2218,13 @@
     </row>
     <row r="105">
       <c r="A105" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B105" s="7" t="n"/>
       <c r="C105" s="7" t="n"/>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E105" s="7" t="n"/>
@@ -2234,13 +2234,13 @@
     </row>
     <row r="106">
       <c r="A106" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B106" s="7" t="n"/>
       <c r="C106" s="7" t="n"/>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E106" s="7" t="n"/>
@@ -2252,13 +2252,13 @@
       <c r="A107" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B107" s="7" t="n"/>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>Kenny Gainwell</t>
+        </is>
+      </c>
       <c r="C107" s="7" t="n"/>
-      <c r="D107" s="7" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
+      <c r="D107" s="7" t="n"/>
       <c r="E107" s="7" t="n"/>
       <c r="F107" s="7" t="n"/>
       <c r="G107" s="7" t="n"/>
@@ -2268,15 +2268,15 @@
       <c r="A108" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B108" s="7" t="n"/>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>Rachaad White</t>
+        </is>
+      </c>
       <c r="C108" s="7" t="n"/>
       <c r="D108" s="7" t="n"/>
       <c r="E108" s="7" t="n"/>
-      <c r="F108" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F108" s="7" t="n"/>
       <c r="G108" s="7" t="n"/>
       <c r="H108" s="7" t="n"/>
     </row>
@@ -2311,7 +2311,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 105 players, top value 85.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 105 players, top value 77.</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 0; 32 players used week 3 medians): implied = average of the seed value at the player's projection-rank slot among the projected players at the position</t>
+          <t xml:space="preserve">   (Projections page snapshot 0; 32 players used week 3 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.8 x (implied - sheet), then rescaled so the total equals the sheet total. 80 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.6 x (implied - sheet), then rescaled so the total equals the sheet total. 79 players moved.</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2408,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.9, WR 3.2, TE 3.5, QB 0.0.</t>
+          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.9, WR 3.1, TE 4.5, QB 0.0.</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2435,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Puka Nacua 65-&gt;50, Jaxon Smith-Njigba 82-&gt;67, Ja'Marr Chase 67-&gt;53, Amon-Ra St. Brown 66-&gt;52, Chris Olave 56-&gt;42, Trey McBride 47-&gt;33, Bijan Robinson 74-&gt;61, Jahmyr Gibbs 85-&gt;72</t>
+          <t>Largest moves vs. the baseline in this file: Puka Nacua 65-&gt;56, Jaxon Smith-Njigba 71-&gt;62, Chris Olave 50-&gt;41, Ja'Marr Chase 64-&gt;56, Amon-Ra St. Brown 63-&gt;55, Justin Jefferson 46-&gt;38, De'Von Achane 41-&gt;33, Drake London 31-&gt;23</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -618,7 +618,7 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
@@ -634,15 +634,15 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>62</v>
-      </c>
-      <c r="B6" s="7" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="7" t="n"/>
       <c r="G6" s="7" t="n"/>
@@ -650,11 +650,11 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C7" s="7" t="n"/>
@@ -666,15 +666,15 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Jonathan Taylor</t>
-        </is>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B8" s="7" t="n"/>
       <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="7" t="n"/>
@@ -682,11 +682,11 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C9" s="7" t="n"/>
@@ -714,13 +714,13 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Puka Nacua</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -730,13 +730,13 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E12" s="7" t="n"/>
@@ -746,13 +746,13 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Puka Nacua</t>
         </is>
       </c>
       <c r="E13" s="7" t="n"/>
@@ -762,15 +762,15 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
@@ -778,7 +778,7 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
@@ -794,11 +794,11 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>James Cook III</t>
         </is>
       </c>
       <c r="C16" s="7" t="n"/>
@@ -810,15 +810,15 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>43</v>
-      </c>
-      <c r="B17" s="7" t="n"/>
+        <v>40</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D17" s="7" t="n"/>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
@@ -826,15 +826,15 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="B18" s="7" t="n"/>
+        <v>39</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
@@ -842,7 +842,7 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
@@ -858,47 +858,47 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>De'Von Achane</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
       <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
@@ -906,11 +906,11 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Saquon Barkley</t>
+          <t>De'Von Achane</t>
         </is>
       </c>
       <c r="C23" s="7" t="n"/>
@@ -924,13 +924,13 @@
       <c r="A24" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+      <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
@@ -938,17 +938,17 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="B25" s="7" t="n"/>
+        <v>30</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C26" s="7" t="n"/>
@@ -970,15 +970,15 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="B27" s="7" t="n"/>
+        <v>27</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D27" s="7" t="n"/>
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
@@ -986,43 +986,43 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D28" s="7" t="n"/>
       <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G28" s="7" t="n"/>
       <c r="H28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D29" s="7" t="n"/>
       <c r="E29" s="7" t="n"/>
-      <c r="F29" s="7" t="n"/>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G29" s="7" t="n"/>
       <c r="H29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C30" s="7" t="n"/>
@@ -1034,31 +1034,31 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="7" t="n"/>
       <c r="G31" s="7" t="n"/>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+      <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
@@ -1070,23 +1070,23 @@
       </c>
       <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D33" s="7" t="n"/>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
-      <c r="H33" s="7" t="n"/>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C34" s="7" t="n"/>
@@ -1098,15 +1098,15 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="B35" s="7" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C35" s="7" t="n"/>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D35" s="7" t="n"/>
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="7" t="n"/>
@@ -1114,15 +1114,15 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="B36" s="7" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C36" s="7" t="n"/>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D36" s="7" t="n"/>
       <c r="E36" s="7" t="n"/>
       <c r="F36" s="7" t="n"/>
       <c r="G36" s="7" t="n"/>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
@@ -1148,13 +1148,13 @@
       <c r="A38" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+      <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="n"/>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E38" s="7" t="n"/>
       <c r="F38" s="7" t="n"/>
       <c r="G38" s="7" t="n"/>
@@ -1162,11 +1162,11 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="C39" s="7" t="n"/>
@@ -1178,13 +1178,13 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E40" s="7" t="n"/>
@@ -1194,15 +1194,15 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="B41" s="7" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D41" s="7" t="n"/>
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="7" t="n"/>
@@ -1212,13 +1212,13 @@
       <c r="A42" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+      <c r="B42" s="7" t="n"/>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="n"/>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="7" t="n"/>
@@ -1226,15 +1226,15 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B43" s="7" t="n"/>
       <c r="C43" s="7" t="n"/>
-      <c r="D43" s="7" t="n"/>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E43" s="7" t="n"/>
       <c r="F43" s="7" t="n"/>
       <c r="G43" s="7" t="n"/>
@@ -1244,13 +1244,13 @@
       <c r="A44" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B44" s="7" t="n"/>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D44" s="7" t="n"/>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="7" t="n"/>
@@ -1262,25 +1262,25 @@
       </c>
       <c r="B45" s="7" t="n"/>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="n"/>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E45" s="7" t="n"/>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F45" s="7" t="n"/>
       <c r="G45" s="7" t="n"/>
       <c r="H45" s="7" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E46" s="7" t="n"/>
@@ -1290,31 +1290,31 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="n"/>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E47" s="7" t="n"/>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F47" s="7" t="n"/>
       <c r="G47" s="7" t="n"/>
       <c r="H47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B48" s="7" t="n"/>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="n"/>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
@@ -1322,31 +1322,31 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B49" s="7" t="n"/>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D49" s="7" t="n"/>
       <c r="E49" s="7" t="n"/>
-      <c r="F49" s="7" t="n"/>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G49" s="7" t="n"/>
       <c r="H49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B50" s="7" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
       <c r="F50" s="7" t="n"/>
       <c r="G50" s="7" t="n"/>
@@ -1354,15 +1354,15 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B51" s="7" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C51" s="7" t="n"/>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
       <c r="F51" s="7" t="n"/>
       <c r="G51" s="7" t="n"/>
@@ -1370,13 +1370,13 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B52" s="7" t="n"/>
       <c r="C52" s="7" t="n"/>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E52" s="7" t="n"/>
@@ -1386,17 +1386,17 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B53" s="7" t="n"/>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="7" t="n"/>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E53" s="7" t="n"/>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F53" s="7" t="n"/>
       <c r="G53" s="7" t="n"/>
       <c r="H53" s="7" t="n"/>
     </row>
@@ -1404,15 +1404,15 @@
       <c r="A54" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
       <c r="D54" s="7" t="n"/>
       <c r="E54" s="7" t="n"/>
-      <c r="F54" s="7" t="n"/>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G54" s="7" t="n"/>
       <c r="H54" s="7" t="n"/>
     </row>
@@ -1436,13 +1436,13 @@
       <c r="A56" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B56" s="7" t="n"/>
       <c r="C56" s="7" t="n"/>
-      <c r="D56" s="7" t="n"/>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="n"/>
@@ -1456,7 +1456,7 @@
       <c r="C57" s="7" t="n"/>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E57" s="7" t="n"/>
@@ -1468,13 +1468,13 @@
       <c r="A58" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+      <c r="B58" s="7" t="n"/>
       <c r="C58" s="7" t="n"/>
-      <c r="D58" s="7" t="n"/>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E58" s="7" t="n"/>
       <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n"/>
@@ -1486,25 +1486,25 @@
       </c>
       <c r="B59" s="7" t="n"/>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
       <c r="F59" s="7" t="n"/>
       <c r="G59" s="7" t="n"/>
-      <c r="H59" s="7" t="n"/>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B60" s="7" t="n"/>
       <c r="C60" s="7" t="n"/>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="E60" s="7" t="n"/>
@@ -1514,15 +1514,15 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B61" s="7" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
       <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
@@ -1530,19 +1530,19 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B62" s="7" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C62" s="7" t="n"/>
       <c r="D62" s="7" t="n"/>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="7" t="n"/>
-      <c r="H62" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C64" s="7" t="n"/>
@@ -1580,13 +1580,13 @@
       <c r="A65" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B65" s="7" t="n"/>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C65" s="7" t="n"/>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D65" s="7" t="n"/>
       <c r="E65" s="7" t="n"/>
       <c r="F65" s="7" t="n"/>
       <c r="G65" s="7" t="n"/>
@@ -1600,7 +1600,7 @@
       <c r="C66" s="7" t="n"/>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E66" s="7" t="n"/>
@@ -1616,7 +1616,7 @@
       <c r="C67" s="7" t="n"/>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E67" s="7" t="n"/>
@@ -1632,7 +1632,7 @@
       <c r="C68" s="7" t="n"/>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E68" s="7" t="n"/>
@@ -1646,13 +1646,13 @@
       </c>
       <c r="B69" s="7" t="n"/>
       <c r="C69" s="7" t="n"/>
-      <c r="D69" s="7" t="n"/>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E69" s="7" t="n"/>
-      <c r="F69" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F69" s="7" t="n"/>
       <c r="G69" s="7" t="n"/>
       <c r="H69" s="7" t="n"/>
     </row>
@@ -1666,7 +1666,7 @@
       <c r="E70" s="7" t="n"/>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>Isaiah Likely</t>
+          <t>Colston Loveland</t>
         </is>
       </c>
       <c r="G70" s="7" t="n"/>
@@ -1680,13 +1680,13 @@
       <c r="C71" s="7" t="n"/>
       <c r="D71" s="7" t="n"/>
       <c r="E71" s="7" t="n"/>
-      <c r="F71" s="7" t="n"/>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G71" s="7" t="n"/>
-      <c r="H71" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H71" s="7" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
@@ -1700,7 +1700,7 @@
       <c r="G72" s="7" t="n"/>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
     </row>
@@ -1716,25 +1716,25 @@
       <c r="G73" s="7" t="n"/>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>Joe Burrow</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B74" s="7" t="n"/>
       <c r="C74" s="7" t="n"/>
       <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
       <c r="F74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
-      <c r="H74" s="7" t="n"/>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C75" s="7" t="n"/>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C76" s="7" t="n"/>
@@ -1772,13 +1772,13 @@
       <c r="A77" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B77" s="7" t="n"/>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
       <c r="C77" s="7" t="n"/>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D77" s="7" t="n"/>
       <c r="E77" s="7" t="n"/>
       <c r="F77" s="7" t="n"/>
       <c r="G77" s="7" t="n"/>
@@ -1802,27 +1802,27 @@
     </row>
     <row r="79">
       <c r="A79" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B79" s="7" t="n"/>
       <c r="C79" s="7" t="n"/>
       <c r="D79" s="7" t="n"/>
       <c r="E79" s="7" t="n"/>
-      <c r="F79" s="7" t="n"/>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G79" s="7" t="n"/>
       <c r="H79" s="7" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C80" s="7" t="n"/>
@@ -1834,15 +1834,15 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>Mike Washington Jr.</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B81" s="7" t="n"/>
       <c r="C81" s="7" t="n"/>
-      <c r="D81" s="7" t="n"/>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>Terry McLaurin</t>
+        </is>
+      </c>
       <c r="E81" s="7" t="n"/>
       <c r="F81" s="7" t="n"/>
       <c r="G81" s="7" t="n"/>
@@ -1850,15 +1850,15 @@
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>Rico Dowdle</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B82" s="7" t="n"/>
       <c r="C82" s="7" t="n"/>
-      <c r="D82" s="7" t="n"/>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E82" s="7" t="n"/>
       <c r="F82" s="7" t="n"/>
       <c r="G82" s="7" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C83" s="7" t="n"/>
@@ -1884,13 +1884,13 @@
       <c r="A84" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B84" s="7" t="n"/>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>Jonathon Brooks</t>
+        </is>
+      </c>
       <c r="C84" s="7" t="n"/>
-      <c r="D84" s="7" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D84" s="7" t="n"/>
       <c r="E84" s="7" t="n"/>
       <c r="F84" s="7" t="n"/>
       <c r="G84" s="7" t="n"/>
@@ -1900,13 +1900,13 @@
       <c r="A85" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B85" s="7" t="n"/>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>Mike Washington Jr.</t>
+        </is>
+      </c>
       <c r="C85" s="7" t="n"/>
-      <c r="D85" s="7" t="inlineStr">
-        <is>
-          <t>KC Concepcion</t>
-        </is>
-      </c>
+      <c r="D85" s="7" t="n"/>
       <c r="E85" s="7" t="n"/>
       <c r="F85" s="7" t="n"/>
       <c r="G85" s="7" t="n"/>
@@ -1916,13 +1916,13 @@
       <c r="A86" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B86" s="7" t="n"/>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>Rico Dowdle</t>
+        </is>
+      </c>
       <c r="C86" s="7" t="n"/>
-      <c r="D86" s="7" t="inlineStr">
-        <is>
-          <t>Quentin Johnston</t>
-        </is>
-      </c>
+      <c r="D86" s="7" t="n"/>
       <c r="E86" s="7" t="n"/>
       <c r="F86" s="7" t="n"/>
       <c r="G86" s="7" t="n"/>
@@ -1936,7 +1936,7 @@
       <c r="C87" s="7" t="n"/>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr.</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E87" s="7" t="n"/>
@@ -1952,7 +1952,7 @@
       <c r="C88" s="7" t="n"/>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E88" s="7" t="n"/>
@@ -1968,7 +1968,7 @@
       <c r="C89" s="7" t="n"/>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E89" s="7" t="n"/>
@@ -1982,13 +1982,13 @@
       </c>
       <c r="B90" s="7" t="n"/>
       <c r="C90" s="7" t="n"/>
-      <c r="D90" s="7" t="n"/>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>KC Concepcion</t>
+        </is>
+      </c>
       <c r="E90" s="7" t="n"/>
-      <c r="F90" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F90" s="7" t="n"/>
       <c r="G90" s="7" t="n"/>
       <c r="H90" s="7" t="n"/>
     </row>
@@ -1998,13 +1998,13 @@
       </c>
       <c r="B91" s="7" t="n"/>
       <c r="C91" s="7" t="n"/>
-      <c r="D91" s="7" t="n"/>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>Quentin Johnston</t>
+        </is>
+      </c>
       <c r="E91" s="7" t="n"/>
-      <c r="F91" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F91" s="7" t="n"/>
       <c r="G91" s="7" t="n"/>
       <c r="H91" s="7" t="n"/>
     </row>
@@ -2014,27 +2014,27 @@
       </c>
       <c r="B92" s="7" t="n"/>
       <c r="C92" s="7" t="n"/>
-      <c r="D92" s="7" t="n"/>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Reed</t>
+        </is>
+      </c>
       <c r="E92" s="7" t="n"/>
       <c r="F92" s="7" t="n"/>
       <c r="G92" s="7" t="n"/>
-      <c r="H92" s="7" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B93" s="7" t="n"/>
       <c r="C93" s="7" t="n"/>
-      <c r="D93" s="7" t="n"/>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>Jordyn Tyson</t>
+        </is>
+      </c>
       <c r="E93" s="7" t="n"/>
       <c r="F93" s="7" t="n"/>
       <c r="G93" s="7" t="n"/>
@@ -2042,47 +2042,47 @@
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B94" s="7" t="n"/>
       <c r="C94" s="7" t="n"/>
       <c r="D94" s="7" t="n"/>
       <c r="E94" s="7" t="n"/>
-      <c r="F94" s="7" t="n"/>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G94" s="7" t="n"/>
       <c r="H94" s="7" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B95" s="7" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B95" s="7" t="n"/>
       <c r="C95" s="7" t="n"/>
       <c r="D95" s="7" t="n"/>
       <c r="E95" s="7" t="n"/>
       <c r="F95" s="7" t="n"/>
       <c r="G95" s="7" t="n"/>
-      <c r="H95" s="7" t="n"/>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B96" s="7" t="n"/>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C96" s="7" t="n"/>
-      <c r="D96" s="7" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D96" s="7" t="n"/>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="7" t="n"/>
       <c r="G96" s="7" t="n"/>
@@ -2092,13 +2092,13 @@
       <c r="A97" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B97" s="7" t="n"/>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C97" s="7" t="n"/>
-      <c r="D97" s="7" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D97" s="7" t="n"/>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="7" t="n"/>
       <c r="G97" s="7" t="n"/>
@@ -2112,7 +2112,7 @@
       <c r="C98" s="7" t="n"/>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E98" s="7" t="n"/>
@@ -2128,7 +2128,7 @@
       <c r="C99" s="7" t="n"/>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E99" s="7" t="n"/>
@@ -2311,7 +2311,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 105 players, top value 77.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 105 players, top value 78.</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 0; 32 players used week 3 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 1; 13 players used week 3 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2349,14 +2349,14 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.6 x (implied - sheet), then rescaled so the total equals the sheet total. 79 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.6 x (implied - sheet), then rescaled so the total equals the sheet total. 85 players moved.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   No projection this week (value kept): Puka Nacua, Josh Jacobs, De'Zhaun Stribling, Jayden Daniels, Jordan Mason, Alec Pierce, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Jaxson Dart, Ja'Kobi Lane.</t>
+          <t xml:space="preserve">   No projection this week (value kept): Josh Jacobs, De'Zhaun Stribling, Jayden Daniels, Jordan Mason, Alec Pierce, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Jaxson Dart, Ja'Kobi Lane.</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2408,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.9, WR 3.1, TE 4.5, QB 0.0.</t>
+          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.8, WR 3.1, TE 4.5, QB 0.0.</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2435,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Puka Nacua 65-&gt;56, Jaxon Smith-Njigba 71-&gt;62, Chris Olave 50-&gt;41, Ja'Marr Chase 64-&gt;56, Amon-Ra St. Brown 63-&gt;55, Justin Jefferson 46-&gt;38, De'Von Achane 41-&gt;33, Drake London 31-&gt;23</t>
+          <t>Largest moves vs. the baseline in this file: Puka Nacua 59-&gt;49, Jaxon Smith-Njigba 68-&gt;58, Ja'Marr Chase 64-&gt;55, Amon-Ra St. Brown 63-&gt;54, De'Von Achane 41-&gt;32, Chris Olave 58-&gt;49, Trey McBride 36-&gt;27, Christian McCaffrey 65-&gt;57</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -618,7 +618,7 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
@@ -634,15 +634,15 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>62</v>
-      </c>
-      <c r="B6" s="7" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="7" t="n"/>
       <c r="G6" s="7" t="n"/>
@@ -654,7 +654,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C7" s="7" t="n"/>
@@ -670,7 +670,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C8" s="7" t="n"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="C9" s="7" t="n"/>
@@ -698,15 +698,15 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>56</v>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="n"/>
@@ -714,13 +714,13 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Puka Nacua</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -730,13 +730,13 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E12" s="7" t="n"/>
@@ -746,15 +746,15 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="B13" s="7" t="n"/>
+        <v>52</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D13" s="7" t="n"/>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
@@ -762,15 +762,15 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
@@ -778,7 +778,7 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
@@ -794,15 +794,15 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
@@ -812,13 +812,13 @@
       <c r="A17" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="B17" s="7" t="n"/>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D17" s="7" t="n"/>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
@@ -826,15 +826,15 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="B18" s="7" t="n"/>
+        <v>40</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
@@ -842,7 +842,7 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
@@ -858,43 +858,43 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>De'Von Achane</t>
-        </is>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
       <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>De'Von Achane</t>
         </is>
       </c>
       <c r="C22" s="7" t="n"/>
@@ -906,15 +906,15 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
@@ -922,11 +922,11 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C24" s="7" t="n"/>
@@ -938,31 +938,31 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
@@ -970,31 +970,31 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D27" s="7" t="n"/>
       <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G27" s="7" t="n"/>
       <c r="H27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="B28" s="7" t="n"/>
+        <v>27</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D28" s="7" t="n"/>
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="7" t="n"/>
@@ -1004,13 +1004,13 @@
       <c r="A29" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="B29" s="7" t="n"/>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D29" s="7" t="n"/>
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="7" t="n"/>
@@ -1018,11 +1018,11 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="C30" s="7" t="n"/>
@@ -1034,27 +1034,27 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
       <c r="D31" s="7" t="n"/>
       <c r="E31" s="7" t="n"/>
-      <c r="F31" s="7" t="n"/>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G31" s="7" t="n"/>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C32" s="7" t="n"/>
@@ -1066,15 +1066,15 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="B33" s="7" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D33" s="7" t="n"/>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
@@ -1082,31 +1082,31 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
       <c r="D34" s="7" t="n"/>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="n"/>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="B35" s="7" t="n"/>
+        <v>24</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C35" s="7" t="n"/>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D35" s="7" t="n"/>
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="7" t="n"/>
@@ -1114,13 +1114,13 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E36" s="7" t="n"/>
@@ -1130,13 +1130,13 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E37" s="7" t="n"/>
@@ -1148,13 +1148,13 @@
       <c r="A38" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+      <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="n"/>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E38" s="7" t="n"/>
       <c r="F38" s="7" t="n"/>
       <c r="G38" s="7" t="n"/>
@@ -1162,15 +1162,15 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
-      <c r="D39" s="7" t="n"/>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E39" s="7" t="n"/>
       <c r="F39" s="7" t="n"/>
       <c r="G39" s="7" t="n"/>
@@ -1178,13 +1178,13 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E40" s="7" t="n"/>
@@ -1194,15 +1194,15 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="B41" s="7" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D41" s="7" t="n"/>
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="7" t="n"/>
@@ -1212,13 +1212,13 @@
       <c r="A42" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+      <c r="B42" s="7" t="n"/>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="n"/>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="7" t="n"/>
@@ -1226,11 +1226,11 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C43" s="7" t="n"/>
@@ -1242,13 +1242,13 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="n"/>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E44" s="7" t="n"/>
@@ -1258,23 +1258,23 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B45" s="7" t="n"/>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="n"/>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E45" s="7" t="n"/>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F45" s="7" t="n"/>
       <c r="G45" s="7" t="n"/>
       <c r="H45" s="7" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
@@ -1290,31 +1290,31 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="B47" s="7" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C47" s="7" t="n"/>
       <c r="D47" s="7" t="n"/>
       <c r="E47" s="7" t="n"/>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F47" s="7" t="n"/>
       <c r="G47" s="7" t="n"/>
       <c r="H47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B48" s="7" t="n"/>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="n"/>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
@@ -1338,15 +1338,15 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B50" s="7" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
       <c r="F50" s="7" t="n"/>
       <c r="G50" s="7" t="n"/>
@@ -1356,13 +1356,13 @@
       <c r="A51" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B51" s="7" t="n"/>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C51" s="7" t="n"/>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
       <c r="F51" s="7" t="n"/>
       <c r="G51" s="7" t="n"/>
@@ -1376,7 +1376,7 @@
       <c r="C52" s="7" t="n"/>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E52" s="7" t="n"/>
@@ -1386,17 +1386,17 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B53" s="7" t="n"/>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="7" t="n"/>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E53" s="7" t="n"/>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F53" s="7" t="n"/>
       <c r="G53" s="7" t="n"/>
       <c r="H53" s="7" t="n"/>
     </row>
@@ -1404,15 +1404,15 @@
       <c r="A54" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
       <c r="D54" s="7" t="n"/>
       <c r="E54" s="7" t="n"/>
-      <c r="F54" s="7" t="n"/>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G54" s="7" t="n"/>
       <c r="H54" s="7" t="n"/>
     </row>
@@ -1454,59 +1454,59 @@
       </c>
       <c r="B57" s="7" t="n"/>
       <c r="C57" s="7" t="n"/>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
-      <c r="F57" s="7" t="n"/>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G57" s="7" t="n"/>
       <c r="H57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B58" s="7" t="n"/>
       <c r="C58" s="7" t="n"/>
       <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
-      <c r="F58" s="7" t="n"/>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B59" s="7" t="n"/>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
       <c r="F59" s="7" t="n"/>
       <c r="G59" s="7" t="n"/>
-      <c r="H59" s="7" t="n"/>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B60" s="7" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C60" s="7" t="n"/>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D60" s="7" t="n"/>
       <c r="E60" s="7" t="n"/>
       <c r="F60" s="7" t="n"/>
       <c r="G60" s="7" t="n"/>
@@ -1514,15 +1514,15 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B61" s="7" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
       <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
@@ -1530,31 +1530,31 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B62" s="7" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C62" s="7" t="n"/>
       <c r="D62" s="7" t="n"/>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="7" t="n"/>
-      <c r="H62" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B63" s="7" t="n"/>
       <c r="C63" s="7" t="n"/>
-      <c r="D63" s="7" t="n"/>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E63" s="7" t="n"/>
       <c r="F63" s="7" t="n"/>
       <c r="G63" s="7" t="n"/>
@@ -1562,15 +1562,15 @@
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B64" s="7" t="n"/>
       <c r="C64" s="7" t="n"/>
-      <c r="D64" s="7" t="n"/>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E64" s="7" t="n"/>
       <c r="F64" s="7" t="n"/>
       <c r="G64" s="7" t="n"/>
@@ -1578,13 +1578,13 @@
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B65" s="7" t="n"/>
       <c r="C65" s="7" t="n"/>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E65" s="7" t="n"/>
@@ -1594,81 +1594,81 @@
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B66" s="7" t="n"/>
       <c r="C66" s="7" t="n"/>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>Jameson Williams</t>
-        </is>
-      </c>
+      <c r="D66" s="7" t="n"/>
       <c r="E66" s="7" t="n"/>
-      <c r="F66" s="7" t="n"/>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G66" s="7" t="n"/>
       <c r="H66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B67" s="7" t="n"/>
       <c r="C67" s="7" t="n"/>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>De'Zhaun Stribling</t>
-        </is>
-      </c>
+      <c r="D67" s="7" t="n"/>
       <c r="E67" s="7" t="n"/>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
-      <c r="H67" s="7" t="n"/>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B68" s="7" t="n"/>
       <c r="C68" s="7" t="n"/>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D68" s="7" t="n"/>
       <c r="E68" s="7" t="n"/>
       <c r="F68" s="7" t="n"/>
       <c r="G68" s="7" t="n"/>
-      <c r="H68" s="7" t="n"/>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B69" s="7" t="n"/>
       <c r="C69" s="7" t="n"/>
       <c r="D69" s="7" t="n"/>
       <c r="E69" s="7" t="n"/>
-      <c r="F69" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F69" s="7" t="n"/>
       <c r="G69" s="7" t="n"/>
-      <c r="H69" s="7" t="n"/>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B70" s="7" t="n"/>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C70" s="7" t="n"/>
       <c r="D70" s="7" t="n"/>
       <c r="E70" s="7" t="n"/>
-      <c r="F70" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F70" s="7" t="n"/>
       <c r="G70" s="7" t="n"/>
       <c r="H70" s="7" t="n"/>
     </row>
@@ -1676,49 +1676,49 @@
       <c r="A71" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B71" s="7" t="n"/>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
       <c r="C71" s="7" t="n"/>
       <c r="D71" s="7" t="n"/>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
-      <c r="H71" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H71" s="7" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B72" s="7" t="n"/>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>J.K. Dobbins</t>
+        </is>
+      </c>
       <c r="C72" s="7" t="n"/>
       <c r="D72" s="7" t="n"/>
       <c r="E72" s="7" t="n"/>
       <c r="F72" s="7" t="n"/>
       <c r="G72" s="7" t="n"/>
-      <c r="H72" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H72" s="7" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B73" s="7" t="n"/>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C73" s="7" t="n"/>
       <c r="D73" s="7" t="n"/>
       <c r="E73" s="7" t="n"/>
       <c r="F73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
-      <c r="H73" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C74" s="7" t="n"/>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C75" s="7" t="n"/>
@@ -1756,13 +1756,13 @@
       <c r="A76" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+      <c r="B76" s="7" t="n"/>
       <c r="C76" s="7" t="n"/>
-      <c r="D76" s="7" t="n"/>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E76" s="7" t="n"/>
       <c r="F76" s="7" t="n"/>
       <c r="G76" s="7" t="n"/>
@@ -1776,7 +1776,7 @@
       <c r="C77" s="7" t="n"/>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E77" s="7" t="n"/>
@@ -1792,7 +1792,7 @@
       <c r="C78" s="7" t="n"/>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E78" s="7" t="n"/>
@@ -1802,15 +1802,15 @@
     </row>
     <row r="79">
       <c r="A79" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B79" s="7" t="n"/>
       <c r="C79" s="7" t="n"/>
-      <c r="D79" s="7" t="n"/>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>Marvin Harrison Jr.</t>
+        </is>
+      </c>
       <c r="E79" s="7" t="n"/>
       <c r="F79" s="7" t="n"/>
       <c r="G79" s="7" t="n"/>
@@ -1818,43 +1818,43 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>Jonathon Brooks</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B80" s="7" t="n"/>
       <c r="C80" s="7" t="n"/>
       <c r="D80" s="7" t="n"/>
       <c r="E80" s="7" t="n"/>
-      <c r="F80" s="7" t="n"/>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G80" s="7" t="n"/>
       <c r="H80" s="7" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>Mike Washington Jr.</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B81" s="7" t="n"/>
       <c r="C81" s="7" t="n"/>
       <c r="D81" s="7" t="n"/>
       <c r="E81" s="7" t="n"/>
-      <c r="F81" s="7" t="n"/>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G81" s="7" t="n"/>
       <c r="H81" s="7" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C82" s="7" t="n"/>
@@ -1866,11 +1866,11 @@
     </row>
     <row r="83">
       <c r="A83" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C83" s="7" t="n"/>
@@ -1882,15 +1882,15 @@
     </row>
     <row r="84">
       <c r="A84" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B84" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>Rico Dowdle</t>
+        </is>
+      </c>
       <c r="C84" s="7" t="n"/>
-      <c r="D84" s="7" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D84" s="7" t="n"/>
       <c r="E84" s="7" t="n"/>
       <c r="F84" s="7" t="n"/>
       <c r="G84" s="7" t="n"/>
@@ -1898,13 +1898,13 @@
     </row>
     <row r="85">
       <c r="A85" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B85" s="7" t="n"/>
       <c r="C85" s="7" t="n"/>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E85" s="7" t="n"/>
@@ -1914,13 +1914,13 @@
     </row>
     <row r="86">
       <c r="A86" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B86" s="7" t="n"/>
       <c r="C86" s="7" t="n"/>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E86" s="7" t="n"/>
@@ -1930,13 +1930,13 @@
     </row>
     <row r="87">
       <c r="A87" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B87" s="7" t="n"/>
       <c r="C87" s="7" t="n"/>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr.</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E87" s="7" t="n"/>
@@ -1946,13 +1946,13 @@
     </row>
     <row r="88">
       <c r="A88" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B88" s="7" t="n"/>
       <c r="C88" s="7" t="n"/>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E88" s="7" t="n"/>
@@ -1962,13 +1962,13 @@
     </row>
     <row r="89">
       <c r="A89" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B89" s="7" t="n"/>
       <c r="C89" s="7" t="n"/>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E89" s="7" t="n"/>
@@ -1978,33 +1978,33 @@
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B90" s="7" t="n"/>
       <c r="C90" s="7" t="n"/>
       <c r="D90" s="7" t="n"/>
       <c r="E90" s="7" t="n"/>
-      <c r="F90" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F90" s="7" t="n"/>
       <c r="G90" s="7" t="n"/>
-      <c r="H90" s="7" t="n"/>
+      <c r="H90" s="7" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B91" s="7" t="n"/>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C91" s="7" t="n"/>
       <c r="D91" s="7" t="n"/>
       <c r="E91" s="7" t="n"/>
-      <c r="F91" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F91" s="7" t="n"/>
       <c r="G91" s="7" t="n"/>
       <c r="H91" s="7" t="n"/>
     </row>
@@ -2012,29 +2012,29 @@
       <c r="A92" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B92" s="7" t="n"/>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C92" s="7" t="n"/>
       <c r="D92" s="7" t="n"/>
       <c r="E92" s="7" t="n"/>
       <c r="F92" s="7" t="n"/>
       <c r="G92" s="7" t="n"/>
-      <c r="H92" s="7" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B93" s="7" t="n"/>
       <c r="C93" s="7" t="n"/>
-      <c r="D93" s="7" t="n"/>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E93" s="7" t="n"/>
       <c r="F93" s="7" t="n"/>
       <c r="G93" s="7" t="n"/>
@@ -2042,15 +2042,15 @@
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B94" s="7" t="n"/>
       <c r="C94" s="7" t="n"/>
-      <c r="D94" s="7" t="n"/>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="7" t="n"/>
       <c r="G94" s="7" t="n"/>
@@ -2058,15 +2058,15 @@
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B95" s="7" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B95" s="7" t="n"/>
       <c r="C95" s="7" t="n"/>
-      <c r="D95" s="7" t="n"/>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>Chris Godwin Jr.</t>
+        </is>
+      </c>
       <c r="E95" s="7" t="n"/>
       <c r="F95" s="7" t="n"/>
       <c r="G95" s="7" t="n"/>
@@ -2074,13 +2074,13 @@
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B96" s="7" t="n"/>
       <c r="C96" s="7" t="n"/>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Ja'Kobi Lane</t>
         </is>
       </c>
       <c r="E96" s="7" t="n"/>
@@ -2090,51 +2090,51 @@
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B97" s="7" t="n"/>
       <c r="C97" s="7" t="n"/>
-      <c r="D97" s="7" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D97" s="7" t="n"/>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="7" t="n"/>
       <c r="G97" s="7" t="n"/>
-      <c r="H97" s="7" t="n"/>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>Jalen Hurts</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B98" s="7" t="n"/>
       <c r="C98" s="7" t="n"/>
-      <c r="D98" s="7" t="inlineStr">
-        <is>
-          <t>Brian Thomas Jr.</t>
-        </is>
-      </c>
+      <c r="D98" s="7" t="n"/>
       <c r="E98" s="7" t="n"/>
       <c r="F98" s="7" t="n"/>
       <c r="G98" s="7" t="n"/>
-      <c r="H98" s="7" t="n"/>
+      <c r="H98" s="7" t="inlineStr">
+        <is>
+          <t>Justin Herbert</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B99" s="7" t="n"/>
       <c r="C99" s="7" t="n"/>
-      <c r="D99" s="7" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D99" s="7" t="n"/>
       <c r="E99" s="7" t="n"/>
       <c r="F99" s="7" t="n"/>
       <c r="G99" s="7" t="n"/>
-      <c r="H99" s="7" t="n"/>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
@@ -2144,7 +2144,7 @@
       <c r="C100" s="7" t="n"/>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E100" s="7" t="n"/>
@@ -2154,63 +2154,63 @@
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B101" s="7" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C101" s="7" t="n"/>
       <c r="D101" s="7" t="n"/>
       <c r="E101" s="7" t="n"/>
       <c r="F101" s="7" t="n"/>
       <c r="G101" s="7" t="n"/>
-      <c r="H101" s="7" t="inlineStr">
-        <is>
-          <t>Jalen Hurts</t>
-        </is>
-      </c>
+      <c r="H101" s="7" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B102" s="7" t="n"/>
       <c r="C102" s="7" t="n"/>
-      <c r="D102" s="7" t="n"/>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
       <c r="E102" s="7" t="n"/>
       <c r="F102" s="7" t="n"/>
       <c r="G102" s="7" t="n"/>
-      <c r="H102" s="7" t="inlineStr">
-        <is>
-          <t>Justin Herbert</t>
-        </is>
-      </c>
+      <c r="H102" s="7" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B103" s="7" t="n"/>
       <c r="C103" s="7" t="n"/>
-      <c r="D103" s="7" t="n"/>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>KC Concepcion</t>
+        </is>
+      </c>
       <c r="E103" s="7" t="n"/>
       <c r="F103" s="7" t="n"/>
       <c r="G103" s="7" t="n"/>
-      <c r="H103" s="7" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H103" s="7" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B104" s="7" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+      <c r="B104" s="7" t="n"/>
       <c r="C104" s="7" t="n"/>
-      <c r="D104" s="7" t="n"/>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Reed</t>
+        </is>
+      </c>
       <c r="E104" s="7" t="n"/>
       <c r="F104" s="7" t="n"/>
       <c r="G104" s="7" t="n"/>
@@ -2224,7 +2224,7 @@
       <c r="C105" s="7" t="n"/>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E105" s="7" t="n"/>
@@ -2234,15 +2234,15 @@
     </row>
     <row r="106">
       <c r="A106" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B106" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>Kenny Gainwell</t>
+        </is>
+      </c>
       <c r="C106" s="7" t="n"/>
-      <c r="D106" s="7" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
+      <c r="D106" s="7" t="n"/>
       <c r="E106" s="7" t="n"/>
       <c r="F106" s="7" t="n"/>
       <c r="G106" s="7" t="n"/>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>Kenny Gainwell</t>
+          <t>Rachaad White</t>
         </is>
       </c>
       <c r="C107" s="7" t="n"/>
@@ -2268,13 +2268,13 @@
       <c r="A108" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B108" s="7" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
+      <c r="B108" s="7" t="n"/>
       <c r="C108" s="7" t="n"/>
-      <c r="D108" s="7" t="n"/>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E108" s="7" t="n"/>
       <c r="F108" s="7" t="n"/>
       <c r="G108" s="7" t="n"/>
@@ -2311,7 +2311,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 105 players, top value 77.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 105 players, top value 76.</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 0; 32 players used week 3 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 1; 13 players used week 3 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2349,14 +2349,14 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.6 x (implied - sheet), then rescaled so the total equals the sheet total. 79 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 83 players moved.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   No projection this week (value kept): Puka Nacua, Josh Jacobs, De'Zhaun Stribling, Jayden Daniels, Jordan Mason, Alec Pierce, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Jaxson Dart, Ja'Kobi Lane.</t>
+          <t xml:space="preserve">   No projection this week (value kept): Josh Jacobs, De'Zhaun Stribling, Jayden Daniels, Jordan Mason, Alec Pierce, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Jaxson Dart, Ja'Kobi Lane.</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2408,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.9, WR 3.1, TE 4.5, QB 0.0.</t>
+          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.8, WR 2.9, TE 4.5, QB 0.0.</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2435,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Puka Nacua 65-&gt;56, Jaxon Smith-Njigba 71-&gt;62, Chris Olave 50-&gt;41, Ja'Marr Chase 64-&gt;56, Amon-Ra St. Brown 63-&gt;55, Justin Jefferson 46-&gt;38, De'Von Achane 41-&gt;33, Drake London 31-&gt;23</t>
+          <t>Largest moves vs. the baseline in this file: Puka Nacua 60-&gt;51, Jaxon Smith-Njigba 66-&gt;57, Amon-Ra St. Brown 62-&gt;54, De'Von Achane 41-&gt;33, Chris Olave 54-&gt;46, Trey McBride 34-&gt;26, Ja'Marr Chase 64-&gt;57, Justin Jefferson 47-&gt;40</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -512,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H108"/>
+  <dimension ref="A1:H107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -682,7 +682,7 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
@@ -826,31 +826,31 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="n"/>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="B19" s="7" t="n"/>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
@@ -858,13 +858,13 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>CeeDee Lamb</t>
+          <t>Justin Jefferson</t>
         </is>
       </c>
       <c r="E20" s="7" t="n"/>
@@ -874,31 +874,31 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>De'Von Achane</t>
-        </is>
-      </c>
+      <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
@@ -910,13 +910,13 @@
       </c>
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G23" s="7" t="n"/>
       <c r="H23" s="7" t="n"/>
     </row>
@@ -938,17 +938,17 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
     </row>
@@ -960,7 +960,7 @@
       <c r="C26" s="7" t="n"/>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Nico Collins</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E26" s="7" t="n"/>
@@ -974,13 +974,13 @@
       </c>
       <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
       <c r="H27" s="7" t="n"/>
     </row>
@@ -1034,17 +1034,17 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="B31" s="7" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C31" s="7" t="n"/>
       <c r="D31" s="7" t="n"/>
       <c r="E31" s="7" t="n"/>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F31" s="7" t="n"/>
       <c r="G31" s="7" t="n"/>
       <c r="H31" s="7" t="n"/>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="C32" s="7" t="n"/>
@@ -1068,45 +1068,45 @@
       <c r="A33" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+      <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
       <c r="D33" s="7" t="n"/>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
-      <c r="H33" s="7" t="n"/>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="B34" s="7" t="n"/>
+        <v>24</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C34" s="7" t="n"/>
       <c r="D34" s="7" t="n"/>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
-      <c r="D35" s="7" t="n"/>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="7" t="n"/>
@@ -1114,13 +1114,13 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E36" s="7" t="n"/>
@@ -1136,7 +1136,7 @@
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E37" s="7" t="n"/>
@@ -1146,13 +1146,13 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E38" s="7" t="n"/>
@@ -1168,7 +1168,7 @@
       <c r="C39" s="7" t="n"/>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E39" s="7" t="n"/>
@@ -1178,15 +1178,15 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="B40" s="7" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D40" s="7" t="n"/>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
@@ -1196,13 +1196,13 @@
       <c r="A41" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+      <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="n"/>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="7" t="n"/>
@@ -1210,15 +1210,15 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="B42" s="7" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D42" s="7" t="n"/>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="7" t="n"/>
@@ -1228,13 +1228,13 @@
       <c r="A43" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B43" s="7" t="n"/>
       <c r="C43" s="7" t="n"/>
-      <c r="D43" s="7" t="n"/>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E43" s="7" t="n"/>
       <c r="F43" s="7" t="n"/>
       <c r="G43" s="7" t="n"/>
@@ -1248,7 +1248,7 @@
       <c r="C44" s="7" t="n"/>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E44" s="7" t="n"/>
@@ -1258,13 +1258,13 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B45" s="7" t="n"/>
       <c r="C45" s="7" t="n"/>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E45" s="7" t="n"/>
@@ -1274,15 +1274,15 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B46" s="7" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D46" s="7" t="n"/>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="7" t="n"/>
@@ -1292,13 +1292,13 @@
       <c r="A47" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+      <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="n"/>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E47" s="7" t="n"/>
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="7" t="n"/>
@@ -1306,13 +1306,13 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B48" s="7" t="n"/>
       <c r="C48" s="7" t="n"/>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E48" s="7" t="n"/>
@@ -1322,15 +1322,15 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B49" s="7" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D49" s="7" t="n"/>
       <c r="E49" s="7" t="n"/>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n"/>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="C50" s="7" t="n"/>
@@ -1356,13 +1356,13 @@
       <c r="A51" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B51" s="7" t="n"/>
       <c r="C51" s="7" t="n"/>
-      <c r="D51" s="7" t="n"/>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E51" s="7" t="n"/>
       <c r="F51" s="7" t="n"/>
       <c r="G51" s="7" t="n"/>
@@ -1370,13 +1370,13 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B52" s="7" t="n"/>
       <c r="C52" s="7" t="n"/>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E52" s="7" t="n"/>
@@ -1390,29 +1390,29 @@
       </c>
       <c r="B53" s="7" t="n"/>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D53" s="7" t="n"/>
       <c r="E53" s="7" t="n"/>
-      <c r="F53" s="7" t="n"/>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G53" s="7" t="n"/>
       <c r="H53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B54" s="7" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C54" s="7" t="n"/>
       <c r="D54" s="7" t="n"/>
       <c r="E54" s="7" t="n"/>
-      <c r="F54" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F54" s="7" t="n"/>
       <c r="G54" s="7" t="n"/>
       <c r="H54" s="7" t="n"/>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Jadarian Price</t>
         </is>
       </c>
       <c r="C55" s="7" t="n"/>
@@ -1436,15 +1436,15 @@
       <c r="A56" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B56" s="7" t="n"/>
       <c r="C56" s="7" t="n"/>
       <c r="D56" s="7" t="n"/>
       <c r="E56" s="7" t="n"/>
-      <c r="F56" s="7" t="n"/>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G56" s="7" t="n"/>
       <c r="H56" s="7" t="n"/>
     </row>
@@ -1458,7 +1458,7 @@
       <c r="E57" s="7" t="n"/>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Colston Loveland</t>
+          <t>George Kittle</t>
         </is>
       </c>
       <c r="G57" s="7" t="n"/>
@@ -1466,35 +1466,35 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B58" s="7" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C58" s="7" t="n"/>
       <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B59" s="7" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C59" s="7" t="n"/>
       <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
       <c r="F59" s="7" t="n"/>
       <c r="G59" s="7" t="n"/>
-      <c r="H59" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H59" s="7" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C60" s="7" t="n"/>
@@ -1516,13 +1516,13 @@
       <c r="A61" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+      <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="n"/>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E61" s="7" t="n"/>
       <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
@@ -1532,13 +1532,13 @@
       <c r="A62" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B62" s="7" t="n"/>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="n"/>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="7" t="n"/>
@@ -1552,7 +1552,7 @@
       <c r="C63" s="7" t="n"/>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E63" s="7" t="n"/>
@@ -1566,13 +1566,13 @@
       </c>
       <c r="B64" s="7" t="n"/>
       <c r="C64" s="7" t="n"/>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D64" s="7" t="n"/>
       <c r="E64" s="7" t="n"/>
-      <c r="F64" s="7" t="n"/>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G64" s="7" t="n"/>
       <c r="H64" s="7" t="n"/>
     </row>
@@ -1582,15 +1582,15 @@
       </c>
       <c r="B65" s="7" t="n"/>
       <c r="C65" s="7" t="n"/>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D65" s="7" t="n"/>
       <c r="E65" s="7" t="n"/>
       <c r="F65" s="7" t="n"/>
       <c r="G65" s="7" t="n"/>
-      <c r="H65" s="7" t="n"/>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
@@ -1600,13 +1600,13 @@
       <c r="C66" s="7" t="n"/>
       <c r="D66" s="7" t="n"/>
       <c r="E66" s="7" t="n"/>
-      <c r="F66" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F66" s="7" t="n"/>
       <c r="G66" s="7" t="n"/>
-      <c r="H66" s="7" t="n"/>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
@@ -1620,7 +1620,7 @@
       <c r="G67" s="7" t="n"/>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>Joe Burrow</t>
+          <t>Drake Maye</t>
         </is>
       </c>
     </row>
@@ -1636,25 +1636,25 @@
       <c r="G68" s="7" t="n"/>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B69" s="7" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C69" s="7" t="n"/>
       <c r="D69" s="7" t="n"/>
       <c r="E69" s="7" t="n"/>
       <c r="F69" s="7" t="n"/>
       <c r="G69" s="7" t="n"/>
-      <c r="H69" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C70" s="7" t="n"/>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C71" s="7" t="n"/>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="C72" s="7" t="n"/>
@@ -1706,11 +1706,11 @@
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C73" s="7" t="n"/>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr.</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C74" s="7" t="n"/>
@@ -1740,13 +1740,13 @@
       <c r="A75" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+      <c r="B75" s="7" t="n"/>
       <c r="C75" s="7" t="n"/>
-      <c r="D75" s="7" t="n"/>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E75" s="7" t="n"/>
       <c r="F75" s="7" t="n"/>
       <c r="G75" s="7" t="n"/>
@@ -1760,7 +1760,7 @@
       <c r="C76" s="7" t="n"/>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E76" s="7" t="n"/>
@@ -1776,7 +1776,7 @@
       <c r="C77" s="7" t="n"/>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E77" s="7" t="n"/>
@@ -1792,7 +1792,7 @@
       <c r="C78" s="7" t="n"/>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E78" s="7" t="n"/>
@@ -1806,13 +1806,13 @@
       </c>
       <c r="B79" s="7" t="n"/>
       <c r="C79" s="7" t="n"/>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D79" s="7" t="n"/>
       <c r="E79" s="7" t="n"/>
-      <c r="F79" s="7" t="n"/>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G79" s="7" t="n"/>
       <c r="H79" s="7" t="n"/>
     </row>
@@ -1826,7 +1826,7 @@
       <c r="E80" s="7" t="n"/>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>Harold Fannin Jr.</t>
         </is>
       </c>
       <c r="G80" s="7" t="n"/>
@@ -1834,17 +1834,17 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B81" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>Jonathon Brooks</t>
+        </is>
+      </c>
       <c r="C81" s="7" t="n"/>
       <c r="D81" s="7" t="n"/>
       <c r="E81" s="7" t="n"/>
-      <c r="F81" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F81" s="7" t="n"/>
       <c r="G81" s="7" t="n"/>
       <c r="H81" s="7" t="n"/>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C82" s="7" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C83" s="7" t="n"/>
@@ -1884,13 +1884,13 @@
       <c r="A84" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>Rico Dowdle</t>
-        </is>
-      </c>
+      <c r="B84" s="7" t="n"/>
       <c r="C84" s="7" t="n"/>
-      <c r="D84" s="7" t="n"/>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E84" s="7" t="n"/>
       <c r="F84" s="7" t="n"/>
       <c r="G84" s="7" t="n"/>
@@ -1904,7 +1904,7 @@
       <c r="C85" s="7" t="n"/>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E85" s="7" t="n"/>
@@ -1920,7 +1920,7 @@
       <c r="C86" s="7" t="n"/>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E86" s="7" t="n"/>
@@ -1936,7 +1936,7 @@
       <c r="C87" s="7" t="n"/>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E87" s="7" t="n"/>
@@ -1952,7 +1952,7 @@
       <c r="C88" s="7" t="n"/>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E88" s="7" t="n"/>
@@ -1966,43 +1966,43 @@
       </c>
       <c r="B89" s="7" t="n"/>
       <c r="C89" s="7" t="n"/>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>Quentin Johnston</t>
-        </is>
-      </c>
+      <c r="D89" s="7" t="n"/>
       <c r="E89" s="7" t="n"/>
       <c r="F89" s="7" t="n"/>
       <c r="G89" s="7" t="n"/>
-      <c r="H89" s="7" t="n"/>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B90" s="7" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C90" s="7" t="n"/>
       <c r="D90" s="7" t="n"/>
       <c r="E90" s="7" t="n"/>
       <c r="F90" s="7" t="n"/>
       <c r="G90" s="7" t="n"/>
-      <c r="H90" s="7" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H90" s="7" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B91" s="7" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+      <c r="B91" s="7" t="n"/>
       <c r="C91" s="7" t="n"/>
-      <c r="D91" s="7" t="n"/>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E91" s="7" t="n"/>
       <c r="F91" s="7" t="n"/>
       <c r="G91" s="7" t="n"/>
@@ -2012,13 +2012,13 @@
       <c r="A92" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+      <c r="B92" s="7" t="n"/>
       <c r="C92" s="7" t="n"/>
-      <c r="D92" s="7" t="n"/>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E92" s="7" t="n"/>
       <c r="F92" s="7" t="n"/>
       <c r="G92" s="7" t="n"/>
@@ -2032,7 +2032,7 @@
       <c r="C93" s="7" t="n"/>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E93" s="7" t="n"/>
@@ -2046,15 +2046,15 @@
       </c>
       <c r="B94" s="7" t="n"/>
       <c r="C94" s="7" t="n"/>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D94" s="7" t="n"/>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="7" t="n"/>
       <c r="G94" s="7" t="n"/>
-      <c r="H94" s="7" t="n"/>
+      <c r="H94" s="7" t="inlineStr">
+        <is>
+          <t>Jalen Hurts</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
@@ -2062,27 +2062,27 @@
       </c>
       <c r="B95" s="7" t="n"/>
       <c r="C95" s="7" t="n"/>
-      <c r="D95" s="7" t="inlineStr">
-        <is>
-          <t>Chris Godwin Jr.</t>
-        </is>
-      </c>
+      <c r="D95" s="7" t="n"/>
       <c r="E95" s="7" t="n"/>
       <c r="F95" s="7" t="n"/>
       <c r="G95" s="7" t="n"/>
-      <c r="H95" s="7" t="n"/>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>Justin Herbert</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B96" s="7" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C96" s="7" t="n"/>
-      <c r="D96" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
+      <c r="D96" s="7" t="n"/>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="7" t="n"/>
       <c r="G96" s="7" t="n"/>
@@ -2090,39 +2090,39 @@
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B97" s="7" t="n"/>
       <c r="C97" s="7" t="n"/>
-      <c r="D97" s="7" t="n"/>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>Carnell Tate</t>
+        </is>
+      </c>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="7" t="n"/>
       <c r="G97" s="7" t="n"/>
-      <c r="H97" s="7" t="inlineStr">
-        <is>
-          <t>Jalen Hurts</t>
-        </is>
-      </c>
+      <c r="H97" s="7" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B98" s="7" t="n"/>
       <c r="C98" s="7" t="n"/>
-      <c r="D98" s="7" t="n"/>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E98" s="7" t="n"/>
       <c r="F98" s="7" t="n"/>
       <c r="G98" s="7" t="n"/>
-      <c r="H98" s="7" t="inlineStr">
-        <is>
-          <t>Justin Herbert</t>
-        </is>
-      </c>
+      <c r="H98" s="7" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B99" s="7" t="n"/>
       <c r="C99" s="7" t="n"/>
@@ -2138,15 +2138,15 @@
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B100" s="7" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C100" s="7" t="n"/>
-      <c r="D100" s="7" t="inlineStr">
-        <is>
-          <t>Carnell Tate</t>
-        </is>
-      </c>
+      <c r="D100" s="7" t="n"/>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="7" t="n"/>
       <c r="G100" s="7" t="n"/>
@@ -2156,13 +2156,13 @@
       <c r="A101" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B101" s="7" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+      <c r="B101" s="7" t="n"/>
       <c r="C101" s="7" t="n"/>
-      <c r="D101" s="7" t="n"/>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
       <c r="E101" s="7" t="n"/>
       <c r="F101" s="7" t="n"/>
       <c r="G101" s="7" t="n"/>
@@ -2176,7 +2176,7 @@
       <c r="C102" s="7" t="n"/>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E102" s="7" t="n"/>
@@ -2192,7 +2192,7 @@
       <c r="C103" s="7" t="n"/>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E103" s="7" t="n"/>
@@ -2208,7 +2208,7 @@
       <c r="C104" s="7" t="n"/>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E104" s="7" t="n"/>
@@ -2218,15 +2218,15 @@
     </row>
     <row r="105">
       <c r="A105" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B105" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>Kenny Gainwell</t>
+        </is>
+      </c>
       <c r="C105" s="7" t="n"/>
-      <c r="D105" s="7" t="inlineStr">
-        <is>
-          <t>Jordyn Tyson</t>
-        </is>
-      </c>
+      <c r="D105" s="7" t="n"/>
       <c r="E105" s="7" t="n"/>
       <c r="F105" s="7" t="n"/>
       <c r="G105" s="7" t="n"/>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>Kenny Gainwell</t>
+          <t>Rachaad White</t>
         </is>
       </c>
       <c r="C106" s="7" t="n"/>
@@ -2252,33 +2252,17 @@
       <c r="A107" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B107" s="7" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
+      <c r="B107" s="7" t="n"/>
       <c r="C107" s="7" t="n"/>
-      <c r="D107" s="7" t="n"/>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E107" s="7" t="n"/>
       <c r="F107" s="7" t="n"/>
       <c r="G107" s="7" t="n"/>
       <c r="H107" s="7" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B108" s="7" t="n"/>
-      <c r="C108" s="7" t="n"/>
-      <c r="D108" s="7" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
-      <c r="E108" s="7" t="n"/>
-      <c r="F108" s="7" t="n"/>
-      <c r="G108" s="7" t="n"/>
-      <c r="H108" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2311,7 +2295,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 105 players, top value 76.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 76.</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 1; 13 players used week 3 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 1; 12 players used week 3 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2333,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 83 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 81 players moved.</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Puka Nacua 60-&gt;51, Jaxon Smith-Njigba 66-&gt;57, Amon-Ra St. Brown 62-&gt;54, De'Von Achane 41-&gt;33, Chris Olave 54-&gt;46, Trey McBride 34-&gt;26, Ja'Marr Chase 64-&gt;57, Justin Jefferson 47-&gt;40</t>
+          <t>Largest moves vs. the baseline in this file: Puka Nacua 60-&gt;51, Jaxon Smith-Njigba 66-&gt;57, Amon-Ra St. Brown 62-&gt;54, Chris Olave 54-&gt;46, Trey McBride 41-&gt;33, Ja'Marr Chase 64-&gt;57, Justin Jefferson 47-&gt;40, CeeDee Lamb 45-&gt;38</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -810,35 +810,35 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>43</v>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="n"/>
       <c r="D17" s="7" t="n"/>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="n"/>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="B18" s="7" t="n"/>
+        <v>43</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
@@ -890,17 +890,17 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
     </row>
@@ -910,45 +910,45 @@
       </c>
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
       <c r="H23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="B25" s="7" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
     </row>
@@ -2333,7 +2333,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 81 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 83 players moved.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Puka Nacua 60-&gt;51, Jaxon Smith-Njigba 66-&gt;57, Amon-Ra St. Brown 62-&gt;54, Chris Olave 54-&gt;46, Trey McBride 41-&gt;33, Ja'Marr Chase 64-&gt;57, Justin Jefferson 47-&gt;40, CeeDee Lamb 45-&gt;38</t>
+          <t>Largest moves vs. the baseline in this file: Puka Nacua 60-&gt;51, Jaxon Smith-Njigba 66-&gt;57, Amon-Ra St. Brown 62-&gt;54, Chris Olave 54-&gt;46, Trey McBride 43.4286-&gt;36, Ja'Marr Chase 64-&gt;57, Justin Jefferson 47-&gt;40, CeeDee Lamb 45-&gt;38</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -634,11 +634,11 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C6" s="7" t="n"/>
@@ -654,7 +654,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C7" s="7" t="n"/>
@@ -670,7 +670,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="C8" s="7" t="n"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C9" s="7" t="n"/>
@@ -730,15 +730,15 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="B12" s="7" t="n"/>
+        <v>56</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D12" s="7" t="n"/>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="n"/>
@@ -746,15 +746,15 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>52</v>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
@@ -762,7 +762,7 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
@@ -778,15 +778,15 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="B15" s="7" t="n"/>
       <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E15" s="7" t="n"/>
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="7" t="n"/>
@@ -794,43 +794,43 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D16" s="7" t="n"/>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="B17" s="7" t="n"/>
+        <v>43</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C17" s="7" t="n"/>
       <c r="D17" s="7" t="n"/>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Saquon Barkley</t>
+          <t>Ashton Jeanty</t>
         </is>
       </c>
       <c r="C18" s="7" t="n"/>
@@ -844,13 +844,13 @@
       <c r="A19" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+      <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
@@ -858,13 +858,13 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Justin Jefferson</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="E20" s="7" t="n"/>
@@ -874,39 +874,39 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n"/>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G21" s="7" t="n"/>
       <c r="H21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="B22" s="7" t="n"/>
+        <v>35</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C22" s="7" t="n"/>
       <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
@@ -924,43 +924,43 @@
       <c r="A24" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="B24" s="7" t="n"/>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Nico Collins</t>
         </is>
       </c>
       <c r="E26" s="7" t="n"/>
@@ -970,15 +970,15 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="B27" s="7" t="n"/>
+        <v>29</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D27" s="7" t="n"/>
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
@@ -986,7 +986,7 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
@@ -1002,15 +1002,15 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="7" t="n"/>
@@ -1018,11 +1018,11 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="C30" s="7" t="n"/>
@@ -1034,11 +1034,11 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C31" s="7" t="n"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="C32" s="7" t="n"/>
@@ -1066,31 +1066,31 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="B33" s="7" t="n"/>
+        <v>24</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C33" s="7" t="n"/>
       <c r="D33" s="7" t="n"/>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+      <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="n"/>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="7" t="n"/>
@@ -1098,23 +1098,23 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D35" s="7" t="n"/>
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="7" t="n"/>
-      <c r="H35" s="7" t="n"/>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
@@ -1162,15 +1162,15 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="B39" s="7" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C39" s="7" t="n"/>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D39" s="7" t="n"/>
       <c r="E39" s="7" t="n"/>
       <c r="F39" s="7" t="n"/>
       <c r="G39" s="7" t="n"/>
@@ -1178,15 +1178,15 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="n"/>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
@@ -1194,13 +1194,13 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E41" s="7" t="n"/>
@@ -1210,11 +1210,11 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C42" s="7" t="n"/>
@@ -1226,13 +1226,13 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B43" s="7" t="n"/>
       <c r="C43" s="7" t="n"/>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E43" s="7" t="n"/>
@@ -1242,15 +1242,15 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="B44" s="7" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D44" s="7" t="n"/>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="7" t="n"/>
@@ -1276,13 +1276,13 @@
       <c r="A46" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+      <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="n"/>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="7" t="n"/>
@@ -1290,13 +1290,13 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="n"/>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E47" s="7" t="n"/>
@@ -1306,15 +1306,15 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B48" s="7" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D48" s="7" t="n"/>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="C49" s="7" t="n"/>
@@ -1340,13 +1340,13 @@
       <c r="A50" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B50" s="7" t="n"/>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="n"/>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E50" s="7" t="n"/>
       <c r="F50" s="7" t="n"/>
       <c r="G50" s="7" t="n"/>
@@ -1360,7 +1360,7 @@
       <c r="C51" s="7" t="n"/>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E51" s="7" t="n"/>
@@ -1370,19 +1370,19 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B52" s="7" t="n"/>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D52" s="7" t="n"/>
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="7" t="n"/>
-      <c r="H52" s="7" t="n"/>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
@@ -1390,13 +1390,13 @@
       </c>
       <c r="B53" s="7" t="n"/>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="7" t="n"/>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E53" s="7" t="n"/>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F53" s="7" t="n"/>
       <c r="G53" s="7" t="n"/>
       <c r="H53" s="7" t="n"/>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Jadarian Price</t>
         </is>
       </c>
       <c r="C54" s="7" t="n"/>
@@ -1420,15 +1420,15 @@
       <c r="A55" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B55" s="7" t="n"/>
       <c r="C55" s="7" t="n"/>
       <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7" t="n"/>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G55" s="7" t="n"/>
       <c r="H55" s="7" t="n"/>
     </row>
@@ -1466,11 +1466,11 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C58" s="7" t="n"/>
@@ -1482,17 +1482,17 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B59" s="7" t="n"/>
       <c r="C59" s="7" t="n"/>
       <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
-      <c r="F59" s="7" t="n"/>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G59" s="7" t="n"/>
       <c r="H59" s="7" t="n"/>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C60" s="7" t="n"/>
@@ -1516,13 +1516,13 @@
       <c r="A61" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B61" s="7" t="n"/>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
       <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
@@ -1532,13 +1532,13 @@
       <c r="A62" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B62" s="7" t="n"/>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D62" s="7" t="n"/>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="7" t="n"/>
@@ -1552,7 +1552,7 @@
       <c r="C63" s="7" t="n"/>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E63" s="7" t="n"/>
@@ -1566,13 +1566,13 @@
       </c>
       <c r="B64" s="7" t="n"/>
       <c r="C64" s="7" t="n"/>
-      <c r="D64" s="7" t="n"/>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E64" s="7" t="n"/>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F64" s="7" t="n"/>
       <c r="G64" s="7" t="n"/>
       <c r="H64" s="7" t="n"/>
     </row>
@@ -1582,15 +1582,15 @@
       </c>
       <c r="B65" s="7" t="n"/>
       <c r="C65" s="7" t="n"/>
-      <c r="D65" s="7" t="n"/>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E65" s="7" t="n"/>
       <c r="F65" s="7" t="n"/>
       <c r="G65" s="7" t="n"/>
-      <c r="H65" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H65" s="7" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
@@ -1620,7 +1620,7 @@
       <c r="G67" s="7" t="n"/>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>Drake Maye</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       <c r="G68" s="7" t="n"/>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Drake Maye</t>
         </is>
       </c>
     </row>
@@ -1706,15 +1706,15 @@
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B73" s="7" t="n"/>
       <c r="C73" s="7" t="n"/>
-      <c r="D73" s="7" t="n"/>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E73" s="7" t="n"/>
       <c r="F73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C74" s="7" t="n"/>
@@ -1740,13 +1740,13 @@
       <c r="A75" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B75" s="7" t="n"/>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C75" s="7" t="n"/>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D75" s="7" t="n"/>
       <c r="E75" s="7" t="n"/>
       <c r="F75" s="7" t="n"/>
       <c r="G75" s="7" t="n"/>
@@ -1776,7 +1776,7 @@
       <c r="C77" s="7" t="n"/>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E77" s="7" t="n"/>
@@ -1790,45 +1790,45 @@
       </c>
       <c r="B78" s="7" t="n"/>
       <c r="C78" s="7" t="n"/>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D78" s="7" t="n"/>
       <c r="E78" s="7" t="n"/>
-      <c r="F78" s="7" t="n"/>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G78" s="7" t="n"/>
       <c r="H78" s="7" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B79" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>Jonathon Brooks</t>
+        </is>
+      </c>
       <c r="C79" s="7" t="n"/>
       <c r="D79" s="7" t="n"/>
       <c r="E79" s="7" t="n"/>
-      <c r="F79" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F79" s="7" t="n"/>
       <c r="G79" s="7" t="n"/>
       <c r="H79" s="7" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B80" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>Mike Washington Jr.</t>
+        </is>
+      </c>
       <c r="C80" s="7" t="n"/>
       <c r="D80" s="7" t="n"/>
       <c r="E80" s="7" t="n"/>
-      <c r="F80" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F80" s="7" t="n"/>
       <c r="G80" s="7" t="n"/>
       <c r="H80" s="7" t="n"/>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C81" s="7" t="n"/>
@@ -1852,13 +1852,13 @@
       <c r="A82" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>Mike Washington Jr.</t>
-        </is>
-      </c>
+      <c r="B82" s="7" t="n"/>
       <c r="C82" s="7" t="n"/>
-      <c r="D82" s="7" t="n"/>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E82" s="7" t="n"/>
       <c r="F82" s="7" t="n"/>
       <c r="G82" s="7" t="n"/>
@@ -1868,13 +1868,13 @@
       <c r="A83" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>Rico Dowdle</t>
-        </is>
-      </c>
+      <c r="B83" s="7" t="n"/>
       <c r="C83" s="7" t="n"/>
-      <c r="D83" s="7" t="n"/>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>Terry McLaurin</t>
+        </is>
+      </c>
       <c r="E83" s="7" t="n"/>
       <c r="F83" s="7" t="n"/>
       <c r="G83" s="7" t="n"/>
@@ -1888,7 +1888,7 @@
       <c r="C84" s="7" t="n"/>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E84" s="7" t="n"/>
@@ -1904,7 +1904,7 @@
       <c r="C85" s="7" t="n"/>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E85" s="7" t="n"/>
@@ -1920,7 +1920,7 @@
       <c r="C86" s="7" t="n"/>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E86" s="7" t="n"/>
@@ -1936,7 +1936,7 @@
       <c r="C87" s="7" t="n"/>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E87" s="7" t="n"/>
@@ -1952,7 +1952,7 @@
       <c r="C88" s="7" t="n"/>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E88" s="7" t="n"/>
@@ -1968,41 +1968,41 @@
       <c r="C89" s="7" t="n"/>
       <c r="D89" s="7" t="n"/>
       <c r="E89" s="7" t="n"/>
-      <c r="F89" s="7" t="n"/>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G89" s="7" t="n"/>
-      <c r="H89" s="7" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H89" s="7" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B90" s="7" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B90" s="7" t="n"/>
       <c r="C90" s="7" t="n"/>
       <c r="D90" s="7" t="n"/>
       <c r="E90" s="7" t="n"/>
       <c r="F90" s="7" t="n"/>
       <c r="G90" s="7" t="n"/>
-      <c r="H90" s="7" t="n"/>
+      <c r="H90" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B91" s="7" t="n"/>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C91" s="7" t="n"/>
-      <c r="D91" s="7" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D91" s="7" t="n"/>
       <c r="E91" s="7" t="n"/>
       <c r="F91" s="7" t="n"/>
       <c r="G91" s="7" t="n"/>
@@ -2030,15 +2030,15 @@
       </c>
       <c r="B93" s="7" t="n"/>
       <c r="C93" s="7" t="n"/>
-      <c r="D93" s="7" t="inlineStr">
-        <is>
-          <t>Chris Godwin Jr.</t>
-        </is>
-      </c>
+      <c r="D93" s="7" t="n"/>
       <c r="E93" s="7" t="n"/>
       <c r="F93" s="7" t="n"/>
       <c r="G93" s="7" t="n"/>
-      <c r="H93" s="7" t="n"/>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>Jalen Hurts</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
@@ -2052,25 +2052,25 @@
       <c r="G94" s="7" t="n"/>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B95" s="7" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C95" s="7" t="n"/>
       <c r="D95" s="7" t="n"/>
       <c r="E95" s="7" t="n"/>
       <c r="F95" s="7" t="n"/>
       <c r="G95" s="7" t="n"/>
-      <c r="H95" s="7" t="inlineStr">
-        <is>
-          <t>Justin Herbert</t>
-        </is>
-      </c>
+      <c r="H95" s="7" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
@@ -2096,7 +2096,7 @@
       <c r="C97" s="7" t="n"/>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E97" s="7" t="n"/>
@@ -2112,7 +2112,7 @@
       <c r="C98" s="7" t="n"/>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E98" s="7" t="n"/>
@@ -2126,31 +2126,31 @@
       </c>
       <c r="B99" s="7" t="n"/>
       <c r="C99" s="7" t="n"/>
-      <c r="D99" s="7" t="n"/>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E99" s="7" t="n"/>
       <c r="F99" s="7" t="n"/>
       <c r="G99" s="7" t="n"/>
-      <c r="H99" s="7" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B100" s="7" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B100" s="7" t="n"/>
       <c r="C100" s="7" t="n"/>
       <c r="D100" s="7" t="n"/>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="7" t="n"/>
       <c r="G100" s="7" t="n"/>
-      <c r="H100" s="7" t="n"/>
+      <c r="H100" s="7" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 1; 12 players used week 3 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 2; 9 players used week 3 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 83 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 82 players moved.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Puka Nacua 60-&gt;51, Jaxon Smith-Njigba 66-&gt;57, Amon-Ra St. Brown 62-&gt;54, Chris Olave 54-&gt;46, Trey McBride 43.4286-&gt;36, Ja'Marr Chase 64-&gt;57, Justin Jefferson 47-&gt;40, CeeDee Lamb 45-&gt;38</t>
+          <t>Largest moves vs. the baseline in this file: Puka Nacua 61-&gt;52, Jaxon Smith-Njigba 66-&gt;57, Chris Olave 55-&gt;47, Trey McBride 43.4286-&gt;36, Ja'Marr Chase 64-&gt;57, Amon-Ra St. Brown 63-&gt;56, Justin Jefferson 47-&gt;40, CeeDee Lamb 45-&gt;38</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -618,7 +618,7 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C6" s="7" t="n"/>
@@ -654,7 +654,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C7" s="7" t="n"/>
@@ -666,15 +666,15 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B8" s="7" t="n"/>
       <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="7" t="n"/>
@@ -700,13 +700,13 @@
       <c r="A10" s="6" t="n">
         <v>57</v>
       </c>
-      <c r="B10" s="7" t="n"/>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="n"/>
@@ -720,7 +720,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -732,13 +732,13 @@
       <c r="A12" s="6" t="n">
         <v>56</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+      <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="n"/>
@@ -746,15 +746,15 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>56</v>
-      </c>
-      <c r="B13" s="7" t="n"/>
+        <v>54</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D13" s="7" t="n"/>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
@@ -778,7 +778,7 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15" s="7" t="n"/>
       <c r="C15" s="7" t="n"/>
@@ -826,7 +826,7 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
@@ -878,43 +878,43 @@
       </c>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
       <c r="H21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
       <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="B23" s="7" t="n"/>
+        <v>35</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
@@ -954,15 +954,15 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="B26" s="7" t="n"/>
+        <v>31</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
@@ -970,15 +970,15 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
@@ -1002,15 +1002,15 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="7" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D29" s="7" t="n"/>
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="7" t="n"/>
@@ -1018,11 +1018,11 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="C30" s="7" t="n"/>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="C31" s="7" t="n"/>
@@ -1050,15 +1050,15 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C39" s="7" t="n"/>
@@ -1196,13 +1196,13 @@
       <c r="A41" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B41" s="7" t="n"/>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D41" s="7" t="n"/>
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="7" t="n"/>
@@ -1210,15 +1210,15 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B42" s="7" t="n"/>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="n"/>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="7" t="n"/>
@@ -1290,7 +1290,7 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="n"/>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="C48" s="7" t="n"/>
@@ -1324,13 +1324,13 @@
       <c r="A49" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B49" s="7" t="n"/>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="n"/>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E49" s="7" t="n"/>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n"/>
@@ -1344,7 +1344,7 @@
       <c r="C50" s="7" t="n"/>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E50" s="7" t="n"/>
@@ -1354,15 +1354,15 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B51" s="7" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C51" s="7" t="n"/>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
       <c r="F51" s="7" t="n"/>
       <c r="G51" s="7" t="n"/>
@@ -1370,19 +1370,19 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B52" s="7" t="n"/>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="7" t="n"/>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="7" t="n"/>
-      <c r="H52" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
@@ -1390,45 +1390,45 @@
       </c>
       <c r="B53" s="7" t="n"/>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D53" s="7" t="n"/>
       <c r="E53" s="7" t="n"/>
-      <c r="F53" s="7" t="n"/>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G53" s="7" t="n"/>
       <c r="H53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
       <c r="D54" s="7" t="n"/>
       <c r="E54" s="7" t="n"/>
       <c r="F54" s="7" t="n"/>
       <c r="G54" s="7" t="n"/>
-      <c r="H54" s="7" t="n"/>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B55" s="7" t="n"/>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C55" s="7" t="n"/>
       <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F55" s="7" t="n"/>
       <c r="G55" s="7" t="n"/>
       <c r="H55" s="7" t="n"/>
     </row>
@@ -1482,17 +1482,17 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B59" s="7" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C59" s="7" t="n"/>
       <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F59" s="7" t="n"/>
       <c r="G59" s="7" t="n"/>
       <c r="H59" s="7" t="n"/>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C60" s="7" t="n"/>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C61" s="7" t="n"/>
@@ -1532,13 +1532,13 @@
       <c r="A62" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B62" s="7" t="n"/>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="n"/>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="7" t="n"/>
@@ -1552,7 +1552,7 @@
       <c r="C63" s="7" t="n"/>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="E63" s="7" t="n"/>
@@ -1568,7 +1568,7 @@
       <c r="C64" s="7" t="n"/>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E64" s="7" t="n"/>
@@ -1582,13 +1582,13 @@
       </c>
       <c r="B65" s="7" t="n"/>
       <c r="C65" s="7" t="n"/>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D65" s="7" t="n"/>
       <c r="E65" s="7" t="n"/>
-      <c r="F65" s="7" t="n"/>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G65" s="7" t="n"/>
       <c r="H65" s="7" t="n"/>
     </row>
@@ -1722,17 +1722,17 @@
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B74" s="7" t="n"/>
       <c r="C74" s="7" t="n"/>
       <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
-      <c r="F74" s="7" t="n"/>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G74" s="7" t="n"/>
       <c r="H74" s="7" t="n"/>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C75" s="7" t="n"/>
@@ -1756,13 +1756,13 @@
       <c r="A76" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B76" s="7" t="n"/>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C76" s="7" t="n"/>
-      <c r="D76" s="7" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D76" s="7" t="n"/>
       <c r="E76" s="7" t="n"/>
       <c r="F76" s="7" t="n"/>
       <c r="G76" s="7" t="n"/>
@@ -1776,7 +1776,7 @@
       <c r="C77" s="7" t="n"/>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E77" s="7" t="n"/>
@@ -1790,13 +1790,13 @@
       </c>
       <c r="B78" s="7" t="n"/>
       <c r="C78" s="7" t="n"/>
-      <c r="D78" s="7" t="n"/>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>Marvin Harrison Jr.</t>
+        </is>
+      </c>
       <c r="E78" s="7" t="n"/>
-      <c r="F78" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F78" s="7" t="n"/>
       <c r="G78" s="7" t="n"/>
       <c r="H78" s="7" t="n"/>
     </row>
@@ -1988,7 +1988,7 @@
       <c r="G90" s="7" t="n"/>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       <c r="G93" s="7" t="n"/>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       <c r="G94" s="7" t="n"/>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="C95" s="7" t="n"/>
@@ -2076,13 +2076,13 @@
       <c r="A96" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B96" s="7" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+      <c r="B96" s="7" t="n"/>
       <c r="C96" s="7" t="n"/>
-      <c r="D96" s="7" t="n"/>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="7" t="n"/>
       <c r="G96" s="7" t="n"/>
@@ -2096,7 +2096,7 @@
       <c r="C97" s="7" t="n"/>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E97" s="7" t="n"/>
@@ -2112,7 +2112,7 @@
       <c r="C98" s="7" t="n"/>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Ja'Kobi Lane</t>
         </is>
       </c>
       <c r="E98" s="7" t="n"/>
@@ -2126,31 +2126,31 @@
       </c>
       <c r="B99" s="7" t="n"/>
       <c r="C99" s="7" t="n"/>
-      <c r="D99" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
+      <c r="D99" s="7" t="n"/>
       <c r="E99" s="7" t="n"/>
       <c r="F99" s="7" t="n"/>
       <c r="G99" s="7" t="n"/>
-      <c r="H99" s="7" t="n"/>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B100" s="7" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C100" s="7" t="n"/>
       <c r="D100" s="7" t="n"/>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="7" t="n"/>
       <c r="G100" s="7" t="n"/>
-      <c r="H100" s="7" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H100" s="7" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
@@ -2160,7 +2160,7 @@
       <c r="C101" s="7" t="n"/>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E101" s="7" t="n"/>
@@ -2176,7 +2176,7 @@
       <c r="C102" s="7" t="n"/>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E102" s="7" t="n"/>
@@ -2192,7 +2192,7 @@
       <c r="C103" s="7" t="n"/>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E103" s="7" t="n"/>
@@ -2202,15 +2202,15 @@
     </row>
     <row r="104">
       <c r="A104" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B104" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>Kenny Gainwell</t>
+        </is>
+      </c>
       <c r="C104" s="7" t="n"/>
-      <c r="D104" s="7" t="inlineStr">
-        <is>
-          <t>Jordyn Tyson</t>
-        </is>
-      </c>
+      <c r="D104" s="7" t="n"/>
       <c r="E104" s="7" t="n"/>
       <c r="F104" s="7" t="n"/>
       <c r="G104" s="7" t="n"/>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>Kenny Gainwell</t>
+          <t>Rachaad White</t>
         </is>
       </c>
       <c r="C105" s="7" t="n"/>
@@ -2236,13 +2236,13 @@
       <c r="A106" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B106" s="7" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
+      <c r="B106" s="7" t="n"/>
       <c r="C106" s="7" t="n"/>
-      <c r="D106" s="7" t="n"/>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
       <c r="E106" s="7" t="n"/>
       <c r="F106" s="7" t="n"/>
       <c r="G106" s="7" t="n"/>
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 2; 9 players used week 3 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 3; 9 players used week 3 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 82 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 78 players moved.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Puka Nacua 61-&gt;52, Jaxon Smith-Njigba 66-&gt;57, Chris Olave 55-&gt;47, Trey McBride 43.4286-&gt;36, Ja'Marr Chase 64-&gt;57, Amon-Ra St. Brown 63-&gt;56, Justin Jefferson 47-&gt;40, CeeDee Lamb 45-&gt;38</t>
+          <t>Largest moves vs. the baseline in this file: Puka Nacua 61-&gt;52, Jaxon Smith-Njigba 66-&gt;57, Chris Olave 54-&gt;46, Trey McBride 43.4286-&gt;36, Ja'Marr Chase 65-&gt;58, Amon-Ra St. Brown 63-&gt;56, Justin Jefferson 47-&gt;40, CeeDee Lamb 45-&gt;38</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -634,11 +634,11 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C6" s="7" t="n"/>
@@ -650,11 +650,11 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C7" s="7" t="n"/>
@@ -666,7 +666,7 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B8" s="7" t="n"/>
       <c r="C8" s="7" t="n"/>
@@ -682,15 +682,15 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B9" s="7" t="n"/>
       <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="7" t="n"/>
@@ -698,11 +698,11 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C10" s="7" t="n"/>
@@ -714,15 +714,15 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="B11" s="7" t="n"/>
+        <v>56</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D11" s="7" t="n"/>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
@@ -746,7 +746,7 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
@@ -778,7 +778,7 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B15" s="7" t="n"/>
       <c r="C15" s="7" t="n"/>
@@ -814,7 +814,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C17" s="7" t="n"/>
@@ -826,7 +826,7 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
@@ -842,15 +842,15 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="B19" s="7" t="n"/>
+        <v>41</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
@@ -858,13 +858,13 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>CeeDee Lamb</t>
+          <t>Justin Jefferson</t>
         </is>
       </c>
       <c r="E20" s="7" t="n"/>
@@ -874,13 +874,13 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="E21" s="7" t="n"/>
@@ -892,29 +892,29 @@
       <c r="A22" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="B22" s="7" t="n"/>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C22" s="7" t="n"/>
       <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
@@ -922,17 +922,17 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
     </row>
@@ -954,11 +954,11 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C26" s="7" t="n"/>
@@ -1002,11 +1002,11 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="C29" s="7" t="n"/>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C30" s="7" t="n"/>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="C31" s="7" t="n"/>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
@@ -1120,7 +1120,7 @@
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E36" s="7" t="n"/>
@@ -1130,13 +1130,13 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E37" s="7" t="n"/>
@@ -1146,15 +1146,15 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="B38" s="7" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D38" s="7" t="n"/>
       <c r="E38" s="7" t="n"/>
       <c r="F38" s="7" t="n"/>
       <c r="G38" s="7" t="n"/>
@@ -1162,11 +1162,11 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C39" s="7" t="n"/>
@@ -1194,15 +1194,15 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="n"/>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="7" t="n"/>
@@ -1216,7 +1216,7 @@
       <c r="C42" s="7" t="n"/>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E42" s="7" t="n"/>
@@ -1242,15 +1242,15 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="n"/>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="7" t="n"/>
@@ -1260,13 +1260,13 @@
       <c r="A45" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B45" s="7" t="n"/>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D45" s="7" t="n"/>
       <c r="E45" s="7" t="n"/>
       <c r="F45" s="7" t="n"/>
       <c r="G45" s="7" t="n"/>
@@ -1290,7 +1290,7 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="n"/>
@@ -1306,15 +1306,15 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B48" s="7" t="n"/>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="n"/>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
@@ -1324,13 +1324,13 @@
       <c r="A49" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B49" s="7" t="n"/>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D49" s="7" t="n"/>
       <c r="E49" s="7" t="n"/>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n"/>
@@ -1344,7 +1344,7 @@
       <c r="C50" s="7" t="n"/>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E50" s="7" t="n"/>
@@ -1354,17 +1354,17 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B51" s="7" t="n"/>
       <c r="C51" s="7" t="n"/>
       <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
-      <c r="F51" s="7" t="n"/>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G51" s="7" t="n"/>
       <c r="H51" s="7" t="n"/>
     </row>
@@ -1372,13 +1372,13 @@
       <c r="A52" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B52" s="7" t="n"/>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D52" s="7" t="n"/>
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="7" t="n"/>
@@ -1388,15 +1388,15 @@
       <c r="A53" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B53" s="7" t="n"/>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C53" s="7" t="n"/>
       <c r="D53" s="7" t="n"/>
       <c r="E53" s="7" t="n"/>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F53" s="7" t="n"/>
       <c r="G53" s="7" t="n"/>
       <c r="H53" s="7" t="n"/>
     </row>
@@ -1406,31 +1406,31 @@
       </c>
       <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
-      <c r="D54" s="7" t="n"/>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E54" s="7" t="n"/>
       <c r="F54" s="7" t="n"/>
       <c r="G54" s="7" t="n"/>
-      <c r="H54" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B55" s="7" t="n"/>
       <c r="C55" s="7" t="n"/>
       <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
       <c r="F55" s="7" t="n"/>
       <c r="G55" s="7" t="n"/>
-      <c r="H55" s="7" t="n"/>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
@@ -1482,15 +1482,15 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B59" s="7" t="n"/>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="7" t="n"/>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E59" s="7" t="n"/>
       <c r="F59" s="7" t="n"/>
       <c r="G59" s="7" t="n"/>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C60" s="7" t="n"/>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C61" s="7" t="n"/>
@@ -1532,13 +1532,13 @@
       <c r="A62" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B62" s="7" t="n"/>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D62" s="7" t="n"/>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="7" t="n"/>
@@ -1548,13 +1548,13 @@
       <c r="A63" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B63" s="7" t="n"/>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C63" s="7" t="n"/>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D63" s="7" t="n"/>
       <c r="E63" s="7" t="n"/>
       <c r="F63" s="7" t="n"/>
       <c r="G63" s="7" t="n"/>
@@ -1568,7 +1568,7 @@
       <c r="C64" s="7" t="n"/>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="E64" s="7" t="n"/>
@@ -1582,13 +1582,13 @@
       </c>
       <c r="B65" s="7" t="n"/>
       <c r="C65" s="7" t="n"/>
-      <c r="D65" s="7" t="n"/>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E65" s="7" t="n"/>
-      <c r="F65" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F65" s="7" t="n"/>
       <c r="G65" s="7" t="n"/>
       <c r="H65" s="7" t="n"/>
     </row>
@@ -1600,13 +1600,13 @@
       <c r="C66" s="7" t="n"/>
       <c r="D66" s="7" t="n"/>
       <c r="E66" s="7" t="n"/>
-      <c r="F66" s="7" t="n"/>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G66" s="7" t="n"/>
-      <c r="H66" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
@@ -1620,7 +1620,7 @@
       <c r="G67" s="7" t="n"/>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
     </row>
@@ -1636,25 +1636,25 @@
       <c r="G68" s="7" t="n"/>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>Drake Maye</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B69" s="7" t="n"/>
       <c r="C69" s="7" t="n"/>
       <c r="D69" s="7" t="n"/>
       <c r="E69" s="7" t="n"/>
       <c r="F69" s="7" t="n"/>
       <c r="G69" s="7" t="n"/>
-      <c r="H69" s="7" t="n"/>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
@@ -1988,7 +1988,7 @@
       <c r="G90" s="7" t="n"/>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
     </row>
@@ -2012,13 +2012,13 @@
       <c r="A92" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B92" s="7" t="n"/>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C92" s="7" t="n"/>
-      <c r="D92" s="7" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D92" s="7" t="n"/>
       <c r="E92" s="7" t="n"/>
       <c r="F92" s="7" t="n"/>
       <c r="G92" s="7" t="n"/>
@@ -2030,15 +2030,15 @@
       </c>
       <c r="B93" s="7" t="n"/>
       <c r="C93" s="7" t="n"/>
-      <c r="D93" s="7" t="n"/>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E93" s="7" t="n"/>
       <c r="F93" s="7" t="n"/>
       <c r="G93" s="7" t="n"/>
-      <c r="H93" s="7" t="inlineStr">
-        <is>
-          <t>Justin Herbert</t>
-        </is>
-      </c>
+      <c r="H93" s="7" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
@@ -2046,75 +2046,75 @@
       </c>
       <c r="B94" s="7" t="n"/>
       <c r="C94" s="7" t="n"/>
-      <c r="D94" s="7" t="n"/>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="7" t="n"/>
       <c r="G94" s="7" t="n"/>
-      <c r="H94" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H94" s="7" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B95" s="7" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B95" s="7" t="n"/>
       <c r="C95" s="7" t="n"/>
       <c r="D95" s="7" t="n"/>
       <c r="E95" s="7" t="n"/>
       <c r="F95" s="7" t="n"/>
       <c r="G95" s="7" t="n"/>
-      <c r="H95" s="7" t="n"/>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>Jalen Hurts</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B96" s="7" t="n"/>
       <c r="C96" s="7" t="n"/>
-      <c r="D96" s="7" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D96" s="7" t="n"/>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="7" t="n"/>
       <c r="G96" s="7" t="n"/>
-      <c r="H96" s="7" t="n"/>
+      <c r="H96" s="7" t="inlineStr">
+        <is>
+          <t>Justin Herbert</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B97" s="7" t="n"/>
       <c r="C97" s="7" t="n"/>
-      <c r="D97" s="7" t="inlineStr">
-        <is>
-          <t>Carnell Tate</t>
-        </is>
-      </c>
+      <c r="D97" s="7" t="n"/>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="7" t="n"/>
       <c r="G97" s="7" t="n"/>
-      <c r="H97" s="7" t="n"/>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B98" s="7" t="n"/>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C98" s="7" t="n"/>
-      <c r="D98" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
+      <c r="D98" s="7" t="n"/>
       <c r="E98" s="7" t="n"/>
       <c r="F98" s="7" t="n"/>
       <c r="G98" s="7" t="n"/>
@@ -2126,27 +2126,27 @@
       </c>
       <c r="B99" s="7" t="n"/>
       <c r="C99" s="7" t="n"/>
-      <c r="D99" s="7" t="n"/>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E99" s="7" t="n"/>
       <c r="F99" s="7" t="n"/>
       <c r="G99" s="7" t="n"/>
-      <c r="H99" s="7" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B100" s="7" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B100" s="7" t="n"/>
       <c r="C100" s="7" t="n"/>
-      <c r="D100" s="7" t="n"/>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>Carnell Tate</t>
+        </is>
+      </c>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="7" t="n"/>
       <c r="G100" s="7" t="n"/>
@@ -2160,7 +2160,7 @@
       <c r="C101" s="7" t="n"/>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E101" s="7" t="n"/>
@@ -2176,7 +2176,7 @@
       <c r="C102" s="7" t="n"/>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E102" s="7" t="n"/>
@@ -2192,7 +2192,7 @@
       <c r="C103" s="7" t="n"/>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E103" s="7" t="n"/>
@@ -2202,15 +2202,15 @@
     </row>
     <row r="104">
       <c r="A104" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B104" s="7" t="inlineStr">
-        <is>
-          <t>Kenny Gainwell</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B104" s="7" t="n"/>
       <c r="C104" s="7" t="n"/>
-      <c r="D104" s="7" t="n"/>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>Jordyn Tyson</t>
+        </is>
+      </c>
       <c r="E104" s="7" t="n"/>
       <c r="F104" s="7" t="n"/>
       <c r="G104" s="7" t="n"/>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>Rachaad White</t>
+          <t>Kenny Gainwell</t>
         </is>
       </c>
       <c r="C105" s="7" t="n"/>
@@ -2236,13 +2236,13 @@
       <c r="A106" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B106" s="7" t="n"/>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>Rachaad White</t>
+        </is>
+      </c>
       <c r="C106" s="7" t="n"/>
-      <c r="D106" s="7" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
+      <c r="D106" s="7" t="n"/>
       <c r="E106" s="7" t="n"/>
       <c r="F106" s="7" t="n"/>
       <c r="G106" s="7" t="n"/>
@@ -2295,7 +2295,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 76.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 75.</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 3; 9 players used week 3 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 4; 9 players used week 3 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 78 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 81 players moved.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Puka Nacua 61-&gt;52, Jaxon Smith-Njigba 66-&gt;57, Chris Olave 54-&gt;46, Trey McBride 43.4286-&gt;36, Ja'Marr Chase 65-&gt;58, Amon-Ra St. Brown 63-&gt;56, Justin Jefferson 47-&gt;40, CeeDee Lamb 45-&gt;38</t>
+          <t>Largest moves vs. the baseline in this file: Puka Nacua 61-&gt;53, Jaxon Smith-Njigba 67-&gt;59, Chris Olave 53-&gt;45, Trey McBride 42.8571-&gt;35, Amon-Ra St. Brown 63-&gt;56, Justin Jefferson 47-&gt;40, CeeDee Lamb 45-&gt;38, Drake London 43-&gt;36</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -618,7 +618,7 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
@@ -634,11 +634,11 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C6" s="7" t="n"/>
@@ -650,11 +650,11 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C7" s="7" t="n"/>
@@ -666,7 +666,7 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B8" s="7" t="n"/>
       <c r="C8" s="7" t="n"/>
@@ -684,13 +684,13 @@
       <c r="A9" s="6" t="n">
         <v>59</v>
       </c>
-      <c r="B9" s="7" t="n"/>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D9" s="7" t="n"/>
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="7" t="n"/>
@@ -698,15 +698,15 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="n"/>
@@ -714,11 +714,11 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C11" s="7" t="n"/>
@@ -730,7 +730,7 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
@@ -762,7 +762,7 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
@@ -810,11 +810,11 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Ashton Jeanty</t>
         </is>
       </c>
       <c r="C17" s="7" t="n"/>
@@ -826,15 +826,15 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
@@ -842,7 +842,7 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
@@ -858,15 +858,15 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="B20" s="7" t="n"/>
+        <v>39</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
@@ -890,15 +890,15 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
@@ -910,29 +910,29 @@
       </c>
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G23" s="7" t="n"/>
       <c r="H23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="B24" s="7" t="n"/>
+        <v>34</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
     </row>
@@ -940,31 +940,31 @@
       <c r="A25" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="B25" s="7" t="n"/>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
       <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="7" t="n"/>
     </row>
@@ -988,13 +988,13 @@
       <c r="A28" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+      <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="7" t="n"/>
@@ -1050,15 +1050,15 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="B32" s="7" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
@@ -1066,11 +1066,11 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C33" s="7" t="n"/>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
@@ -1136,7 +1136,7 @@
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E37" s="7" t="n"/>
@@ -1146,15 +1146,15 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="n"/>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E38" s="7" t="n"/>
       <c r="F38" s="7" t="n"/>
       <c r="G38" s="7" t="n"/>
@@ -1162,11 +1162,11 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C39" s="7" t="n"/>
@@ -1178,15 +1178,15 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B40" s="7" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D40" s="7" t="n"/>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
@@ -1200,7 +1200,7 @@
       <c r="C41" s="7" t="n"/>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E41" s="7" t="n"/>
@@ -1210,13 +1210,13 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B42" s="7" t="n"/>
       <c r="C42" s="7" t="n"/>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E42" s="7" t="n"/>
@@ -1232,7 +1232,7 @@
       <c r="C43" s="7" t="n"/>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E43" s="7" t="n"/>
@@ -1248,7 +1248,7 @@
       <c r="C44" s="7" t="n"/>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E44" s="7" t="n"/>
@@ -1260,13 +1260,13 @@
       <c r="A45" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+      <c r="B45" s="7" t="n"/>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="n"/>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E45" s="7" t="n"/>
       <c r="F45" s="7" t="n"/>
       <c r="G45" s="7" t="n"/>
@@ -1276,13 +1276,13 @@
       <c r="A46" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B46" s="7" t="n"/>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D46" s="7" t="n"/>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="7" t="n"/>
@@ -1292,13 +1292,13 @@
       <c r="A47" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B47" s="7" t="n"/>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D47" s="7" t="n"/>
       <c r="E47" s="7" t="n"/>
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="7" t="n"/>
@@ -1312,7 +1312,7 @@
       <c r="C48" s="7" t="n"/>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E48" s="7" t="n"/>
@@ -1322,15 +1322,15 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B49" s="7" t="n"/>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="n"/>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E49" s="7" t="n"/>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n"/>
@@ -1354,17 +1354,17 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B51" s="7" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C51" s="7" t="n"/>
       <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F51" s="7" t="n"/>
       <c r="G51" s="7" t="n"/>
       <c r="H51" s="7" t="n"/>
     </row>
@@ -1372,13 +1372,13 @@
       <c r="A52" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+      <c r="B52" s="7" t="n"/>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="7" t="n"/>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="7" t="n"/>
@@ -1388,29 +1388,29 @@
       <c r="A53" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B53" s="7" t="n"/>
       <c r="C53" s="7" t="n"/>
       <c r="D53" s="7" t="n"/>
       <c r="E53" s="7" t="n"/>
-      <c r="F53" s="7" t="n"/>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G53" s="7" t="n"/>
       <c r="H53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B54" s="7" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C54" s="7" t="n"/>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D54" s="7" t="n"/>
       <c r="E54" s="7" t="n"/>
       <c r="F54" s="7" t="n"/>
       <c r="G54" s="7" t="n"/>
@@ -1418,19 +1418,19 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B55" s="7" t="n"/>
       <c r="C55" s="7" t="n"/>
       <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7" t="n"/>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G55" s="7" t="n"/>
-      <c r="H55" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
@@ -1442,7 +1442,7 @@
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>Colston Loveland</t>
+          <t>George Kittle</t>
         </is>
       </c>
       <c r="G56" s="7" t="n"/>
@@ -1450,17 +1450,17 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B57" s="7" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C57" s="7" t="n"/>
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
       <c r="H57" s="7" t="n"/>
     </row>
@@ -1468,29 +1468,29 @@
       <c r="A58" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+      <c r="B58" s="7" t="n"/>
       <c r="C58" s="7" t="n"/>
       <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
       <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n"/>
-      <c r="H58" s="7" t="n"/>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B59" s="7" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
       <c r="F59" s="7" t="n"/>
       <c r="G59" s="7" t="n"/>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C60" s="7" t="n"/>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C61" s="7" t="n"/>
@@ -1532,13 +1532,13 @@
       <c r="A62" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+      <c r="B62" s="7" t="n"/>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="n"/>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="7" t="n"/>
@@ -1548,13 +1548,13 @@
       <c r="A63" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B63" s="7" t="n"/>
       <c r="C63" s="7" t="n"/>
-      <c r="D63" s="7" t="n"/>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E63" s="7" t="n"/>
       <c r="F63" s="7" t="n"/>
       <c r="G63" s="7" t="n"/>
@@ -1568,7 +1568,7 @@
       <c r="C64" s="7" t="n"/>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E64" s="7" t="n"/>
@@ -1582,13 +1582,13 @@
       </c>
       <c r="B65" s="7" t="n"/>
       <c r="C65" s="7" t="n"/>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D65" s="7" t="n"/>
       <c r="E65" s="7" t="n"/>
-      <c r="F65" s="7" t="n"/>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G65" s="7" t="n"/>
       <c r="H65" s="7" t="n"/>
     </row>
@@ -1600,13 +1600,13 @@
       <c r="C66" s="7" t="n"/>
       <c r="D66" s="7" t="n"/>
       <c r="E66" s="7" t="n"/>
-      <c r="F66" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F66" s="7" t="n"/>
       <c r="G66" s="7" t="n"/>
-      <c r="H66" s="7" t="n"/>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
@@ -1620,7 +1620,7 @@
       <c r="G67" s="7" t="n"/>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
     </row>
@@ -1636,25 +1636,25 @@
       <c r="G68" s="7" t="n"/>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Drake Maye</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B69" s="7" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C69" s="7" t="n"/>
       <c r="D69" s="7" t="n"/>
       <c r="E69" s="7" t="n"/>
       <c r="F69" s="7" t="n"/>
       <c r="G69" s="7" t="n"/>
-      <c r="H69" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
@@ -1710,29 +1710,29 @@
       </c>
       <c r="B73" s="7" t="n"/>
       <c r="C73" s="7" t="n"/>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D73" s="7" t="n"/>
       <c r="E73" s="7" t="n"/>
-      <c r="F73" s="7" t="n"/>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G73" s="7" t="n"/>
       <c r="H73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B74" s="7" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C74" s="7" t="n"/>
       <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
-      <c r="F74" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
       <c r="H74" s="7" t="n"/>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr.</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C75" s="7" t="n"/>
@@ -1756,13 +1756,13 @@
       <c r="A76" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+      <c r="B76" s="7" t="n"/>
       <c r="C76" s="7" t="n"/>
-      <c r="D76" s="7" t="n"/>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E76" s="7" t="n"/>
       <c r="F76" s="7" t="n"/>
       <c r="G76" s="7" t="n"/>
@@ -1776,7 +1776,7 @@
       <c r="C77" s="7" t="n"/>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E77" s="7" t="n"/>
@@ -1786,15 +1786,15 @@
     </row>
     <row r="78">
       <c r="A78" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B78" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>Jonathon Brooks</t>
+        </is>
+      </c>
       <c r="C78" s="7" t="n"/>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D78" s="7" t="n"/>
       <c r="E78" s="7" t="n"/>
       <c r="F78" s="7" t="n"/>
       <c r="G78" s="7" t="n"/>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C79" s="7" t="n"/>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C80" s="7" t="n"/>
@@ -1836,13 +1836,13 @@
       <c r="A81" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>Rico Dowdle</t>
-        </is>
-      </c>
+      <c r="B81" s="7" t="n"/>
       <c r="C81" s="7" t="n"/>
-      <c r="D81" s="7" t="n"/>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E81" s="7" t="n"/>
       <c r="F81" s="7" t="n"/>
       <c r="G81" s="7" t="n"/>
@@ -1856,7 +1856,7 @@
       <c r="C82" s="7" t="n"/>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E82" s="7" t="n"/>
@@ -1872,7 +1872,7 @@
       <c r="C83" s="7" t="n"/>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E83" s="7" t="n"/>
@@ -2012,13 +2012,13 @@
       <c r="A92" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+      <c r="B92" s="7" t="n"/>
       <c r="C92" s="7" t="n"/>
-      <c r="D92" s="7" t="n"/>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E92" s="7" t="n"/>
       <c r="F92" s="7" t="n"/>
       <c r="G92" s="7" t="n"/>
@@ -2030,15 +2030,15 @@
       </c>
       <c r="B93" s="7" t="n"/>
       <c r="C93" s="7" t="n"/>
-      <c r="D93" s="7" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D93" s="7" t="n"/>
       <c r="E93" s="7" t="n"/>
       <c r="F93" s="7" t="n"/>
       <c r="G93" s="7" t="n"/>
-      <c r="H93" s="7" t="n"/>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>Jalen Hurts</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
@@ -2046,75 +2046,75 @@
       </c>
       <c r="B94" s="7" t="n"/>
       <c r="C94" s="7" t="n"/>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
+      <c r="D94" s="7" t="n"/>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="7" t="n"/>
       <c r="G94" s="7" t="n"/>
-      <c r="H94" s="7" t="n"/>
+      <c r="H94" s="7" t="inlineStr">
+        <is>
+          <t>Justin Herbert</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B95" s="7" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C95" s="7" t="n"/>
       <c r="D95" s="7" t="n"/>
       <c r="E95" s="7" t="n"/>
       <c r="F95" s="7" t="n"/>
       <c r="G95" s="7" t="n"/>
-      <c r="H95" s="7" t="inlineStr">
-        <is>
-          <t>Jalen Hurts</t>
-        </is>
-      </c>
+      <c r="H95" s="7" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B96" s="7" t="n"/>
       <c r="C96" s="7" t="n"/>
-      <c r="D96" s="7" t="n"/>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="7" t="n"/>
       <c r="G96" s="7" t="n"/>
-      <c r="H96" s="7" t="inlineStr">
-        <is>
-          <t>Justin Herbert</t>
-        </is>
-      </c>
+      <c r="H96" s="7" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B97" s="7" t="n"/>
       <c r="C97" s="7" t="n"/>
-      <c r="D97" s="7" t="n"/>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>Carnell Tate</t>
+        </is>
+      </c>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="7" t="n"/>
       <c r="G97" s="7" t="n"/>
-      <c r="H97" s="7" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H97" s="7" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B98" s="7" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+      <c r="B98" s="7" t="n"/>
       <c r="C98" s="7" t="n"/>
-      <c r="D98" s="7" t="n"/>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E98" s="7" t="n"/>
       <c r="F98" s="7" t="n"/>
       <c r="G98" s="7" t="n"/>
@@ -2126,27 +2126,27 @@
       </c>
       <c r="B99" s="7" t="n"/>
       <c r="C99" s="7" t="n"/>
-      <c r="D99" s="7" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D99" s="7" t="n"/>
       <c r="E99" s="7" t="n"/>
       <c r="F99" s="7" t="n"/>
       <c r="G99" s="7" t="n"/>
-      <c r="H99" s="7" t="n"/>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B100" s="7" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C100" s="7" t="n"/>
-      <c r="D100" s="7" t="inlineStr">
-        <is>
-          <t>Carnell Tate</t>
-        </is>
-      </c>
+      <c r="D100" s="7" t="n"/>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="7" t="n"/>
       <c r="G100" s="7" t="n"/>
@@ -2295,7 +2295,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 75.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 76.</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 4; 9 players used week 3 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 5; 9 players used week 3 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Puka Nacua 61-&gt;53, Jaxon Smith-Njigba 67-&gt;59, Chris Olave 53-&gt;45, Trey McBride 42.8571-&gt;35, Amon-Ra St. Brown 63-&gt;56, Justin Jefferson 47-&gt;40, CeeDee Lamb 45-&gt;38, Drake London 43-&gt;36</t>
+          <t>Largest moves vs. the baseline in this file: Puka Nacua 56-&gt;47, Jaxon Smith-Njigba 67-&gt;59, Amon-Ra St. Brown 62-&gt;54, Chris Olave 53-&gt;45, Trey McBride 43.4286-&gt;36, Ja'Marr Chase 67-&gt;60, Justin Jefferson 47-&gt;40, CeeDee Lamb 45-&gt;38</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C6" s="7" t="n"/>
@@ -650,15 +650,15 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Jonathan Taylor</t>
-        </is>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="B7" s="7" t="n"/>
       <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="7" t="n"/>
@@ -668,13 +668,13 @@
       <c r="A8" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="B8" s="7" t="n"/>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D8" s="7" t="n"/>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="7" t="n"/>
@@ -682,15 +682,15 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="B9" s="7" t="n"/>
       <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="7" t="n"/>
@@ -700,13 +700,13 @@
       <c r="A10" s="6" t="n">
         <v>59</v>
       </c>
-      <c r="B10" s="7" t="n"/>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="n"/>
@@ -718,7 +718,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="C11" s="7" t="n"/>
@@ -730,7 +730,7 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
@@ -746,7 +746,7 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
@@ -874,7 +874,7 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
@@ -922,7 +922,7 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
@@ -940,37 +940,37 @@
       <c r="A25" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+      <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="B26" s="7" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C26" s="7" t="n"/>
       <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
@@ -1018,11 +1018,11 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C30" s="7" t="n"/>
@@ -1034,11 +1034,11 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C31" s="7" t="n"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="C32" s="7" t="n"/>
@@ -1082,13 +1082,13 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E34" s="7" t="n"/>
@@ -1102,31 +1102,31 @@
       </c>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
-      <c r="D35" s="7" t="n"/>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="7" t="n"/>
-      <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D36" s="7" t="n"/>
       <c r="E36" s="7" t="n"/>
       <c r="F36" s="7" t="n"/>
       <c r="G36" s="7" t="n"/>
-      <c r="H36" s="7" t="n"/>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
@@ -1136,7 +1136,7 @@
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E37" s="7" t="n"/>
@@ -1146,15 +1146,15 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="B38" s="7" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D38" s="7" t="n"/>
       <c r="E38" s="7" t="n"/>
       <c r="F38" s="7" t="n"/>
       <c r="G38" s="7" t="n"/>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C39" s="7" t="n"/>
@@ -1180,13 +1180,13 @@
       <c r="A40" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="n"/>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B42" s="7" t="n"/>
       <c r="C42" s="7" t="n"/>
@@ -1232,7 +1232,7 @@
       <c r="C43" s="7" t="n"/>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E43" s="7" t="n"/>
@@ -1242,15 +1242,15 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B44" s="7" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D44" s="7" t="n"/>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="7" t="n"/>
@@ -1276,13 +1276,13 @@
       <c r="A46" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+      <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="n"/>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="7" t="n"/>
@@ -1354,31 +1354,31 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B51" s="7" t="n"/>
       <c r="C51" s="7" t="n"/>
       <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
       <c r="F51" s="7" t="n"/>
       <c r="G51" s="7" t="n"/>
-      <c r="H51" s="7" t="n"/>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B52" s="7" t="n"/>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D52" s="7" t="n"/>
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="7" t="n"/>
@@ -1390,29 +1390,29 @@
       </c>
       <c r="B53" s="7" t="n"/>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="7" t="n"/>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E53" s="7" t="n"/>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F53" s="7" t="n"/>
       <c r="G53" s="7" t="n"/>
       <c r="H53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
       <c r="D54" s="7" t="n"/>
       <c r="E54" s="7" t="n"/>
-      <c r="F54" s="7" t="n"/>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G54" s="7" t="n"/>
       <c r="H54" s="7" t="n"/>
     </row>
@@ -1420,15 +1420,15 @@
       <c r="A55" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B55" s="7" t="n"/>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C55" s="7" t="n"/>
       <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F55" s="7" t="n"/>
       <c r="G55" s="7" t="n"/>
       <c r="H55" s="7" t="n"/>
     </row>
@@ -1442,7 +1442,7 @@
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Colston Loveland</t>
         </is>
       </c>
       <c r="G56" s="7" t="n"/>
@@ -1450,17 +1450,17 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B57" s="7" t="n"/>
       <c r="C57" s="7" t="n"/>
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
-      <c r="F57" s="7" t="n"/>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G57" s="7" t="n"/>
       <c r="H57" s="7" t="n"/>
     </row>
@@ -1468,17 +1468,17 @@
       <c r="A58" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B58" s="7" t="n"/>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C58" s="7" t="n"/>
       <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
       <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n"/>
-      <c r="H58" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
@@ -1584,13 +1584,13 @@
       <c r="C65" s="7" t="n"/>
       <c r="D65" s="7" t="n"/>
       <c r="E65" s="7" t="n"/>
-      <c r="F65" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F65" s="7" t="n"/>
       <c r="G65" s="7" t="n"/>
-      <c r="H65" s="7" t="n"/>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
@@ -1604,7 +1604,7 @@
       <c r="G66" s="7" t="n"/>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
     </row>
@@ -1620,25 +1620,25 @@
       <c r="G67" s="7" t="n"/>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Drake Maye</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B68" s="7" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C68" s="7" t="n"/>
       <c r="D68" s="7" t="n"/>
       <c r="E68" s="7" t="n"/>
       <c r="F68" s="7" t="n"/>
       <c r="G68" s="7" t="n"/>
-      <c r="H68" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C69" s="7" t="n"/>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C70" s="7" t="n"/>
@@ -1714,7 +1714,7 @@
       <c r="E73" s="7" t="n"/>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G73" s="7" t="n"/>
@@ -1722,17 +1722,17 @@
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B74" s="7" t="n"/>
       <c r="C74" s="7" t="n"/>
       <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
-      <c r="F74" s="7" t="n"/>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G74" s="7" t="n"/>
       <c r="H74" s="7" t="n"/>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C75" s="7" t="n"/>
@@ -1760,7 +1760,7 @@
       <c r="C76" s="7" t="n"/>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E76" s="7" t="n"/>
@@ -1776,7 +1776,7 @@
       <c r="C77" s="7" t="n"/>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E77" s="7" t="n"/>
@@ -1786,15 +1786,15 @@
     </row>
     <row r="78">
       <c r="A78" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>Jonathon Brooks</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B78" s="7" t="n"/>
       <c r="C78" s="7" t="n"/>
-      <c r="D78" s="7" t="n"/>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>Marvin Harrison Jr.</t>
+        </is>
+      </c>
       <c r="E78" s="7" t="n"/>
       <c r="F78" s="7" t="n"/>
       <c r="G78" s="7" t="n"/>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C79" s="7" t="n"/>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C80" s="7" t="n"/>
@@ -1836,13 +1836,13 @@
       <c r="A81" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B81" s="7" t="n"/>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>Rico Dowdle</t>
+        </is>
+      </c>
       <c r="C81" s="7" t="n"/>
-      <c r="D81" s="7" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D81" s="7" t="n"/>
       <c r="E81" s="7" t="n"/>
       <c r="F81" s="7" t="n"/>
       <c r="G81" s="7" t="n"/>
@@ -1872,7 +1872,7 @@
       <c r="C83" s="7" t="n"/>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E83" s="7" t="n"/>
@@ -1888,7 +1888,7 @@
       <c r="C84" s="7" t="n"/>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E84" s="7" t="n"/>
@@ -1904,7 +1904,7 @@
       <c r="C85" s="7" t="n"/>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E85" s="7" t="n"/>
@@ -1920,7 +1920,7 @@
       <c r="C86" s="7" t="n"/>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E86" s="7" t="n"/>
@@ -1936,7 +1936,7 @@
       <c r="C87" s="7" t="n"/>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E87" s="7" t="n"/>
@@ -1950,13 +1950,13 @@
       </c>
       <c r="B88" s="7" t="n"/>
       <c r="C88" s="7" t="n"/>
-      <c r="D88" s="7" t="inlineStr">
-        <is>
-          <t>Chris Godwin Jr.</t>
-        </is>
-      </c>
+      <c r="D88" s="7" t="n"/>
       <c r="E88" s="7" t="n"/>
-      <c r="F88" s="7" t="n"/>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G88" s="7" t="n"/>
       <c r="H88" s="7" t="n"/>
     </row>
@@ -1968,41 +1968,41 @@
       <c r="C89" s="7" t="n"/>
       <c r="D89" s="7" t="n"/>
       <c r="E89" s="7" t="n"/>
-      <c r="F89" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F89" s="7" t="n"/>
       <c r="G89" s="7" t="n"/>
-      <c r="H89" s="7" t="n"/>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B90" s="7" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C90" s="7" t="n"/>
       <c r="D90" s="7" t="n"/>
       <c r="E90" s="7" t="n"/>
       <c r="F90" s="7" t="n"/>
       <c r="G90" s="7" t="n"/>
-      <c r="H90" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H90" s="7" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B91" s="7" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+      <c r="B91" s="7" t="n"/>
       <c r="C91" s="7" t="n"/>
-      <c r="D91" s="7" t="n"/>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E91" s="7" t="n"/>
       <c r="F91" s="7" t="n"/>
       <c r="G91" s="7" t="n"/>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>Woody Marks</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="C95" s="7" t="n"/>
@@ -2076,13 +2076,13 @@
       <c r="A96" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B96" s="7" t="n"/>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C96" s="7" t="n"/>
-      <c r="D96" s="7" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D96" s="7" t="n"/>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="7" t="n"/>
       <c r="G96" s="7" t="n"/>
@@ -2096,7 +2096,7 @@
       <c r="C97" s="7" t="n"/>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E97" s="7" t="n"/>
@@ -2112,7 +2112,7 @@
       <c r="C98" s="7" t="n"/>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E98" s="7" t="n"/>
@@ -2126,31 +2126,31 @@
       </c>
       <c r="B99" s="7" t="n"/>
       <c r="C99" s="7" t="n"/>
-      <c r="D99" s="7" t="n"/>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E99" s="7" t="n"/>
       <c r="F99" s="7" t="n"/>
       <c r="G99" s="7" t="n"/>
-      <c r="H99" s="7" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B100" s="7" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B100" s="7" t="n"/>
       <c r="C100" s="7" t="n"/>
       <c r="D100" s="7" t="n"/>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="7" t="n"/>
       <c r="G100" s="7" t="n"/>
-      <c r="H100" s="7" t="n"/>
+      <c r="H100" s="7" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 5; 9 players used week 3 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 6; 9 players used week 3 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 81 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 79 players moved.</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.8, WR 2.9, TE 4.5, QB 0.0.</t>
+          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.9, WR 2.9, TE 4.5, QB 0.0.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Puka Nacua 56-&gt;47, Jaxon Smith-Njigba 67-&gt;59, Amon-Ra St. Brown 62-&gt;54, Chris Olave 53-&gt;45, Trey McBride 43.4286-&gt;36, Ja'Marr Chase 67-&gt;60, Justin Jefferson 47-&gt;40, CeeDee Lamb 45-&gt;38</t>
+          <t>Largest moves vs. the baseline in this file: Puka Nacua 55-&gt;46, Jaxon Smith-Njigba 68-&gt;60, Chris Olave 53-&gt;45, Trey McBride 43.4286-&gt;36, Ja'Marr Chase 68-&gt;61, Amon-Ra St. Brown 63-&gt;56, Justin Jefferson 47-&gt;40, CeeDee Lamb 46-&gt;39</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -634,7 +634,7 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B7" s="7" t="n"/>
       <c r="C7" s="7" t="n"/>
@@ -666,7 +666,7 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="7" t="n"/>
       <c r="C9" s="7" t="n"/>
@@ -698,11 +698,11 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="C10" s="7" t="n"/>
@@ -718,7 +718,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C11" s="7" t="n"/>
@@ -730,15 +730,15 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>56</v>
-      </c>
-      <c r="B12" s="7" t="n"/>
+        <v>53</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D12" s="7" t="n"/>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="n"/>
@@ -746,15 +746,15 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
@@ -762,13 +762,13 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Puka Nacua</t>
+          <t>Chris Olave</t>
         </is>
       </c>
       <c r="E14" s="7" t="n"/>
@@ -778,35 +778,35 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B15" s="7" t="n"/>
       <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D15" s="7" t="n"/>
       <c r="E15" s="7" t="n"/>
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
@@ -826,7 +826,7 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
@@ -842,7 +842,7 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
@@ -890,7 +890,7 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
@@ -922,7 +922,7 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C30" s="7" t="n"/>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="C31" s="7" t="n"/>
@@ -1050,11 +1050,11 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C32" s="7" t="n"/>
@@ -1082,13 +1082,13 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E34" s="7" t="n"/>
@@ -1102,43 +1102,43 @@
       </c>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D35" s="7" t="n"/>
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="7" t="n"/>
-      <c r="H35" s="7" t="n"/>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
-      <c r="D36" s="7" t="n"/>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E36" s="7" t="n"/>
       <c r="F36" s="7" t="n"/>
       <c r="G36" s="7" t="n"/>
-      <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="B37" s="7" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D37" s="7" t="n"/>
       <c r="E37" s="7" t="n"/>
       <c r="F37" s="7" t="n"/>
       <c r="G37" s="7" t="n"/>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C38" s="7" t="n"/>
@@ -1164,13 +1164,13 @@
       <c r="A39" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
-      <c r="D39" s="7" t="n"/>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E39" s="7" t="n"/>
       <c r="F39" s="7" t="n"/>
       <c r="G39" s="7" t="n"/>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B42" s="7" t="n"/>
       <c r="C42" s="7" t="n"/>
@@ -1226,7 +1226,7 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B43" s="7" t="n"/>
       <c r="C43" s="7" t="n"/>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Jadarian Price</t>
         </is>
       </c>
       <c r="C44" s="7" t="n"/>
@@ -1258,15 +1258,15 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B45" s="7" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D45" s="7" t="n"/>
       <c r="E45" s="7" t="n"/>
       <c r="F45" s="7" t="n"/>
       <c r="G45" s="7" t="n"/>
@@ -1290,15 +1290,15 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="n"/>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E47" s="7" t="n"/>
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="7" t="n"/>
@@ -1306,13 +1306,13 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B48" s="7" t="n"/>
       <c r="C48" s="7" t="n"/>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E48" s="7" t="n"/>
@@ -1322,15 +1322,15 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B49" s="7" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D49" s="7" t="n"/>
       <c r="E49" s="7" t="n"/>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n"/>
@@ -1342,13 +1342,13 @@
       </c>
       <c r="B50" s="7" t="n"/>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
-      <c r="F50" s="7" t="n"/>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G50" s="7" t="n"/>
       <c r="H50" s="7" t="n"/>
     </row>
@@ -1392,7 +1392,7 @@
       <c r="C53" s="7" t="n"/>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E53" s="7" t="n"/>
@@ -1406,27 +1406,27 @@
       </c>
       <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
-      <c r="D54" s="7" t="n"/>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E54" s="7" t="n"/>
-      <c r="F54" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F54" s="7" t="n"/>
       <c r="G54" s="7" t="n"/>
       <c r="H54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B55" s="7" t="n"/>
       <c r="C55" s="7" t="n"/>
-      <c r="D55" s="7" t="n"/>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E55" s="7" t="n"/>
       <c r="F55" s="7" t="n"/>
       <c r="G55" s="7" t="n"/>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
       <c r="C62" s="7" t="n"/>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E62" s="7" t="n"/>
@@ -1550,13 +1550,13 @@
       </c>
       <c r="B63" s="7" t="n"/>
       <c r="C63" s="7" t="n"/>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D63" s="7" t="n"/>
       <c r="E63" s="7" t="n"/>
-      <c r="F63" s="7" t="n"/>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G63" s="7" t="n"/>
       <c r="H63" s="7" t="n"/>
     </row>
@@ -1566,15 +1566,15 @@
       </c>
       <c r="B64" s="7" t="n"/>
       <c r="C64" s="7" t="n"/>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D64" s="7" t="n"/>
       <c r="E64" s="7" t="n"/>
       <c r="F64" s="7" t="n"/>
       <c r="G64" s="7" t="n"/>
-      <c r="H64" s="7" t="n"/>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
@@ -1588,7 +1588,7 @@
       <c r="G65" s="7" t="n"/>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
     </row>
@@ -1604,25 +1604,25 @@
       <c r="G66" s="7" t="n"/>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Drake Maye</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B67" s="7" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C67" s="7" t="n"/>
       <c r="D67" s="7" t="n"/>
       <c r="E67" s="7" t="n"/>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
-      <c r="H67" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C68" s="7" t="n"/>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="C69" s="7" t="n"/>
@@ -1660,13 +1660,13 @@
       <c r="A70" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+      <c r="B70" s="7" t="n"/>
       <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="n"/>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E70" s="7" t="n"/>
       <c r="F70" s="7" t="n"/>
       <c r="G70" s="7" t="n"/>
@@ -1676,13 +1676,13 @@
       <c r="A71" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
+      <c r="B71" s="7" t="n"/>
       <c r="C71" s="7" t="n"/>
-      <c r="D71" s="7" t="n"/>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
@@ -1690,11 +1690,11 @@
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C72" s="7" t="n"/>
@@ -1706,33 +1706,33 @@
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B73" s="7" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>J.K. Dobbins</t>
+        </is>
+      </c>
       <c r="C73" s="7" t="n"/>
       <c r="D73" s="7" t="n"/>
       <c r="E73" s="7" t="n"/>
-      <c r="F73" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
       <c r="H73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B74" s="7" t="n"/>
       <c r="C74" s="7" t="n"/>
-      <c r="D74" s="7" t="n"/>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E74" s="7" t="n"/>
-      <c r="F74" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
       <c r="H74" s="7" t="n"/>
     </row>
@@ -1740,13 +1740,13 @@
       <c r="A75" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B75" s="7" t="n"/>
       <c r="C75" s="7" t="n"/>
-      <c r="D75" s="7" t="n"/>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E75" s="7" t="n"/>
       <c r="F75" s="7" t="n"/>
       <c r="G75" s="7" t="n"/>
@@ -1760,7 +1760,7 @@
       <c r="C76" s="7" t="n"/>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E76" s="7" t="n"/>
@@ -1774,13 +1774,13 @@
       </c>
       <c r="B77" s="7" t="n"/>
       <c r="C77" s="7" t="n"/>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D77" s="7" t="n"/>
       <c r="E77" s="7" t="n"/>
-      <c r="F77" s="7" t="n"/>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G77" s="7" t="n"/>
       <c r="H77" s="7" t="n"/>
     </row>
@@ -1790,13 +1790,13 @@
       </c>
       <c r="B78" s="7" t="n"/>
       <c r="C78" s="7" t="n"/>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D78" s="7" t="n"/>
       <c r="E78" s="7" t="n"/>
-      <c r="F78" s="7" t="n"/>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G78" s="7" t="n"/>
       <c r="H78" s="7" t="n"/>
     </row>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C79" s="7" t="n"/>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C80" s="7" t="n"/>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C81" s="7" t="n"/>
@@ -1852,13 +1852,13 @@
       <c r="A82" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B82" s="7" t="n"/>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>Rico Dowdle</t>
+        </is>
+      </c>
       <c r="C82" s="7" t="n"/>
-      <c r="D82" s="7" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D82" s="7" t="n"/>
       <c r="E82" s="7" t="n"/>
       <c r="F82" s="7" t="n"/>
       <c r="G82" s="7" t="n"/>
@@ -1872,7 +1872,7 @@
       <c r="C83" s="7" t="n"/>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E83" s="7" t="n"/>
@@ -1888,7 +1888,7 @@
       <c r="C84" s="7" t="n"/>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E84" s="7" t="n"/>
@@ -1904,7 +1904,7 @@
       <c r="C85" s="7" t="n"/>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E85" s="7" t="n"/>
@@ -1920,7 +1920,7 @@
       <c r="C86" s="7" t="n"/>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E86" s="7" t="n"/>
@@ -1936,7 +1936,7 @@
       <c r="C87" s="7" t="n"/>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr.</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E87" s="7" t="n"/>
@@ -1950,13 +1950,13 @@
       </c>
       <c r="B88" s="7" t="n"/>
       <c r="C88" s="7" t="n"/>
-      <c r="D88" s="7" t="n"/>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>Quentin Johnston</t>
+        </is>
+      </c>
       <c r="E88" s="7" t="n"/>
-      <c r="F88" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F88" s="7" t="n"/>
       <c r="G88" s="7" t="n"/>
       <c r="H88" s="7" t="n"/>
     </row>
@@ -1966,43 +1966,43 @@
       </c>
       <c r="B89" s="7" t="n"/>
       <c r="C89" s="7" t="n"/>
-      <c r="D89" s="7" t="n"/>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>Chris Godwin Jr.</t>
+        </is>
+      </c>
       <c r="E89" s="7" t="n"/>
       <c r="F89" s="7" t="n"/>
       <c r="G89" s="7" t="n"/>
-      <c r="H89" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H89" s="7" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B90" s="7" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B90" s="7" t="n"/>
       <c r="C90" s="7" t="n"/>
       <c r="D90" s="7" t="n"/>
       <c r="E90" s="7" t="n"/>
       <c r="F90" s="7" t="n"/>
       <c r="G90" s="7" t="n"/>
-      <c r="H90" s="7" t="n"/>
+      <c r="H90" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B91" s="7" t="n"/>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C91" s="7" t="n"/>
-      <c r="D91" s="7" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D91" s="7" t="n"/>
       <c r="E91" s="7" t="n"/>
       <c r="F91" s="7" t="n"/>
       <c r="G91" s="7" t="n"/>
@@ -2012,13 +2012,13 @@
       <c r="A92" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B92" s="7" t="n"/>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C92" s="7" t="n"/>
-      <c r="D92" s="7" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D92" s="7" t="n"/>
       <c r="E92" s="7" t="n"/>
       <c r="F92" s="7" t="n"/>
       <c r="G92" s="7" t="n"/>
@@ -2030,15 +2030,15 @@
       </c>
       <c r="B93" s="7" t="n"/>
       <c r="C93" s="7" t="n"/>
-      <c r="D93" s="7" t="n"/>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>Terry McLaurin</t>
+        </is>
+      </c>
       <c r="E93" s="7" t="n"/>
       <c r="F93" s="7" t="n"/>
       <c r="G93" s="7" t="n"/>
-      <c r="H93" s="7" t="inlineStr">
-        <is>
-          <t>Jalen Hurts</t>
-        </is>
-      </c>
+      <c r="H93" s="7" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
@@ -2046,63 +2046,63 @@
       </c>
       <c r="B94" s="7" t="n"/>
       <c r="C94" s="7" t="n"/>
-      <c r="D94" s="7" t="n"/>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="7" t="n"/>
       <c r="G94" s="7" t="n"/>
-      <c r="H94" s="7" t="inlineStr">
-        <is>
-          <t>Justin Herbert</t>
-        </is>
-      </c>
+      <c r="H94" s="7" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B95" s="7" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B95" s="7" t="n"/>
       <c r="C95" s="7" t="n"/>
       <c r="D95" s="7" t="n"/>
       <c r="E95" s="7" t="n"/>
       <c r="F95" s="7" t="n"/>
       <c r="G95" s="7" t="n"/>
-      <c r="H95" s="7" t="n"/>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>Jalen Hurts</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B96" s="7" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B96" s="7" t="n"/>
       <c r="C96" s="7" t="n"/>
       <c r="D96" s="7" t="n"/>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="7" t="n"/>
       <c r="G96" s="7" t="n"/>
-      <c r="H96" s="7" t="n"/>
+      <c r="H96" s="7" t="inlineStr">
+        <is>
+          <t>Justin Herbert</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B97" s="7" t="n"/>
       <c r="C97" s="7" t="n"/>
-      <c r="D97" s="7" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D97" s="7" t="n"/>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="7" t="n"/>
       <c r="G97" s="7" t="n"/>
-      <c r="H97" s="7" t="n"/>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
@@ -2112,7 +2112,7 @@
       <c r="C98" s="7" t="n"/>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E98" s="7" t="n"/>
@@ -2128,7 +2128,7 @@
       <c r="C99" s="7" t="n"/>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E99" s="7" t="n"/>
@@ -2138,19 +2138,19 @@
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B100" s="7" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C100" s="7" t="n"/>
       <c r="D100" s="7" t="n"/>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="7" t="n"/>
       <c r="G100" s="7" t="n"/>
-      <c r="H100" s="7" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H100" s="7" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
@@ -2160,7 +2160,7 @@
       <c r="C101" s="7" t="n"/>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E101" s="7" t="n"/>
@@ -2295,7 +2295,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 76.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 77.</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 6; 9 players used week 3 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 7; 9 players used week 3 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 79 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 83 players moved.</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.9, WR 2.9, TE 4.5, QB 0.0.</t>
+          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.8, WR 2.8, TE 4.5, QB 0.0.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Puka Nacua 55-&gt;46, Jaxon Smith-Njigba 68-&gt;60, Chris Olave 53-&gt;45, Trey McBride 43.4286-&gt;36, Ja'Marr Chase 68-&gt;61, Amon-Ra St. Brown 63-&gt;56, Justin Jefferson 47-&gt;40, CeeDee Lamb 46-&gt;39</t>
+          <t>Largest moves vs. the baseline in this file: Puka Nacua 53-&gt;43, Jaxon Smith-Njigba 68-&gt;59, Amon-Ra St. Brown 62-&gt;53, Chris Olave 53-&gt;44, Ja'Marr Chase 68-&gt;60, Justin Jefferson 47-&gt;39, CeeDee Lamb 46-&gt;38, Drake London 45-&gt;37</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C6" s="7" t="n"/>
@@ -652,13 +652,13 @@
       <c r="A7" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="B7" s="7" t="n"/>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Jonathan Taylor</t>
+        </is>
+      </c>
       <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="7" t="n"/>
@@ -666,15 +666,15 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="B8" s="7" t="n"/>
       <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="7" t="n"/>
@@ -730,7 +730,7 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
@@ -762,7 +762,7 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
@@ -794,15 +794,15 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>43</v>
-      </c>
-      <c r="B16" s="7" t="n"/>
+        <v>41</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D16" s="7" t="n"/>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
@@ -812,13 +812,13 @@
       <c r="A17" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+      <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
@@ -826,7 +826,7 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
@@ -842,7 +842,7 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
@@ -922,43 +922,43 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="B25" s="7" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C26" s="7" t="n"/>
@@ -970,7 +970,7 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
@@ -988,13 +988,13 @@
       <c r="A28" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="7" t="n"/>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D28" s="7" t="n"/>
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="7" t="n"/>
@@ -1002,15 +1002,15 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="7" t="n"/>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C31" s="7" t="n"/>
@@ -1050,11 +1050,11 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="C32" s="7" t="n"/>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
@@ -1098,43 +1098,43 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
-      <c r="D35" s="7" t="n"/>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="7" t="n"/>
-      <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D36" s="7" t="n"/>
       <c r="E36" s="7" t="n"/>
       <c r="F36" s="7" t="n"/>
       <c r="G36" s="7" t="n"/>
-      <c r="H36" s="7" t="n"/>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C37" s="7" t="n"/>
@@ -1146,15 +1146,15 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="n"/>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E38" s="7" t="n"/>
       <c r="F38" s="7" t="n"/>
       <c r="G38" s="7" t="n"/>
@@ -1162,7 +1162,7 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
@@ -1178,15 +1178,15 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B40" s="7" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D40" s="7" t="n"/>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
@@ -1226,7 +1226,7 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B43" s="7" t="n"/>
       <c r="C43" s="7" t="n"/>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="C44" s="7" t="n"/>
@@ -1258,15 +1258,15 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B45" s="7" t="n"/>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="n"/>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E45" s="7" t="n"/>
       <c r="F45" s="7" t="n"/>
       <c r="G45" s="7" t="n"/>
@@ -1290,15 +1290,15 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B47" s="7" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D47" s="7" t="n"/>
       <c r="E47" s="7" t="n"/>
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="7" t="n"/>
@@ -1306,13 +1306,13 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B48" s="7" t="n"/>
       <c r="C48" s="7" t="n"/>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E48" s="7" t="n"/>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="C49" s="7" t="n"/>
@@ -1354,31 +1354,31 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B51" s="7" t="n"/>
       <c r="C51" s="7" t="n"/>
-      <c r="D51" s="7" t="n"/>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E51" s="7" t="n"/>
       <c r="F51" s="7" t="n"/>
       <c r="G51" s="7" t="n"/>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+      <c r="B52" s="7" t="n"/>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="7" t="n"/>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="7" t="n"/>
@@ -1392,7 +1392,7 @@
       <c r="C53" s="7" t="n"/>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E53" s="7" t="n"/>
@@ -1402,15 +1402,15 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B54" s="7" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C54" s="7" t="n"/>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D54" s="7" t="n"/>
       <c r="E54" s="7" t="n"/>
       <c r="F54" s="7" t="n"/>
       <c r="G54" s="7" t="n"/>
@@ -1418,17 +1418,17 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B55" s="7" t="n"/>
       <c r="C55" s="7" t="n"/>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7" t="n"/>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G55" s="7" t="n"/>
       <c r="H55" s="7" t="n"/>
     </row>
@@ -1442,7 +1442,7 @@
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>Colston Loveland</t>
+          <t>George Kittle</t>
         </is>
       </c>
       <c r="G56" s="7" t="n"/>
@@ -1450,27 +1450,27 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B57" s="7" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C57" s="7" t="n"/>
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
       <c r="H57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C58" s="7" t="n"/>
@@ -1482,11 +1482,11 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C59" s="7" t="n"/>
@@ -1498,11 +1498,11 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C60" s="7" t="n"/>
@@ -1514,15 +1514,15 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="n"/>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E61" s="7" t="n"/>
       <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
@@ -1530,39 +1530,39 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B62" s="7" t="n"/>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D62" s="7" t="n"/>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="7" t="n"/>
-      <c r="H62" s="7" t="n"/>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B63" s="7" t="n"/>
       <c r="C63" s="7" t="n"/>
       <c r="D63" s="7" t="n"/>
       <c r="E63" s="7" t="n"/>
-      <c r="F63" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F63" s="7" t="n"/>
       <c r="G63" s="7" t="n"/>
-      <c r="H63" s="7" t="n"/>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B64" s="7" t="n"/>
       <c r="C64" s="7" t="n"/>
@@ -1572,7 +1572,7 @@
       <c r="G64" s="7" t="n"/>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
     </row>
@@ -1580,17 +1580,17 @@
       <c r="A65" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B65" s="7" t="n"/>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C65" s="7" t="n"/>
       <c r="D65" s="7" t="n"/>
       <c r="E65" s="7" t="n"/>
       <c r="F65" s="7" t="n"/>
       <c r="G65" s="7" t="n"/>
-      <c r="H65" s="7" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H65" s="7" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
@@ -1600,29 +1600,29 @@
       <c r="C66" s="7" t="n"/>
       <c r="D66" s="7" t="n"/>
       <c r="E66" s="7" t="n"/>
-      <c r="F66" s="7" t="n"/>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G66" s="7" t="n"/>
-      <c r="H66" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B67" s="7" t="n"/>
       <c r="C67" s="7" t="n"/>
       <c r="D67" s="7" t="n"/>
       <c r="E67" s="7" t="n"/>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
-      <c r="H67" s="7" t="n"/>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C68" s="7" t="n"/>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C69" s="7" t="n"/>
@@ -1660,13 +1660,13 @@
       <c r="A70" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B70" s="7" t="n"/>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D70" s="7" t="n"/>
       <c r="E70" s="7" t="n"/>
       <c r="F70" s="7" t="n"/>
       <c r="G70" s="7" t="n"/>
@@ -1676,13 +1676,13 @@
       <c r="A71" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B71" s="7" t="n"/>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>J.K. Dobbins</t>
+        </is>
+      </c>
       <c r="C71" s="7" t="n"/>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D71" s="7" t="n"/>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
@@ -1690,15 +1690,15 @@
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B72" s="7" t="n"/>
       <c r="C72" s="7" t="n"/>
-      <c r="D72" s="7" t="n"/>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E72" s="7" t="n"/>
       <c r="F72" s="7" t="n"/>
       <c r="G72" s="7" t="n"/>
@@ -1706,15 +1706,15 @@
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B73" s="7" t="n"/>
       <c r="C73" s="7" t="n"/>
-      <c r="D73" s="7" t="n"/>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E73" s="7" t="n"/>
       <c r="F73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
@@ -1724,13 +1724,13 @@
       <c r="A74" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B74" s="7" t="n"/>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C74" s="7" t="n"/>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
       <c r="F74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
@@ -1744,7 +1744,7 @@
       <c r="C75" s="7" t="n"/>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E75" s="7" t="n"/>
@@ -1760,7 +1760,7 @@
       <c r="C76" s="7" t="n"/>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E76" s="7" t="n"/>
@@ -1774,13 +1774,13 @@
       </c>
       <c r="B77" s="7" t="n"/>
       <c r="C77" s="7" t="n"/>
-      <c r="D77" s="7" t="n"/>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E77" s="7" t="n"/>
-      <c r="F77" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F77" s="7" t="n"/>
       <c r="G77" s="7" t="n"/>
       <c r="H77" s="7" t="n"/>
     </row>
@@ -1790,45 +1790,45 @@
       </c>
       <c r="B78" s="7" t="n"/>
       <c r="C78" s="7" t="n"/>
-      <c r="D78" s="7" t="n"/>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>Marvin Harrison Jr.</t>
+        </is>
+      </c>
       <c r="E78" s="7" t="n"/>
-      <c r="F78" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F78" s="7" t="n"/>
       <c r="G78" s="7" t="n"/>
       <c r="H78" s="7" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B79" s="7" t="n"/>
       <c r="C79" s="7" t="n"/>
       <c r="D79" s="7" t="n"/>
       <c r="E79" s="7" t="n"/>
-      <c r="F79" s="7" t="n"/>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G79" s="7" t="n"/>
       <c r="H79" s="7" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>Jonathon Brooks</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B80" s="7" t="n"/>
       <c r="C80" s="7" t="n"/>
       <c r="D80" s="7" t="n"/>
       <c r="E80" s="7" t="n"/>
-      <c r="F80" s="7" t="n"/>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G80" s="7" t="n"/>
       <c r="H80" s="7" t="n"/>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C81" s="7" t="n"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C82" s="7" t="n"/>
@@ -1868,13 +1868,13 @@
       <c r="A83" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B83" s="7" t="n"/>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>Rico Dowdle</t>
+        </is>
+      </c>
       <c r="C83" s="7" t="n"/>
-      <c r="D83" s="7" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D83" s="7" t="n"/>
       <c r="E83" s="7" t="n"/>
       <c r="F83" s="7" t="n"/>
       <c r="G83" s="7" t="n"/>
@@ -1888,7 +1888,7 @@
       <c r="C84" s="7" t="n"/>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E84" s="7" t="n"/>
@@ -1904,7 +1904,7 @@
       <c r="C85" s="7" t="n"/>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E85" s="7" t="n"/>
@@ -1920,7 +1920,7 @@
       <c r="C86" s="7" t="n"/>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E86" s="7" t="n"/>
@@ -1936,7 +1936,7 @@
       <c r="C87" s="7" t="n"/>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E87" s="7" t="n"/>
@@ -1966,31 +1966,31 @@
       </c>
       <c r="B89" s="7" t="n"/>
       <c r="C89" s="7" t="n"/>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>Chris Godwin Jr.</t>
-        </is>
-      </c>
+      <c r="D89" s="7" t="n"/>
       <c r="E89" s="7" t="n"/>
       <c r="F89" s="7" t="n"/>
       <c r="G89" s="7" t="n"/>
-      <c r="H89" s="7" t="n"/>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B90" s="7" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C90" s="7" t="n"/>
       <c r="D90" s="7" t="n"/>
       <c r="E90" s="7" t="n"/>
       <c r="F90" s="7" t="n"/>
       <c r="G90" s="7" t="n"/>
-      <c r="H90" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H90" s="7" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>Blake Corum</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="C91" s="7" t="n"/>
@@ -2012,13 +2012,13 @@
       <c r="A92" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+      <c r="B92" s="7" t="n"/>
       <c r="C92" s="7" t="n"/>
-      <c r="D92" s="7" t="n"/>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>Chris Godwin Jr.</t>
+        </is>
+      </c>
       <c r="E92" s="7" t="n"/>
       <c r="F92" s="7" t="n"/>
       <c r="G92" s="7" t="n"/>
@@ -2032,7 +2032,7 @@
       <c r="C93" s="7" t="n"/>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Ja'Kobi Lane</t>
         </is>
       </c>
       <c r="E93" s="7" t="n"/>
@@ -2046,15 +2046,15 @@
       </c>
       <c r="B94" s="7" t="n"/>
       <c r="C94" s="7" t="n"/>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
+      <c r="D94" s="7" t="n"/>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="7" t="n"/>
       <c r="G94" s="7" t="n"/>
-      <c r="H94" s="7" t="n"/>
+      <c r="H94" s="7" t="inlineStr">
+        <is>
+          <t>Jalen Hurts</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
@@ -2068,7 +2068,7 @@
       <c r="G95" s="7" t="n"/>
       <c r="H95" s="7" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
@@ -2084,25 +2084,25 @@
       <c r="G96" s="7" t="n"/>
       <c r="H96" s="7" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Jaxson Dart</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B97" s="7" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C97" s="7" t="n"/>
       <c r="D97" s="7" t="n"/>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="7" t="n"/>
       <c r="G97" s="7" t="n"/>
-      <c r="H97" s="7" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H97" s="7" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
@@ -2112,7 +2112,7 @@
       <c r="C98" s="7" t="n"/>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E98" s="7" t="n"/>
@@ -2128,7 +2128,7 @@
       <c r="C99" s="7" t="n"/>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E99" s="7" t="n"/>
@@ -2138,15 +2138,15 @@
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B100" s="7" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B100" s="7" t="n"/>
       <c r="C100" s="7" t="n"/>
-      <c r="D100" s="7" t="n"/>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="7" t="n"/>
       <c r="G100" s="7" t="n"/>
@@ -2295,7 +2295,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 77.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 76.</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 7; 9 players used week 3 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 8; 8 players used week 3 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 83 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 82 players moved.</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.8, WR 2.8, TE 4.5, QB 0.0.</t>
+          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.9, WR 2.8, TE 4.5, QB 0.0.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Puka Nacua 53-&gt;43, Jaxon Smith-Njigba 68-&gt;59, Amon-Ra St. Brown 62-&gt;53, Chris Olave 53-&gt;44, Ja'Marr Chase 68-&gt;60, Justin Jefferson 47-&gt;39, CeeDee Lamb 46-&gt;38, Drake London 45-&gt;37</t>
+          <t>Largest moves vs. the baseline in this file: Puka Nacua 51-&gt;41, Jaxon Smith-Njigba 68-&gt;59, Amon-Ra St. Brown 63-&gt;55, Chris Olave 53-&gt;45, Drake London 45-&gt;37, DeVonta Smith 28-&gt;20, Garrett Wilson 35-&gt;27, Trey McBride 43.4286-&gt;36</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -634,7 +634,7 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B8" s="7" t="n"/>
       <c r="C8" s="7" t="n"/>
@@ -682,15 +682,15 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="B9" s="7" t="n"/>
+        <v>58</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D9" s="7" t="n"/>
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="7" t="n"/>
@@ -700,13 +700,13 @@
       <c r="A10" s="6" t="n">
         <v>58</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+      <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="n"/>
@@ -730,15 +730,15 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="n"/>
@@ -746,15 +746,15 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="B13" s="7" t="n"/>
+        <v>53</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D13" s="7" t="n"/>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
@@ -768,7 +768,7 @@
       <c r="C14" s="7" t="n"/>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>Puka Nacua</t>
         </is>
       </c>
       <c r="E14" s="7" t="n"/>
@@ -794,15 +794,15 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
@@ -812,13 +812,13 @@
       <c r="A17" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="B17" s="7" t="n"/>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D17" s="7" t="n"/>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
@@ -846,7 +846,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="C19" s="7" t="n"/>
@@ -858,11 +858,11 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Saquon Barkley</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C20" s="7" t="n"/>
@@ -874,7 +874,7 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
@@ -890,7 +890,7 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
@@ -922,23 +922,23 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="B24" s="7" t="n"/>
+        <v>35</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
@@ -954,23 +954,23 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
       <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
@@ -1066,15 +1066,15 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="n"/>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
@@ -1084,13 +1084,13 @@
       <c r="A34" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="B34" s="7" t="n"/>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D34" s="7" t="n"/>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="7" t="n"/>
@@ -1098,47 +1098,47 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D35" s="7" t="n"/>
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="7" t="n"/>
-      <c r="H35" s="7" t="n"/>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
-      <c r="D36" s="7" t="n"/>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E36" s="7" t="n"/>
       <c r="F36" s="7" t="n"/>
       <c r="G36" s="7" t="n"/>
-      <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7" t="n"/>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E37" s="7" t="n"/>
       <c r="F37" s="7" t="n"/>
       <c r="G37" s="7" t="n"/>
@@ -1152,7 +1152,7 @@
       <c r="C38" s="7" t="n"/>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E38" s="7" t="n"/>
@@ -1162,15 +1162,15 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="B39" s="7" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C39" s="7" t="n"/>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D39" s="7" t="n"/>
       <c r="E39" s="7" t="n"/>
       <c r="F39" s="7" t="n"/>
       <c r="G39" s="7" t="n"/>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C40" s="7" t="n"/>
@@ -1200,7 +1200,7 @@
       <c r="C41" s="7" t="n"/>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E41" s="7" t="n"/>
@@ -1216,7 +1216,7 @@
       <c r="C42" s="7" t="n"/>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E42" s="7" t="n"/>
@@ -1226,13 +1226,13 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B43" s="7" t="n"/>
       <c r="C43" s="7" t="n"/>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E43" s="7" t="n"/>
@@ -1244,13 +1244,13 @@
       <c r="A44" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+      <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="n"/>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="7" t="n"/>
@@ -1258,15 +1258,15 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B45" s="7" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D45" s="7" t="n"/>
       <c r="E45" s="7" t="n"/>
       <c r="F45" s="7" t="n"/>
       <c r="G45" s="7" t="n"/>
@@ -1306,7 +1306,7 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B48" s="7" t="n"/>
       <c r="C48" s="7" t="n"/>
@@ -1324,13 +1324,13 @@
       <c r="A49" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+      <c r="B49" s="7" t="n"/>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="n"/>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E49" s="7" t="n"/>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n"/>
@@ -1354,31 +1354,31 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B51" s="7" t="n"/>
       <c r="C51" s="7" t="n"/>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
       <c r="F51" s="7" t="n"/>
       <c r="G51" s="7" t="n"/>
-      <c r="H51" s="7" t="n"/>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B52" s="7" t="n"/>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D52" s="7" t="n"/>
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="7" t="n"/>
@@ -1392,7 +1392,7 @@
       <c r="C53" s="7" t="n"/>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E53" s="7" t="n"/>
@@ -1402,15 +1402,15 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
-      <c r="D54" s="7" t="n"/>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E54" s="7" t="n"/>
       <c r="F54" s="7" t="n"/>
       <c r="G54" s="7" t="n"/>
@@ -1420,15 +1420,15 @@
       <c r="A55" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B55" s="7" t="n"/>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C55" s="7" t="n"/>
       <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F55" s="7" t="n"/>
       <c r="G55" s="7" t="n"/>
       <c r="H55" s="7" t="n"/>
     </row>
@@ -1442,7 +1442,7 @@
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Colston Loveland</t>
         </is>
       </c>
       <c r="G56" s="7" t="n"/>
@@ -1516,13 +1516,13 @@
       <c r="A61" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B61" s="7" t="n"/>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
       <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
@@ -1534,15 +1534,15 @@
       </c>
       <c r="B62" s="7" t="n"/>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="n"/>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="7" t="n"/>
-      <c r="H62" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
@@ -1552,13 +1552,13 @@
       <c r="C63" s="7" t="n"/>
       <c r="D63" s="7" t="n"/>
       <c r="E63" s="7" t="n"/>
-      <c r="F63" s="7" t="n"/>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G63" s="7" t="n"/>
-      <c r="H63" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
@@ -1572,25 +1572,25 @@
       <c r="G64" s="7" t="n"/>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B65" s="7" t="n"/>
       <c r="C65" s="7" t="n"/>
       <c r="D65" s="7" t="n"/>
       <c r="E65" s="7" t="n"/>
       <c r="F65" s="7" t="n"/>
       <c r="G65" s="7" t="n"/>
-      <c r="H65" s="7" t="n"/>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C70" s="7" t="n"/>
@@ -1676,13 +1676,13 @@
       <c r="A71" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
+      <c r="B71" s="7" t="n"/>
       <c r="C71" s="7" t="n"/>
-      <c r="D71" s="7" t="n"/>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
@@ -1690,15 +1690,15 @@
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B72" s="7" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C72" s="7" t="n"/>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D72" s="7" t="n"/>
       <c r="E72" s="7" t="n"/>
       <c r="F72" s="7" t="n"/>
       <c r="G72" s="7" t="n"/>
@@ -1706,15 +1706,15 @@
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B73" s="7" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C73" s="7" t="n"/>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D73" s="7" t="n"/>
       <c r="E73" s="7" t="n"/>
       <c r="F73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
@@ -1724,13 +1724,13 @@
       <c r="A74" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B74" s="7" t="n"/>
       <c r="C74" s="7" t="n"/>
-      <c r="D74" s="7" t="n"/>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E74" s="7" t="n"/>
       <c r="F74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
@@ -1744,7 +1744,7 @@
       <c r="C75" s="7" t="n"/>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E75" s="7" t="n"/>
@@ -1776,7 +1776,7 @@
       <c r="C77" s="7" t="n"/>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E77" s="7" t="n"/>
@@ -1790,13 +1790,13 @@
       </c>
       <c r="B78" s="7" t="n"/>
       <c r="C78" s="7" t="n"/>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D78" s="7" t="n"/>
       <c r="E78" s="7" t="n"/>
-      <c r="F78" s="7" t="n"/>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G78" s="7" t="n"/>
       <c r="H78" s="7" t="n"/>
     </row>
@@ -1810,7 +1810,7 @@
       <c r="E79" s="7" t="n"/>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>Harold Fannin Jr.</t>
         </is>
       </c>
       <c r="G79" s="7" t="n"/>
@@ -1818,17 +1818,17 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B80" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>Jonathon Brooks</t>
+        </is>
+      </c>
       <c r="C80" s="7" t="n"/>
       <c r="D80" s="7" t="n"/>
       <c r="E80" s="7" t="n"/>
-      <c r="F80" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F80" s="7" t="n"/>
       <c r="G80" s="7" t="n"/>
       <c r="H80" s="7" t="n"/>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C81" s="7" t="n"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C82" s="7" t="n"/>
@@ -1868,13 +1868,13 @@
       <c r="A83" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>Rico Dowdle</t>
-        </is>
-      </c>
+      <c r="B83" s="7" t="n"/>
       <c r="C83" s="7" t="n"/>
-      <c r="D83" s="7" t="n"/>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E83" s="7" t="n"/>
       <c r="F83" s="7" t="n"/>
       <c r="G83" s="7" t="n"/>
@@ -1888,7 +1888,7 @@
       <c r="C84" s="7" t="n"/>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E84" s="7" t="n"/>
@@ -1952,7 +1952,7 @@
       <c r="C88" s="7" t="n"/>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E88" s="7" t="n"/>
@@ -1966,27 +1966,27 @@
       </c>
       <c r="B89" s="7" t="n"/>
       <c r="C89" s="7" t="n"/>
-      <c r="D89" s="7" t="n"/>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>Quentin Johnston</t>
+        </is>
+      </c>
       <c r="E89" s="7" t="n"/>
       <c r="F89" s="7" t="n"/>
       <c r="G89" s="7" t="n"/>
-      <c r="H89" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H89" s="7" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B90" s="7" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B90" s="7" t="n"/>
       <c r="C90" s="7" t="n"/>
-      <c r="D90" s="7" t="n"/>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>Chris Godwin Jr.</t>
+        </is>
+      </c>
       <c r="E90" s="7" t="n"/>
       <c r="F90" s="7" t="n"/>
       <c r="G90" s="7" t="n"/>
@@ -1994,31 +1994,31 @@
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B91" s="7" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B91" s="7" t="n"/>
       <c r="C91" s="7" t="n"/>
       <c r="D91" s="7" t="n"/>
       <c r="E91" s="7" t="n"/>
       <c r="F91" s="7" t="n"/>
       <c r="G91" s="7" t="n"/>
-      <c r="H91" s="7" t="n"/>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B92" s="7" t="n"/>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C92" s="7" t="n"/>
-      <c r="D92" s="7" t="inlineStr">
-        <is>
-          <t>Chris Godwin Jr.</t>
-        </is>
-      </c>
+      <c r="D92" s="7" t="n"/>
       <c r="E92" s="7" t="n"/>
       <c r="F92" s="7" t="n"/>
       <c r="G92" s="7" t="n"/>
@@ -2028,13 +2028,13 @@
       <c r="A93" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B93" s="7" t="n"/>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C93" s="7" t="n"/>
-      <c r="D93" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
+      <c r="D93" s="7" t="n"/>
       <c r="E93" s="7" t="n"/>
       <c r="F93" s="7" t="n"/>
       <c r="G93" s="7" t="n"/>
@@ -2046,15 +2046,15 @@
       </c>
       <c r="B94" s="7" t="n"/>
       <c r="C94" s="7" t="n"/>
-      <c r="D94" s="7" t="n"/>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="7" t="n"/>
       <c r="G94" s="7" t="n"/>
-      <c r="H94" s="7" t="inlineStr">
-        <is>
-          <t>Jalen Hurts</t>
-        </is>
-      </c>
+      <c r="H94" s="7" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
@@ -2068,7 +2068,7 @@
       <c r="G95" s="7" t="n"/>
       <c r="H95" s="7" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
     </row>
@@ -2084,37 +2084,37 @@
       <c r="G96" s="7" t="n"/>
       <c r="H96" s="7" t="inlineStr">
         <is>
-          <t>Jaxson Dart</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B97" s="7" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B97" s="7" t="n"/>
       <c r="C97" s="7" t="n"/>
       <c r="D97" s="7" t="n"/>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="7" t="n"/>
       <c r="G97" s="7" t="n"/>
-      <c r="H97" s="7" t="n"/>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B98" s="7" t="n"/>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C98" s="7" t="n"/>
-      <c r="D98" s="7" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D98" s="7" t="n"/>
       <c r="E98" s="7" t="n"/>
       <c r="F98" s="7" t="n"/>
       <c r="G98" s="7" t="n"/>
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 8; 8 players used week 3 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 9; 8 players used week 3 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 82 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 83 players moved.</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.9, WR 2.8, TE 4.5, QB 0.0.</t>
+          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.8, WR 2.8, TE 4.5, QB 0.0.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Puka Nacua 51-&gt;41, Jaxon Smith-Njigba 68-&gt;59, Amon-Ra St. Brown 63-&gt;55, Chris Olave 53-&gt;45, Drake London 45-&gt;37, DeVonta Smith 28-&gt;20, Garrett Wilson 35-&gt;27, Trey McBride 43.4286-&gt;36</t>
+          <t>Largest moves vs. the baseline in this file: Puka Nacua 55-&gt;45, Jaxon Smith-Njigba 67-&gt;58, Chris Olave 52-&gt;43, Amon-Ra St. Brown 62-&gt;54, CeeDee Lamb 44-&gt;36, Drake London 44-&gt;36, Garrett Wilson 35-&gt;27, Trey McBride 43.4286-&gt;36</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -668,13 +668,13 @@
       <c r="A8" s="6" t="n">
         <v>59</v>
       </c>
-      <c r="B8" s="7" t="n"/>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D8" s="7" t="n"/>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="7" t="n"/>
@@ -682,15 +682,15 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B9" s="7" t="n"/>
       <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="7" t="n"/>
@@ -730,15 +730,15 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="B12" s="7" t="n"/>
+        <v>57</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D12" s="7" t="n"/>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="n"/>
@@ -746,15 +746,15 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
@@ -762,7 +762,7 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
@@ -794,7 +794,7 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
@@ -826,15 +826,15 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="B18" s="7" t="n"/>
+        <v>39</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
@@ -844,13 +844,13 @@
       <c r="A19" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+      <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
@@ -858,15 +858,15 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
@@ -874,15 +874,15 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="B21" s="7" t="n"/>
+        <v>37</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
@@ -896,7 +896,7 @@
       <c r="C22" s="7" t="n"/>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="E22" s="7" t="n"/>
@@ -922,11 +922,11 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C24" s="7" t="n"/>
@@ -938,39 +938,39 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="B26" s="7" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C26" s="7" t="n"/>
       <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
@@ -986,11 +986,11 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C28" s="7" t="n"/>
@@ -1002,15 +1002,15 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" s="7" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D29" s="7" t="n"/>
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="7" t="n"/>
@@ -1018,11 +1018,11 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C30" s="7" t="n"/>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="C31" s="7" t="n"/>
@@ -1052,13 +1052,13 @@
       <c r="A32" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+      <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
@@ -1120,7 +1120,7 @@
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E36" s="7" t="n"/>
@@ -1130,13 +1130,13 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E37" s="7" t="n"/>
@@ -1200,7 +1200,7 @@
       <c r="C41" s="7" t="n"/>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E41" s="7" t="n"/>
@@ -1242,13 +1242,13 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="n"/>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E44" s="7" t="n"/>
@@ -1258,15 +1258,15 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B45" s="7" t="n"/>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="n"/>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E45" s="7" t="n"/>
       <c r="F45" s="7" t="n"/>
       <c r="G45" s="7" t="n"/>
@@ -1276,13 +1276,13 @@
       <c r="A46" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B46" s="7" t="n"/>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D46" s="7" t="n"/>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="7" t="n"/>
@@ -1306,13 +1306,13 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B48" s="7" t="n"/>
       <c r="C48" s="7" t="n"/>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E48" s="7" t="n"/>
@@ -1322,17 +1322,17 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B49" s="7" t="n"/>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D49" s="7" t="n"/>
       <c r="E49" s="7" t="n"/>
-      <c r="F49" s="7" t="n"/>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G49" s="7" t="n"/>
       <c r="H49" s="7" t="n"/>
     </row>
@@ -1342,43 +1342,43 @@
       </c>
       <c r="B50" s="7" t="n"/>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="n"/>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E50" s="7" t="n"/>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F50" s="7" t="n"/>
       <c r="G50" s="7" t="n"/>
       <c r="H50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B51" s="7" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C51" s="7" t="n"/>
       <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
       <c r="F51" s="7" t="n"/>
       <c r="G51" s="7" t="n"/>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+      <c r="B52" s="7" t="n"/>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="7" t="n"/>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="7" t="n"/>
@@ -1386,15 +1386,15 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B53" s="7" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D53" s="7" t="n"/>
       <c r="E53" s="7" t="n"/>
       <c r="F53" s="7" t="n"/>
       <c r="G53" s="7" t="n"/>
@@ -1402,13 +1402,13 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E54" s="7" t="n"/>
@@ -1420,15 +1420,15 @@
       <c r="A55" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B55" s="7" t="n"/>
       <c r="C55" s="7" t="n"/>
       <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7" t="n"/>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G55" s="7" t="n"/>
       <c r="H55" s="7" t="n"/>
     </row>
@@ -1440,13 +1440,13 @@
       <c r="C56" s="7" t="n"/>
       <c r="D56" s="7" t="n"/>
       <c r="E56" s="7" t="n"/>
-      <c r="F56" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="n"/>
-      <c r="H56" s="7" t="n"/>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
@@ -1554,7 +1554,7 @@
       <c r="E63" s="7" t="n"/>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G63" s="7" t="n"/>
@@ -1568,13 +1568,13 @@
       <c r="C64" s="7" t="n"/>
       <c r="D64" s="7" t="n"/>
       <c r="E64" s="7" t="n"/>
-      <c r="F64" s="7" t="n"/>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G64" s="7" t="n"/>
-      <c r="H64" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
@@ -1588,25 +1588,25 @@
       <c r="G65" s="7" t="n"/>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B66" s="7" t="n"/>
       <c r="C66" s="7" t="n"/>
       <c r="D66" s="7" t="n"/>
       <c r="E66" s="7" t="n"/>
-      <c r="F66" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F66" s="7" t="n"/>
       <c r="G66" s="7" t="n"/>
-      <c r="H66" s="7" t="n"/>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
@@ -1690,15 +1690,15 @@
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B72" s="7" t="n"/>
       <c r="C72" s="7" t="n"/>
-      <c r="D72" s="7" t="n"/>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E72" s="7" t="n"/>
       <c r="F72" s="7" t="n"/>
       <c r="G72" s="7" t="n"/>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C73" s="7" t="n"/>
@@ -1724,13 +1724,13 @@
       <c r="A74" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B74" s="7" t="n"/>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C74" s="7" t="n"/>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
       <c r="F74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
@@ -1744,7 +1744,7 @@
       <c r="C75" s="7" t="n"/>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E75" s="7" t="n"/>
@@ -1760,7 +1760,7 @@
       <c r="C76" s="7" t="n"/>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E76" s="7" t="n"/>
@@ -1774,45 +1774,45 @@
       </c>
       <c r="B77" s="7" t="n"/>
       <c r="C77" s="7" t="n"/>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D77" s="7" t="n"/>
       <c r="E77" s="7" t="n"/>
-      <c r="F77" s="7" t="n"/>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G77" s="7" t="n"/>
       <c r="H77" s="7" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B78" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>Jonathon Brooks</t>
+        </is>
+      </c>
       <c r="C78" s="7" t="n"/>
       <c r="D78" s="7" t="n"/>
       <c r="E78" s="7" t="n"/>
-      <c r="F78" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F78" s="7" t="n"/>
       <c r="G78" s="7" t="n"/>
       <c r="H78" s="7" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B79" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>Mike Washington Jr.</t>
+        </is>
+      </c>
       <c r="C79" s="7" t="n"/>
       <c r="D79" s="7" t="n"/>
       <c r="E79" s="7" t="n"/>
-      <c r="F79" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F79" s="7" t="n"/>
       <c r="G79" s="7" t="n"/>
       <c r="H79" s="7" t="n"/>
     </row>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C80" s="7" t="n"/>
@@ -1836,13 +1836,13 @@
       <c r="A81" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>Mike Washington Jr.</t>
-        </is>
-      </c>
+      <c r="B81" s="7" t="n"/>
       <c r="C81" s="7" t="n"/>
-      <c r="D81" s="7" t="n"/>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E81" s="7" t="n"/>
       <c r="F81" s="7" t="n"/>
       <c r="G81" s="7" t="n"/>
@@ -1852,13 +1852,13 @@
       <c r="A82" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>Rico Dowdle</t>
-        </is>
-      </c>
+      <c r="B82" s="7" t="n"/>
       <c r="C82" s="7" t="n"/>
-      <c r="D82" s="7" t="n"/>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E82" s="7" t="n"/>
       <c r="F82" s="7" t="n"/>
       <c r="G82" s="7" t="n"/>
@@ -1872,7 +1872,7 @@
       <c r="C83" s="7" t="n"/>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E83" s="7" t="n"/>
@@ -1888,7 +1888,7 @@
       <c r="C84" s="7" t="n"/>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E84" s="7" t="n"/>
@@ -1904,7 +1904,7 @@
       <c r="C85" s="7" t="n"/>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E85" s="7" t="n"/>
@@ -1920,7 +1920,7 @@
       <c r="C86" s="7" t="n"/>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E86" s="7" t="n"/>
@@ -1936,7 +1936,7 @@
       <c r="C87" s="7" t="n"/>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E87" s="7" t="n"/>
@@ -1952,7 +1952,7 @@
       <c r="C88" s="7" t="n"/>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E88" s="7" t="n"/>
@@ -1968,7 +1968,7 @@
       <c r="C89" s="7" t="n"/>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E89" s="7" t="n"/>
@@ -1982,13 +1982,13 @@
       </c>
       <c r="B90" s="7" t="n"/>
       <c r="C90" s="7" t="n"/>
-      <c r="D90" s="7" t="inlineStr">
-        <is>
-          <t>Chris Godwin Jr.</t>
-        </is>
-      </c>
+      <c r="D90" s="7" t="n"/>
       <c r="E90" s="7" t="n"/>
-      <c r="F90" s="7" t="n"/>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G90" s="7" t="n"/>
       <c r="H90" s="7" t="n"/>
     </row>
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 9; 8 players used week 3 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 10; 8 players used week 3 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Puka Nacua 55-&gt;45, Jaxon Smith-Njigba 67-&gt;58, Chris Olave 52-&gt;43, Amon-Ra St. Brown 62-&gt;54, CeeDee Lamb 44-&gt;36, Drake London 44-&gt;36, Garrett Wilson 35-&gt;27, Trey McBride 43.4286-&gt;36</t>
+          <t>Largest moves vs. the baseline in this file: Puka Nacua 58-&gt;49, Jaxon Smith-Njigba 67-&gt;58, Chris Olave 51-&gt;42, Amon-Ra St. Brown 62-&gt;54, CeeDee Lamb 44-&gt;36, Garrett Wilson 33-&gt;25, Trey McBride 43.4286-&gt;36, Ja'Marr Chase 66-&gt;59</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -618,7 +618,7 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
@@ -634,11 +634,11 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C6" s="7" t="n"/>
@@ -654,7 +654,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="C7" s="7" t="n"/>
@@ -666,15 +666,15 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="B8" s="7" t="n"/>
       <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="7" t="n"/>
@@ -682,15 +682,15 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="B9" s="7" t="n"/>
+        <v>58</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Jonathan Taylor</t>
+        </is>
+      </c>
       <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D9" s="7" t="n"/>
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="7" t="n"/>
@@ -698,13 +698,13 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E10" s="7" t="n"/>
@@ -714,15 +714,15 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
@@ -730,11 +730,11 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>James Cook III</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C12" s="7" t="n"/>
@@ -746,15 +746,15 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="B13" s="7" t="n"/>
+        <v>55</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D13" s="7" t="n"/>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
@@ -762,13 +762,13 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Puka Nacua</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E14" s="7" t="n"/>
@@ -778,29 +778,29 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="B15" s="7" t="n"/>
+        <v>46</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C15" s="7" t="n"/>
       <c r="D15" s="7" t="n"/>
       <c r="E15" s="7" t="n"/>
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>Justin Jefferson</t>
         </is>
       </c>
       <c r="E16" s="7" t="n"/>
@@ -810,11 +810,11 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="C17" s="7" t="n"/>
@@ -826,31 +826,31 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="n"/>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="B19" s="7" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
@@ -858,13 +858,13 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="E20" s="7" t="n"/>
@@ -874,7 +874,7 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
@@ -890,65 +890,65 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
       <c r="H23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="B25" s="7" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
     </row>
@@ -956,13 +956,13 @@
       <c r="A26" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+      <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
@@ -970,13 +970,13 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Nico Collins</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E27" s="7" t="n"/>
@@ -986,15 +986,15 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="7" t="n"/>
@@ -1002,11 +1002,11 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C29" s="7" t="n"/>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
@@ -1050,15 +1050,15 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="B32" s="7" t="n"/>
+        <v>24</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
@@ -1082,15 +1082,15 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="n"/>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="7" t="n"/>
@@ -1098,23 +1098,23 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="B35" s="7" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C35" s="7" t="n"/>
       <c r="D35" s="7" t="n"/>
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="7" t="n"/>
-      <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
@@ -1130,29 +1130,29 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D37" s="7" t="n"/>
       <c r="E37" s="7" t="n"/>
       <c r="F37" s="7" t="n"/>
       <c r="G37" s="7" t="n"/>
-      <c r="H37" s="7" t="n"/>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E38" s="7" t="n"/>
@@ -1164,13 +1164,13 @@
       <c r="A39" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+      <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
-      <c r="D39" s="7" t="n"/>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E39" s="7" t="n"/>
       <c r="F39" s="7" t="n"/>
       <c r="G39" s="7" t="n"/>
@@ -1178,11 +1178,11 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C40" s="7" t="n"/>
@@ -1194,13 +1194,13 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E41" s="7" t="n"/>
@@ -1210,13 +1210,13 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B42" s="7" t="n"/>
       <c r="C42" s="7" t="n"/>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E42" s="7" t="n"/>
@@ -1226,15 +1226,15 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B43" s="7" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C43" s="7" t="n"/>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D43" s="7" t="n"/>
       <c r="E43" s="7" t="n"/>
       <c r="F43" s="7" t="n"/>
       <c r="G43" s="7" t="n"/>
@@ -1242,7 +1242,7 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="n"/>
@@ -1258,15 +1258,15 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B45" s="7" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D45" s="7" t="n"/>
       <c r="E45" s="7" t="n"/>
       <c r="F45" s="7" t="n"/>
       <c r="G45" s="7" t="n"/>
@@ -1276,29 +1276,29 @@
       <c r="A46" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+      <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
       <c r="D46" s="7" t="n"/>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="7" t="n"/>
-      <c r="H46" s="7" t="n"/>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="n"/>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E47" s="7" t="n"/>
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="7" t="n"/>
@@ -1306,15 +1306,15 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B48" s="7" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D48" s="7" t="n"/>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
@@ -1322,7 +1322,7 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B49" s="7" t="n"/>
       <c r="C49" s="7" t="n"/>
@@ -1338,15 +1338,15 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B50" s="7" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
       <c r="F50" s="7" t="n"/>
       <c r="G50" s="7" t="n"/>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C51" s="7" t="n"/>
@@ -1372,13 +1372,13 @@
       <c r="A52" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B52" s="7" t="n"/>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D52" s="7" t="n"/>
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="7" t="n"/>
@@ -1386,7 +1386,7 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
@@ -1402,13 +1402,13 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E54" s="7" t="n"/>
@@ -1418,63 +1418,63 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B55" s="7" t="n"/>
       <c r="C55" s="7" t="n"/>
-      <c r="D55" s="7" t="n"/>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F55" s="7" t="n"/>
       <c r="G55" s="7" t="n"/>
       <c r="H55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B56" s="7" t="n"/>
       <c r="C56" s="7" t="n"/>
-      <c r="D56" s="7" t="n"/>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="n"/>
-      <c r="H56" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B57" s="7" t="n"/>
       <c r="C57" s="7" t="n"/>
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
-      <c r="F57" s="7" t="n"/>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G57" s="7" t="n"/>
       <c r="H57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B58" s="7" t="n"/>
       <c r="C58" s="7" t="n"/>
-      <c r="D58" s="7" t="n"/>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E58" s="7" t="n"/>
       <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n"/>
@@ -1482,17 +1482,17 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B59" s="7" t="n"/>
       <c r="C59" s="7" t="n"/>
       <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
-      <c r="F59" s="7" t="n"/>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G59" s="7" t="n"/>
       <c r="H59" s="7" t="n"/>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C60" s="7" t="n"/>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C61" s="7" t="n"/>
@@ -1532,13 +1532,13 @@
       <c r="A62" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B62" s="7" t="n"/>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D62" s="7" t="n"/>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="7" t="n"/>
@@ -1550,13 +1550,13 @@
       </c>
       <c r="B63" s="7" t="n"/>
       <c r="C63" s="7" t="n"/>
-      <c r="D63" s="7" t="n"/>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E63" s="7" t="n"/>
-      <c r="F63" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F63" s="7" t="n"/>
       <c r="G63" s="7" t="n"/>
       <c r="H63" s="7" t="n"/>
     </row>
@@ -1566,13 +1566,13 @@
       </c>
       <c r="B64" s="7" t="n"/>
       <c r="C64" s="7" t="n"/>
-      <c r="D64" s="7" t="n"/>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E64" s="7" t="n"/>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F64" s="7" t="n"/>
       <c r="G64" s="7" t="n"/>
       <c r="H64" s="7" t="n"/>
     </row>
@@ -1584,13 +1584,13 @@
       <c r="C65" s="7" t="n"/>
       <c r="D65" s="7" t="n"/>
       <c r="E65" s="7" t="n"/>
-      <c r="F65" s="7" t="n"/>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G65" s="7" t="n"/>
-      <c r="H65" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H65" s="7" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
@@ -1600,17 +1600,17 @@
       <c r="C66" s="7" t="n"/>
       <c r="D66" s="7" t="n"/>
       <c r="E66" s="7" t="n"/>
-      <c r="F66" s="7" t="n"/>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G66" s="7" t="n"/>
-      <c r="H66" s="7" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B67" s="7" t="n"/>
       <c r="C67" s="7" t="n"/>
@@ -1620,33 +1620,33 @@
       <c r="G67" s="7" t="n"/>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>Drake Maye</t>
+          <t>Joe Burrow</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B68" s="7" t="n"/>
       <c r="C68" s="7" t="n"/>
       <c r="D68" s="7" t="n"/>
       <c r="E68" s="7" t="n"/>
       <c r="F68" s="7" t="n"/>
       <c r="G68" s="7" t="n"/>
-      <c r="H68" s="7" t="n"/>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C69" s="7" t="n"/>
@@ -1658,11 +1658,11 @@
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="C70" s="7" t="n"/>
@@ -1674,31 +1674,31 @@
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B71" s="7" t="n"/>
       <c r="C71" s="7" t="n"/>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D71" s="7" t="n"/>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
-      <c r="H71" s="7" t="n"/>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B72" s="7" t="n"/>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
       <c r="C72" s="7" t="n"/>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D72" s="7" t="n"/>
       <c r="E72" s="7" t="n"/>
       <c r="F72" s="7" t="n"/>
       <c r="G72" s="7" t="n"/>
@@ -1706,11 +1706,11 @@
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr.</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C73" s="7" t="n"/>
@@ -1722,15 +1722,15 @@
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B74" s="7" t="n"/>
       <c r="C74" s="7" t="n"/>
-      <c r="D74" s="7" t="n"/>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E74" s="7" t="n"/>
       <c r="F74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
@@ -1744,7 +1744,7 @@
       <c r="C75" s="7" t="n"/>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E75" s="7" t="n"/>
@@ -1760,7 +1760,7 @@
       <c r="C76" s="7" t="n"/>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E76" s="7" t="n"/>
@@ -1774,13 +1774,13 @@
       </c>
       <c r="B77" s="7" t="n"/>
       <c r="C77" s="7" t="n"/>
-      <c r="D77" s="7" t="n"/>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>Marvin Harrison Jr.</t>
+        </is>
+      </c>
       <c r="E77" s="7" t="n"/>
-      <c r="F77" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F77" s="7" t="n"/>
       <c r="G77" s="7" t="n"/>
       <c r="H77" s="7" t="n"/>
     </row>
@@ -1836,13 +1836,13 @@
       <c r="A81" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B81" s="7" t="n"/>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>J.K. Dobbins</t>
+        </is>
+      </c>
       <c r="C81" s="7" t="n"/>
-      <c r="D81" s="7" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D81" s="7" t="n"/>
       <c r="E81" s="7" t="n"/>
       <c r="F81" s="7" t="n"/>
       <c r="G81" s="7" t="n"/>
@@ -1852,13 +1852,13 @@
       <c r="A82" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B82" s="7" t="n"/>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C82" s="7" t="n"/>
-      <c r="D82" s="7" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D82" s="7" t="n"/>
       <c r="E82" s="7" t="n"/>
       <c r="F82" s="7" t="n"/>
       <c r="G82" s="7" t="n"/>
@@ -1872,7 +1872,7 @@
       <c r="C83" s="7" t="n"/>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E83" s="7" t="n"/>
@@ -1888,7 +1888,7 @@
       <c r="C84" s="7" t="n"/>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E84" s="7" t="n"/>
@@ -1904,7 +1904,7 @@
       <c r="C85" s="7" t="n"/>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E85" s="7" t="n"/>
@@ -1920,7 +1920,7 @@
       <c r="C86" s="7" t="n"/>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E86" s="7" t="n"/>
@@ -1936,7 +1936,7 @@
       <c r="C87" s="7" t="n"/>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E87" s="7" t="n"/>
@@ -1952,7 +1952,7 @@
       <c r="C88" s="7" t="n"/>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E88" s="7" t="n"/>
@@ -1966,13 +1966,13 @@
       </c>
       <c r="B89" s="7" t="n"/>
       <c r="C89" s="7" t="n"/>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>Chris Godwin Jr.</t>
-        </is>
-      </c>
+      <c r="D89" s="7" t="n"/>
       <c r="E89" s="7" t="n"/>
-      <c r="F89" s="7" t="n"/>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G89" s="7" t="n"/>
       <c r="H89" s="7" t="n"/>
     </row>
@@ -1984,13 +1984,13 @@
       <c r="C90" s="7" t="n"/>
       <c r="D90" s="7" t="n"/>
       <c r="E90" s="7" t="n"/>
-      <c r="F90" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F90" s="7" t="n"/>
       <c r="G90" s="7" t="n"/>
-      <c r="H90" s="7" t="n"/>
+      <c r="H90" s="7" t="inlineStr">
+        <is>
+          <t>Jalen Hurts</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
@@ -2004,25 +2004,25 @@
       <c r="G91" s="7" t="n"/>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B92" s="7" t="n"/>
       <c r="C92" s="7" t="n"/>
       <c r="D92" s="7" t="n"/>
       <c r="E92" s="7" t="n"/>
       <c r="F92" s="7" t="n"/>
       <c r="G92" s="7" t="n"/>
-      <c r="H92" s="7" t="n"/>
+      <c r="H92" s="7" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
@@ -2048,7 +2048,7 @@
       <c r="C94" s="7" t="n"/>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E94" s="7" t="n"/>
@@ -2062,15 +2062,15 @@
       </c>
       <c r="B95" s="7" t="n"/>
       <c r="C95" s="7" t="n"/>
-      <c r="D95" s="7" t="n"/>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>Terry McLaurin</t>
+        </is>
+      </c>
       <c r="E95" s="7" t="n"/>
       <c r="F95" s="7" t="n"/>
       <c r="G95" s="7" t="n"/>
-      <c r="H95" s="7" t="inlineStr">
-        <is>
-          <t>Jalen Hurts</t>
-        </is>
-      </c>
+      <c r="H95" s="7" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
@@ -2078,15 +2078,15 @@
       </c>
       <c r="B96" s="7" t="n"/>
       <c r="C96" s="7" t="n"/>
-      <c r="D96" s="7" t="n"/>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="7" t="n"/>
       <c r="G96" s="7" t="n"/>
-      <c r="H96" s="7" t="inlineStr">
-        <is>
-          <t>Justin Herbert</t>
-        </is>
-      </c>
+      <c r="H96" s="7" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
@@ -2128,7 +2128,7 @@
       <c r="C99" s="7" t="n"/>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E99" s="7" t="n"/>
@@ -2144,7 +2144,7 @@
       <c r="C100" s="7" t="n"/>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E100" s="7" t="n"/>
@@ -2154,13 +2154,13 @@
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B101" s="7" t="n"/>
       <c r="C101" s="7" t="n"/>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E101" s="7" t="n"/>
@@ -2170,13 +2170,13 @@
     </row>
     <row r="102">
       <c r="A102" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B102" s="7" t="n"/>
       <c r="C102" s="7" t="n"/>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E102" s="7" t="n"/>
@@ -2192,7 +2192,7 @@
       <c r="C103" s="7" t="n"/>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E103" s="7" t="n"/>
@@ -2208,7 +2208,7 @@
       <c r="C104" s="7" t="n"/>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E104" s="7" t="n"/>
@@ -2218,15 +2218,15 @@
     </row>
     <row r="105">
       <c r="A105" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B105" s="7" t="inlineStr">
-        <is>
-          <t>Kenny Gainwell</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B105" s="7" t="n"/>
       <c r="C105" s="7" t="n"/>
-      <c r="D105" s="7" t="n"/>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>Jordyn Tyson</t>
+        </is>
+      </c>
       <c r="E105" s="7" t="n"/>
       <c r="F105" s="7" t="n"/>
       <c r="G105" s="7" t="n"/>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>Rachaad White</t>
+          <t>Kenny Gainwell</t>
         </is>
       </c>
       <c r="C106" s="7" t="n"/>
@@ -2252,13 +2252,13 @@
       <c r="A107" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B107" s="7" t="n"/>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>Rachaad White</t>
+        </is>
+      </c>
       <c r="C107" s="7" t="n"/>
-      <c r="D107" s="7" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D107" s="7" t="n"/>
       <c r="E107" s="7" t="n"/>
       <c r="F107" s="7" t="n"/>
       <c r="G107" s="7" t="n"/>
@@ -2295,7 +2295,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 76.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 75.</t>
         </is>
       </c>
     </row>
@@ -2312,14 +2312,14 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>0) Weekly re-seed. The sheet values were first moved toward the 2026 week 4 Half PPR medians</t>
+          <t>0) Weekly re-seed. The sheet values were first moved toward the 2026 week 5 Half PPR medians</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 10; 8 players used week 3 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 0; 25 players used week 4 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,14 +2333,14 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 83 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 73 players moved.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   No projection this week (value kept): Josh Jacobs, De'Zhaun Stribling, Jayden Daniels, Jordan Mason, Alec Pierce, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Jaxson Dart, Ja'Kobi Lane.</t>
+          <t xml:space="preserve">   No projection this week (value kept): Justin Jefferson, A.J. Brown, Breece Hall, Travis Etienne Jr., Josh Jacobs, De'Zhaun Stribling, Jordan Mason, Alec Pierce, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Blake Corum, Kenny Gainwell, Jaxson Dart, Rachaad White, Ja'Kobi Lane.</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.8, WR 2.8, TE 4.5, QB 0.0.</t>
+          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.8, WR 2.6, TE 4.5, QB 0.0.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Puka Nacua 58-&gt;49, Jaxon Smith-Njigba 67-&gt;58, Chris Olave 51-&gt;42, Amon-Ra St. Brown 62-&gt;54, CeeDee Lamb 44-&gt;36, Garrett Wilson 33-&gt;25, Trey McBride 43.4286-&gt;36, Ja'Marr Chase 66-&gt;59</t>
+          <t>Largest moves vs. the baseline in this file: Chris Olave 41-&gt;32, Puka Nacua 68-&gt;60, Jaxon Smith-Njigba 64-&gt;56, Trey McBride 42.8571-&gt;35, Ja'Marr Chase 64-&gt;57, Amon-Ra St. Brown 62-&gt;55, Justin Jefferson 53-&gt;46, CeeDee Lamb 49-&gt;42</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -778,15 +778,15 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="B15" s="7" t="n"/>
       <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E15" s="7" t="n"/>
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="7" t="n"/>
@@ -796,13 +796,13 @@
       <c r="A16" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="B16" s="7" t="n"/>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D16" s="7" t="n"/>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
@@ -810,7 +810,7 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
@@ -842,15 +842,15 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
@@ -860,13 +860,13 @@
       <c r="A20" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="B20" s="7" t="n"/>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
@@ -906,7 +906,7 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
@@ -926,29 +926,29 @@
       </c>
       <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
     </row>
@@ -956,13 +956,13 @@
       <c r="A26" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="B26" s="7" t="n"/>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E36" s="7" t="n"/>
@@ -1134,31 +1134,31 @@
       </c>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7" t="n"/>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E37" s="7" t="n"/>
       <c r="F37" s="7" t="n"/>
       <c r="G37" s="7" t="n"/>
-      <c r="H37" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>DeVonta Smith</t>
-        </is>
-      </c>
+      <c r="D38" s="7" t="n"/>
       <c r="E38" s="7" t="n"/>
       <c r="F38" s="7" t="n"/>
       <c r="G38" s="7" t="n"/>
-      <c r="H38" s="7" t="n"/>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
@@ -1168,7 +1168,7 @@
       <c r="C39" s="7" t="n"/>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E39" s="7" t="n"/>
@@ -1212,13 +1212,13 @@
       <c r="A42" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B42" s="7" t="n"/>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D42" s="7" t="n"/>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="7" t="n"/>
@@ -1228,13 +1228,13 @@
       <c r="A43" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B43" s="7" t="n"/>
       <c r="C43" s="7" t="n"/>
-      <c r="D43" s="7" t="n"/>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E43" s="7" t="n"/>
       <c r="F43" s="7" t="n"/>
       <c r="G43" s="7" t="n"/>
@@ -1246,15 +1246,15 @@
       </c>
       <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D44" s="7" t="n"/>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="7" t="n"/>
-      <c r="H44" s="7" t="n"/>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
@@ -1278,15 +1278,15 @@
       </c>
       <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="n"/>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="7" t="n"/>
-      <c r="H46" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
@@ -1326,29 +1326,29 @@
       </c>
       <c r="B49" s="7" t="n"/>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="n"/>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E49" s="7" t="n"/>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n"/>
       <c r="H49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B50" s="7" t="n"/>
       <c r="C50" s="7" t="n"/>
       <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
-      <c r="F50" s="7" t="n"/>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G50" s="7" t="n"/>
       <c r="H50" s="7" t="n"/>
     </row>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="C51" s="7" t="n"/>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C52" s="7" t="n"/>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C53" s="7" t="n"/>
@@ -1408,7 +1408,7 @@
       <c r="C54" s="7" t="n"/>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E54" s="7" t="n"/>
@@ -1424,7 +1424,7 @@
       <c r="C55" s="7" t="n"/>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E55" s="7" t="n"/>
@@ -1434,15 +1434,15 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B56" s="7" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C56" s="7" t="n"/>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D56" s="7" t="n"/>
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="n"/>
@@ -1450,17 +1450,17 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B57" s="7" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C57" s="7" t="n"/>
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
       <c r="H57" s="7" t="n"/>
     </row>
@@ -1472,7 +1472,7 @@
       <c r="C58" s="7" t="n"/>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E58" s="7" t="n"/>
@@ -1486,29 +1486,29 @@
       </c>
       <c r="B59" s="7" t="n"/>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="7" t="n"/>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E59" s="7" t="n"/>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F59" s="7" t="n"/>
       <c r="G59" s="7" t="n"/>
       <c r="H59" s="7" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B60" s="7" t="n"/>
       <c r="C60" s="7" t="n"/>
       <c r="D60" s="7" t="n"/>
       <c r="E60" s="7" t="n"/>
-      <c r="F60" s="7" t="n"/>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G60" s="7" t="n"/>
       <c r="H60" s="7" t="n"/>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C61" s="7" t="n"/>
@@ -1532,13 +1532,13 @@
       <c r="A62" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B62" s="7" t="n"/>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="n"/>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="7" t="n"/>
@@ -1550,13 +1550,13 @@
       </c>
       <c r="B63" s="7" t="n"/>
       <c r="C63" s="7" t="n"/>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D63" s="7" t="n"/>
       <c r="E63" s="7" t="n"/>
-      <c r="F63" s="7" t="n"/>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G63" s="7" t="n"/>
       <c r="H63" s="7" t="n"/>
     </row>
@@ -1566,13 +1566,13 @@
       </c>
       <c r="B64" s="7" t="n"/>
       <c r="C64" s="7" t="n"/>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D64" s="7" t="n"/>
       <c r="E64" s="7" t="n"/>
-      <c r="F64" s="7" t="n"/>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G64" s="7" t="n"/>
       <c r="H64" s="7" t="n"/>
     </row>
@@ -1584,109 +1584,109 @@
       <c r="C65" s="7" t="n"/>
       <c r="D65" s="7" t="n"/>
       <c r="E65" s="7" t="n"/>
-      <c r="F65" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F65" s="7" t="n"/>
       <c r="G65" s="7" t="n"/>
-      <c r="H65" s="7" t="n"/>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B66" s="7" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C66" s="7" t="n"/>
       <c r="D66" s="7" t="n"/>
       <c r="E66" s="7" t="n"/>
-      <c r="F66" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F66" s="7" t="n"/>
       <c r="G66" s="7" t="n"/>
       <c r="H66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B67" s="7" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C67" s="7" t="n"/>
       <c r="D67" s="7" t="n"/>
       <c r="E67" s="7" t="n"/>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
-      <c r="H67" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B68" s="7" t="n"/>
       <c r="C68" s="7" t="n"/>
       <c r="D68" s="7" t="n"/>
       <c r="E68" s="7" t="n"/>
-      <c r="F68" s="7" t="n"/>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G68" s="7" t="n"/>
-      <c r="H68" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+      <c r="B69" s="7" t="n"/>
       <c r="C69" s="7" t="n"/>
       <c r="D69" s="7" t="n"/>
       <c r="E69" s="7" t="n"/>
       <c r="F69" s="7" t="n"/>
       <c r="G69" s="7" t="n"/>
-      <c r="H69" s="7" t="n"/>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+      <c r="B70" s="7" t="n"/>
       <c r="C70" s="7" t="n"/>
       <c r="D70" s="7" t="n"/>
       <c r="E70" s="7" t="n"/>
       <c r="F70" s="7" t="n"/>
       <c r="G70" s="7" t="n"/>
-      <c r="H70" s="7" t="n"/>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B71" s="7" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C71" s="7" t="n"/>
       <c r="D71" s="7" t="n"/>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
-      <c r="H71" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H71" s="7" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
@@ -1708,13 +1708,13 @@
       <c r="A73" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+      <c r="B73" s="7" t="n"/>
       <c r="C73" s="7" t="n"/>
-      <c r="D73" s="7" t="n"/>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E73" s="7" t="n"/>
       <c r="F73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
@@ -1722,15 +1722,15 @@
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B74" s="7" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C74" s="7" t="n"/>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
       <c r="F74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C78" s="7" t="n"/>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C79" s="7" t="n"/>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C80" s="7" t="n"/>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C81" s="7" t="n"/>
@@ -1872,7 +1872,7 @@
       <c r="C83" s="7" t="n"/>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E83" s="7" t="n"/>
@@ -2048,7 +2048,7 @@
       <c r="C94" s="7" t="n"/>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E94" s="7" t="n"/>
@@ -2064,7 +2064,7 @@
       <c r="C95" s="7" t="n"/>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E95" s="7" t="n"/>
@@ -2128,7 +2128,7 @@
       <c r="C99" s="7" t="n"/>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E99" s="7" t="n"/>
@@ -2144,7 +2144,7 @@
       <c r="C100" s="7" t="n"/>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E100" s="7" t="n"/>
@@ -2160,7 +2160,7 @@
       <c r="C101" s="7" t="n"/>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E101" s="7" t="n"/>
@@ -2170,13 +2170,13 @@
     </row>
     <row r="102">
       <c r="A102" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B102" s="7" t="n"/>
       <c r="C102" s="7" t="n"/>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E102" s="7" t="n"/>
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 0; 25 players used week 4 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 1; 24 players used week 4 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 73 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 76 players moved.</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.8, WR 2.6, TE 4.5, QB 0.0.</t>
+          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.8, WR 2.8, TE 4.5, QB 0.0.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Chris Olave 41-&gt;32, Puka Nacua 68-&gt;60, Jaxon Smith-Njigba 64-&gt;56, Trey McBride 42.8571-&gt;35, Ja'Marr Chase 64-&gt;57, Amon-Ra St. Brown 62-&gt;55, Justin Jefferson 53-&gt;46, CeeDee Lamb 49-&gt;42</t>
+          <t>Largest moves vs. the baseline in this file: Puka Nacua 68-&gt;60, Jaxon Smith-Njigba 64-&gt;56, Chris Olave 41-&gt;33, Trey McBride 42.8571-&gt;35, Ja'Marr Chase 64-&gt;57, Amon-Ra St. Brown 62-&gt;55, CeeDee Lamb 50-&gt;43, Drake London 41-&gt;34</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -652,13 +652,13 @@
       <c r="A7" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+      <c r="B7" s="7" t="n"/>
       <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="7" t="n"/>
@@ -666,15 +666,15 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="B8" s="7" t="n"/>
+        <v>58</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D8" s="7" t="n"/>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="7" t="n"/>
@@ -698,15 +698,15 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="B10" s="7" t="n"/>
+        <v>58</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="n"/>
@@ -714,13 +714,13 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -730,15 +730,15 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="n"/>
@@ -748,13 +748,13 @@
       <c r="A13" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+      <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
@@ -762,15 +762,15 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="B14" s="7" t="n"/>
+        <v>49</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D14" s="7" t="n"/>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
@@ -780,13 +780,13 @@
       <c r="A15" s="6" t="n">
         <v>47</v>
       </c>
-      <c r="B15" s="7" t="n"/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D15" s="7" t="n"/>
       <c r="E15" s="7" t="n"/>
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="7" t="n"/>
@@ -796,13 +796,13 @@
       <c r="A16" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+      <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
@@ -810,7 +810,7 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
@@ -926,29 +926,29 @@
       </c>
       <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="B25" s="7" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
     </row>
@@ -956,13 +956,13 @@
       <c r="A26" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+      <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
@@ -1226,7 +1226,7 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B43" s="7" t="n"/>
       <c r="C43" s="7" t="n"/>
@@ -1322,15 +1322,15 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B49" s="7" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D49" s="7" t="n"/>
       <c r="E49" s="7" t="n"/>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n"/>
@@ -1338,17 +1338,17 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B50" s="7" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C50" s="7" t="n"/>
       <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F50" s="7" t="n"/>
       <c r="G50" s="7" t="n"/>
       <c r="H50" s="7" t="n"/>
     </row>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C51" s="7" t="n"/>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Jadarian Price</t>
         </is>
       </c>
       <c r="C52" s="7" t="n"/>
@@ -1388,13 +1388,13 @@
       <c r="A53" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+      <c r="B53" s="7" t="n"/>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="7" t="n"/>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E53" s="7" t="n"/>
       <c r="F53" s="7" t="n"/>
       <c r="G53" s="7" t="n"/>
@@ -1434,33 +1434,33 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B56" s="7" t="n"/>
       <c r="C56" s="7" t="n"/>
       <c r="D56" s="7" t="n"/>
       <c r="E56" s="7" t="n"/>
-      <c r="F56" s="7" t="n"/>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G56" s="7" t="n"/>
       <c r="H56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B57" s="7" t="n"/>
       <c r="C57" s="7" t="n"/>
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
-      <c r="F57" s="7" t="n"/>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G57" s="7" t="n"/>
       <c r="H57" s="7" t="n"/>
     </row>
@@ -1468,13 +1468,13 @@
       <c r="A58" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B58" s="7" t="n"/>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C58" s="7" t="n"/>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
       <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n"/>
@@ -1498,17 +1498,17 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B60" s="7" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C60" s="7" t="n"/>
       <c r="D60" s="7" t="n"/>
       <c r="E60" s="7" t="n"/>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F60" s="7" t="n"/>
       <c r="G60" s="7" t="n"/>
       <c r="H60" s="7" t="n"/>
     </row>
@@ -1516,13 +1516,13 @@
       <c r="A61" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="n"/>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E61" s="7" t="n"/>
       <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
@@ -1872,7 +1872,7 @@
       <c r="C83" s="7" t="n"/>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E83" s="7" t="n"/>
@@ -1888,7 +1888,7 @@
       <c r="C84" s="7" t="n"/>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E84" s="7" t="n"/>
@@ -1904,7 +1904,7 @@
       <c r="C85" s="7" t="n"/>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E85" s="7" t="n"/>
@@ -1920,7 +1920,7 @@
       <c r="C86" s="7" t="n"/>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E86" s="7" t="n"/>
@@ -1936,7 +1936,7 @@
       <c r="C87" s="7" t="n"/>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E87" s="7" t="n"/>
@@ -1950,13 +1950,13 @@
       </c>
       <c r="B88" s="7" t="n"/>
       <c r="C88" s="7" t="n"/>
-      <c r="D88" s="7" t="inlineStr">
-        <is>
-          <t>Chris Godwin Jr.</t>
-        </is>
-      </c>
+      <c r="D88" s="7" t="n"/>
       <c r="E88" s="7" t="n"/>
-      <c r="F88" s="7" t="n"/>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G88" s="7" t="n"/>
       <c r="H88" s="7" t="n"/>
     </row>
@@ -1968,13 +1968,13 @@
       <c r="C89" s="7" t="n"/>
       <c r="D89" s="7" t="n"/>
       <c r="E89" s="7" t="n"/>
-      <c r="F89" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F89" s="7" t="n"/>
       <c r="G89" s="7" t="n"/>
-      <c r="H89" s="7" t="n"/>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>Jalen Hurts</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
@@ -1988,7 +1988,7 @@
       <c r="G90" s="7" t="n"/>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
@@ -2004,37 +2004,37 @@
       <c r="G91" s="7" t="n"/>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B92" s="7" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C92" s="7" t="n"/>
       <c r="D92" s="7" t="n"/>
       <c r="E92" s="7" t="n"/>
       <c r="F92" s="7" t="n"/>
       <c r="G92" s="7" t="n"/>
-      <c r="H92" s="7" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+      <c r="B93" s="7" t="n"/>
       <c r="C93" s="7" t="n"/>
-      <c r="D93" s="7" t="n"/>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E93" s="7" t="n"/>
       <c r="F93" s="7" t="n"/>
       <c r="G93" s="7" t="n"/>
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 1; 24 players used week 4 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 2; 23 players used week 4 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 76 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 77 players moved.</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.8, WR 2.8, TE 4.5, QB 0.0.</t>
+          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.8, WR 2.6, TE 4.5, QB 0.0.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Puka Nacua 68-&gt;60, Jaxon Smith-Njigba 64-&gt;56, Chris Olave 41-&gt;33, Trey McBride 42.8571-&gt;35, Ja'Marr Chase 64-&gt;57, Amon-Ra St. Brown 62-&gt;55, CeeDee Lamb 50-&gt;43, Drake London 41-&gt;34</t>
+          <t>Largest moves vs. the baseline in this file: Chris Olave 41-&gt;32, Puka Nacua 68-&gt;60, Jaxon Smith-Njigba 64-&gt;56, Trey McBride 42.8571-&gt;35, Ja'Marr Chase 64-&gt;57, Amon-Ra St. Brown 62-&gt;55, Justin Jefferson 53-&gt;46, CeeDee Lamb 50-&gt;43</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -618,7 +618,7 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B7" s="7" t="n"/>
       <c r="C7" s="7" t="n"/>
@@ -666,11 +666,11 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C8" s="7" t="n"/>
@@ -682,11 +682,11 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>James Cook III</t>
         </is>
       </c>
       <c r="C9" s="7" t="n"/>
@@ -698,15 +698,15 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="n"/>
@@ -714,15 +714,15 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="B11" s="7" t="n"/>
+        <v>54</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D11" s="7" t="n"/>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
@@ -730,7 +730,7 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
@@ -746,7 +746,7 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
@@ -762,11 +762,11 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Ashton Jeanty</t>
         </is>
       </c>
       <c r="C14" s="7" t="n"/>
@@ -778,11 +778,11 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="C15" s="7" t="n"/>
@@ -794,15 +794,15 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="B16" s="7" t="n"/>
+        <v>45</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D16" s="7" t="n"/>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
@@ -812,13 +812,13 @@
       <c r="A17" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+      <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
@@ -842,7 +842,7 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
@@ -858,7 +858,7 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
@@ -910,29 +910,29 @@
       </c>
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G23" s="7" t="n"/>
       <c r="H23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="B24" s="7" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
     </row>
@@ -940,13 +940,13 @@
       <c r="A25" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+      <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E25" s="7" t="n"/>
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
@@ -954,15 +954,15 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B26" s="7" t="n"/>
+        <v>31</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
@@ -970,7 +970,7 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
@@ -986,7 +986,7 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
@@ -1004,13 +1004,13 @@
       <c r="A29" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+      <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="7" t="n"/>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
@@ -1082,15 +1082,15 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="B34" s="7" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D34" s="7" t="n"/>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="7" t="n"/>
@@ -1098,15 +1098,15 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
-      <c r="D35" s="7" t="n"/>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="7" t="n"/>
@@ -1114,31 +1114,31 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D36" s="7" t="n"/>
       <c r="E36" s="7" t="n"/>
       <c r="F36" s="7" t="n"/>
       <c r="G36" s="7" t="n"/>
-      <c r="H36" s="7" t="n"/>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="B37" s="7" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D37" s="7" t="n"/>
       <c r="E37" s="7" t="n"/>
       <c r="F37" s="7" t="n"/>
       <c r="G37" s="7" t="n"/>
@@ -1146,29 +1146,29 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="n"/>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E38" s="7" t="n"/>
       <c r="F38" s="7" t="n"/>
       <c r="G38" s="7" t="n"/>
-      <c r="H38" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E39" s="7" t="n"/>
@@ -1178,15 +1178,15 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="n"/>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="C42" s="7" t="n"/>
@@ -1228,13 +1228,13 @@
       <c r="A43" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B43" s="7" t="n"/>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C43" s="7" t="n"/>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D43" s="7" t="n"/>
       <c r="E43" s="7" t="n"/>
       <c r="F43" s="7" t="n"/>
       <c r="G43" s="7" t="n"/>
@@ -1246,27 +1246,27 @@
       </c>
       <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="n"/>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="7" t="n"/>
-      <c r="H44" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H44" s="7" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+      <c r="B45" s="7" t="n"/>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="n"/>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E45" s="7" t="n"/>
       <c r="F45" s="7" t="n"/>
       <c r="G45" s="7" t="n"/>
@@ -1280,7 +1280,7 @@
       <c r="C46" s="7" t="n"/>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E46" s="7" t="n"/>
@@ -1294,19 +1294,19 @@
       </c>
       <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D47" s="7" t="n"/>
       <c r="E47" s="7" t="n"/>
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="7" t="n"/>
-      <c r="H47" s="7" t="n"/>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
@@ -1372,13 +1372,13 @@
       <c r="A52" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B52" s="7" t="n"/>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="7" t="n"/>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="7" t="n"/>
@@ -1392,7 +1392,7 @@
       <c r="C53" s="7" t="n"/>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E53" s="7" t="n"/>
@@ -1406,27 +1406,27 @@
       </c>
       <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D54" s="7" t="n"/>
       <c r="E54" s="7" t="n"/>
       <c r="F54" s="7" t="n"/>
       <c r="G54" s="7" t="n"/>
-      <c r="H54" s="7" t="n"/>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B55" s="7" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C55" s="7" t="n"/>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
       <c r="F55" s="7" t="n"/>
       <c r="G55" s="7" t="n"/>
@@ -1434,33 +1434,33 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B56" s="7" t="n"/>
       <c r="C56" s="7" t="n"/>
-      <c r="D56" s="7" t="n"/>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E56" s="7" t="n"/>
-      <c r="F56" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="n"/>
       <c r="H56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B57" s="7" t="n"/>
       <c r="C57" s="7" t="n"/>
-      <c r="D57" s="7" t="n"/>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E57" s="7" t="n"/>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
       <c r="H57" s="7" t="n"/>
     </row>
@@ -1468,15 +1468,15 @@
       <c r="A58" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+      <c r="B58" s="7" t="n"/>
       <c r="C58" s="7" t="n"/>
       <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
-      <c r="F58" s="7" t="n"/>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
     </row>
@@ -1486,13 +1486,13 @@
       </c>
       <c r="B59" s="7" t="n"/>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
-      <c r="F59" s="7" t="n"/>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G59" s="7" t="n"/>
       <c r="H59" s="7" t="n"/>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C60" s="7" t="n"/>
@@ -1516,13 +1516,13 @@
       <c r="A61" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B61" s="7" t="n"/>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
       <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
@@ -1550,13 +1550,13 @@
       </c>
       <c r="B63" s="7" t="n"/>
       <c r="C63" s="7" t="n"/>
-      <c r="D63" s="7" t="n"/>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E63" s="7" t="n"/>
-      <c r="F63" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F63" s="7" t="n"/>
       <c r="G63" s="7" t="n"/>
       <c r="H63" s="7" t="n"/>
     </row>
@@ -1570,7 +1570,7 @@
       <c r="E64" s="7" t="n"/>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G64" s="7" t="n"/>
@@ -1584,27 +1584,27 @@
       <c r="C65" s="7" t="n"/>
       <c r="D65" s="7" t="n"/>
       <c r="E65" s="7" t="n"/>
-      <c r="F65" s="7" t="n"/>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G65" s="7" t="n"/>
-      <c r="H65" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H65" s="7" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B66" s="7" t="n"/>
       <c r="C66" s="7" t="n"/>
       <c r="D66" s="7" t="n"/>
       <c r="E66" s="7" t="n"/>
-      <c r="F66" s="7" t="n"/>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G66" s="7" t="n"/>
       <c r="H66" s="7" t="n"/>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C67" s="7" t="n"/>
@@ -1628,15 +1628,15 @@
       <c r="A68" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B68" s="7" t="n"/>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C68" s="7" t="n"/>
       <c r="D68" s="7" t="n"/>
       <c r="E68" s="7" t="n"/>
-      <c r="F68" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F68" s="7" t="n"/>
       <c r="G68" s="7" t="n"/>
       <c r="H68" s="7" t="n"/>
     </row>
@@ -1658,19 +1658,19 @@
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B70" s="7" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C70" s="7" t="n"/>
       <c r="D70" s="7" t="n"/>
       <c r="E70" s="7" t="n"/>
       <c r="F70" s="7" t="n"/>
       <c r="G70" s="7" t="n"/>
-      <c r="H70" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C71" s="7" t="n"/>
@@ -1692,13 +1692,13 @@
       <c r="A72" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+      <c r="B72" s="7" t="n"/>
       <c r="C72" s="7" t="n"/>
-      <c r="D72" s="7" t="n"/>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E72" s="7" t="n"/>
       <c r="F72" s="7" t="n"/>
       <c r="G72" s="7" t="n"/>
@@ -1710,15 +1710,15 @@
       </c>
       <c r="B73" s="7" t="n"/>
       <c r="C73" s="7" t="n"/>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D73" s="7" t="n"/>
       <c r="E73" s="7" t="n"/>
       <c r="F73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
-      <c r="H73" s="7" t="n"/>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C74" s="7" t="n"/>
@@ -1760,7 +1760,7 @@
       <c r="C76" s="7" t="n"/>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E76" s="7" t="n"/>
@@ -1770,15 +1770,15 @@
     </row>
     <row r="77">
       <c r="A77" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B77" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C77" s="7" t="n"/>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D77" s="7" t="n"/>
       <c r="E77" s="7" t="n"/>
       <c r="F77" s="7" t="n"/>
       <c r="G77" s="7" t="n"/>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C78" s="7" t="n"/>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C79" s="7" t="n"/>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C80" s="7" t="n"/>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="C81" s="7" t="n"/>
@@ -1852,13 +1852,13 @@
       <c r="A82" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+      <c r="B82" s="7" t="n"/>
       <c r="C82" s="7" t="n"/>
-      <c r="D82" s="7" t="n"/>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E82" s="7" t="n"/>
       <c r="F82" s="7" t="n"/>
       <c r="G82" s="7" t="n"/>
@@ -2108,13 +2108,13 @@
       <c r="A98" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B98" s="7" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+      <c r="B98" s="7" t="n"/>
       <c r="C98" s="7" t="n"/>
-      <c r="D98" s="7" t="n"/>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E98" s="7" t="n"/>
       <c r="F98" s="7" t="n"/>
       <c r="G98" s="7" t="n"/>
@@ -2128,7 +2128,7 @@
       <c r="C99" s="7" t="n"/>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E99" s="7" t="n"/>
@@ -2144,7 +2144,7 @@
       <c r="C100" s="7" t="n"/>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E100" s="7" t="n"/>
@@ -2154,15 +2154,15 @@
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B101" s="7" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C101" s="7" t="n"/>
-      <c r="D101" s="7" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D101" s="7" t="n"/>
       <c r="E101" s="7" t="n"/>
       <c r="F101" s="7" t="n"/>
       <c r="G101" s="7" t="n"/>
@@ -2295,7 +2295,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 75.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 77.</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 2; 23 players used week 4 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 2; 22 players used week 4 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 77 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 81 players moved.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Chris Olave 41-&gt;32, Puka Nacua 68-&gt;60, Jaxon Smith-Njigba 64-&gt;56, Trey McBride 42.8571-&gt;35, Ja'Marr Chase 64-&gt;57, Amon-Ra St. Brown 62-&gt;55, Justin Jefferson 53-&gt;46, CeeDee Lamb 50-&gt;43</t>
+          <t>Largest moves vs. the baseline in this file: Puka Nacua 68-&gt;58, Jaxon Smith-Njigba 64-&gt;54, Chris Olave 40-&gt;30, Ja'Marr Chase 64-&gt;55, Amon-Ra St. Brown 62-&gt;53, Justin Jefferson 53-&gt;45, CeeDee Lamb 50-&gt;42, Drake London 40-&gt;32</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -618,7 +618,7 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
@@ -634,15 +634,15 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="7" t="n"/>
       <c r="G6" s="7" t="n"/>
@@ -650,15 +650,15 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="B7" s="7" t="n"/>
+        <v>59</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="7" t="n"/>
@@ -684,13 +684,13 @@
       <c r="A9" s="6" t="n">
         <v>56</v>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+      <c r="B9" s="7" t="n"/>
       <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="7" t="n"/>
@@ -698,7 +698,7 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
@@ -714,7 +714,7 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
@@ -730,13 +730,13 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E12" s="7" t="n"/>
@@ -746,15 +746,15 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="B13" s="7" t="n"/>
+        <v>49</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D13" s="7" t="n"/>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
@@ -762,11 +762,11 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="C14" s="7" t="n"/>
@@ -782,7 +782,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Ashton Jeanty</t>
         </is>
       </c>
       <c r="C15" s="7" t="n"/>
@@ -794,7 +794,7 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
@@ -810,13 +810,13 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="n"/>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Justin Jefferson</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="E17" s="7" t="n"/>
@@ -844,13 +844,13 @@
       <c r="A19" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="B19" s="7" t="n"/>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
@@ -858,15 +858,15 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
@@ -874,7 +874,7 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
@@ -906,31 +906,31 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="B23" s="7" t="n"/>
+        <v>35</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C23" s="7" t="n"/>
       <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
       <c r="H23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
@@ -938,23 +938,23 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
@@ -970,13 +970,13 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Chris Olave</t>
         </is>
       </c>
       <c r="E27" s="7" t="n"/>
@@ -986,13 +986,13 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Nico Collins</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E28" s="7" t="n"/>
@@ -1002,15 +1002,15 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="B29" s="7" t="n"/>
+        <v>31</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D29" s="7" t="n"/>
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="7" t="n"/>
@@ -1018,15 +1018,15 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="n"/>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E30" s="7" t="n"/>
       <c r="F30" s="7" t="n"/>
       <c r="G30" s="7" t="n"/>
@@ -1050,15 +1050,15 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
@@ -1068,13 +1068,13 @@
       <c r="A33" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="B33" s="7" t="n"/>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D33" s="7" t="n"/>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
@@ -1104,7 +1104,7 @@
       <c r="C35" s="7" t="n"/>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E35" s="7" t="n"/>
@@ -1118,43 +1118,43 @@
       </c>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
-      <c r="D36" s="7" t="n"/>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E36" s="7" t="n"/>
       <c r="F36" s="7" t="n"/>
       <c r="G36" s="7" t="n"/>
-      <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="7" t="n"/>
       <c r="E37" s="7" t="n"/>
       <c r="F37" s="7" t="n"/>
       <c r="G37" s="7" t="n"/>
-      <c r="H37" s="7" t="n"/>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B38" s="7" t="n"/>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D38" s="7" t="n"/>
       <c r="E38" s="7" t="n"/>
       <c r="F38" s="7" t="n"/>
       <c r="G38" s="7" t="n"/>
@@ -1168,7 +1168,7 @@
       <c r="C39" s="7" t="n"/>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E39" s="7" t="n"/>
@@ -1178,13 +1178,13 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E40" s="7" t="n"/>
@@ -1226,7 +1226,7 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
@@ -1294,31 +1294,31 @@
       </c>
       <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="n"/>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E47" s="7" t="n"/>
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="7" t="n"/>
-      <c r="H47" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B48" s="7" t="n"/>
       <c r="C48" s="7" t="n"/>
       <c r="D48" s="7" t="n"/>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
-      <c r="H48" s="7" t="n"/>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C49" s="7" t="n"/>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="C50" s="7" t="n"/>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C51" s="7" t="n"/>
@@ -1372,13 +1372,13 @@
       <c r="A52" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B52" s="7" t="n"/>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D52" s="7" t="n"/>
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="7" t="n"/>
@@ -1392,7 +1392,7 @@
       <c r="C53" s="7" t="n"/>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E53" s="7" t="n"/>
@@ -1406,59 +1406,59 @@
       </c>
       <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
-      <c r="D54" s="7" t="n"/>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E54" s="7" t="n"/>
       <c r="F54" s="7" t="n"/>
       <c r="G54" s="7" t="n"/>
-      <c r="H54" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B55" s="7" t="n"/>
       <c r="C55" s="7" t="n"/>
       <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7" t="n"/>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G55" s="7" t="n"/>
       <c r="H55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B56" s="7" t="n"/>
       <c r="C56" s="7" t="n"/>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D56" s="7" t="n"/>
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="n"/>
-      <c r="H56" s="7" t="n"/>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B57" s="7" t="n"/>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C57" s="7" t="n"/>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
       <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
@@ -1468,15 +1468,15 @@
       <c r="A58" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B58" s="7" t="n"/>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C58" s="7" t="n"/>
       <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
     </row>
@@ -1490,7 +1490,7 @@
       <c r="E59" s="7" t="n"/>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Colston Loveland</t>
+          <t>Tyler Warren</t>
         </is>
       </c>
       <c r="G59" s="7" t="n"/>
@@ -1536,7 +1536,7 @@
       <c r="C62" s="7" t="n"/>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E62" s="7" t="n"/>
@@ -1612,25 +1612,25 @@
       <c r="A67" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+      <c r="B67" s="7" t="n"/>
       <c r="C67" s="7" t="n"/>
       <c r="D67" s="7" t="n"/>
       <c r="E67" s="7" t="n"/>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
-      <c r="H67" s="7" t="n"/>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C68" s="7" t="n"/>
@@ -1642,31 +1642,31 @@
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B69" s="7" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C69" s="7" t="n"/>
       <c r="D69" s="7" t="n"/>
       <c r="E69" s="7" t="n"/>
       <c r="F69" s="7" t="n"/>
       <c r="G69" s="7" t="n"/>
-      <c r="H69" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+      <c r="B70" s="7" t="n"/>
       <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="n"/>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E70" s="7" t="n"/>
       <c r="F70" s="7" t="n"/>
       <c r="G70" s="7" t="n"/>
@@ -1676,13 +1676,13 @@
       <c r="A71" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+      <c r="B71" s="7" t="n"/>
       <c r="C71" s="7" t="n"/>
-      <c r="D71" s="7" t="n"/>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>Terry McLaurin</t>
+        </is>
+      </c>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
@@ -1710,43 +1710,43 @@
       </c>
       <c r="B73" s="7" t="n"/>
       <c r="C73" s="7" t="n"/>
-      <c r="D73" s="7" t="n"/>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E73" s="7" t="n"/>
       <c r="F73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
-      <c r="H73" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B74" s="7" t="n"/>
       <c r="C74" s="7" t="n"/>
       <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
       <c r="F74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
-      <c r="H74" s="7" t="n"/>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B75" s="7" t="n"/>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C75" s="7" t="n"/>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D75" s="7" t="n"/>
       <c r="E75" s="7" t="n"/>
       <c r="F75" s="7" t="n"/>
       <c r="G75" s="7" t="n"/>
@@ -1760,7 +1760,7 @@
       <c r="C76" s="7" t="n"/>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E76" s="7" t="n"/>
@@ -1770,15 +1770,15 @@
     </row>
     <row r="77">
       <c r="A77" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B77" s="7" t="n"/>
       <c r="C77" s="7" t="n"/>
-      <c r="D77" s="7" t="n"/>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>Marvin Harrison Jr.</t>
+        </is>
+      </c>
       <c r="E77" s="7" t="n"/>
       <c r="F77" s="7" t="n"/>
       <c r="G77" s="7" t="n"/>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="C78" s="7" t="n"/>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C79" s="7" t="n"/>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C80" s="7" t="n"/>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Blake Corum</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C81" s="7" t="n"/>
@@ -1852,13 +1852,13 @@
       <c r="A82" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B82" s="7" t="n"/>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>Rico Dowdle</t>
+        </is>
+      </c>
       <c r="C82" s="7" t="n"/>
-      <c r="D82" s="7" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D82" s="7" t="n"/>
       <c r="E82" s="7" t="n"/>
       <c r="F82" s="7" t="n"/>
       <c r="G82" s="7" t="n"/>
@@ -1930,15 +1930,15 @@
     </row>
     <row r="87">
       <c r="A87" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B87" s="7" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>J.K. Dobbins</t>
+        </is>
+      </c>
       <c r="C87" s="7" t="n"/>
-      <c r="D87" s="7" t="inlineStr">
-        <is>
-          <t>Chris Godwin Jr.</t>
-        </is>
-      </c>
+      <c r="D87" s="7" t="n"/>
       <c r="E87" s="7" t="n"/>
       <c r="F87" s="7" t="n"/>
       <c r="G87" s="7" t="n"/>
@@ -1946,79 +1946,79 @@
     </row>
     <row r="88">
       <c r="A88" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B88" s="7" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C88" s="7" t="n"/>
       <c r="D88" s="7" t="n"/>
       <c r="E88" s="7" t="n"/>
-      <c r="F88" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F88" s="7" t="n"/>
       <c r="G88" s="7" t="n"/>
       <c r="H88" s="7" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B89" s="7" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C89" s="7" t="n"/>
       <c r="D89" s="7" t="n"/>
       <c r="E89" s="7" t="n"/>
       <c r="F89" s="7" t="n"/>
       <c r="G89" s="7" t="n"/>
-      <c r="H89" s="7" t="inlineStr">
-        <is>
-          <t>Jalen Hurts</t>
-        </is>
-      </c>
+      <c r="H89" s="7" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B90" s="7" t="n"/>
       <c r="C90" s="7" t="n"/>
-      <c r="D90" s="7" t="n"/>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E90" s="7" t="n"/>
       <c r="F90" s="7" t="n"/>
       <c r="G90" s="7" t="n"/>
-      <c r="H90" s="7" t="inlineStr">
-        <is>
-          <t>Justin Herbert</t>
-        </is>
-      </c>
+      <c r="H90" s="7" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B91" s="7" t="n"/>
       <c r="C91" s="7" t="n"/>
-      <c r="D91" s="7" t="n"/>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>Chris Godwin Jr.</t>
+        </is>
+      </c>
       <c r="E91" s="7" t="n"/>
       <c r="F91" s="7" t="n"/>
       <c r="G91" s="7" t="n"/>
-      <c r="H91" s="7" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H91" s="7" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+      <c r="B92" s="7" t="n"/>
       <c r="C92" s="7" t="n"/>
-      <c r="D92" s="7" t="n"/>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E92" s="7" t="n"/>
       <c r="F92" s="7" t="n"/>
       <c r="G92" s="7" t="n"/>
@@ -2030,13 +2030,13 @@
       </c>
       <c r="B93" s="7" t="n"/>
       <c r="C93" s="7" t="n"/>
-      <c r="D93" s="7" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D93" s="7" t="n"/>
       <c r="E93" s="7" t="n"/>
-      <c r="F93" s="7" t="n"/>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G93" s="7" t="n"/>
       <c r="H93" s="7" t="n"/>
     </row>
@@ -2046,15 +2046,15 @@
       </c>
       <c r="B94" s="7" t="n"/>
       <c r="C94" s="7" t="n"/>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D94" s="7" t="n"/>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="7" t="n"/>
       <c r="G94" s="7" t="n"/>
-      <c r="H94" s="7" t="n"/>
+      <c r="H94" s="7" t="inlineStr">
+        <is>
+          <t>Jalen Hurts</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
@@ -2062,15 +2062,15 @@
       </c>
       <c r="B95" s="7" t="n"/>
       <c r="C95" s="7" t="n"/>
-      <c r="D95" s="7" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
+      <c r="D95" s="7" t="n"/>
       <c r="E95" s="7" t="n"/>
       <c r="F95" s="7" t="n"/>
       <c r="G95" s="7" t="n"/>
-      <c r="H95" s="7" t="n"/>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>Justin Herbert</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
@@ -2078,15 +2078,15 @@
       </c>
       <c r="B96" s="7" t="n"/>
       <c r="C96" s="7" t="n"/>
-      <c r="D96" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
+      <c r="D96" s="7" t="n"/>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="7" t="n"/>
       <c r="G96" s="7" t="n"/>
-      <c r="H96" s="7" t="n"/>
+      <c r="H96" s="7" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
@@ -2112,7 +2112,7 @@
       <c r="C98" s="7" t="n"/>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E98" s="7" t="n"/>
@@ -2156,13 +2156,13 @@
       <c r="A101" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B101" s="7" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+      <c r="B101" s="7" t="n"/>
       <c r="C101" s="7" t="n"/>
-      <c r="D101" s="7" t="n"/>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>Carnell Tate</t>
+        </is>
+      </c>
       <c r="E101" s="7" t="n"/>
       <c r="F101" s="7" t="n"/>
       <c r="G101" s="7" t="n"/>
@@ -2176,7 +2176,7 @@
       <c r="C102" s="7" t="n"/>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E102" s="7" t="n"/>
@@ -2295,7 +2295,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 77.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 76.</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 2; 22 players used week 4 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 3; 18 players used week 4 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,14 +2333,14 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 81 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 80 players moved.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   No projection this week (value kept): Justin Jefferson, A.J. Brown, Breece Hall, Travis Etienne Jr., Josh Jacobs, De'Zhaun Stribling, Jordan Mason, Alec Pierce, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Blake Corum, Kenny Gainwell, Jaxson Dart, Rachaad White, Ja'Kobi Lane.</t>
+          <t xml:space="preserve">   No projection this week (value kept): A.J. Brown, Breece Hall, Travis Etienne Jr., Josh Jacobs, De'Zhaun Stribling, Jordan Mason, Alec Pierce, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Blake Corum, Kenny Gainwell, Jaxson Dart, Ja'Kobi Lane.</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.8, WR 2.6, TE 4.5, QB 0.0.</t>
+          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.8, WR 2.8, TE 4.5, QB 0.0.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Puka Nacua 68-&gt;58, Jaxon Smith-Njigba 64-&gt;54, Chris Olave 40-&gt;30, Ja'Marr Chase 64-&gt;55, Amon-Ra St. Brown 62-&gt;53, Justin Jefferson 53-&gt;45, CeeDee Lamb 50-&gt;42, Drake London 40-&gt;32</t>
+          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 65-&gt;56, Chris Olave 41-&gt;32, Puka Nacua 69-&gt;61, Ja'Marr Chase 64-&gt;56, Amon-Ra St. Brown 63-&gt;55, Drake London 43-&gt;35, Trey McBride 43.4286-&gt;36, Justin Jefferson 46-&gt;39</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -618,7 +618,7 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
@@ -698,13 +698,13 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E10" s="7" t="n"/>
@@ -714,7 +714,7 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
@@ -730,13 +730,13 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E12" s="7" t="n"/>
@@ -762,15 +762,15 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
@@ -782,7 +782,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C15" s="7" t="n"/>
@@ -798,7 +798,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="C16" s="7" t="n"/>
@@ -810,15 +810,15 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="B17" s="7" t="n"/>
+        <v>44</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D17" s="7" t="n"/>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
@@ -842,11 +842,11 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Ashton Jeanty</t>
         </is>
       </c>
       <c r="C19" s="7" t="n"/>
@@ -858,15 +858,15 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="B20" s="7" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
@@ -874,15 +874,15 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
@@ -922,7 +922,7 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
@@ -942,29 +942,29 @@
       </c>
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
       <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="7" t="n"/>
     </row>
@@ -972,13 +972,13 @@
       <c r="A27" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="B27" s="7" t="n"/>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D27" s="7" t="n"/>
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
@@ -1066,15 +1066,15 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="n"/>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
@@ -1082,11 +1082,11 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C34" s="7" t="n"/>
@@ -1098,19 +1098,19 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D35" s="7" t="n"/>
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="7" t="n"/>
-      <c r="H35" s="7" t="n"/>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
@@ -1120,7 +1120,7 @@
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E36" s="7" t="n"/>
@@ -1134,15 +1134,15 @@
       </c>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7" t="n"/>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E37" s="7" t="n"/>
       <c r="F37" s="7" t="n"/>
       <c r="G37" s="7" t="n"/>
-      <c r="H37" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
@@ -1194,15 +1194,15 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="B41" s="7" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D41" s="7" t="n"/>
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="7" t="n"/>
@@ -1248,7 +1248,7 @@
       <c r="C44" s="7" t="n"/>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E44" s="7" t="n"/>
@@ -1258,13 +1258,13 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B45" s="7" t="n"/>
       <c r="C45" s="7" t="n"/>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E45" s="7" t="n"/>
@@ -1294,31 +1294,31 @@
       </c>
       <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D47" s="7" t="n"/>
       <c r="E47" s="7" t="n"/>
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="7" t="n"/>
-      <c r="H47" s="7" t="n"/>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B48" s="7" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C48" s="7" t="n"/>
       <c r="D48" s="7" t="n"/>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
-      <c r="H48" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H48" s="7" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr.</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="C49" s="7" t="n"/>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C50" s="7" t="n"/>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C51" s="7" t="n"/>
@@ -1372,13 +1372,13 @@
       <c r="A52" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+      <c r="B52" s="7" t="n"/>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="7" t="n"/>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="7" t="n"/>
@@ -1392,7 +1392,7 @@
       <c r="C53" s="7" t="n"/>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E53" s="7" t="n"/>
@@ -1486,27 +1486,27 @@
       </c>
       <c r="B59" s="7" t="n"/>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="7" t="n"/>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E59" s="7" t="n"/>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F59" s="7" t="n"/>
       <c r="G59" s="7" t="n"/>
       <c r="H59" s="7" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B60" s="7" t="n"/>
       <c r="C60" s="7" t="n"/>
-      <c r="D60" s="7" t="n"/>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E60" s="7" t="n"/>
       <c r="F60" s="7" t="n"/>
       <c r="G60" s="7" t="n"/>
@@ -1514,17 +1514,17 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
       <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
-      <c r="F61" s="7" t="n"/>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G61" s="7" t="n"/>
       <c r="H61" s="7" t="n"/>
     </row>
@@ -1532,13 +1532,13 @@
       <c r="A62" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B62" s="7" t="n"/>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D62" s="7" t="n"/>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="7" t="n"/>
@@ -1548,13 +1548,13 @@
       <c r="A63" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B63" s="7" t="n"/>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C63" s="7" t="n"/>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D63" s="7" t="n"/>
       <c r="E63" s="7" t="n"/>
       <c r="F63" s="7" t="n"/>
       <c r="G63" s="7" t="n"/>
@@ -1566,13 +1566,13 @@
       </c>
       <c r="B64" s="7" t="n"/>
       <c r="C64" s="7" t="n"/>
-      <c r="D64" s="7" t="n"/>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E64" s="7" t="n"/>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F64" s="7" t="n"/>
       <c r="G64" s="7" t="n"/>
       <c r="H64" s="7" t="n"/>
     </row>
@@ -1586,7 +1586,7 @@
       <c r="E65" s="7" t="n"/>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G65" s="7" t="n"/>
@@ -1602,7 +1602,7 @@
       <c r="E66" s="7" t="n"/>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Tucker Kraft</t>
         </is>
       </c>
       <c r="G66" s="7" t="n"/>
@@ -1610,35 +1610,35 @@
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B67" s="7" t="n"/>
       <c r="C67" s="7" t="n"/>
       <c r="D67" s="7" t="n"/>
       <c r="E67" s="7" t="n"/>
-      <c r="F67" s="7" t="n"/>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G67" s="7" t="n"/>
-      <c r="H67" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B68" s="7" t="n"/>
       <c r="C68" s="7" t="n"/>
       <c r="D68" s="7" t="n"/>
       <c r="E68" s="7" t="n"/>
       <c r="F68" s="7" t="n"/>
       <c r="G68" s="7" t="n"/>
-      <c r="H68" s="7" t="n"/>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C69" s="7" t="n"/>
@@ -1664,7 +1664,7 @@
       <c r="C70" s="7" t="n"/>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="E70" s="7" t="n"/>
@@ -1680,7 +1680,7 @@
       <c r="C71" s="7" t="n"/>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E71" s="7" t="n"/>
@@ -1694,27 +1694,27 @@
       </c>
       <c r="B72" s="7" t="n"/>
       <c r="C72" s="7" t="n"/>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D72" s="7" t="n"/>
       <c r="E72" s="7" t="n"/>
       <c r="F72" s="7" t="n"/>
       <c r="G72" s="7" t="n"/>
-      <c r="H72" s="7" t="n"/>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B73" s="7" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C73" s="7" t="n"/>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D73" s="7" t="n"/>
       <c r="E73" s="7" t="n"/>
       <c r="F73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
@@ -1722,31 +1722,31 @@
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B74" s="7" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C74" s="7" t="n"/>
       <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
       <c r="F74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
-      <c r="H74" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H74" s="7" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+      <c r="B75" s="7" t="n"/>
       <c r="C75" s="7" t="n"/>
-      <c r="D75" s="7" t="n"/>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>Terry McLaurin</t>
+        </is>
+      </c>
       <c r="E75" s="7" t="n"/>
       <c r="F75" s="7" t="n"/>
       <c r="G75" s="7" t="n"/>
@@ -1868,13 +1868,13 @@
       <c r="A83" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B83" s="7" t="n"/>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>J.K. Dobbins</t>
+        </is>
+      </c>
       <c r="C83" s="7" t="n"/>
-      <c r="D83" s="7" t="inlineStr">
-        <is>
-          <t>Jameson Williams</t>
-        </is>
-      </c>
+      <c r="D83" s="7" t="n"/>
       <c r="E83" s="7" t="n"/>
       <c r="F83" s="7" t="n"/>
       <c r="G83" s="7" t="n"/>
@@ -1884,13 +1884,13 @@
       <c r="A84" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B84" s="7" t="n"/>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C84" s="7" t="n"/>
-      <c r="D84" s="7" t="inlineStr">
-        <is>
-          <t>De'Zhaun Stribling</t>
-        </is>
-      </c>
+      <c r="D84" s="7" t="n"/>
       <c r="E84" s="7" t="n"/>
       <c r="F84" s="7" t="n"/>
       <c r="G84" s="7" t="n"/>
@@ -1904,7 +1904,7 @@
       <c r="C85" s="7" t="n"/>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E85" s="7" t="n"/>
@@ -1920,7 +1920,7 @@
       <c r="C86" s="7" t="n"/>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E86" s="7" t="n"/>
@@ -1930,15 +1930,15 @@
     </row>
     <row r="87">
       <c r="A87" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B87" s="7" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B87" s="7" t="n"/>
       <c r="C87" s="7" t="n"/>
-      <c r="D87" s="7" t="n"/>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E87" s="7" t="n"/>
       <c r="F87" s="7" t="n"/>
       <c r="G87" s="7" t="n"/>
@@ -1946,15 +1946,15 @@
     </row>
     <row r="88">
       <c r="A88" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B88" s="7" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B88" s="7" t="n"/>
       <c r="C88" s="7" t="n"/>
-      <c r="D88" s="7" t="n"/>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>Quentin Johnston</t>
+        </is>
+      </c>
       <c r="E88" s="7" t="n"/>
       <c r="F88" s="7" t="n"/>
       <c r="G88" s="7" t="n"/>
@@ -1962,15 +1962,15 @@
     </row>
     <row r="89">
       <c r="A89" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B89" s="7" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B89" s="7" t="n"/>
       <c r="C89" s="7" t="n"/>
-      <c r="D89" s="7" t="n"/>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>Chris Godwin Jr.</t>
+        </is>
+      </c>
       <c r="E89" s="7" t="n"/>
       <c r="F89" s="7" t="n"/>
       <c r="G89" s="7" t="n"/>
@@ -1978,83 +1978,83 @@
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B90" s="7" t="n"/>
       <c r="C90" s="7" t="n"/>
-      <c r="D90" s="7" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D90" s="7" t="n"/>
       <c r="E90" s="7" t="n"/>
-      <c r="F90" s="7" t="n"/>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G90" s="7" t="n"/>
       <c r="H90" s="7" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B91" s="7" t="n"/>
       <c r="C91" s="7" t="n"/>
-      <c r="D91" s="7" t="inlineStr">
-        <is>
-          <t>Chris Godwin Jr.</t>
-        </is>
-      </c>
+      <c r="D91" s="7" t="n"/>
       <c r="E91" s="7" t="n"/>
       <c r="F91" s="7" t="n"/>
       <c r="G91" s="7" t="n"/>
-      <c r="H91" s="7" t="n"/>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>Jalen Hurts</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B92" s="7" t="n"/>
       <c r="C92" s="7" t="n"/>
-      <c r="D92" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
+      <c r="D92" s="7" t="n"/>
       <c r="E92" s="7" t="n"/>
       <c r="F92" s="7" t="n"/>
       <c r="G92" s="7" t="n"/>
-      <c r="H92" s="7" t="n"/>
+      <c r="H92" s="7" t="inlineStr">
+        <is>
+          <t>Justin Herbert</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B93" s="7" t="n"/>
       <c r="C93" s="7" t="n"/>
       <c r="D93" s="7" t="n"/>
       <c r="E93" s="7" t="n"/>
-      <c r="F93" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F93" s="7" t="n"/>
       <c r="G93" s="7" t="n"/>
-      <c r="H93" s="7" t="n"/>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B94" s="7" t="n"/>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C94" s="7" t="n"/>
       <c r="D94" s="7" t="n"/>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="7" t="n"/>
       <c r="G94" s="7" t="n"/>
-      <c r="H94" s="7" t="inlineStr">
-        <is>
-          <t>Jalen Hurts</t>
-        </is>
-      </c>
+      <c r="H94" s="7" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
@@ -2062,15 +2062,15 @@
       </c>
       <c r="B95" s="7" t="n"/>
       <c r="C95" s="7" t="n"/>
-      <c r="D95" s="7" t="n"/>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E95" s="7" t="n"/>
       <c r="F95" s="7" t="n"/>
       <c r="G95" s="7" t="n"/>
-      <c r="H95" s="7" t="inlineStr">
-        <is>
-          <t>Justin Herbert</t>
-        </is>
-      </c>
+      <c r="H95" s="7" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
@@ -2078,15 +2078,15 @@
       </c>
       <c r="B96" s="7" t="n"/>
       <c r="C96" s="7" t="n"/>
-      <c r="D96" s="7" t="n"/>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="7" t="n"/>
       <c r="G96" s="7" t="n"/>
-      <c r="H96" s="7" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H96" s="7" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 3; 18 players used week 4 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 4; 15 players used week 4 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 80 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 82 players moved.</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.8, WR 2.8, TE 4.5, QB 0.0.</t>
+          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.6, WR 2.8, TE 4.5, QB 0.0.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 65-&gt;56, Chris Olave 41-&gt;32, Puka Nacua 69-&gt;61, Ja'Marr Chase 64-&gt;56, Amon-Ra St. Brown 63-&gt;55, Drake London 43-&gt;35, Trey McBride 43.4286-&gt;36, Justin Jefferson 46-&gt;39</t>
+          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 65-&gt;56, Chris Olave 42-&gt;33, Puka Nacua 69-&gt;61, Ja'Marr Chase 60-&gt;52, Amon-Ra St. Brown 63-&gt;55, Drake London 42-&gt;34, Trey McBride 43.4286-&gt;36, Christian McCaffrey 60-&gt;53</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -634,15 +634,15 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>61</v>
-      </c>
-      <c r="B6" s="7" t="n"/>
+        <v>59</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="7" t="n"/>
       <c r="G6" s="7" t="n"/>
@@ -652,13 +652,13 @@
       <c r="A7" s="6" t="n">
         <v>59</v>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+      <c r="B7" s="7" t="n"/>
       <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="7" t="n"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>James Cook III</t>
+          <t>Ashton Jeanty</t>
         </is>
       </c>
       <c r="C13" s="7" t="n"/>
@@ -762,15 +762,15 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="B14" s="7" t="n"/>
+        <v>49</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D14" s="7" t="n"/>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
@@ -778,7 +778,7 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
@@ -810,15 +810,15 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
@@ -828,33 +828,33 @@
       <c r="A18" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="B18" s="7" t="n"/>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>43</v>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
       <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
@@ -874,7 +874,7 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
@@ -922,31 +922,31 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="B25" s="7" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
@@ -954,17 +954,17 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="7" t="n"/>
     </row>
@@ -972,13 +972,13 @@
       <c r="A27" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+      <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
@@ -986,15 +986,15 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B28" s="7" t="n"/>
+        <v>31</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D28" s="7" t="n"/>
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="7" t="n"/>
@@ -1004,13 +1004,13 @@
       <c r="A29" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+      <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="7" t="n"/>
@@ -1024,7 +1024,7 @@
       <c r="C30" s="7" t="n"/>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Nico Collins</t>
+          <t>Chris Olave</t>
         </is>
       </c>
       <c r="E30" s="7" t="n"/>
@@ -1034,15 +1034,15 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="7" t="n"/>
       <c r="G31" s="7" t="n"/>
@@ -1052,13 +1052,13 @@
       <c r="A32" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="B32" s="7" t="n"/>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
@@ -1072,7 +1072,7 @@
       <c r="C33" s="7" t="n"/>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E33" s="7" t="n"/>
@@ -1082,45 +1082,45 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
       <c r="D34" s="7" t="n"/>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="n"/>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="B35" s="7" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C35" s="7" t="n"/>
       <c r="D35" s="7" t="n"/>
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="7" t="n"/>
-      <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E36" s="7" t="n"/>
@@ -1130,13 +1130,13 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E37" s="7" t="n"/>
@@ -1148,13 +1148,13 @@
       <c r="A38" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+      <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="n"/>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E38" s="7" t="n"/>
       <c r="F38" s="7" t="n"/>
       <c r="G38" s="7" t="n"/>
@@ -1168,7 +1168,7 @@
       <c r="C39" s="7" t="n"/>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E39" s="7" t="n"/>
@@ -1184,7 +1184,7 @@
       <c r="C40" s="7" t="n"/>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E40" s="7" t="n"/>
@@ -1194,11 +1194,11 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C41" s="7" t="n"/>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C42" s="7" t="n"/>
@@ -1226,11 +1226,11 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="C43" s="7" t="n"/>
@@ -1244,13 +1244,13 @@
       <c r="A44" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B44" s="7" t="n"/>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D44" s="7" t="n"/>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="7" t="n"/>
@@ -1264,7 +1264,7 @@
       <c r="C45" s="7" t="n"/>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E45" s="7" t="n"/>
@@ -1274,13 +1274,13 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E46" s="7" t="n"/>
@@ -1306,15 +1306,15 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B48" s="7" t="n"/>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="n"/>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C49" s="7" t="n"/>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="C50" s="7" t="n"/>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C51" s="7" t="n"/>
@@ -1372,13 +1372,13 @@
       <c r="A52" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B52" s="7" t="n"/>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D52" s="7" t="n"/>
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="7" t="n"/>
@@ -1392,7 +1392,7 @@
       <c r="C53" s="7" t="n"/>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E53" s="7" t="n"/>
@@ -1488,7 +1488,7 @@
       <c r="C59" s="7" t="n"/>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E59" s="7" t="n"/>
@@ -1502,29 +1502,29 @@
       </c>
       <c r="B60" s="7" t="n"/>
       <c r="C60" s="7" t="n"/>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D60" s="7" t="n"/>
       <c r="E60" s="7" t="n"/>
-      <c r="F60" s="7" t="n"/>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G60" s="7" t="n"/>
       <c r="H60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B61" s="7" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C61" s="7" t="n"/>
       <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
       <c r="H61" s="7" t="n"/>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C62" s="7" t="n"/>
@@ -1548,13 +1548,13 @@
       <c r="A63" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B63" s="7" t="n"/>
       <c r="C63" s="7" t="n"/>
-      <c r="D63" s="7" t="n"/>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E63" s="7" t="n"/>
       <c r="F63" s="7" t="n"/>
       <c r="G63" s="7" t="n"/>
@@ -1566,13 +1566,13 @@
       </c>
       <c r="B64" s="7" t="n"/>
       <c r="C64" s="7" t="n"/>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D64" s="7" t="n"/>
       <c r="E64" s="7" t="n"/>
-      <c r="F64" s="7" t="n"/>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G64" s="7" t="n"/>
       <c r="H64" s="7" t="n"/>
     </row>
@@ -1602,7 +1602,7 @@
       <c r="E66" s="7" t="n"/>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>George Kittle</t>
         </is>
       </c>
       <c r="G66" s="7" t="n"/>
@@ -1610,17 +1610,17 @@
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B67" s="7" t="n"/>
       <c r="C67" s="7" t="n"/>
-      <c r="D67" s="7" t="n"/>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E67" s="7" t="n"/>
-      <c r="F67" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
       <c r="H67" s="7" t="n"/>
     </row>
@@ -2112,7 +2112,7 @@
       <c r="C98" s="7" t="n"/>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E98" s="7" t="n"/>
@@ -2128,7 +2128,7 @@
       <c r="C99" s="7" t="n"/>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E99" s="7" t="n"/>
@@ -2144,7 +2144,7 @@
       <c r="C100" s="7" t="n"/>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E100" s="7" t="n"/>
@@ -2176,7 +2176,7 @@
       <c r="C102" s="7" t="n"/>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E102" s="7" t="n"/>
@@ -2192,7 +2192,7 @@
       <c r="C103" s="7" t="n"/>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E103" s="7" t="n"/>
@@ -2208,7 +2208,7 @@
       <c r="C104" s="7" t="n"/>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E104" s="7" t="n"/>
@@ -2224,7 +2224,7 @@
       <c r="C105" s="7" t="n"/>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E105" s="7" t="n"/>
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 4; 15 players used week 4 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 5; 15 players used week 4 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 65-&gt;56, Chris Olave 42-&gt;33, Puka Nacua 69-&gt;61, Ja'Marr Chase 60-&gt;52, Amon-Ra St. Brown 63-&gt;55, Drake London 42-&gt;34, Trey McBride 43.4286-&gt;36, Christian McCaffrey 60-&gt;53</t>
+          <t>Largest moves vs. the baseline in this file: Puka Nacua 68-&gt;59, Jaxon Smith-Njigba 65-&gt;56, Chris Olave 39-&gt;30, Ja'Marr Chase 60-&gt;52, Amon-Ra St. Brown 63-&gt;55, Justin Jefferson 44-&gt;36, Drake London 40-&gt;32, Trey McBride 43.4286-&gt;36</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -714,7 +714,7 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
@@ -778,15 +778,15 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B15" s="7" t="n"/>
       <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E15" s="7" t="n"/>
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="7" t="n"/>
@@ -794,11 +794,11 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C16" s="7" t="n"/>
@@ -810,15 +810,15 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="B17" s="7" t="n"/>
+        <v>46</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D17" s="7" t="n"/>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
@@ -874,7 +874,7 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
@@ -922,33 +922,33 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
     </row>
@@ -956,13 +956,13 @@
       <c r="A26" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="B26" s="7" t="n"/>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
@@ -986,15 +986,15 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="7" t="n"/>
@@ -1004,13 +1004,13 @@
       <c r="A29" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="B29" s="7" t="n"/>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D29" s="7" t="n"/>
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="7" t="n"/>
@@ -1034,13 +1034,13 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E31" s="7" t="n"/>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
@@ -1066,15 +1066,15 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="B33" s="7" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D33" s="7" t="n"/>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
@@ -1082,45 +1082,45 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="n"/>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
       <c r="D35" s="7" t="n"/>
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="7" t="n"/>
-      <c r="H35" s="7" t="n"/>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E36" s="7" t="n"/>
@@ -1130,13 +1130,13 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E37" s="7" t="n"/>
@@ -1148,13 +1148,13 @@
       <c r="A38" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B38" s="7" t="n"/>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D38" s="7" t="n"/>
       <c r="E38" s="7" t="n"/>
       <c r="F38" s="7" t="n"/>
       <c r="G38" s="7" t="n"/>
@@ -1168,7 +1168,7 @@
       <c r="C39" s="7" t="n"/>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E39" s="7" t="n"/>
@@ -1184,7 +1184,7 @@
       <c r="C40" s="7" t="n"/>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E40" s="7" t="n"/>
@@ -1194,11 +1194,11 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="C41" s="7" t="n"/>
@@ -1212,13 +1212,13 @@
       <c r="A42" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+      <c r="B42" s="7" t="n"/>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="n"/>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="7" t="n"/>
@@ -1226,11 +1226,11 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C43" s="7" t="n"/>
@@ -1244,13 +1244,13 @@
       <c r="A44" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="n"/>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="7" t="n"/>
@@ -1264,7 +1264,7 @@
       <c r="C45" s="7" t="n"/>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E45" s="7" t="n"/>
@@ -1274,15 +1274,15 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B46" s="7" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D46" s="7" t="n"/>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="7" t="n"/>
@@ -1322,15 +1322,15 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B49" s="7" t="n"/>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="n"/>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E49" s="7" t="n"/>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n"/>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C50" s="7" t="n"/>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="C51" s="7" t="n"/>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C52" s="7" t="n"/>
@@ -1388,13 +1388,13 @@
       <c r="A53" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B53" s="7" t="n"/>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D53" s="7" t="n"/>
       <c r="E53" s="7" t="n"/>
       <c r="F53" s="7" t="n"/>
       <c r="G53" s="7" t="n"/>
@@ -1404,13 +1404,13 @@
       <c r="A54" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B54" s="7" t="n"/>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C54" s="7" t="n"/>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D54" s="7" t="n"/>
       <c r="E54" s="7" t="n"/>
       <c r="F54" s="7" t="n"/>
       <c r="G54" s="7" t="n"/>
@@ -1422,13 +1422,13 @@
       </c>
       <c r="B55" s="7" t="n"/>
       <c r="C55" s="7" t="n"/>
-      <c r="D55" s="7" t="n"/>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F55" s="7" t="n"/>
       <c r="G55" s="7" t="n"/>
       <c r="H55" s="7" t="n"/>
     </row>
@@ -1440,29 +1440,29 @@
       <c r="C56" s="7" t="n"/>
       <c r="D56" s="7" t="n"/>
       <c r="E56" s="7" t="n"/>
-      <c r="F56" s="7" t="n"/>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G56" s="7" t="n"/>
-      <c r="H56" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B57" s="7" t="n"/>
       <c r="C57" s="7" t="n"/>
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
       <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
-      <c r="H57" s="7" t="n"/>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C58" s="7" t="n"/>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C61" s="7" t="n"/>
@@ -1566,13 +1566,13 @@
       </c>
       <c r="B64" s="7" t="n"/>
       <c r="C64" s="7" t="n"/>
-      <c r="D64" s="7" t="n"/>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E64" s="7" t="n"/>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F64" s="7" t="n"/>
       <c r="G64" s="7" t="n"/>
       <c r="H64" s="7" t="n"/>
     </row>
@@ -1586,7 +1586,7 @@
       <c r="E65" s="7" t="n"/>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>Isaiah Likely</t>
+          <t>Tyler Warren</t>
         </is>
       </c>
       <c r="G65" s="7" t="n"/>
@@ -1602,7 +1602,7 @@
       <c r="E66" s="7" t="n"/>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G66" s="7" t="n"/>
@@ -1610,17 +1610,17 @@
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B67" s="7" t="n"/>
       <c r="C67" s="7" t="n"/>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D67" s="7" t="n"/>
       <c r="E67" s="7" t="n"/>
-      <c r="F67" s="7" t="n"/>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G67" s="7" t="n"/>
       <c r="H67" s="7" t="n"/>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C69" s="7" t="n"/>
@@ -1660,13 +1660,13 @@
       <c r="A70" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B70" s="7" t="n"/>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
       <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D70" s="7" t="n"/>
       <c r="E70" s="7" t="n"/>
       <c r="F70" s="7" t="n"/>
       <c r="G70" s="7" t="n"/>
@@ -1680,7 +1680,7 @@
       <c r="C71" s="7" t="n"/>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="E71" s="7" t="n"/>
@@ -1694,31 +1694,31 @@
       </c>
       <c r="B72" s="7" t="n"/>
       <c r="C72" s="7" t="n"/>
-      <c r="D72" s="7" t="n"/>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E72" s="7" t="n"/>
       <c r="F72" s="7" t="n"/>
       <c r="G72" s="7" t="n"/>
-      <c r="H72" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H72" s="7" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B73" s="7" t="n"/>
       <c r="C73" s="7" t="n"/>
       <c r="D73" s="7" t="n"/>
       <c r="E73" s="7" t="n"/>
       <c r="F73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
-      <c r="H73" s="7" t="n"/>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C74" s="7" t="n"/>
@@ -1740,13 +1740,13 @@
       <c r="A75" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B75" s="7" t="n"/>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C75" s="7" t="n"/>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D75" s="7" t="n"/>
       <c r="E75" s="7" t="n"/>
       <c r="F75" s="7" t="n"/>
       <c r="G75" s="7" t="n"/>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C79" s="7" t="n"/>
@@ -1868,13 +1868,13 @@
       <c r="A83" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
+      <c r="B83" s="7" t="n"/>
       <c r="C83" s="7" t="n"/>
-      <c r="D83" s="7" t="n"/>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>Terry McLaurin</t>
+        </is>
+      </c>
       <c r="E83" s="7" t="n"/>
       <c r="F83" s="7" t="n"/>
       <c r="G83" s="7" t="n"/>
@@ -1884,13 +1884,13 @@
       <c r="A84" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+      <c r="B84" s="7" t="n"/>
       <c r="C84" s="7" t="n"/>
-      <c r="D84" s="7" t="n"/>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E84" s="7" t="n"/>
       <c r="F84" s="7" t="n"/>
       <c r="G84" s="7" t="n"/>
@@ -1904,7 +1904,7 @@
       <c r="C85" s="7" t="n"/>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E85" s="7" t="n"/>
@@ -1920,7 +1920,7 @@
       <c r="C86" s="7" t="n"/>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E86" s="7" t="n"/>
@@ -1936,7 +1936,7 @@
       <c r="C87" s="7" t="n"/>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E87" s="7" t="n"/>
@@ -1952,7 +1952,7 @@
       <c r="C88" s="7" t="n"/>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E88" s="7" t="n"/>
@@ -1966,13 +1966,13 @@
       </c>
       <c r="B89" s="7" t="n"/>
       <c r="C89" s="7" t="n"/>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>Chris Godwin Jr.</t>
-        </is>
-      </c>
+      <c r="D89" s="7" t="n"/>
       <c r="E89" s="7" t="n"/>
-      <c r="F89" s="7" t="n"/>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G89" s="7" t="n"/>
       <c r="H89" s="7" t="n"/>
     </row>
@@ -1984,13 +1984,13 @@
       <c r="C90" s="7" t="n"/>
       <c r="D90" s="7" t="n"/>
       <c r="E90" s="7" t="n"/>
-      <c r="F90" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F90" s="7" t="n"/>
       <c r="G90" s="7" t="n"/>
-      <c r="H90" s="7" t="n"/>
+      <c r="H90" s="7" t="inlineStr">
+        <is>
+          <t>Jalen Hurts</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
@@ -2004,7 +2004,7 @@
       <c r="G91" s="7" t="n"/>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
@@ -2020,25 +2020,25 @@
       <c r="G92" s="7" t="n"/>
       <c r="H92" s="7" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B93" s="7" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C93" s="7" t="n"/>
       <c r="D93" s="7" t="n"/>
       <c r="E93" s="7" t="n"/>
       <c r="F93" s="7" t="n"/>
       <c r="G93" s="7" t="n"/>
-      <c r="H93" s="7" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H93" s="7" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
@@ -2080,7 +2080,7 @@
       <c r="C96" s="7" t="n"/>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E96" s="7" t="n"/>
@@ -2094,31 +2094,31 @@
       </c>
       <c r="B97" s="7" t="n"/>
       <c r="C97" s="7" t="n"/>
-      <c r="D97" s="7" t="n"/>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="7" t="n"/>
       <c r="G97" s="7" t="n"/>
-      <c r="H97" s="7" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H97" s="7" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B98" s="7" t="n"/>
       <c r="C98" s="7" t="n"/>
-      <c r="D98" s="7" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D98" s="7" t="n"/>
       <c r="E98" s="7" t="n"/>
       <c r="F98" s="7" t="n"/>
       <c r="G98" s="7" t="n"/>
-      <c r="H98" s="7" t="n"/>
+      <c r="H98" s="7" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
@@ -2128,7 +2128,7 @@
       <c r="C99" s="7" t="n"/>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E99" s="7" t="n"/>
@@ -2154,13 +2154,13 @@
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B101" s="7" t="n"/>
       <c r="C101" s="7" t="n"/>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E101" s="7" t="n"/>
@@ -2176,7 +2176,7 @@
       <c r="C102" s="7" t="n"/>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E102" s="7" t="n"/>
@@ -2192,7 +2192,7 @@
       <c r="C103" s="7" t="n"/>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E103" s="7" t="n"/>
@@ -2208,7 +2208,7 @@
       <c r="C104" s="7" t="n"/>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E104" s="7" t="n"/>
@@ -2224,7 +2224,7 @@
       <c r="C105" s="7" t="n"/>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E105" s="7" t="n"/>
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 5; 15 players used week 4 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 6; 14 players used week 4 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,14 +2333,14 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 82 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 83 players moved.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   No projection this week (value kept): A.J. Brown, Breece Hall, Travis Etienne Jr., Josh Jacobs, De'Zhaun Stribling, Jordan Mason, Alec Pierce, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Blake Corum, Kenny Gainwell, Jaxson Dart, Ja'Kobi Lane.</t>
+          <t xml:space="preserve">   No projection this week (value kept): A.J. Brown, Breece Hall, Travis Etienne Jr., Josh Jacobs, De'Zhaun Stribling, Jordan Mason, Alec Pierce, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Kenny Gainwell, Jaxson Dart, Ja'Kobi Lane.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Puka Nacua 68-&gt;59, Jaxon Smith-Njigba 65-&gt;56, Chris Olave 39-&gt;30, Ja'Marr Chase 60-&gt;52, Amon-Ra St. Brown 63-&gt;55, Justin Jefferson 44-&gt;36, Drake London 40-&gt;32, Trey McBride 43.4286-&gt;36</t>
+          <t>Largest moves vs. the baseline in this file: Puka Nacua 68-&gt;59, Jaxon Smith-Njigba 65-&gt;56, Chris Olave 39-&gt;30, Ja'Marr Chase 59-&gt;51, Amon-Ra St. Brown 63-&gt;55, Drake London 43-&gt;35, Trey McBride 43.4286-&gt;36, Christian McCaffrey 61-&gt;54</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -730,7 +730,7 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>James Cook III</t>
         </is>
       </c>
       <c r="C13" s="7" t="n"/>
@@ -762,11 +762,11 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>James Cook III</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="C14" s="7" t="n"/>
@@ -778,7 +778,7 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B15" s="7" t="n"/>
       <c r="C15" s="7" t="n"/>
@@ -810,11 +810,11 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="C17" s="7" t="n"/>
@@ -828,33 +828,33 @@
       <c r="A18" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+      <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="n"/>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="B19" s="7" t="n"/>
+        <v>43</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C19" s="7" t="n"/>
       <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
@@ -922,7 +922,7 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
@@ -986,15 +986,15 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B28" s="7" t="n"/>
+        <v>31</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D28" s="7" t="n"/>
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="7" t="n"/>
@@ -1004,13 +1004,13 @@
       <c r="A29" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+      <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="7" t="n"/>
@@ -1024,7 +1024,7 @@
       <c r="C30" s="7" t="n"/>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>Nico Collins</t>
         </is>
       </c>
       <c r="E30" s="7" t="n"/>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
@@ -1082,35 +1082,35 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D34" s="7" t="n"/>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="n"/>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
-      <c r="D35" s="7" t="n"/>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="7" t="n"/>
-      <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
@@ -1120,7 +1120,7 @@
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E36" s="7" t="n"/>
@@ -1184,7 +1184,7 @@
       <c r="C40" s="7" t="n"/>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E40" s="7" t="n"/>
@@ -1194,15 +1194,15 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="n"/>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="7" t="n"/>
@@ -1212,13 +1212,13 @@
       <c r="A42" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B42" s="7" t="n"/>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D42" s="7" t="n"/>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="7" t="n"/>
@@ -1226,11 +1226,11 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="C43" s="7" t="n"/>
@@ -1242,15 +1242,15 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B44" s="7" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D44" s="7" t="n"/>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="7" t="n"/>
@@ -1264,7 +1264,7 @@
       <c r="C45" s="7" t="n"/>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E45" s="7" t="n"/>
@@ -1276,13 +1276,13 @@
       <c r="A46" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+      <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="n"/>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="7" t="n"/>
@@ -1294,31 +1294,31 @@
       </c>
       <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="n"/>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E47" s="7" t="n"/>
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="7" t="n"/>
-      <c r="H47" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B48" s="7" t="n"/>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D48" s="7" t="n"/>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
-      <c r="H48" s="7" t="n"/>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
@@ -1338,19 +1338,19 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B50" s="7" t="n"/>
       <c r="C50" s="7" t="n"/>
       <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
       <c r="F50" s="7" t="n"/>
       <c r="G50" s="7" t="n"/>
-      <c r="H50" s="7" t="n"/>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C51" s="7" t="n"/>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="C52" s="7" t="n"/>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C53" s="7" t="n"/>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C54" s="7" t="n"/>
@@ -1450,19 +1450,19 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B57" s="7" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C57" s="7" t="n"/>
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
       <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
-      <c r="H57" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
@@ -1488,7 +1488,7 @@
       <c r="C59" s="7" t="n"/>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E59" s="7" t="n"/>
@@ -1502,29 +1502,29 @@
       </c>
       <c r="B60" s="7" t="n"/>
       <c r="C60" s="7" t="n"/>
-      <c r="D60" s="7" t="n"/>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E60" s="7" t="n"/>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F60" s="7" t="n"/>
       <c r="G60" s="7" t="n"/>
       <c r="H60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
       <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
-      <c r="F61" s="7" t="n"/>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G61" s="7" t="n"/>
       <c r="H61" s="7" t="n"/>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C62" s="7" t="n"/>
@@ -1548,13 +1548,13 @@
       <c r="A63" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B63" s="7" t="n"/>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C63" s="7" t="n"/>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D63" s="7" t="n"/>
       <c r="E63" s="7" t="n"/>
       <c r="F63" s="7" t="n"/>
       <c r="G63" s="7" t="n"/>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C69" s="7" t="n"/>
@@ -1660,13 +1660,13 @@
       <c r="A70" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+      <c r="B70" s="7" t="n"/>
       <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="n"/>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E70" s="7" t="n"/>
       <c r="F70" s="7" t="n"/>
       <c r="G70" s="7" t="n"/>
@@ -1680,7 +1680,7 @@
       <c r="C71" s="7" t="n"/>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E71" s="7" t="n"/>
@@ -1694,31 +1694,31 @@
       </c>
       <c r="B72" s="7" t="n"/>
       <c r="C72" s="7" t="n"/>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D72" s="7" t="n"/>
       <c r="E72" s="7" t="n"/>
       <c r="F72" s="7" t="n"/>
       <c r="G72" s="7" t="n"/>
-      <c r="H72" s="7" t="n"/>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B73" s="7" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C73" s="7" t="n"/>
       <c r="D73" s="7" t="n"/>
       <c r="E73" s="7" t="n"/>
       <c r="F73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
-      <c r="H73" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C74" s="7" t="n"/>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C79" s="7" t="n"/>
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 6; 14 players used week 4 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 7; 13 players used week 4 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Puka Nacua 68-&gt;59, Jaxon Smith-Njigba 65-&gt;56, Chris Olave 39-&gt;30, Ja'Marr Chase 59-&gt;51, Amon-Ra St. Brown 63-&gt;55, Drake London 43-&gt;35, Trey McBride 43.4286-&gt;36, Christian McCaffrey 61-&gt;54</t>
+          <t>Largest moves vs. the baseline in this file: Puka Nacua 68-&gt;59, Jaxon Smith-Njigba 65-&gt;56, Chris Olave 40-&gt;31, Ja'Marr Chase 60-&gt;52, Amon-Ra St. Brown 63-&gt;55, Drake London 42-&gt;34, Trey McBride 43.4286-&gt;36, Christian McCaffrey 61-&gt;54</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -666,7 +666,7 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
@@ -842,11 +842,11 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C19" s="7" t="n"/>
@@ -858,15 +858,15 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
@@ -874,15 +874,15 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="B21" s="7" t="n"/>
+        <v>39</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
@@ -908,13 +908,13 @@
       <c r="A23" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+      <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
@@ -924,13 +924,13 @@
       <c r="A24" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="B24" s="7" t="n"/>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
@@ -940,31 +940,31 @@
       <c r="A25" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="B25" s="7" t="n"/>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
       <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="7" t="n"/>
     </row>
@@ -972,13 +972,13 @@
       <c r="A27" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="B27" s="7" t="n"/>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D27" s="7" t="n"/>
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
@@ -986,15 +986,15 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="7" t="n"/>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
@@ -1050,11 +1050,11 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C32" s="7" t="n"/>
@@ -1066,11 +1066,11 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="C33" s="7" t="n"/>
@@ -1104,7 +1104,7 @@
       <c r="C35" s="7" t="n"/>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E35" s="7" t="n"/>
@@ -1120,7 +1120,7 @@
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E36" s="7" t="n"/>
@@ -1130,15 +1130,15 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="B37" s="7" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D37" s="7" t="n"/>
       <c r="E37" s="7" t="n"/>
       <c r="F37" s="7" t="n"/>
       <c r="G37" s="7" t="n"/>
@@ -1148,13 +1148,13 @@
       <c r="A38" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+      <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="n"/>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E38" s="7" t="n"/>
       <c r="F38" s="7" t="n"/>
       <c r="G38" s="7" t="n"/>
@@ -1168,7 +1168,7 @@
       <c r="C39" s="7" t="n"/>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E39" s="7" t="n"/>
@@ -1178,15 +1178,15 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B40" s="7" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D40" s="7" t="n"/>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
@@ -1200,7 +1200,7 @@
       <c r="C41" s="7" t="n"/>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E41" s="7" t="n"/>
@@ -1210,15 +1210,15 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B42" s="7" t="n"/>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="n"/>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="7" t="n"/>
@@ -1242,7 +1242,7 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
@@ -1258,13 +1258,13 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B45" s="7" t="n"/>
       <c r="C45" s="7" t="n"/>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E45" s="7" t="n"/>
@@ -1274,13 +1274,13 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E46" s="7" t="n"/>
@@ -1296,7 +1296,7 @@
       <c r="C47" s="7" t="n"/>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E47" s="7" t="n"/>
@@ -1316,53 +1316,53 @@
       <c r="G48" s="7" t="n"/>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Joe Burrow</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B49" s="7" t="n"/>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D49" s="7" t="n"/>
       <c r="E49" s="7" t="n"/>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n"/>
-      <c r="H49" s="7" t="n"/>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B50" s="7" t="n"/>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C50" s="7" t="n"/>
       <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
       <c r="F50" s="7" t="n"/>
       <c r="G50" s="7" t="n"/>
-      <c r="H50" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B51" s="7" t="n"/>
       <c r="C51" s="7" t="n"/>
-      <c r="D51" s="7" t="n"/>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E51" s="7" t="n"/>
       <c r="F51" s="7" t="n"/>
       <c r="G51" s="7" t="n"/>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C52" s="7" t="n"/>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="C53" s="7" t="n"/>
@@ -1420,13 +1420,13 @@
       <c r="A55" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B55" s="7" t="n"/>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C55" s="7" t="n"/>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
       <c r="F55" s="7" t="n"/>
       <c r="G55" s="7" t="n"/>
@@ -1438,29 +1438,29 @@
       </c>
       <c r="B56" s="7" t="n"/>
       <c r="C56" s="7" t="n"/>
-      <c r="D56" s="7" t="n"/>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E56" s="7" t="n"/>
-      <c r="F56" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="n"/>
       <c r="H56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B57" s="7" t="n"/>
       <c r="C57" s="7" t="n"/>
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
-      <c r="F57" s="7" t="n"/>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G57" s="7" t="n"/>
       <c r="H57" s="7" t="n"/>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C69" s="7" t="n"/>
@@ -1660,13 +1660,13 @@
       <c r="A70" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B70" s="7" t="n"/>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
       <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D70" s="7" t="n"/>
       <c r="E70" s="7" t="n"/>
       <c r="F70" s="7" t="n"/>
       <c r="G70" s="7" t="n"/>
@@ -1676,13 +1676,13 @@
       <c r="A71" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B71" s="7" t="n"/>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C71" s="7" t="n"/>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D71" s="7" t="n"/>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
@@ -1694,27 +1694,27 @@
       </c>
       <c r="B72" s="7" t="n"/>
       <c r="C72" s="7" t="n"/>
-      <c r="D72" s="7" t="n"/>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E72" s="7" t="n"/>
       <c r="F72" s="7" t="n"/>
       <c r="G72" s="7" t="n"/>
-      <c r="H72" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H72" s="7" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B73" s="7" t="n"/>
       <c r="C73" s="7" t="n"/>
-      <c r="D73" s="7" t="n"/>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E73" s="7" t="n"/>
       <c r="F73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
@@ -1722,15 +1722,15 @@
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B74" s="7" t="n"/>
       <c r="C74" s="7" t="n"/>
-      <c r="D74" s="7" t="n"/>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E74" s="7" t="n"/>
       <c r="F74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
@@ -1738,19 +1738,19 @@
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B75" s="7" t="n"/>
       <c r="C75" s="7" t="n"/>
       <c r="D75" s="7" t="n"/>
       <c r="E75" s="7" t="n"/>
       <c r="F75" s="7" t="n"/>
       <c r="G75" s="7" t="n"/>
-      <c r="H75" s="7" t="n"/>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n">
@@ -1760,7 +1760,7 @@
       <c r="C76" s="7" t="n"/>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E76" s="7" t="n"/>
@@ -1770,15 +1770,15 @@
     </row>
     <row r="77">
       <c r="A77" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B77" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C77" s="7" t="n"/>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D77" s="7" t="n"/>
       <c r="E77" s="7" t="n"/>
       <c r="F77" s="7" t="n"/>
       <c r="G77" s="7" t="n"/>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C78" s="7" t="n"/>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C79" s="7" t="n"/>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C80" s="7" t="n"/>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C81" s="7" t="n"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="C82" s="7" t="n"/>
@@ -1872,7 +1872,7 @@
       <c r="C83" s="7" t="n"/>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E83" s="7" t="n"/>
@@ -2080,7 +2080,7 @@
       <c r="C96" s="7" t="n"/>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Ja'Kobi Lane</t>
         </is>
       </c>
       <c r="E96" s="7" t="n"/>
@@ -2094,31 +2094,31 @@
       </c>
       <c r="B97" s="7" t="n"/>
       <c r="C97" s="7" t="n"/>
-      <c r="D97" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
+      <c r="D97" s="7" t="n"/>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="7" t="n"/>
       <c r="G97" s="7" t="n"/>
-      <c r="H97" s="7" t="n"/>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B98" s="7" t="n"/>
       <c r="C98" s="7" t="n"/>
-      <c r="D98" s="7" t="n"/>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>Terry McLaurin</t>
+        </is>
+      </c>
       <c r="E98" s="7" t="n"/>
       <c r="F98" s="7" t="n"/>
       <c r="G98" s="7" t="n"/>
-      <c r="H98" s="7" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H98" s="7" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 7; 13 players used week 4 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 8; 15 players used week 4 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 83 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 81 players moved.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Puka Nacua 68-&gt;59, Jaxon Smith-Njigba 65-&gt;56, Chris Olave 40-&gt;31, Ja'Marr Chase 60-&gt;52, Amon-Ra St. Brown 63-&gt;55, Drake London 42-&gt;34, Trey McBride 43.4286-&gt;36, Christian McCaffrey 61-&gt;54</t>
+          <t>Largest moves vs. the baseline in this file: Puka Nacua 68-&gt;59, Jaxon Smith-Njigba 65-&gt;56, Chris Olave 40-&gt;31, Ja'Marr Chase 60-&gt;52, Amon-Ra St. Brown 63-&gt;55, Drake London 43-&gt;35, Trey McBride 43.4286-&gt;36, Christian McCaffrey 61-&gt;54</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -634,15 +634,15 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="7" t="n"/>
       <c r="G6" s="7" t="n"/>
@@ -652,13 +652,13 @@
       <c r="A7" s="6" t="n">
         <v>59</v>
       </c>
-      <c r="B7" s="7" t="n"/>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="7" t="n"/>
@@ -778,7 +778,7 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B15" s="7" t="n"/>
       <c r="C15" s="7" t="n"/>
@@ -794,11 +794,11 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="C16" s="7" t="n"/>
@@ -814,7 +814,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C17" s="7" t="n"/>
@@ -858,15 +858,15 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="B20" s="7" t="n"/>
+        <v>39</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
@@ -876,13 +876,13 @@
       <c r="A21" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+      <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
@@ -1050,11 +1050,11 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="C32" s="7" t="n"/>
@@ -1066,11 +1066,11 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C33" s="7" t="n"/>
@@ -1104,7 +1104,7 @@
       <c r="C35" s="7" t="n"/>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E35" s="7" t="n"/>
@@ -1152,7 +1152,7 @@
       <c r="C38" s="7" t="n"/>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E38" s="7" t="n"/>
@@ -1168,7 +1168,7 @@
       <c r="C39" s="7" t="n"/>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E39" s="7" t="n"/>
@@ -1200,7 +1200,7 @@
       <c r="C41" s="7" t="n"/>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E41" s="7" t="n"/>
@@ -1210,15 +1210,15 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="B42" s="7" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D42" s="7" t="n"/>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="7" t="n"/>
@@ -1226,11 +1226,11 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="C43" s="7" t="n"/>
@@ -1244,13 +1244,13 @@
       <c r="A44" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="n"/>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="7" t="n"/>
@@ -1316,37 +1316,37 @@
       <c r="G48" s="7" t="n"/>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>Joe Burrow</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B49" s="7" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C49" s="7" t="n"/>
       <c r="D49" s="7" t="n"/>
       <c r="E49" s="7" t="n"/>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n"/>
-      <c r="H49" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B50" s="7" t="n"/>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="n"/>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E50" s="7" t="n"/>
       <c r="F50" s="7" t="n"/>
       <c r="G50" s="7" t="n"/>
@@ -1358,15 +1358,15 @@
       </c>
       <c r="B51" s="7" t="n"/>
       <c r="C51" s="7" t="n"/>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
       <c r="F51" s="7" t="n"/>
       <c r="G51" s="7" t="n"/>
-      <c r="H51" s="7" t="n"/>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
@@ -1440,7 +1440,7 @@
       <c r="C56" s="7" t="n"/>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E56" s="7" t="n"/>
@@ -1454,29 +1454,29 @@
       </c>
       <c r="B57" s="7" t="n"/>
       <c r="C57" s="7" t="n"/>
-      <c r="D57" s="7" t="n"/>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E57" s="7" t="n"/>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
       <c r="H57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B58" s="7" t="n"/>
       <c r="C58" s="7" t="n"/>
       <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
-      <c r="F58" s="7" t="n"/>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
     </row>
@@ -1484,13 +1484,13 @@
       <c r="A59" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B59" s="7" t="n"/>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
       <c r="F59" s="7" t="n"/>
       <c r="G59" s="7" t="n"/>
@@ -1504,7 +1504,7 @@
       <c r="C60" s="7" t="n"/>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E60" s="7" t="n"/>
@@ -1518,29 +1518,29 @@
       </c>
       <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="n"/>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E61" s="7" t="n"/>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
       <c r="H61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B62" s="7" t="n"/>
       <c r="C62" s="7" t="n"/>
       <c r="D62" s="7" t="n"/>
       <c r="E62" s="7" t="n"/>
-      <c r="F62" s="7" t="n"/>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G62" s="7" t="n"/>
       <c r="H62" s="7" t="n"/>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C63" s="7" t="n"/>
@@ -1564,13 +1564,13 @@
       <c r="A64" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B64" s="7" t="n"/>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C64" s="7" t="n"/>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D64" s="7" t="n"/>
       <c r="E64" s="7" t="n"/>
       <c r="F64" s="7" t="n"/>
       <c r="G64" s="7" t="n"/>
@@ -1628,33 +1628,33 @@
       <c r="A68" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B68" s="7" t="n"/>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C68" s="7" t="n"/>
       <c r="D68" s="7" t="n"/>
       <c r="E68" s="7" t="n"/>
       <c r="F68" s="7" t="n"/>
       <c r="G68" s="7" t="n"/>
-      <c r="H68" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B69" s="7" t="n"/>
       <c r="C69" s="7" t="n"/>
       <c r="D69" s="7" t="n"/>
       <c r="E69" s="7" t="n"/>
       <c r="F69" s="7" t="n"/>
       <c r="G69" s="7" t="n"/>
-      <c r="H69" s="7" t="n"/>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
@@ -1676,13 +1676,13 @@
       <c r="A71" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+      <c r="B71" s="7" t="n"/>
       <c r="C71" s="7" t="n"/>
-      <c r="D71" s="7" t="n"/>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
@@ -1696,7 +1696,7 @@
       <c r="C72" s="7" t="n"/>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E72" s="7" t="n"/>
@@ -1710,27 +1710,27 @@
       </c>
       <c r="B73" s="7" t="n"/>
       <c r="C73" s="7" t="n"/>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D73" s="7" t="n"/>
       <c r="E73" s="7" t="n"/>
       <c r="F73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
-      <c r="H73" s="7" t="n"/>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B74" s="7" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C74" s="7" t="n"/>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
       <c r="F74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
@@ -1738,19 +1738,19 @@
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B75" s="7" t="n"/>
       <c r="C75" s="7" t="n"/>
-      <c r="D75" s="7" t="n"/>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E75" s="7" t="n"/>
       <c r="F75" s="7" t="n"/>
       <c r="G75" s="7" t="n"/>
-      <c r="H75" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H75" s="7" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C78" s="7" t="n"/>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C79" s="7" t="n"/>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C80" s="7" t="n"/>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C81" s="7" t="n"/>
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 8; 15 players used week 4 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 9; 13 players used week 4 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 81 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 85 players moved.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Puka Nacua 68-&gt;59, Jaxon Smith-Njigba 65-&gt;56, Chris Olave 40-&gt;31, Ja'Marr Chase 60-&gt;52, Amon-Ra St. Brown 63-&gt;55, Drake London 43-&gt;35, Trey McBride 43.4286-&gt;36, Christian McCaffrey 61-&gt;54</t>
+          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 65-&gt;56, Chris Olave 40-&gt;31, Puka Nacua 69-&gt;61, Ja'Marr Chase 60-&gt;52, Amon-Ra St. Brown 63-&gt;55, Drake London 43-&gt;35, Trey McBride 43.4286-&gt;36, Christian McCaffrey 61-&gt;54</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -634,7 +634,7 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
@@ -650,11 +650,11 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C7" s="7" t="n"/>
@@ -666,11 +666,11 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C8" s="7" t="n"/>
@@ -682,15 +682,15 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>56</v>
-      </c>
-      <c r="B9" s="7" t="n"/>
+        <v>54</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D9" s="7" t="n"/>
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="7" t="n"/>
@@ -698,13 +698,13 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="E10" s="7" t="n"/>
@@ -714,15 +714,15 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
@@ -730,7 +730,7 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
@@ -746,11 +746,11 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>James Cook III</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="C13" s="7" t="n"/>
@@ -762,7 +762,7 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
@@ -780,13 +780,13 @@
       <c r="A15" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="B15" s="7" t="n"/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D15" s="7" t="n"/>
       <c r="E15" s="7" t="n"/>
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="7" t="n"/>
@@ -796,13 +796,13 @@
       <c r="A16" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+      <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
@@ -810,11 +810,11 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="C17" s="7" t="n"/>
@@ -828,41 +828,41 @@
       <c r="A18" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="B18" s="7" t="n"/>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
       <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Saquon Barkley</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C20" s="7" t="n"/>
@@ -876,13 +876,13 @@
       <c r="A21" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="B21" s="7" t="n"/>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
@@ -890,33 +890,33 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G23" s="7" t="n"/>
       <c r="H23" s="7" t="n"/>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C24" s="7" t="n"/>
@@ -938,15 +938,15 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E25" s="7" t="n"/>
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
@@ -970,7 +970,7 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
@@ -1066,35 +1066,35 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
       <c r="D33" s="7" t="n"/>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
-      <c r="H33" s="7" t="n"/>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="B34" s="7" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C34" s="7" t="n"/>
       <c r="D34" s="7" t="n"/>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
@@ -1104,7 +1104,7 @@
       <c r="C35" s="7" t="n"/>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E35" s="7" t="n"/>
@@ -1114,15 +1114,15 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="B36" s="7" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C36" s="7" t="n"/>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D36" s="7" t="n"/>
       <c r="E36" s="7" t="n"/>
       <c r="F36" s="7" t="n"/>
       <c r="G36" s="7" t="n"/>
@@ -1132,13 +1132,13 @@
       <c r="A37" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+      <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7" t="n"/>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E37" s="7" t="n"/>
       <c r="F37" s="7" t="n"/>
       <c r="G37" s="7" t="n"/>
@@ -1152,7 +1152,7 @@
       <c r="C38" s="7" t="n"/>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E38" s="7" t="n"/>
@@ -1162,15 +1162,15 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B39" s="7" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C39" s="7" t="n"/>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D39" s="7" t="n"/>
       <c r="E39" s="7" t="n"/>
       <c r="F39" s="7" t="n"/>
       <c r="G39" s="7" t="n"/>
@@ -1180,13 +1180,13 @@
       <c r="A40" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+      <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="n"/>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
@@ -1194,15 +1194,15 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="B41" s="7" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D41" s="7" t="n"/>
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="7" t="n"/>
@@ -1212,13 +1212,13 @@
       <c r="A42" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+      <c r="B42" s="7" t="n"/>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="n"/>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="7" t="n"/>
@@ -1226,15 +1226,15 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B43" s="7" t="n"/>
       <c r="C43" s="7" t="n"/>
-      <c r="D43" s="7" t="n"/>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E43" s="7" t="n"/>
       <c r="F43" s="7" t="n"/>
       <c r="G43" s="7" t="n"/>
@@ -1242,13 +1242,13 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="n"/>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E44" s="7" t="n"/>
@@ -1258,13 +1258,13 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B45" s="7" t="n"/>
       <c r="C45" s="7" t="n"/>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E45" s="7" t="n"/>
@@ -1280,7 +1280,7 @@
       <c r="C46" s="7" t="n"/>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E46" s="7" t="n"/>
@@ -1290,15 +1290,15 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B47" s="7" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D47" s="7" t="n"/>
       <c r="E47" s="7" t="n"/>
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="7" t="n"/>
@@ -1306,47 +1306,47 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B48" s="7" t="n"/>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="n"/>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
-      <c r="H48" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H48" s="7" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B49" s="7" t="n"/>
       <c r="C49" s="7" t="n"/>
       <c r="D49" s="7" t="n"/>
       <c r="E49" s="7" t="n"/>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n"/>
-      <c r="H49" s="7" t="n"/>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B50" s="7" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
       <c r="F50" s="7" t="n"/>
       <c r="G50" s="7" t="n"/>
@@ -1354,19 +1354,19 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B51" s="7" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C51" s="7" t="n"/>
       <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
       <c r="F51" s="7" t="n"/>
       <c r="G51" s="7" t="n"/>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr.</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C52" s="7" t="n"/>
@@ -1388,13 +1388,13 @@
       <c r="A53" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+      <c r="B53" s="7" t="n"/>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="7" t="n"/>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E53" s="7" t="n"/>
       <c r="F53" s="7" t="n"/>
       <c r="G53" s="7" t="n"/>
@@ -1404,29 +1404,29 @@
       <c r="A54" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+      <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
       <c r="D54" s="7" t="n"/>
       <c r="E54" s="7" t="n"/>
-      <c r="F54" s="7" t="n"/>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G54" s="7" t="n"/>
       <c r="H54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B55" s="7" t="n"/>
       <c r="C55" s="7" t="n"/>
-      <c r="D55" s="7" t="n"/>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E55" s="7" t="n"/>
       <c r="F55" s="7" t="n"/>
       <c r="G55" s="7" t="n"/>
@@ -1434,7 +1434,7 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B56" s="7" t="n"/>
       <c r="C56" s="7" t="n"/>
@@ -1450,43 +1450,43 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B57" s="7" t="n"/>
       <c r="C57" s="7" t="n"/>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
-      <c r="F57" s="7" t="n"/>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G57" s="7" t="n"/>
       <c r="H57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B58" s="7" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C58" s="7" t="n"/>
       <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C59" s="7" t="n"/>
@@ -1498,15 +1498,15 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B60" s="7" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C60" s="7" t="n"/>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D60" s="7" t="n"/>
       <c r="E60" s="7" t="n"/>
       <c r="F60" s="7" t="n"/>
       <c r="G60" s="7" t="n"/>
@@ -1514,15 +1514,15 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B61" s="7" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
       <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
@@ -1530,17 +1530,17 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B62" s="7" t="n"/>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="n"/>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E62" s="7" t="n"/>
-      <c r="F62" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F62" s="7" t="n"/>
       <c r="G62" s="7" t="n"/>
       <c r="H62" s="7" t="n"/>
     </row>
@@ -1548,15 +1548,15 @@
       <c r="A63" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+      <c r="B63" s="7" t="n"/>
       <c r="C63" s="7" t="n"/>
       <c r="D63" s="7" t="n"/>
       <c r="E63" s="7" t="n"/>
-      <c r="F63" s="7" t="n"/>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G63" s="7" t="n"/>
       <c r="H63" s="7" t="n"/>
     </row>
@@ -1564,15 +1564,15 @@
       <c r="A64" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B64" s="7" t="n"/>
       <c r="C64" s="7" t="n"/>
       <c r="D64" s="7" t="n"/>
       <c r="E64" s="7" t="n"/>
-      <c r="F64" s="7" t="n"/>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G64" s="7" t="n"/>
       <c r="H64" s="7" t="n"/>
     </row>
@@ -1586,7 +1586,7 @@
       <c r="E65" s="7" t="n"/>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>Tyler Warren</t>
+          <t>George Kittle</t>
         </is>
       </c>
       <c r="G65" s="7" t="n"/>
@@ -1600,37 +1600,37 @@
       <c r="C66" s="7" t="n"/>
       <c r="D66" s="7" t="n"/>
       <c r="E66" s="7" t="n"/>
-      <c r="F66" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F66" s="7" t="n"/>
       <c r="G66" s="7" t="n"/>
-      <c r="H66" s="7" t="n"/>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B67" s="7" t="n"/>
       <c r="C67" s="7" t="n"/>
       <c r="D67" s="7" t="n"/>
       <c r="E67" s="7" t="n"/>
-      <c r="F67" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
-      <c r="H67" s="7" t="n"/>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C68" s="7" t="n"/>
@@ -1642,31 +1642,31 @@
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B69" s="7" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
       <c r="C69" s="7" t="n"/>
       <c r="D69" s="7" t="n"/>
       <c r="E69" s="7" t="n"/>
       <c r="F69" s="7" t="n"/>
       <c r="G69" s="7" t="n"/>
-      <c r="H69" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+      <c r="B70" s="7" t="n"/>
       <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="n"/>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E70" s="7" t="n"/>
       <c r="F70" s="7" t="n"/>
       <c r="G70" s="7" t="n"/>
@@ -1680,7 +1680,7 @@
       <c r="C71" s="7" t="n"/>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E71" s="7" t="n"/>
@@ -1696,7 +1696,7 @@
       <c r="C72" s="7" t="n"/>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E72" s="7" t="n"/>
@@ -1724,13 +1724,13 @@
       <c r="A74" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+      <c r="B74" s="7" t="n"/>
       <c r="C74" s="7" t="n"/>
-      <c r="D74" s="7" t="n"/>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E74" s="7" t="n"/>
       <c r="F74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
@@ -1744,7 +1744,7 @@
       <c r="C75" s="7" t="n"/>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E75" s="7" t="n"/>
@@ -1760,7 +1760,7 @@
       <c r="C76" s="7" t="n"/>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E76" s="7" t="n"/>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C77" s="7" t="n"/>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="C78" s="7" t="n"/>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C79" s="7" t="n"/>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C80" s="7" t="n"/>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C81" s="7" t="n"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C82" s="7" t="n"/>
@@ -1868,13 +1868,13 @@
       <c r="A83" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B83" s="7" t="n"/>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C83" s="7" t="n"/>
-      <c r="D83" s="7" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
+      <c r="D83" s="7" t="n"/>
       <c r="E83" s="7" t="n"/>
       <c r="F83" s="7" t="n"/>
       <c r="G83" s="7" t="n"/>
@@ -1888,7 +1888,7 @@
       <c r="C84" s="7" t="n"/>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E84" s="7" t="n"/>
@@ -1920,7 +1920,7 @@
       <c r="C86" s="7" t="n"/>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E86" s="7" t="n"/>
@@ -1936,7 +1936,7 @@
       <c r="C87" s="7" t="n"/>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E87" s="7" t="n"/>
@@ -1950,13 +1950,13 @@
       </c>
       <c r="B88" s="7" t="n"/>
       <c r="C88" s="7" t="n"/>
-      <c r="D88" s="7" t="inlineStr">
-        <is>
-          <t>Chris Godwin Jr.</t>
-        </is>
-      </c>
+      <c r="D88" s="7" t="n"/>
       <c r="E88" s="7" t="n"/>
-      <c r="F88" s="7" t="n"/>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G88" s="7" t="n"/>
       <c r="H88" s="7" t="n"/>
     </row>
@@ -1968,13 +1968,13 @@
       <c r="C89" s="7" t="n"/>
       <c r="D89" s="7" t="n"/>
       <c r="E89" s="7" t="n"/>
-      <c r="F89" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F89" s="7" t="n"/>
       <c r="G89" s="7" t="n"/>
-      <c r="H89" s="7" t="n"/>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
@@ -2010,19 +2010,19 @@
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B92" s="7" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C92" s="7" t="n"/>
       <c r="D92" s="7" t="n"/>
       <c r="E92" s="7" t="n"/>
       <c r="F92" s="7" t="n"/>
       <c r="G92" s="7" t="n"/>
-      <c r="H92" s="7" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>Blake Corum</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="C93" s="7" t="n"/>
@@ -2044,13 +2044,13 @@
       <c r="A94" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+      <c r="B94" s="7" t="n"/>
       <c r="C94" s="7" t="n"/>
-      <c r="D94" s="7" t="n"/>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="7" t="n"/>
       <c r="G94" s="7" t="n"/>
@@ -2064,7 +2064,7 @@
       <c r="C95" s="7" t="n"/>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E95" s="7" t="n"/>
@@ -2128,7 +2128,7 @@
       <c r="C99" s="7" t="n"/>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E99" s="7" t="n"/>
@@ -2144,7 +2144,7 @@
       <c r="C100" s="7" t="n"/>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E100" s="7" t="n"/>
@@ -2154,13 +2154,13 @@
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B101" s="7" t="n"/>
       <c r="C101" s="7" t="n"/>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E101" s="7" t="n"/>
@@ -2176,7 +2176,7 @@
       <c r="C102" s="7" t="n"/>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E102" s="7" t="n"/>
@@ -2192,7 +2192,7 @@
       <c r="C103" s="7" t="n"/>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E103" s="7" t="n"/>
@@ -2208,7 +2208,7 @@
       <c r="C104" s="7" t="n"/>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E104" s="7" t="n"/>
@@ -2218,15 +2218,15 @@
     </row>
     <row r="105">
       <c r="A105" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B105" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>Kenny Gainwell</t>
+        </is>
+      </c>
       <c r="C105" s="7" t="n"/>
-      <c r="D105" s="7" t="inlineStr">
-        <is>
-          <t>Jordyn Tyson</t>
-        </is>
-      </c>
+      <c r="D105" s="7" t="n"/>
       <c r="E105" s="7" t="n"/>
       <c r="F105" s="7" t="n"/>
       <c r="G105" s="7" t="n"/>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>Kenny Gainwell</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="C106" s="7" t="n"/>
@@ -2295,7 +2295,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 76.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 77.</t>
         </is>
       </c>
     </row>
@@ -2312,14 +2312,14 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>0) Weekly re-seed. The sheet values were first moved toward the 2026 week 5 Half PPR medians</t>
+          <t>0) Weekly re-seed. The sheet values were first moved toward the 2026 week 6 Half PPR medians</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 9; 13 players used week 4 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 0; 4 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,14 +2333,14 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 85 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 68 players moved.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   No projection this week (value kept): A.J. Brown, Breece Hall, Travis Etienne Jr., Josh Jacobs, De'Zhaun Stribling, Jordan Mason, Alec Pierce, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Kenny Gainwell, Jaxson Dart, Ja'Kobi Lane.</t>
+          <t xml:space="preserve">   No projection this week (value kept): Kenneth Walker III, Saquon Barkley, Javonte Williams, A.J. Brown, Breece Hall, DeVonta Smith, Rashee Rice, Lamar Jackson, Tetairoa McMillan, Travis Etienne Jr., Jadarian Price, Jaylen Warren, DJ Moore, Josh Jacobs, De'Zhaun Stribling, Jordan Mason, Alec Pierce, Brian Thomas Jr., Quentin Johnston, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Kenny Gainwell, Chuba Hubbard, Jaxson Dart, Ja'Kobi Lane.</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.6, WR 2.8, TE 4.5, QB 0.0.</t>
+          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.8, WR 2.7, TE 4.5, QB 0.0.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 65-&gt;56, Chris Olave 40-&gt;31, Puka Nacua 69-&gt;61, Ja'Marr Chase 60-&gt;52, Amon-Ra St. Brown 63-&gt;55, Drake London 43-&gt;35, Trey McBride 43.4286-&gt;36, Christian McCaffrey 61-&gt;54</t>
+          <t>Largest moves vs. the baseline in this file: Puka Nacua 68-&gt;58, Jaxon Smith-Njigba 63-&gt;53, Chris Olave 40-&gt;30, Ja'Marr Chase 60-&gt;51, Amon-Ra St. Brown 62-&gt;53, Justin Jefferson 45-&gt;37, CeeDee Lamb 54-&gt;46, Drake London 42-&gt;34</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -618,7 +618,7 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
@@ -634,15 +634,15 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="B6" s="7" t="n"/>
+        <v>63</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="7" t="n"/>
       <c r="G6" s="7" t="n"/>
@@ -650,11 +650,11 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>James Cook III</t>
         </is>
       </c>
       <c r="C7" s="7" t="n"/>
@@ -666,15 +666,15 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="B8" s="7" t="n"/>
       <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="7" t="n"/>
@@ -682,11 +682,11 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C9" s="7" t="n"/>
@@ -698,13 +698,13 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E10" s="7" t="n"/>
@@ -714,15 +714,15 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="B11" s="7" t="n"/>
+        <v>57</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D11" s="7" t="n"/>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
@@ -730,7 +730,7 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
@@ -746,15 +746,15 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
@@ -762,11 +762,11 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="C14" s="7" t="n"/>
@@ -782,7 +782,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>James Cook III</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="C15" s="7" t="n"/>
@@ -794,15 +794,15 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="B16" s="7" t="n"/>
+        <v>48</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D16" s="7" t="n"/>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
@@ -812,21 +812,21 @@
       <c r="A17" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+      <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="n"/>
       <c r="D17" s="7" t="n"/>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="n"/>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
@@ -842,27 +842,27 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C20" s="7" t="n"/>
@@ -874,15 +874,15 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
@@ -890,15 +890,15 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="B22" s="7" t="n"/>
+        <v>39</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
@@ -906,33 +906,33 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
       <c r="H23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
     </row>
@@ -940,13 +940,13 @@
       <c r="A25" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="B25" s="7" t="n"/>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
@@ -954,23 +954,23 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
@@ -1002,23 +1002,23 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D29" s="7" t="n"/>
       <c r="E29" s="7" t="n"/>
-      <c r="F29" s="7" t="n"/>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G29" s="7" t="n"/>
       <c r="H29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
@@ -1036,13 +1036,13 @@
       <c r="A31" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="B31" s="7" t="n"/>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D31" s="7" t="n"/>
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="7" t="n"/>
       <c r="G31" s="7" t="n"/>
@@ -1050,47 +1050,47 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
       <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
-      <c r="H32" s="7" t="n"/>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="n"/>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="n"/>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="7" t="n"/>
@@ -1098,13 +1098,13 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E35" s="7" t="n"/>
@@ -1114,15 +1114,15 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
-      <c r="D36" s="7" t="n"/>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E36" s="7" t="n"/>
       <c r="F36" s="7" t="n"/>
       <c r="G36" s="7" t="n"/>
@@ -1130,13 +1130,13 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E37" s="7" t="n"/>
@@ -1146,15 +1146,15 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B38" s="7" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D38" s="7" t="n"/>
       <c r="E38" s="7" t="n"/>
       <c r="F38" s="7" t="n"/>
       <c r="G38" s="7" t="n"/>
@@ -1162,15 +1162,15 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
-      <c r="D39" s="7" t="n"/>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E39" s="7" t="n"/>
       <c r="F39" s="7" t="n"/>
       <c r="G39" s="7" t="n"/>
@@ -1180,13 +1180,13 @@
       <c r="A40" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B40" s="7" t="n"/>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D40" s="7" t="n"/>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
@@ -1194,15 +1194,15 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="n"/>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="7" t="n"/>
@@ -1210,15 +1210,15 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B42" s="7" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D42" s="7" t="n"/>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="7" t="n"/>
@@ -1226,13 +1226,13 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B43" s="7" t="n"/>
       <c r="C43" s="7" t="n"/>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E43" s="7" t="n"/>
@@ -1242,15 +1242,15 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B44" s="7" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D44" s="7" t="n"/>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="7" t="n"/>
@@ -1258,15 +1258,15 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B45" s="7" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D45" s="7" t="n"/>
       <c r="E45" s="7" t="n"/>
       <c r="F45" s="7" t="n"/>
       <c r="G45" s="7" t="n"/>
@@ -1274,15 +1274,15 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B46" s="7" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D46" s="7" t="n"/>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="7" t="n"/>
@@ -1290,15 +1290,15 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="n"/>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E47" s="7" t="n"/>
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="7" t="n"/>
@@ -1306,15 +1306,15 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B48" s="7" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D48" s="7" t="n"/>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
@@ -1322,31 +1322,31 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B49" s="7" t="n"/>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="n"/>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E49" s="7" t="n"/>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n"/>
-      <c r="H49" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B50" s="7" t="n"/>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="n"/>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E50" s="7" t="n"/>
       <c r="F50" s="7" t="n"/>
       <c r="G50" s="7" t="n"/>
@@ -1354,27 +1354,27 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B51" s="7" t="n"/>
       <c r="C51" s="7" t="n"/>
       <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
       <c r="F51" s="7" t="n"/>
       <c r="G51" s="7" t="n"/>
-      <c r="H51" s="7" t="n"/>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C52" s="7" t="n"/>
@@ -1386,23 +1386,23 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B53" s="7" t="n"/>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D53" s="7" t="n"/>
       <c r="E53" s="7" t="n"/>
-      <c r="F53" s="7" t="n"/>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G53" s="7" t="n"/>
       <c r="H53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
@@ -1418,15 +1418,15 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B55" s="7" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C55" s="7" t="n"/>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
       <c r="F55" s="7" t="n"/>
       <c r="G55" s="7" t="n"/>
@@ -1434,15 +1434,15 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B56" s="7" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C56" s="7" t="n"/>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D56" s="7" t="n"/>
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="n"/>
@@ -1450,59 +1450,59 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B57" s="7" t="n"/>
       <c r="C57" s="7" t="n"/>
-      <c r="D57" s="7" t="n"/>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E57" s="7" t="n"/>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
       <c r="H57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B58" s="7" t="n"/>
       <c r="C58" s="7" t="n"/>
       <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
-      <c r="F58" s="7" t="n"/>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B59" s="7" t="n"/>
       <c r="C59" s="7" t="n"/>
       <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
-      <c r="F59" s="7" t="n"/>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G59" s="7" t="n"/>
       <c r="H59" s="7" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C60" s="7" t="n"/>
@@ -1514,15 +1514,15 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="n"/>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E61" s="7" t="n"/>
       <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
@@ -1530,7 +1530,7 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B62" s="7" t="n"/>
       <c r="C62" s="7" t="n"/>
@@ -1548,15 +1548,15 @@
       <c r="A63" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B63" s="7" t="n"/>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C63" s="7" t="n"/>
       <c r="D63" s="7" t="n"/>
       <c r="E63" s="7" t="n"/>
-      <c r="F63" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F63" s="7" t="n"/>
       <c r="G63" s="7" t="n"/>
       <c r="H63" s="7" t="n"/>
     </row>
@@ -1564,15 +1564,15 @@
       <c r="A64" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B64" s="7" t="n"/>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C64" s="7" t="n"/>
       <c r="D64" s="7" t="n"/>
       <c r="E64" s="7" t="n"/>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F64" s="7" t="n"/>
       <c r="G64" s="7" t="n"/>
       <c r="H64" s="7" t="n"/>
     </row>
@@ -1584,57 +1584,57 @@
       <c r="C65" s="7" t="n"/>
       <c r="D65" s="7" t="n"/>
       <c r="E65" s="7" t="n"/>
-      <c r="F65" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F65" s="7" t="n"/>
       <c r="G65" s="7" t="n"/>
-      <c r="H65" s="7" t="n"/>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B66" s="7" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C66" s="7" t="n"/>
       <c r="D66" s="7" t="n"/>
       <c r="E66" s="7" t="n"/>
       <c r="F66" s="7" t="n"/>
       <c r="G66" s="7" t="n"/>
-      <c r="H66" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B67" s="7" t="n"/>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C67" s="7" t="n"/>
       <c r="D67" s="7" t="n"/>
       <c r="E67" s="7" t="n"/>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
-      <c r="H67" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B68" s="7" t="n"/>
       <c r="C68" s="7" t="n"/>
-      <c r="D68" s="7" t="n"/>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E68" s="7" t="n"/>
       <c r="F68" s="7" t="n"/>
       <c r="G68" s="7" t="n"/>
@@ -1642,15 +1642,15 @@
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B69" s="7" t="n"/>
       <c r="C69" s="7" t="n"/>
-      <c r="D69" s="7" t="n"/>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E69" s="7" t="n"/>
       <c r="F69" s="7" t="n"/>
       <c r="G69" s="7" t="n"/>
@@ -1658,47 +1658,47 @@
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B70" s="7" t="n"/>
       <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D70" s="7" t="n"/>
       <c r="E70" s="7" t="n"/>
       <c r="F70" s="7" t="n"/>
       <c r="G70" s="7" t="n"/>
-      <c r="H70" s="7" t="n"/>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B71" s="7" t="n"/>
       <c r="C71" s="7" t="n"/>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D71" s="7" t="n"/>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
-      <c r="H71" s="7" t="n"/>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B72" s="7" t="n"/>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
       <c r="C72" s="7" t="n"/>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>Brian Thomas Jr.</t>
-        </is>
-      </c>
+      <c r="D72" s="7" t="n"/>
       <c r="E72" s="7" t="n"/>
       <c r="F72" s="7" t="n"/>
       <c r="G72" s="7" t="n"/>
@@ -1710,19 +1710,19 @@
       </c>
       <c r="B73" s="7" t="n"/>
       <c r="C73" s="7" t="n"/>
-      <c r="D73" s="7" t="n"/>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E73" s="7" t="n"/>
       <c r="F73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
-      <c r="H73" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B74" s="7" t="n"/>
       <c r="C74" s="7" t="n"/>
@@ -1738,13 +1738,13 @@
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B75" s="7" t="n"/>
       <c r="C75" s="7" t="n"/>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E75" s="7" t="n"/>
@@ -1754,27 +1754,27 @@
     </row>
     <row r="76">
       <c r="A76" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B76" s="7" t="n"/>
       <c r="C76" s="7" t="n"/>
-      <c r="D76" s="7" t="inlineStr">
-        <is>
-          <t>Quentin Johnston</t>
-        </is>
-      </c>
+      <c r="D76" s="7" t="n"/>
       <c r="E76" s="7" t="n"/>
-      <c r="F76" s="7" t="n"/>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G76" s="7" t="n"/>
       <c r="H76" s="7" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C77" s="7" t="n"/>
@@ -1786,11 +1786,11 @@
     </row>
     <row r="78">
       <c r="A78" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C78" s="7" t="n"/>
@@ -1802,11 +1802,11 @@
     </row>
     <row r="79">
       <c r="A79" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C79" s="7" t="n"/>
@@ -1818,15 +1818,15 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>Jonathon Brooks</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B80" s="7" t="n"/>
       <c r="C80" s="7" t="n"/>
-      <c r="D80" s="7" t="n"/>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>Quentin Johnston</t>
+        </is>
+      </c>
       <c r="E80" s="7" t="n"/>
       <c r="F80" s="7" t="n"/>
       <c r="G80" s="7" t="n"/>
@@ -1834,15 +1834,15 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>Mike Washington Jr.</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B81" s="7" t="n"/>
       <c r="C81" s="7" t="n"/>
-      <c r="D81" s="7" t="n"/>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>Marvin Harrison Jr.</t>
+        </is>
+      </c>
       <c r="E81" s="7" t="n"/>
       <c r="F81" s="7" t="n"/>
       <c r="G81" s="7" t="n"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C82" s="7" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C83" s="7" t="n"/>
@@ -1884,13 +1884,13 @@
       <c r="A84" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B84" s="7" t="n"/>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>Rico Dowdle</t>
+        </is>
+      </c>
       <c r="C84" s="7" t="n"/>
-      <c r="D84" s="7" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
+      <c r="D84" s="7" t="n"/>
       <c r="E84" s="7" t="n"/>
       <c r="F84" s="7" t="n"/>
       <c r="G84" s="7" t="n"/>
@@ -1900,13 +1900,13 @@
       <c r="A85" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B85" s="7" t="n"/>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C85" s="7" t="n"/>
-      <c r="D85" s="7" t="inlineStr">
-        <is>
-          <t>De'Zhaun Stribling</t>
-        </is>
-      </c>
+      <c r="D85" s="7" t="n"/>
       <c r="E85" s="7" t="n"/>
       <c r="F85" s="7" t="n"/>
       <c r="G85" s="7" t="n"/>
@@ -1920,7 +1920,7 @@
       <c r="C86" s="7" t="n"/>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E86" s="7" t="n"/>
@@ -1936,7 +1936,7 @@
       <c r="C87" s="7" t="n"/>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr.</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E87" s="7" t="n"/>
@@ -1950,13 +1950,13 @@
       </c>
       <c r="B88" s="7" t="n"/>
       <c r="C88" s="7" t="n"/>
-      <c r="D88" s="7" t="n"/>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>De'Zhaun Stribling</t>
+        </is>
+      </c>
       <c r="E88" s="7" t="n"/>
-      <c r="F88" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F88" s="7" t="n"/>
       <c r="G88" s="7" t="n"/>
       <c r="H88" s="7" t="n"/>
     </row>
@@ -1966,15 +1966,15 @@
       </c>
       <c r="B89" s="7" t="n"/>
       <c r="C89" s="7" t="n"/>
-      <c r="D89" s="7" t="n"/>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>Chris Godwin Jr.</t>
+        </is>
+      </c>
       <c r="E89" s="7" t="n"/>
       <c r="F89" s="7" t="n"/>
       <c r="G89" s="7" t="n"/>
-      <c r="H89" s="7" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H89" s="7" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
@@ -1984,13 +1984,13 @@
       <c r="C90" s="7" t="n"/>
       <c r="D90" s="7" t="n"/>
       <c r="E90" s="7" t="n"/>
-      <c r="F90" s="7" t="n"/>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G90" s="7" t="n"/>
-      <c r="H90" s="7" t="inlineStr">
-        <is>
-          <t>Jalen Hurts</t>
-        </is>
-      </c>
+      <c r="H90" s="7" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
@@ -2004,53 +2004,53 @@
       <c r="G91" s="7" t="n"/>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B92" s="7" t="n"/>
       <c r="C92" s="7" t="n"/>
       <c r="D92" s="7" t="n"/>
       <c r="E92" s="7" t="n"/>
       <c r="F92" s="7" t="n"/>
       <c r="G92" s="7" t="n"/>
-      <c r="H92" s="7" t="n"/>
+      <c r="H92" s="7" t="inlineStr">
+        <is>
+          <t>Justin Herbert</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B93" s="7" t="n"/>
       <c r="C93" s="7" t="n"/>
       <c r="D93" s="7" t="n"/>
       <c r="E93" s="7" t="n"/>
       <c r="F93" s="7" t="n"/>
       <c r="G93" s="7" t="n"/>
-      <c r="H93" s="7" t="n"/>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B94" s="7" t="n"/>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C94" s="7" t="n"/>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D94" s="7" t="n"/>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="7" t="n"/>
       <c r="G94" s="7" t="n"/>
@@ -2064,7 +2064,7 @@
       <c r="C95" s="7" t="n"/>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E95" s="7" t="n"/>
@@ -2080,7 +2080,7 @@
       <c r="C96" s="7" t="n"/>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E96" s="7" t="n"/>
@@ -2094,25 +2094,25 @@
       </c>
       <c r="B97" s="7" t="n"/>
       <c r="C97" s="7" t="n"/>
-      <c r="D97" s="7" t="n"/>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="7" t="n"/>
       <c r="G97" s="7" t="n"/>
-      <c r="H97" s="7" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H97" s="7" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B98" s="7" t="n"/>
       <c r="C98" s="7" t="n"/>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Ja'Kobi Lane</t>
         </is>
       </c>
       <c r="E98" s="7" t="n"/>
@@ -2122,19 +2122,19 @@
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B99" s="7" t="n"/>
       <c r="C99" s="7" t="n"/>
-      <c r="D99" s="7" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D99" s="7" t="n"/>
       <c r="E99" s="7" t="n"/>
       <c r="F99" s="7" t="n"/>
       <c r="G99" s="7" t="n"/>
-      <c r="H99" s="7" t="n"/>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
@@ -2144,7 +2144,7 @@
       <c r="C100" s="7" t="n"/>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E100" s="7" t="n"/>
@@ -2154,7 +2154,7 @@
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B101" s="7" t="n"/>
       <c r="C101" s="7" t="n"/>
@@ -2170,13 +2170,13 @@
     </row>
     <row r="102">
       <c r="A102" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B102" s="7" t="n"/>
       <c r="C102" s="7" t="n"/>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E102" s="7" t="n"/>
@@ -2192,7 +2192,7 @@
       <c r="C103" s="7" t="n"/>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E103" s="7" t="n"/>
@@ -2208,7 +2208,7 @@
       <c r="C104" s="7" t="n"/>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E104" s="7" t="n"/>
@@ -2218,15 +2218,15 @@
     </row>
     <row r="105">
       <c r="A105" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B105" s="7" t="inlineStr">
-        <is>
-          <t>Kenny Gainwell</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B105" s="7" t="n"/>
       <c r="C105" s="7" t="n"/>
-      <c r="D105" s="7" t="n"/>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>Jordyn Tyson</t>
+        </is>
+      </c>
       <c r="E105" s="7" t="n"/>
       <c r="F105" s="7" t="n"/>
       <c r="G105" s="7" t="n"/>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Kenny Gainwell</t>
         </is>
       </c>
       <c r="C106" s="7" t="n"/>
@@ -2295,7 +2295,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 77.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 73.</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 0; 4 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 0; 30 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,14 +2333,14 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 68 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 69 players moved.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   No projection this week (value kept): Kenneth Walker III, Saquon Barkley, Javonte Williams, A.J. Brown, Breece Hall, DeVonta Smith, Rashee Rice, Lamar Jackson, Tetairoa McMillan, Travis Etienne Jr., Jadarian Price, Jaylen Warren, DJ Moore, Josh Jacobs, De'Zhaun Stribling, Jordan Mason, Alec Pierce, Brian Thomas Jr., Quentin Johnston, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Kenny Gainwell, Chuba Hubbard, Jaxson Dart, Ja'Kobi Lane.</t>
+          <t xml:space="preserve">   No projection this week (value kept): Saquon Barkley, A.J. Brown, Breece Hall, DeVonta Smith, Rashee Rice, Lamar Jackson, Travis Etienne Jr., Jadarian Price, DJ Moore, Josh Jacobs, De'Zhaun Stribling, Jordan Mason, Alec Pierce, Brian Thomas Jr., Quentin Johnston, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Kenny Gainwell, Jaxson Dart, Ja'Kobi Lane.</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.8, WR 2.7, TE 4.5, QB 0.0.</t>
+          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.6, WR 2.8, TE 4.5, QB 0.0.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Puka Nacua 68-&gt;58, Jaxon Smith-Njigba 63-&gt;53, Chris Olave 40-&gt;30, Ja'Marr Chase 60-&gt;51, Amon-Ra St. Brown 62-&gt;53, Justin Jefferson 45-&gt;37, CeeDee Lamb 54-&gt;46, Drake London 42-&gt;34</t>
+          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 61-&gt;54, Chris Olave 41-&gt;34, DeVonta Smith 27-&gt;20, Rashee Rice 26-&gt;19, Garrett Wilson 29-&gt;22, Trey McBride 41.7143-&gt;35, Puka Nacua 68-&gt;62, Justin Jefferson 46-&gt;40</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -618,7 +618,7 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
@@ -650,15 +650,15 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>62</v>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="B7" s="7" t="n"/>
       <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="7" t="n"/>
@@ -666,15 +666,15 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>62</v>
-      </c>
-      <c r="B8" s="7" t="n"/>
+        <v>60</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Jonathan Taylor</t>
+        </is>
+      </c>
       <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D8" s="7" t="n"/>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="7" t="n"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>James Cook III</t>
         </is>
       </c>
       <c r="C9" s="7" t="n"/>
@@ -698,15 +698,15 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="B10" s="7" t="n"/>
+        <v>57</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="n"/>
@@ -716,13 +716,13 @@
       <c r="A11" s="6" t="n">
         <v>57</v>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+      <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
@@ -730,13 +730,13 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="E12" s="7" t="n"/>
@@ -746,13 +746,13 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E13" s="7" t="n"/>
@@ -762,7 +762,7 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="n"/>
@@ -828,13 +828,13 @@
       <c r="A18" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+      <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
@@ -842,15 +842,15 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="B19" s="7" t="n"/>
+        <v>40</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
@@ -862,7 +862,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C20" s="7" t="n"/>
@@ -908,13 +908,13 @@
       <c r="A23" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="B23" s="7" t="n"/>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
@@ -922,33 +922,33 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
     </row>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
@@ -1050,19 +1050,19 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
@@ -1070,25 +1070,25 @@
       </c>
       <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D33" s="7" t="n"/>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
-      <c r="H33" s="7" t="n"/>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E34" s="7" t="n"/>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
@@ -1148,13 +1148,13 @@
       <c r="A38" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+      <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="n"/>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E38" s="7" t="n"/>
       <c r="F38" s="7" t="n"/>
       <c r="G38" s="7" t="n"/>
@@ -1162,15 +1162,15 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="B39" s="7" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C39" s="7" t="n"/>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>Rashee Rice</t>
-        </is>
-      </c>
+      <c r="D39" s="7" t="n"/>
       <c r="E39" s="7" t="n"/>
       <c r="F39" s="7" t="n"/>
       <c r="G39" s="7" t="n"/>
@@ -1178,15 +1178,15 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="n"/>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
@@ -1194,15 +1194,15 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="B41" s="7" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D41" s="7" t="n"/>
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="7" t="n"/>
@@ -1226,13 +1226,13 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B43" s="7" t="n"/>
       <c r="C43" s="7" t="n"/>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E43" s="7" t="n"/>
@@ -1244,13 +1244,13 @@
       <c r="A44" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+      <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="n"/>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="7" t="n"/>
@@ -1258,11 +1258,11 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C45" s="7" t="n"/>
@@ -1274,11 +1274,11 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C46" s="7" t="n"/>
@@ -1290,15 +1290,15 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B47" s="7" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D47" s="7" t="n"/>
       <c r="E47" s="7" t="n"/>
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="7" t="n"/>
@@ -1308,13 +1308,13 @@
       <c r="A48" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+      <c r="B48" s="7" t="n"/>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="n"/>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
@@ -1328,7 +1328,7 @@
       <c r="C49" s="7" t="n"/>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E49" s="7" t="n"/>
@@ -1338,15 +1338,15 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B50" s="7" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
       <c r="F50" s="7" t="n"/>
       <c r="G50" s="7" t="n"/>
@@ -1354,33 +1354,33 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B51" s="7" t="n"/>
       <c r="C51" s="7" t="n"/>
       <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
-      <c r="F51" s="7" t="n"/>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G51" s="7" t="n"/>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B52" s="7" t="n"/>
       <c r="C52" s="7" t="n"/>
       <c r="D52" s="7" t="n"/>
       <c r="E52" s="7" t="n"/>
-      <c r="F52" s="7" t="n"/>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G52" s="7" t="n"/>
       <c r="H52" s="7" t="n"/>
     </row>
@@ -1392,27 +1392,27 @@
       <c r="C53" s="7" t="n"/>
       <c r="D53" s="7" t="n"/>
       <c r="E53" s="7" t="n"/>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F53" s="7" t="n"/>
       <c r="G53" s="7" t="n"/>
-      <c r="H53" s="7" t="n"/>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B54" s="7" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C54" s="7" t="n"/>
       <c r="D54" s="7" t="n"/>
       <c r="E54" s="7" t="n"/>
-      <c r="F54" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F54" s="7" t="n"/>
       <c r="G54" s="7" t="n"/>
       <c r="H54" s="7" t="n"/>
     </row>
@@ -1420,15 +1420,15 @@
       <c r="A55" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+      <c r="B55" s="7" t="n"/>
       <c r="C55" s="7" t="n"/>
       <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7" t="n"/>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G55" s="7" t="n"/>
       <c r="H55" s="7" t="n"/>
     </row>
@@ -1436,29 +1436,29 @@
       <c r="A56" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B56" s="7" t="n"/>
       <c r="C56" s="7" t="n"/>
       <c r="D56" s="7" t="n"/>
       <c r="E56" s="7" t="n"/>
-      <c r="F56" s="7" t="n"/>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G56" s="7" t="n"/>
       <c r="H56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B57" s="7" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C57" s="7" t="n"/>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
       <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
@@ -1466,33 +1466,33 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B58" s="7" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C58" s="7" t="n"/>
       <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B59" s="7" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C59" s="7" t="n"/>
       <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F59" s="7" t="n"/>
       <c r="G59" s="7" t="n"/>
       <c r="H59" s="7" t="n"/>
     </row>
@@ -1500,13 +1500,13 @@
       <c r="A60" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+      <c r="B60" s="7" t="n"/>
       <c r="C60" s="7" t="n"/>
-      <c r="D60" s="7" t="n"/>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E60" s="7" t="n"/>
       <c r="F60" s="7" t="n"/>
       <c r="G60" s="7" t="n"/>
@@ -1578,31 +1578,31 @@
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B65" s="7" t="n"/>
       <c r="C65" s="7" t="n"/>
-      <c r="D65" s="7" t="n"/>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E65" s="7" t="n"/>
       <c r="F65" s="7" t="n"/>
       <c r="G65" s="7" t="n"/>
-      <c r="H65" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H65" s="7" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+      <c r="B66" s="7" t="n"/>
       <c r="C66" s="7" t="n"/>
-      <c r="D66" s="7" t="n"/>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E66" s="7" t="n"/>
       <c r="F66" s="7" t="n"/>
       <c r="G66" s="7" t="n"/>
@@ -1612,17 +1612,17 @@
       <c r="A67" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+      <c r="B67" s="7" t="n"/>
       <c r="C67" s="7" t="n"/>
       <c r="D67" s="7" t="n"/>
       <c r="E67" s="7" t="n"/>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
-      <c r="H67" s="7" t="n"/>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
@@ -1630,27 +1630,27 @@
       </c>
       <c r="B68" s="7" t="n"/>
       <c r="C68" s="7" t="n"/>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D68" s="7" t="n"/>
       <c r="E68" s="7" t="n"/>
       <c r="F68" s="7" t="n"/>
       <c r="G68" s="7" t="n"/>
-      <c r="H68" s="7" t="n"/>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B69" s="7" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
       <c r="C69" s="7" t="n"/>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D69" s="7" t="n"/>
       <c r="E69" s="7" t="n"/>
       <c r="F69" s="7" t="n"/>
       <c r="G69" s="7" t="n"/>
@@ -1658,47 +1658,47 @@
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B70" s="7" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C70" s="7" t="n"/>
       <c r="D70" s="7" t="n"/>
       <c r="E70" s="7" t="n"/>
       <c r="F70" s="7" t="n"/>
       <c r="G70" s="7" t="n"/>
-      <c r="H70" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B71" s="7" t="n"/>
       <c r="C71" s="7" t="n"/>
-      <c r="D71" s="7" t="n"/>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
-      <c r="H71" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H71" s="7" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+      <c r="B72" s="7" t="n"/>
       <c r="C72" s="7" t="n"/>
-      <c r="D72" s="7" t="n"/>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E72" s="7" t="n"/>
       <c r="F72" s="7" t="n"/>
       <c r="G72" s="7" t="n"/>
@@ -1712,7 +1712,7 @@
       <c r="C73" s="7" t="n"/>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E73" s="7" t="n"/>
@@ -1726,13 +1726,13 @@
       </c>
       <c r="B74" s="7" t="n"/>
       <c r="C74" s="7" t="n"/>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
-      <c r="F74" s="7" t="n"/>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G74" s="7" t="n"/>
       <c r="H74" s="7" t="n"/>
     </row>
@@ -1742,29 +1742,29 @@
       </c>
       <c r="B75" s="7" t="n"/>
       <c r="C75" s="7" t="n"/>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>Brian Thomas Jr.</t>
-        </is>
-      </c>
+      <c r="D75" s="7" t="n"/>
       <c r="E75" s="7" t="n"/>
       <c r="F75" s="7" t="n"/>
       <c r="G75" s="7" t="n"/>
-      <c r="H75" s="7" t="n"/>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B76" s="7" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C76" s="7" t="n"/>
       <c r="D76" s="7" t="n"/>
       <c r="E76" s="7" t="n"/>
-      <c r="F76" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F76" s="7" t="n"/>
       <c r="G76" s="7" t="n"/>
       <c r="H76" s="7" t="n"/>
     </row>
@@ -1788,13 +1788,13 @@
       <c r="A78" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>Jonathon Brooks</t>
-        </is>
-      </c>
+      <c r="B78" s="7" t="n"/>
       <c r="C78" s="7" t="n"/>
-      <c r="D78" s="7" t="n"/>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>Quentin Johnston</t>
+        </is>
+      </c>
       <c r="E78" s="7" t="n"/>
       <c r="F78" s="7" t="n"/>
       <c r="G78" s="7" t="n"/>
@@ -1802,11 +1802,11 @@
     </row>
     <row r="79">
       <c r="A79" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C79" s="7" t="n"/>
@@ -1818,15 +1818,15 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B80" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>Jonathon Brooks</t>
+        </is>
+      </c>
       <c r="C80" s="7" t="n"/>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>Quentin Johnston</t>
-        </is>
-      </c>
+      <c r="D80" s="7" t="n"/>
       <c r="E80" s="7" t="n"/>
       <c r="F80" s="7" t="n"/>
       <c r="G80" s="7" t="n"/>
@@ -1834,15 +1834,15 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B81" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>Mike Washington Jr.</t>
+        </is>
+      </c>
       <c r="C81" s="7" t="n"/>
-      <c r="D81" s="7" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D81" s="7" t="n"/>
       <c r="E81" s="7" t="n"/>
       <c r="F81" s="7" t="n"/>
       <c r="G81" s="7" t="n"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C82" s="7" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C83" s="7" t="n"/>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="C84" s="7" t="n"/>
@@ -1900,13 +1900,13 @@
       <c r="A85" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+      <c r="B85" s="7" t="n"/>
       <c r="C85" s="7" t="n"/>
-      <c r="D85" s="7" t="n"/>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E85" s="7" t="n"/>
       <c r="F85" s="7" t="n"/>
       <c r="G85" s="7" t="n"/>
@@ -1920,7 +1920,7 @@
       <c r="C86" s="7" t="n"/>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E86" s="7" t="n"/>
@@ -1936,7 +1936,7 @@
       <c r="C87" s="7" t="n"/>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E87" s="7" t="n"/>
@@ -1952,7 +1952,7 @@
       <c r="C88" s="7" t="n"/>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E88" s="7" t="n"/>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>Blake Corum</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="C94" s="7" t="n"/>
@@ -2096,7 +2096,7 @@
       <c r="C97" s="7" t="n"/>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>Ja'Kobi Lane</t>
         </is>
       </c>
       <c r="E97" s="7" t="n"/>
@@ -2110,31 +2110,31 @@
       </c>
       <c r="B98" s="7" t="n"/>
       <c r="C98" s="7" t="n"/>
-      <c r="D98" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
+      <c r="D98" s="7" t="n"/>
       <c r="E98" s="7" t="n"/>
       <c r="F98" s="7" t="n"/>
       <c r="G98" s="7" t="n"/>
-      <c r="H98" s="7" t="n"/>
+      <c r="H98" s="7" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B99" s="7" t="n"/>
       <c r="C99" s="7" t="n"/>
-      <c r="D99" s="7" t="n"/>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>Terry McLaurin</t>
+        </is>
+      </c>
       <c r="E99" s="7" t="n"/>
       <c r="F99" s="7" t="n"/>
       <c r="G99" s="7" t="n"/>
-      <c r="H99" s="7" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
@@ -2144,7 +2144,7 @@
       <c r="C100" s="7" t="n"/>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E100" s="7" t="n"/>
@@ -2160,7 +2160,7 @@
       <c r="C101" s="7" t="n"/>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E101" s="7" t="n"/>
@@ -2295,7 +2295,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 73.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 74.</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 0; 30 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 1; 25 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 61-&gt;54, Chris Olave 41-&gt;34, DeVonta Smith 27-&gt;20, Rashee Rice 26-&gt;19, Garrett Wilson 29-&gt;22, Trey McBride 41.7143-&gt;35, Puka Nacua 68-&gt;62, Justin Jefferson 46-&gt;40</t>
+          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 61-&gt;53, Chris Olave 42-&gt;34, Trey McBride 42.2857-&gt;35, Puka Nacua 68-&gt;61, DeVonta Smith 27-&gt;20, Rashee Rice 26-&gt;19, Garrett Wilson 28-&gt;21, Davante Adams 20-&gt;13</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -618,7 +618,7 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
@@ -682,11 +682,11 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>James Cook III</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C9" s="7" t="n"/>
@@ -700,13 +700,13 @@
       <c r="A10" s="6" t="n">
         <v>57</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+      <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="n"/>
@@ -714,15 +714,15 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="B11" s="7" t="n"/>
+        <v>56</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>James Cook III</t>
+        </is>
+      </c>
       <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D11" s="7" t="n"/>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
@@ -730,15 +730,15 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="B12" s="7" t="n"/>
+        <v>56</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D12" s="7" t="n"/>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="n"/>
@@ -746,7 +746,7 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
@@ -762,15 +762,15 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>52</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
@@ -778,11 +778,11 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="C15" s="7" t="n"/>
@@ -794,7 +794,7 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
@@ -826,13 +826,13 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="E18" s="7" t="n"/>
@@ -842,15 +842,15 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
@@ -862,7 +862,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Ashton Jeanty</t>
         </is>
       </c>
       <c r="C20" s="7" t="n"/>
@@ -876,13 +876,13 @@
       <c r="A21" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="B21" s="7" t="n"/>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
@@ -890,15 +890,15 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
@@ -906,11 +906,11 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C23" s="7" t="n"/>
@@ -924,13 +924,13 @@
       <c r="A24" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="B24" s="7" t="n"/>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
@@ -954,15 +954,15 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="B26" s="7" t="n"/>
+        <v>33</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
@@ -972,13 +972,13 @@
       <c r="A27" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+      <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
@@ -986,13 +986,13 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Chris Olave</t>
         </is>
       </c>
       <c r="E28" s="7" t="n"/>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
@@ -1054,41 +1054,41 @@
       </c>
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
-      <c r="H32" s="7" t="n"/>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="n"/>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E34" s="7" t="n"/>
@@ -1098,13 +1098,13 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E35" s="7" t="n"/>
@@ -1162,15 +1162,15 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
-      <c r="D39" s="7" t="n"/>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E39" s="7" t="n"/>
       <c r="F39" s="7" t="n"/>
       <c r="G39" s="7" t="n"/>
@@ -1178,15 +1178,15 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B40" s="7" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D40" s="7" t="n"/>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
@@ -1226,13 +1226,13 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B43" s="7" t="n"/>
       <c r="C43" s="7" t="n"/>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E43" s="7" t="n"/>
@@ -1328,7 +1328,7 @@
       <c r="C49" s="7" t="n"/>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E49" s="7" t="n"/>
@@ -1356,15 +1356,15 @@
       <c r="A51" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B51" s="7" t="n"/>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C51" s="7" t="n"/>
       <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F51" s="7" t="n"/>
       <c r="G51" s="7" t="n"/>
       <c r="H51" s="7" t="n"/>
     </row>
@@ -1378,7 +1378,7 @@
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>Colston Loveland</t>
+          <t>Tyler Warren</t>
         </is>
       </c>
       <c r="G52" s="7" t="n"/>
@@ -1426,7 +1426,7 @@
       <c r="E55" s="7" t="n"/>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>Isaiah Likely</t>
+          <t>Colston Loveland</t>
         </is>
       </c>
       <c r="G55" s="7" t="n"/>
@@ -1442,7 +1442,7 @@
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G56" s="7" t="n"/>
@@ -1450,17 +1450,17 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B57" s="7" t="n"/>
       <c r="C57" s="7" t="n"/>
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
-      <c r="F57" s="7" t="n"/>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G57" s="7" t="n"/>
       <c r="H57" s="7" t="n"/>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C58" s="7" t="n"/>
@@ -1484,13 +1484,13 @@
       <c r="A59" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+      <c r="B59" s="7" t="n"/>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="7" t="n"/>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E59" s="7" t="n"/>
       <c r="F59" s="7" t="n"/>
       <c r="G59" s="7" t="n"/>
@@ -1504,7 +1504,7 @@
       <c r="C60" s="7" t="n"/>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E60" s="7" t="n"/>
@@ -1520,7 +1520,7 @@
       <c r="C61" s="7" t="n"/>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E61" s="7" t="n"/>
@@ -1530,15 +1530,15 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B62" s="7" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D62" s="7" t="n"/>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="7" t="n"/>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="C69" s="7" t="n"/>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Woody Marks</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C70" s="7" t="n"/>
@@ -1676,13 +1676,13 @@
       <c r="A71" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B71" s="7" t="n"/>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C71" s="7" t="n"/>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D71" s="7" t="n"/>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
@@ -1696,7 +1696,7 @@
       <c r="C72" s="7" t="n"/>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E72" s="7" t="n"/>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C76" s="7" t="n"/>
@@ -1772,13 +1772,13 @@
       <c r="A77" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+      <c r="B77" s="7" t="n"/>
       <c r="C77" s="7" t="n"/>
-      <c r="D77" s="7" t="n"/>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E77" s="7" t="n"/>
       <c r="F77" s="7" t="n"/>
       <c r="G77" s="7" t="n"/>
@@ -1792,7 +1792,7 @@
       <c r="C78" s="7" t="n"/>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E78" s="7" t="n"/>
@@ -1802,15 +1802,15 @@
     </row>
     <row r="79">
       <c r="A79" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B79" s="7" t="n"/>
       <c r="C79" s="7" t="n"/>
-      <c r="D79" s="7" t="n"/>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>Quentin Johnston</t>
+        </is>
+      </c>
       <c r="E79" s="7" t="n"/>
       <c r="F79" s="7" t="n"/>
       <c r="G79" s="7" t="n"/>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C80" s="7" t="n"/>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C81" s="7" t="n"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C82" s="7" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C83" s="7" t="n"/>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>Blake Corum</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C84" s="7" t="n"/>
@@ -1900,13 +1900,13 @@
       <c r="A85" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B85" s="7" t="n"/>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C85" s="7" t="n"/>
-      <c r="D85" s="7" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D85" s="7" t="n"/>
       <c r="E85" s="7" t="n"/>
       <c r="F85" s="7" t="n"/>
       <c r="G85" s="7" t="n"/>
@@ -1920,7 +1920,7 @@
       <c r="C86" s="7" t="n"/>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E86" s="7" t="n"/>
@@ -2170,13 +2170,13 @@
     </row>
     <row r="102">
       <c r="A102" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B102" s="7" t="n"/>
       <c r="C102" s="7" t="n"/>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E102" s="7" t="n"/>
@@ -2192,7 +2192,7 @@
       <c r="C103" s="7" t="n"/>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E103" s="7" t="n"/>
@@ -2208,7 +2208,7 @@
       <c r="C104" s="7" t="n"/>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E104" s="7" t="n"/>
@@ -2224,7 +2224,7 @@
       <c r="C105" s="7" t="n"/>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E105" s="7" t="n"/>
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 1; 25 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 2; 20 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,14 +2333,14 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 69 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 68 players moved.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   No projection this week (value kept): Saquon Barkley, A.J. Brown, Breece Hall, DeVonta Smith, Rashee Rice, Lamar Jackson, Travis Etienne Jr., Jadarian Price, DJ Moore, Josh Jacobs, De'Zhaun Stribling, Jordan Mason, Alec Pierce, Brian Thomas Jr., Quentin Johnston, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Kenny Gainwell, Jaxson Dart, Ja'Kobi Lane.</t>
+          <t xml:space="preserve">   No projection this week (value kept): Saquon Barkley, A.J. Brown, Breece Hall, DeVonta Smith, Rashee Rice, Lamar Jackson, Travis Etienne Jr., Jadarian Price, Josh Jacobs, De'Zhaun Stribling, Jordan Mason, Alec Pierce, Brian Thomas Jr., Quentin Johnston, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Kenny Gainwell, Jaxson Dart, Ja'Kobi Lane.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 61-&gt;53, Chris Olave 42-&gt;34, Trey McBride 42.2857-&gt;35, Puka Nacua 68-&gt;61, DeVonta Smith 27-&gt;20, Rashee Rice 26-&gt;19, Garrett Wilson 28-&gt;21, Davante Adams 20-&gt;13</t>
+          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 61-&gt;53, Chris Olave 40-&gt;32, Trey McBride 42.2857-&gt;35, Puka Nacua 68-&gt;61, DeVonta Smith 27-&gt;20, Rashee Rice 26-&gt;19, Garrett Wilson 28-&gt;21, Davante Adams 20-&gt;13</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -618,7 +618,7 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B7" s="7" t="n"/>
       <c r="C7" s="7" t="n"/>
@@ -666,7 +666,7 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
@@ -714,7 +714,7 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
@@ -762,7 +762,7 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
@@ -778,7 +778,7 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
@@ -826,13 +826,13 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>CeeDee Lamb</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E18" s="7" t="n"/>
@@ -844,13 +844,13 @@
       <c r="A19" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="B19" s="7" t="n"/>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
@@ -858,11 +858,11 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C20" s="7" t="n"/>
@@ -874,15 +874,15 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
@@ -906,11 +906,11 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C23" s="7" t="n"/>
@@ -926,7 +926,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C24" s="7" t="n"/>
@@ -976,7 +976,7 @@
       <c r="C27" s="7" t="n"/>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Chris Olave</t>
         </is>
       </c>
       <c r="E27" s="7" t="n"/>
@@ -986,13 +986,13 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E28" s="7" t="n"/>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
@@ -1164,13 +1164,13 @@
       <c r="A39" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B39" s="7" t="n"/>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C39" s="7" t="n"/>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D39" s="7" t="n"/>
       <c r="E39" s="7" t="n"/>
       <c r="F39" s="7" t="n"/>
       <c r="G39" s="7" t="n"/>
@@ -1178,11 +1178,11 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>Jadarian Price</t>
         </is>
       </c>
       <c r="C40" s="7" t="n"/>
@@ -1194,15 +1194,15 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="n"/>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="7" t="n"/>
@@ -1210,15 +1210,15 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B42" s="7" t="n"/>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="n"/>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="7" t="n"/>
@@ -1226,15 +1226,15 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B43" s="7" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C43" s="7" t="n"/>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D43" s="7" t="n"/>
       <c r="E43" s="7" t="n"/>
       <c r="F43" s="7" t="n"/>
       <c r="G43" s="7" t="n"/>
@@ -1244,13 +1244,13 @@
       <c r="A44" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B44" s="7" t="n"/>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D44" s="7" t="n"/>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="7" t="n"/>
@@ -1258,15 +1258,15 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B45" s="7" t="n"/>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="n"/>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E45" s="7" t="n"/>
       <c r="F45" s="7" t="n"/>
       <c r="G45" s="7" t="n"/>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C46" s="7" t="n"/>
@@ -1312,7 +1312,7 @@
       <c r="C48" s="7" t="n"/>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E48" s="7" t="n"/>
@@ -1328,7 +1328,7 @@
       <c r="C49" s="7" t="n"/>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E49" s="7" t="n"/>
@@ -1356,15 +1356,15 @@
       <c r="A51" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+      <c r="B51" s="7" t="n"/>
       <c r="C51" s="7" t="n"/>
       <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
-      <c r="F51" s="7" t="n"/>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G51" s="7" t="n"/>
       <c r="H51" s="7" t="n"/>
     </row>
@@ -1378,7 +1378,7 @@
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>Tyler Warren</t>
+          <t>Colston Loveland</t>
         </is>
       </c>
       <c r="G52" s="7" t="n"/>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="C54" s="7" t="n"/>
@@ -1420,15 +1420,15 @@
       <c r="A55" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B55" s="7" t="n"/>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C55" s="7" t="n"/>
       <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F55" s="7" t="n"/>
       <c r="G55" s="7" t="n"/>
       <c r="H55" s="7" t="n"/>
     </row>
@@ -1442,7 +1442,7 @@
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>Isaiah Likely</t>
+          <t>George Kittle</t>
         </is>
       </c>
       <c r="G56" s="7" t="n"/>
@@ -1450,17 +1450,17 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B57" s="7" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C57" s="7" t="n"/>
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
       <c r="H57" s="7" t="n"/>
     </row>
@@ -1468,13 +1468,13 @@
       <c r="A58" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+      <c r="B58" s="7" t="n"/>
       <c r="C58" s="7" t="n"/>
-      <c r="D58" s="7" t="n"/>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E58" s="7" t="n"/>
       <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n"/>
@@ -1488,7 +1488,7 @@
       <c r="C59" s="7" t="n"/>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E59" s="7" t="n"/>
@@ -1504,7 +1504,7 @@
       <c r="C60" s="7" t="n"/>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E60" s="7" t="n"/>
@@ -1514,15 +1514,15 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B61" s="7" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
       <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C62" s="7" t="n"/>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C63" s="7" t="n"/>
@@ -1564,15 +1564,15 @@
       <c r="A64" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B64" s="7" t="n"/>
       <c r="C64" s="7" t="n"/>
       <c r="D64" s="7" t="n"/>
       <c r="E64" s="7" t="n"/>
-      <c r="F64" s="7" t="n"/>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G64" s="7" t="n"/>
       <c r="H64" s="7" t="n"/>
     </row>
@@ -1580,13 +1580,13 @@
       <c r="A65" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B65" s="7" t="n"/>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C65" s="7" t="n"/>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D65" s="7" t="n"/>
       <c r="E65" s="7" t="n"/>
       <c r="F65" s="7" t="n"/>
       <c r="G65" s="7" t="n"/>
@@ -1596,13 +1596,13 @@
       <c r="A66" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B66" s="7" t="n"/>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C66" s="7" t="n"/>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D66" s="7" t="n"/>
       <c r="E66" s="7" t="n"/>
       <c r="F66" s="7" t="n"/>
       <c r="G66" s="7" t="n"/>
@@ -1614,15 +1614,15 @@
       </c>
       <c r="B67" s="7" t="n"/>
       <c r="C67" s="7" t="n"/>
-      <c r="D67" s="7" t="n"/>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E67" s="7" t="n"/>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
-      <c r="H67" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
@@ -1630,27 +1630,27 @@
       </c>
       <c r="B68" s="7" t="n"/>
       <c r="C68" s="7" t="n"/>
-      <c r="D68" s="7" t="n"/>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E68" s="7" t="n"/>
       <c r="F68" s="7" t="n"/>
       <c r="G68" s="7" t="n"/>
-      <c r="H68" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B69" s="7" t="n"/>
       <c r="C69" s="7" t="n"/>
-      <c r="D69" s="7" t="n"/>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E69" s="7" t="n"/>
       <c r="F69" s="7" t="n"/>
       <c r="G69" s="7" t="n"/>
@@ -1658,63 +1658,63 @@
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B70" s="7" t="n"/>
       <c r="C70" s="7" t="n"/>
       <c r="D70" s="7" t="n"/>
       <c r="E70" s="7" t="n"/>
-      <c r="F70" s="7" t="n"/>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G70" s="7" t="n"/>
       <c r="H70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B71" s="7" t="n"/>
       <c r="C71" s="7" t="n"/>
       <c r="D71" s="7" t="n"/>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
-      <c r="H71" s="7" t="n"/>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B72" s="7" t="n"/>
       <c r="C72" s="7" t="n"/>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D72" s="7" t="n"/>
       <c r="E72" s="7" t="n"/>
       <c r="F72" s="7" t="n"/>
       <c r="G72" s="7" t="n"/>
-      <c r="H72" s="7" t="n"/>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B73" s="7" t="n"/>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
       <c r="C73" s="7" t="n"/>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>Brian Thomas Jr.</t>
-        </is>
-      </c>
+      <c r="D73" s="7" t="n"/>
       <c r="E73" s="7" t="n"/>
       <c r="F73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
@@ -1724,15 +1724,15 @@
       <c r="A74" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B74" s="7" t="n"/>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C74" s="7" t="n"/>
       <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
-      <c r="F74" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
       <c r="H74" s="7" t="n"/>
     </row>
@@ -1742,43 +1742,43 @@
       </c>
       <c r="B75" s="7" t="n"/>
       <c r="C75" s="7" t="n"/>
-      <c r="D75" s="7" t="n"/>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E75" s="7" t="n"/>
       <c r="F75" s="7" t="n"/>
       <c r="G75" s="7" t="n"/>
-      <c r="H75" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H75" s="7" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B76" s="7" t="n"/>
       <c r="C76" s="7" t="n"/>
       <c r="D76" s="7" t="n"/>
       <c r="E76" s="7" t="n"/>
       <c r="F76" s="7" t="n"/>
       <c r="G76" s="7" t="n"/>
-      <c r="H76" s="7" t="n"/>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B77" s="7" t="n"/>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Jonathon Brooks</t>
+        </is>
+      </c>
       <c r="C77" s="7" t="n"/>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D77" s="7" t="n"/>
       <c r="E77" s="7" t="n"/>
       <c r="F77" s="7" t="n"/>
       <c r="G77" s="7" t="n"/>
@@ -1788,13 +1788,13 @@
       <c r="A78" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B78" s="7" t="n"/>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>Mike Washington Jr.</t>
+        </is>
+      </c>
       <c r="C78" s="7" t="n"/>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>Jameson Williams</t>
-        </is>
-      </c>
+      <c r="D78" s="7" t="n"/>
       <c r="E78" s="7" t="n"/>
       <c r="F78" s="7" t="n"/>
       <c r="G78" s="7" t="n"/>
@@ -1808,7 +1808,7 @@
       <c r="C79" s="7" t="n"/>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E79" s="7" t="n"/>
@@ -1818,15 +1818,15 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B80" s="7" t="n"/>
       <c r="C80" s="7" t="n"/>
-      <c r="D80" s="7" t="n"/>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>Marvin Harrison Jr.</t>
+        </is>
+      </c>
       <c r="E80" s="7" t="n"/>
       <c r="F80" s="7" t="n"/>
       <c r="G80" s="7" t="n"/>
@@ -1834,15 +1834,15 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>Jonathon Brooks</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B81" s="7" t="n"/>
       <c r="C81" s="7" t="n"/>
-      <c r="D81" s="7" t="n"/>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>Quentin Johnston</t>
+        </is>
+      </c>
       <c r="E81" s="7" t="n"/>
       <c r="F81" s="7" t="n"/>
       <c r="G81" s="7" t="n"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C82" s="7" t="n"/>
@@ -1936,7 +1936,7 @@
       <c r="C87" s="7" t="n"/>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E87" s="7" t="n"/>
@@ -1952,7 +1952,7 @@
       <c r="C88" s="7" t="n"/>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E88" s="7" t="n"/>
@@ -1968,7 +1968,7 @@
       <c r="C89" s="7" t="n"/>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr.</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E89" s="7" t="n"/>
@@ -1982,13 +1982,13 @@
       </c>
       <c r="B90" s="7" t="n"/>
       <c r="C90" s="7" t="n"/>
-      <c r="D90" s="7" t="n"/>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>Chris Godwin Jr.</t>
+        </is>
+      </c>
       <c r="E90" s="7" t="n"/>
-      <c r="F90" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F90" s="7" t="n"/>
       <c r="G90" s="7" t="n"/>
       <c r="H90" s="7" t="n"/>
     </row>
@@ -2000,13 +2000,13 @@
       <c r="C91" s="7" t="n"/>
       <c r="D91" s="7" t="n"/>
       <c r="E91" s="7" t="n"/>
-      <c r="F91" s="7" t="n"/>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G91" s="7" t="n"/>
-      <c r="H91" s="7" t="inlineStr">
-        <is>
-          <t>Jalen Hurts</t>
-        </is>
-      </c>
+      <c r="H91" s="7" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
@@ -2020,7 +2020,7 @@
       <c r="G92" s="7" t="n"/>
       <c r="H92" s="7" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
     </row>
@@ -2036,37 +2036,37 @@
       <c r="G93" s="7" t="n"/>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B94" s="7" t="n"/>
       <c r="C94" s="7" t="n"/>
       <c r="D94" s="7" t="n"/>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="7" t="n"/>
       <c r="G94" s="7" t="n"/>
-      <c r="H94" s="7" t="n"/>
+      <c r="H94" s="7" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B95" s="7" t="n"/>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C95" s="7" t="n"/>
-      <c r="D95" s="7" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D95" s="7" t="n"/>
       <c r="E95" s="7" t="n"/>
       <c r="F95" s="7" t="n"/>
       <c r="G95" s="7" t="n"/>
@@ -2096,7 +2096,7 @@
       <c r="C97" s="7" t="n"/>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E97" s="7" t="n"/>
@@ -2110,31 +2110,31 @@
       </c>
       <c r="B98" s="7" t="n"/>
       <c r="C98" s="7" t="n"/>
-      <c r="D98" s="7" t="n"/>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E98" s="7" t="n"/>
       <c r="F98" s="7" t="n"/>
       <c r="G98" s="7" t="n"/>
-      <c r="H98" s="7" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H98" s="7" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B99" s="7" t="n"/>
       <c r="C99" s="7" t="n"/>
-      <c r="D99" s="7" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D99" s="7" t="n"/>
       <c r="E99" s="7" t="n"/>
       <c r="F99" s="7" t="n"/>
       <c r="G99" s="7" t="n"/>
-      <c r="H99" s="7" t="n"/>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
@@ -2144,7 +2144,7 @@
       <c r="C100" s="7" t="n"/>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E100" s="7" t="n"/>
@@ -2160,7 +2160,7 @@
       <c r="C101" s="7" t="n"/>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E101" s="7" t="n"/>
@@ -2295,7 +2295,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 74.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 73.</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 2; 20 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 3; 20 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 68 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 67 players moved.</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.6, WR 2.8, TE 4.5, QB 0.0.</t>
+          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.7, WR 2.8, TE 4.5, QB 0.0.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 61-&gt;53, Chris Olave 40-&gt;32, Trey McBride 42.2857-&gt;35, Puka Nacua 68-&gt;61, DeVonta Smith 27-&gt;20, Rashee Rice 26-&gt;19, Garrett Wilson 28-&gt;21, Davante Adams 20-&gt;13</t>
+          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 61-&gt;54, Chris Olave 40-&gt;33, DeVonta Smith 27-&gt;20, Rashee Rice 26-&gt;19, Garrett Wilson 28-&gt;21, Trey McBride 41.7143-&gt;35, Puka Nacua 69-&gt;63, Justin Jefferson 46-&gt;40</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B7" s="7" t="n"/>
       <c r="C7" s="7" t="n"/>
@@ -682,7 +682,7 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
@@ -700,13 +700,13 @@
       <c r="A10" s="6" t="n">
         <v>58</v>
       </c>
-      <c r="B10" s="7" t="n"/>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="n"/>
@@ -714,15 +714,15 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
@@ -734,7 +734,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>James Cook III</t>
         </is>
       </c>
       <c r="C12" s="7" t="n"/>
@@ -794,7 +794,7 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
@@ -842,15 +842,15 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
@@ -858,15 +858,15 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
@@ -874,15 +874,15 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="B21" s="7" t="n"/>
+        <v>39</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
@@ -890,15 +890,15 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="B22" s="7" t="n"/>
+        <v>38</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
@@ -906,11 +906,11 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Ashton Jeanty</t>
         </is>
       </c>
       <c r="C23" s="7" t="n"/>
@@ -922,33 +922,33 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="B25" s="7" t="n"/>
+        <v>34</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
     </row>
@@ -1066,13 +1066,13 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E33" s="7" t="n"/>
@@ -1088,7 +1088,7 @@
       <c r="C34" s="7" t="n"/>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E34" s="7" t="n"/>
@@ -1098,13 +1098,13 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E35" s="7" t="n"/>
@@ -1114,15 +1114,15 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="B36" s="7" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C36" s="7" t="n"/>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D36" s="7" t="n"/>
       <c r="E36" s="7" t="n"/>
       <c r="F36" s="7" t="n"/>
       <c r="G36" s="7" t="n"/>
@@ -1146,13 +1146,13 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E38" s="7" t="n"/>
@@ -1162,15 +1162,15 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
-      <c r="D39" s="7" t="n"/>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E39" s="7" t="n"/>
       <c r="F39" s="7" t="n"/>
       <c r="G39" s="7" t="n"/>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B42" s="7" t="n"/>
       <c r="C42" s="7" t="n"/>
@@ -1226,11 +1226,11 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C43" s="7" t="n"/>
@@ -1242,7 +1242,7 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
@@ -1260,13 +1260,13 @@
       <c r="A45" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B45" s="7" t="n"/>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D45" s="7" t="n"/>
       <c r="E45" s="7" t="n"/>
       <c r="F45" s="7" t="n"/>
       <c r="G45" s="7" t="n"/>
@@ -1274,11 +1274,11 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="C46" s="7" t="n"/>
@@ -1290,15 +1290,15 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="n"/>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E47" s="7" t="n"/>
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="7" t="n"/>
@@ -1308,13 +1308,13 @@
       <c r="A48" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B48" s="7" t="n"/>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D48" s="7" t="n"/>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
@@ -1328,7 +1328,7 @@
       <c r="C49" s="7" t="n"/>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E49" s="7" t="n"/>
@@ -1338,15 +1338,15 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B50" s="7" t="n"/>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="n"/>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E50" s="7" t="n"/>
       <c r="F50" s="7" t="n"/>
       <c r="G50" s="7" t="n"/>
@@ -1356,15 +1356,15 @@
       <c r="A51" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B51" s="7" t="n"/>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C51" s="7" t="n"/>
       <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F51" s="7" t="n"/>
       <c r="G51" s="7" t="n"/>
       <c r="H51" s="7" t="n"/>
     </row>
@@ -1378,7 +1378,7 @@
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>Colston Loveland</t>
+          <t>Tyler Warren</t>
         </is>
       </c>
       <c r="G52" s="7" t="n"/>
@@ -1442,7 +1442,7 @@
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Colston Loveland</t>
         </is>
       </c>
       <c r="G56" s="7" t="n"/>
@@ -1450,33 +1450,33 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B57" s="7" t="n"/>
       <c r="C57" s="7" t="n"/>
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
-      <c r="F57" s="7" t="n"/>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G57" s="7" t="n"/>
       <c r="H57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B58" s="7" t="n"/>
       <c r="C58" s="7" t="n"/>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
-      <c r="F58" s="7" t="n"/>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
     </row>
@@ -1484,13 +1484,13 @@
       <c r="A59" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B59" s="7" t="n"/>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
       <c r="F59" s="7" t="n"/>
       <c r="G59" s="7" t="n"/>
@@ -1504,7 +1504,7 @@
       <c r="C60" s="7" t="n"/>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E60" s="7" t="n"/>
@@ -1514,15 +1514,15 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="n"/>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E61" s="7" t="n"/>
       <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
@@ -1530,15 +1530,15 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B62" s="7" t="n"/>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="n"/>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="7" t="n"/>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C63" s="7" t="n"/>
@@ -1564,15 +1564,15 @@
       <c r="A64" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B64" s="7" t="n"/>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C64" s="7" t="n"/>
       <c r="D64" s="7" t="n"/>
       <c r="E64" s="7" t="n"/>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F64" s="7" t="n"/>
       <c r="G64" s="7" t="n"/>
       <c r="H64" s="7" t="n"/>
     </row>
@@ -1580,13 +1580,13 @@
       <c r="A65" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+      <c r="B65" s="7" t="n"/>
       <c r="C65" s="7" t="n"/>
-      <c r="D65" s="7" t="n"/>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E65" s="7" t="n"/>
       <c r="F65" s="7" t="n"/>
       <c r="G65" s="7" t="n"/>
@@ -1596,13 +1596,13 @@
       <c r="A66" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+      <c r="B66" s="7" t="n"/>
       <c r="C66" s="7" t="n"/>
-      <c r="D66" s="7" t="n"/>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E66" s="7" t="n"/>
       <c r="F66" s="7" t="n"/>
       <c r="G66" s="7" t="n"/>
@@ -1616,7 +1616,7 @@
       <c r="C67" s="7" t="n"/>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="E67" s="7" t="n"/>
@@ -1630,15 +1630,15 @@
       </c>
       <c r="B68" s="7" t="n"/>
       <c r="C68" s="7" t="n"/>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D68" s="7" t="n"/>
       <c r="E68" s="7" t="n"/>
       <c r="F68" s="7" t="n"/>
       <c r="G68" s="7" t="n"/>
-      <c r="H68" s="7" t="n"/>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
@@ -1646,63 +1646,63 @@
       </c>
       <c r="B69" s="7" t="n"/>
       <c r="C69" s="7" t="n"/>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D69" s="7" t="n"/>
       <c r="E69" s="7" t="n"/>
       <c r="F69" s="7" t="n"/>
       <c r="G69" s="7" t="n"/>
-      <c r="H69" s="7" t="n"/>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B70" s="7" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C70" s="7" t="n"/>
       <c r="D70" s="7" t="n"/>
       <c r="E70" s="7" t="n"/>
-      <c r="F70" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F70" s="7" t="n"/>
       <c r="G70" s="7" t="n"/>
       <c r="H70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B71" s="7" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
       <c r="C71" s="7" t="n"/>
       <c r="D71" s="7" t="n"/>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
-      <c r="H71" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H71" s="7" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B72" s="7" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C72" s="7" t="n"/>
       <c r="D72" s="7" t="n"/>
       <c r="E72" s="7" t="n"/>
       <c r="F72" s="7" t="n"/>
       <c r="G72" s="7" t="n"/>
-      <c r="H72" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H72" s="7" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="C73" s="7" t="n"/>
@@ -1724,13 +1724,13 @@
       <c r="A74" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+      <c r="B74" s="7" t="n"/>
       <c r="C74" s="7" t="n"/>
-      <c r="D74" s="7" t="n"/>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E74" s="7" t="n"/>
       <c r="F74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
@@ -1742,13 +1742,13 @@
       </c>
       <c r="B75" s="7" t="n"/>
       <c r="C75" s="7" t="n"/>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>Brian Thomas Jr.</t>
-        </is>
-      </c>
+      <c r="D75" s="7" t="n"/>
       <c r="E75" s="7" t="n"/>
-      <c r="F75" s="7" t="n"/>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G75" s="7" t="n"/>
       <c r="H75" s="7" t="n"/>
     </row>
@@ -1850,17 +1850,17 @@
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B82" s="7" t="n"/>
       <c r="C82" s="7" t="n"/>
       <c r="D82" s="7" t="n"/>
       <c r="E82" s="7" t="n"/>
-      <c r="F82" s="7" t="n"/>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G82" s="7" t="n"/>
       <c r="H82" s="7" t="n"/>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C83" s="7" t="n"/>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C84" s="7" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>Blake Corum</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C85" s="7" t="n"/>
@@ -1916,13 +1916,13 @@
       <c r="A86" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B86" s="7" t="n"/>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C86" s="7" t="n"/>
-      <c r="D86" s="7" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D86" s="7" t="n"/>
       <c r="E86" s="7" t="n"/>
       <c r="F86" s="7" t="n"/>
       <c r="G86" s="7" t="n"/>
@@ -1932,13 +1932,13 @@
       <c r="A87" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B87" s="7" t="n"/>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C87" s="7" t="n"/>
-      <c r="D87" s="7" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D87" s="7" t="n"/>
       <c r="E87" s="7" t="n"/>
       <c r="F87" s="7" t="n"/>
       <c r="G87" s="7" t="n"/>
@@ -1952,7 +1952,7 @@
       <c r="C88" s="7" t="n"/>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E88" s="7" t="n"/>
@@ -1968,7 +1968,7 @@
       <c r="C89" s="7" t="n"/>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E89" s="7" t="n"/>
@@ -1984,7 +1984,7 @@
       <c r="C90" s="7" t="n"/>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr.</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E90" s="7" t="n"/>
@@ -1998,13 +1998,13 @@
       </c>
       <c r="B91" s="7" t="n"/>
       <c r="C91" s="7" t="n"/>
-      <c r="D91" s="7" t="n"/>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>Chris Godwin Jr.</t>
+        </is>
+      </c>
       <c r="E91" s="7" t="n"/>
-      <c r="F91" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F91" s="7" t="n"/>
       <c r="G91" s="7" t="n"/>
       <c r="H91" s="7" t="n"/>
     </row>
@@ -2060,13 +2060,13 @@
       <c r="A95" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B95" s="7" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+      <c r="B95" s="7" t="n"/>
       <c r="C95" s="7" t="n"/>
-      <c r="D95" s="7" t="n"/>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E95" s="7" t="n"/>
       <c r="F95" s="7" t="n"/>
       <c r="G95" s="7" t="n"/>
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 3; 20 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 4; 18 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,14 +2333,14 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 67 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 64 players moved.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   No projection this week (value kept): Saquon Barkley, A.J. Brown, Breece Hall, DeVonta Smith, Rashee Rice, Lamar Jackson, Travis Etienne Jr., Jadarian Price, Josh Jacobs, De'Zhaun Stribling, Jordan Mason, Alec Pierce, Brian Thomas Jr., Quentin Johnston, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Kenny Gainwell, Jaxson Dart, Ja'Kobi Lane.</t>
+          <t xml:space="preserve">   No projection this week (value kept): Saquon Barkley, A.J. Brown, Breece Hall, DeVonta Smith, Rashee Rice, Lamar Jackson, Travis Etienne Jr., Jadarian Price, Josh Jacobs, De'Zhaun Stribling, Jordan Mason, Alec Pierce, Brian Thomas Jr., Quentin Johnston, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Jaxson Dart, Ja'Kobi Lane.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 61-&gt;54, Chris Olave 40-&gt;33, DeVonta Smith 27-&gt;20, Rashee Rice 26-&gt;19, Garrett Wilson 28-&gt;21, Trey McBride 41.7143-&gt;35, Puka Nacua 69-&gt;63, Justin Jefferson 46-&gt;40</t>
+          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 61-&gt;54, Chris Olave 40-&gt;33, DeVonta Smith 27-&gt;20, Rashee Rice 26-&gt;19, Garrett Wilson 27-&gt;20, Trey McBride 41.7143-&gt;35, Puka Nacua 68-&gt;62, Justin Jefferson 46-&gt;40</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -634,7 +634,7 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B7" s="7" t="n"/>
       <c r="C7" s="7" t="n"/>
@@ -682,11 +682,11 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>James Cook III</t>
         </is>
       </c>
       <c r="C9" s="7" t="n"/>
@@ -702,7 +702,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C10" s="7" t="n"/>
@@ -716,13 +716,13 @@
       <c r="A11" s="6" t="n">
         <v>58</v>
       </c>
-      <c r="B11" s="7" t="n"/>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D11" s="7" t="n"/>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
@@ -730,15 +730,15 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>James Cook III</t>
-        </is>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="n"/>
@@ -746,13 +746,13 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E13" s="7" t="n"/>
@@ -768,7 +768,7 @@
       <c r="C14" s="7" t="n"/>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E14" s="7" t="n"/>
@@ -778,7 +778,7 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
@@ -826,13 +826,13 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="E18" s="7" t="n"/>
@@ -842,13 +842,13 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Justin Jefferson</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E19" s="7" t="n"/>
@@ -860,13 +860,13 @@
       <c r="A20" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="B20" s="7" t="n"/>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
@@ -874,15 +874,15 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
@@ -890,11 +890,11 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C22" s="7" t="n"/>
@@ -906,11 +906,11 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C23" s="7" t="n"/>
@@ -924,31 +924,31 @@
       <c r="A24" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="B24" s="7" t="n"/>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
     </row>
@@ -976,7 +976,7 @@
       <c r="C27" s="7" t="n"/>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E27" s="7" t="n"/>
@@ -986,13 +986,13 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Chris Olave</t>
         </is>
       </c>
       <c r="E28" s="7" t="n"/>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
@@ -1066,13 +1066,13 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E33" s="7" t="n"/>
@@ -1082,13 +1082,13 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E34" s="7" t="n"/>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
@@ -1114,15 +1114,15 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
-      <c r="D36" s="7" t="n"/>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E36" s="7" t="n"/>
       <c r="F36" s="7" t="n"/>
       <c r="G36" s="7" t="n"/>
@@ -1130,13 +1130,13 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E37" s="7" t="n"/>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
@@ -1162,13 +1162,13 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E39" s="7" t="n"/>
@@ -1180,13 +1180,13 @@
       <c r="A40" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+      <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="n"/>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
@@ -1194,15 +1194,15 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="B41" s="7" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D41" s="7" t="n"/>
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="7" t="n"/>
@@ -1210,15 +1210,15 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="B42" s="7" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D42" s="7" t="n"/>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="7" t="n"/>
@@ -1226,11 +1226,11 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C43" s="7" t="n"/>
@@ -1242,11 +1242,11 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C44" s="7" t="n"/>
@@ -1258,11 +1258,11 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C45" s="7" t="n"/>
@@ -1274,7 +1274,7 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
@@ -1290,13 +1290,13 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="n"/>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E47" s="7" t="n"/>
@@ -1308,13 +1308,13 @@
       <c r="A48" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+      <c r="B48" s="7" t="n"/>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="n"/>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
@@ -1328,7 +1328,7 @@
       <c r="C49" s="7" t="n"/>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E49" s="7" t="n"/>
@@ -1342,13 +1342,13 @@
       </c>
       <c r="B50" s="7" t="n"/>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
-      <c r="F50" s="7" t="n"/>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G50" s="7" t="n"/>
       <c r="H50" s="7" t="n"/>
     </row>
@@ -1376,43 +1376,43 @@
       <c r="C52" s="7" t="n"/>
       <c r="D52" s="7" t="n"/>
       <c r="E52" s="7" t="n"/>
-      <c r="F52" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F52" s="7" t="n"/>
       <c r="G52" s="7" t="n"/>
-      <c r="H52" s="7" t="n"/>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B53" s="7" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C53" s="7" t="n"/>
       <c r="D53" s="7" t="n"/>
       <c r="E53" s="7" t="n"/>
       <c r="F53" s="7" t="n"/>
       <c r="G53" s="7" t="n"/>
-      <c r="H53" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+      <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
       <c r="D54" s="7" t="n"/>
       <c r="E54" s="7" t="n"/>
-      <c r="F54" s="7" t="n"/>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G54" s="7" t="n"/>
       <c r="H54" s="7" t="n"/>
     </row>
@@ -1420,63 +1420,63 @@
       <c r="A55" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B55" s="7" t="n"/>
       <c r="C55" s="7" t="n"/>
       <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7" t="n"/>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G55" s="7" t="n"/>
       <c r="H55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B56" s="7" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C56" s="7" t="n"/>
       <c r="D56" s="7" t="n"/>
       <c r="E56" s="7" t="n"/>
-      <c r="F56" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="n"/>
       <c r="H56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B57" s="7" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C57" s="7" t="n"/>
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
       <c r="H57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B58" s="7" t="n"/>
       <c r="C58" s="7" t="n"/>
-      <c r="D58" s="7" t="n"/>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E58" s="7" t="n"/>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
     </row>
@@ -1484,13 +1484,13 @@
       <c r="A59" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+      <c r="B59" s="7" t="n"/>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="7" t="n"/>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E59" s="7" t="n"/>
       <c r="F59" s="7" t="n"/>
       <c r="G59" s="7" t="n"/>
@@ -1504,7 +1504,7 @@
       <c r="C60" s="7" t="n"/>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E60" s="7" t="n"/>
@@ -1514,15 +1514,15 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B61" s="7" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
       <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
@@ -1530,15 +1530,15 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B62" s="7" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D62" s="7" t="n"/>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="7" t="n"/>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C63" s="7" t="n"/>
@@ -1564,15 +1564,15 @@
       <c r="A64" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B64" s="7" t="n"/>
       <c r="C64" s="7" t="n"/>
       <c r="D64" s="7" t="n"/>
       <c r="E64" s="7" t="n"/>
-      <c r="F64" s="7" t="n"/>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G64" s="7" t="n"/>
       <c r="H64" s="7" t="n"/>
     </row>
@@ -1652,25 +1652,25 @@
       <c r="G69" s="7" t="n"/>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B70" s="7" t="n"/>
       <c r="C70" s="7" t="n"/>
       <c r="D70" s="7" t="n"/>
       <c r="E70" s="7" t="n"/>
       <c r="F70" s="7" t="n"/>
       <c r="G70" s="7" t="n"/>
-      <c r="H70" s="7" t="n"/>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="C71" s="7" t="n"/>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C72" s="7" t="n"/>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>Woody Marks</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C73" s="7" t="n"/>
@@ -1724,13 +1724,13 @@
       <c r="A74" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B74" s="7" t="n"/>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C74" s="7" t="n"/>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>Brian Thomas Jr.</t>
-        </is>
-      </c>
+      <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
       <c r="F74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
@@ -1742,13 +1742,13 @@
       </c>
       <c r="B75" s="7" t="n"/>
       <c r="C75" s="7" t="n"/>
-      <c r="D75" s="7" t="n"/>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E75" s="7" t="n"/>
-      <c r="F75" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F75" s="7" t="n"/>
       <c r="G75" s="7" t="n"/>
       <c r="H75" s="7" t="n"/>
     </row>
@@ -1760,25 +1760,25 @@
       <c r="C76" s="7" t="n"/>
       <c r="D76" s="7" t="n"/>
       <c r="E76" s="7" t="n"/>
-      <c r="F76" s="7" t="n"/>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G76" s="7" t="n"/>
-      <c r="H76" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H76" s="7" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>Jonathon Brooks</t>
-        </is>
-      </c>
+      <c r="B77" s="7" t="n"/>
       <c r="C77" s="7" t="n"/>
-      <c r="D77" s="7" t="n"/>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E77" s="7" t="n"/>
       <c r="F77" s="7" t="n"/>
       <c r="G77" s="7" t="n"/>
@@ -1788,13 +1788,13 @@
       <c r="A78" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>Mike Washington Jr.</t>
-        </is>
-      </c>
+      <c r="B78" s="7" t="n"/>
       <c r="C78" s="7" t="n"/>
-      <c r="D78" s="7" t="n"/>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>Marvin Harrison Jr.</t>
+        </is>
+      </c>
       <c r="E78" s="7" t="n"/>
       <c r="F78" s="7" t="n"/>
       <c r="G78" s="7" t="n"/>
@@ -1808,7 +1808,7 @@
       <c r="C79" s="7" t="n"/>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E79" s="7" t="n"/>
@@ -1818,15 +1818,15 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B80" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C80" s="7" t="n"/>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D80" s="7" t="n"/>
       <c r="E80" s="7" t="n"/>
       <c r="F80" s="7" t="n"/>
       <c r="G80" s="7" t="n"/>
@@ -1834,15 +1834,15 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B81" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>Jonathon Brooks</t>
+        </is>
+      </c>
       <c r="C81" s="7" t="n"/>
-      <c r="D81" s="7" t="inlineStr">
-        <is>
-          <t>Quentin Johnston</t>
-        </is>
-      </c>
+      <c r="D81" s="7" t="n"/>
       <c r="E81" s="7" t="n"/>
       <c r="F81" s="7" t="n"/>
       <c r="G81" s="7" t="n"/>
@@ -1850,17 +1850,17 @@
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B82" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>Mike Washington Jr.</t>
+        </is>
+      </c>
       <c r="C82" s="7" t="n"/>
       <c r="D82" s="7" t="n"/>
       <c r="E82" s="7" t="n"/>
-      <c r="F82" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F82" s="7" t="n"/>
       <c r="G82" s="7" t="n"/>
       <c r="H82" s="7" t="n"/>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C83" s="7" t="n"/>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C84" s="7" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="C85" s="7" t="n"/>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>Blake Corum</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="C86" s="7" t="n"/>
@@ -1932,13 +1932,13 @@
       <c r="A87" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B87" s="7" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+      <c r="B87" s="7" t="n"/>
       <c r="C87" s="7" t="n"/>
-      <c r="D87" s="7" t="n"/>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E87" s="7" t="n"/>
       <c r="F87" s="7" t="n"/>
       <c r="G87" s="7" t="n"/>
@@ -1952,7 +1952,7 @@
       <c r="C88" s="7" t="n"/>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E88" s="7" t="n"/>
@@ -1968,7 +1968,7 @@
       <c r="C89" s="7" t="n"/>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E89" s="7" t="n"/>
@@ -1984,7 +1984,7 @@
       <c r="C90" s="7" t="n"/>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E90" s="7" t="n"/>
@@ -1998,13 +1998,13 @@
       </c>
       <c r="B91" s="7" t="n"/>
       <c r="C91" s="7" t="n"/>
-      <c r="D91" s="7" t="inlineStr">
-        <is>
-          <t>Chris Godwin Jr.</t>
-        </is>
-      </c>
+      <c r="D91" s="7" t="n"/>
       <c r="E91" s="7" t="n"/>
-      <c r="F91" s="7" t="n"/>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G91" s="7" t="n"/>
       <c r="H91" s="7" t="n"/>
     </row>
@@ -2096,7 +2096,7 @@
       <c r="C97" s="7" t="n"/>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>Ja'Kobi Lane</t>
         </is>
       </c>
       <c r="E97" s="7" t="n"/>
@@ -2110,31 +2110,31 @@
       </c>
       <c r="B98" s="7" t="n"/>
       <c r="C98" s="7" t="n"/>
-      <c r="D98" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
+      <c r="D98" s="7" t="n"/>
       <c r="E98" s="7" t="n"/>
       <c r="F98" s="7" t="n"/>
       <c r="G98" s="7" t="n"/>
-      <c r="H98" s="7" t="n"/>
+      <c r="H98" s="7" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B99" s="7" t="n"/>
       <c r="C99" s="7" t="n"/>
-      <c r="D99" s="7" t="n"/>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>Terry McLaurin</t>
+        </is>
+      </c>
       <c r="E99" s="7" t="n"/>
       <c r="F99" s="7" t="n"/>
       <c r="G99" s="7" t="n"/>
-      <c r="H99" s="7" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
@@ -2144,7 +2144,7 @@
       <c r="C100" s="7" t="n"/>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E100" s="7" t="n"/>
@@ -2160,7 +2160,7 @@
       <c r="C101" s="7" t="n"/>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E101" s="7" t="n"/>
@@ -2295,7 +2295,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 73.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 74.</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 4; 18 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 5; 18 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 64 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 69 players moved.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 61-&gt;54, Chris Olave 40-&gt;33, DeVonta Smith 27-&gt;20, Rashee Rice 26-&gt;19, Garrett Wilson 27-&gt;20, Trey McBride 41.7143-&gt;35, Puka Nacua 68-&gt;62, Justin Jefferson 46-&gt;40</t>
+          <t>Largest moves vs. the baseline in this file: Chris Olave 40-&gt;32, Trey McBride 42.2857-&gt;35, Puka Nacua 68-&gt;61, Jaxon Smith-Njigba 63-&gt;56, DeVonta Smith 27-&gt;20, Rashee Rice 26-&gt;19, Garrett Wilson 26-&gt;19, Ja'Marr Chase 60-&gt;54</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -682,11 +682,11 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>James Cook III</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C9" s="7" t="n"/>
@@ -702,7 +702,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>James Cook III</t>
         </is>
       </c>
       <c r="C10" s="7" t="n"/>
@@ -714,15 +714,15 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
@@ -730,15 +730,15 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>56</v>
-      </c>
-      <c r="B12" s="7" t="n"/>
+        <v>53</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D12" s="7" t="n"/>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="n"/>
@@ -746,13 +746,13 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="E13" s="7" t="n"/>
@@ -762,7 +762,7 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
@@ -794,7 +794,7 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>CeeDee Lamb</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E18" s="7" t="n"/>
@@ -842,15 +842,15 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="B19" s="7" t="n"/>
+        <v>40</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
@@ -860,13 +860,13 @@
       <c r="A20" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+      <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
@@ -880,7 +880,7 @@
       <c r="C21" s="7" t="n"/>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Justin Jefferson</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="E21" s="7" t="n"/>
@@ -894,7 +894,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C22" s="7" t="n"/>
@@ -922,11 +922,11 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C24" s="7" t="n"/>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
@@ -1054,31 +1054,31 @@
       </c>
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D33" s="7" t="n"/>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
-      <c r="H33" s="7" t="n"/>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
@@ -1088,7 +1088,7 @@
       <c r="C34" s="7" t="n"/>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E34" s="7" t="n"/>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
@@ -1162,7 +1162,7 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
@@ -1338,17 +1338,17 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B50" s="7" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C50" s="7" t="n"/>
       <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F50" s="7" t="n"/>
       <c r="G50" s="7" t="n"/>
       <c r="H50" s="7" t="n"/>
     </row>
@@ -1356,47 +1356,47 @@
       <c r="A51" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B51" s="7" t="n"/>
       <c r="C51" s="7" t="n"/>
       <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
       <c r="F51" s="7" t="n"/>
       <c r="G51" s="7" t="n"/>
-      <c r="H51" s="7" t="n"/>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B52" s="7" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C52" s="7" t="n"/>
       <c r="D52" s="7" t="n"/>
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="7" t="n"/>
-      <c r="H52" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B53" s="7" t="n"/>
       <c r="C53" s="7" t="n"/>
       <c r="D53" s="7" t="n"/>
       <c r="E53" s="7" t="n"/>
-      <c r="F53" s="7" t="n"/>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G53" s="7" t="n"/>
       <c r="H53" s="7" t="n"/>
     </row>
@@ -1426,7 +1426,7 @@
       <c r="E55" s="7" t="n"/>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G55" s="7" t="n"/>
@@ -1434,17 +1434,17 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B56" s="7" t="n"/>
       <c r="C56" s="7" t="n"/>
       <c r="D56" s="7" t="n"/>
       <c r="E56" s="7" t="n"/>
-      <c r="F56" s="7" t="n"/>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G56" s="7" t="n"/>
       <c r="H56" s="7" t="n"/>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="C57" s="7" t="n"/>
@@ -1468,13 +1468,13 @@
       <c r="A58" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B58" s="7" t="n"/>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C58" s="7" t="n"/>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
       <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n"/>
@@ -1488,7 +1488,7 @@
       <c r="C59" s="7" t="n"/>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E59" s="7" t="n"/>
@@ -1504,7 +1504,7 @@
       <c r="C60" s="7" t="n"/>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E60" s="7" t="n"/>
@@ -1514,15 +1514,15 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="n"/>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E61" s="7" t="n"/>
       <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C62" s="7" t="n"/>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C63" s="7" t="n"/>
@@ -1564,15 +1564,15 @@
       <c r="A64" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B64" s="7" t="n"/>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C64" s="7" t="n"/>
       <c r="D64" s="7" t="n"/>
       <c r="E64" s="7" t="n"/>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F64" s="7" t="n"/>
       <c r="G64" s="7" t="n"/>
       <c r="H64" s="7" t="n"/>
     </row>
@@ -1600,7 +1600,7 @@
       <c r="C66" s="7" t="n"/>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="E66" s="7" t="n"/>
@@ -1614,15 +1614,15 @@
       </c>
       <c r="B67" s="7" t="n"/>
       <c r="C67" s="7" t="n"/>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D67" s="7" t="n"/>
       <c r="E67" s="7" t="n"/>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
-      <c r="H67" s="7" t="n"/>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
@@ -1636,7 +1636,7 @@
       <c r="G68" s="7" t="n"/>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>Drake Maye</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
     </row>
@@ -1652,25 +1652,25 @@
       <c r="G69" s="7" t="n"/>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B70" s="7" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C70" s="7" t="n"/>
       <c r="D70" s="7" t="n"/>
       <c r="E70" s="7" t="n"/>
       <c r="F70" s="7" t="n"/>
       <c r="G70" s="7" t="n"/>
-      <c r="H70" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C71" s="7" t="n"/>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C72" s="7" t="n"/>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="C73" s="7" t="n"/>
@@ -1724,13 +1724,13 @@
       <c r="A74" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+      <c r="B74" s="7" t="n"/>
       <c r="C74" s="7" t="n"/>
-      <c r="D74" s="7" t="n"/>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E74" s="7" t="n"/>
       <c r="F74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
@@ -1776,7 +1776,7 @@
       <c r="C77" s="7" t="n"/>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E77" s="7" t="n"/>
@@ -1792,7 +1792,7 @@
       <c r="C78" s="7" t="n"/>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E78" s="7" t="n"/>
@@ -1802,15 +1802,15 @@
     </row>
     <row r="79">
       <c r="A79" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B79" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C79" s="7" t="n"/>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>Quentin Johnston</t>
-        </is>
-      </c>
+      <c r="D79" s="7" t="n"/>
       <c r="E79" s="7" t="n"/>
       <c r="F79" s="7" t="n"/>
       <c r="G79" s="7" t="n"/>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C80" s="7" t="n"/>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C81" s="7" t="n"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C82" s="7" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C83" s="7" t="n"/>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="C84" s="7" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>Blake Corum</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="C85" s="7" t="n"/>
@@ -1916,13 +1916,13 @@
       <c r="A86" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+      <c r="B86" s="7" t="n"/>
       <c r="C86" s="7" t="n"/>
-      <c r="D86" s="7" t="n"/>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E86" s="7" t="n"/>
       <c r="F86" s="7" t="n"/>
       <c r="G86" s="7" t="n"/>
@@ -1936,7 +1936,7 @@
       <c r="C87" s="7" t="n"/>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E87" s="7" t="n"/>
@@ -1968,7 +1968,7 @@
       <c r="C89" s="7" t="n"/>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E89" s="7" t="n"/>
@@ -1984,7 +1984,7 @@
       <c r="C90" s="7" t="n"/>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr.</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E90" s="7" t="n"/>
@@ -1998,13 +1998,13 @@
       </c>
       <c r="B91" s="7" t="n"/>
       <c r="C91" s="7" t="n"/>
-      <c r="D91" s="7" t="n"/>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>Chris Godwin Jr.</t>
+        </is>
+      </c>
       <c r="E91" s="7" t="n"/>
-      <c r="F91" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F91" s="7" t="n"/>
       <c r="G91" s="7" t="n"/>
       <c r="H91" s="7" t="n"/>
     </row>
@@ -2016,13 +2016,13 @@
       <c r="C92" s="7" t="n"/>
       <c r="D92" s="7" t="n"/>
       <c r="E92" s="7" t="n"/>
-      <c r="F92" s="7" t="n"/>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G92" s="7" t="n"/>
-      <c r="H92" s="7" t="inlineStr">
-        <is>
-          <t>Jalen Hurts</t>
-        </is>
-      </c>
+      <c r="H92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
@@ -2036,7 +2036,7 @@
       <c r="G93" s="7" t="n"/>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
     </row>
@@ -2052,25 +2052,25 @@
       <c r="G94" s="7" t="n"/>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B95" s="7" t="n"/>
       <c r="C95" s="7" t="n"/>
-      <c r="D95" s="7" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D95" s="7" t="n"/>
       <c r="E95" s="7" t="n"/>
       <c r="F95" s="7" t="n"/>
       <c r="G95" s="7" t="n"/>
-      <c r="H95" s="7" t="n"/>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
@@ -2170,13 +2170,13 @@
     </row>
     <row r="102">
       <c r="A102" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B102" s="7" t="n"/>
       <c r="C102" s="7" t="n"/>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E102" s="7" t="n"/>
@@ -2192,7 +2192,7 @@
       <c r="C103" s="7" t="n"/>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E103" s="7" t="n"/>
@@ -2208,7 +2208,7 @@
       <c r="C104" s="7" t="n"/>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E104" s="7" t="n"/>
@@ -2224,7 +2224,7 @@
       <c r="C105" s="7" t="n"/>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E105" s="7" t="n"/>
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 5; 18 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 6; 18 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 69 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 70 players moved.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Chris Olave 40-&gt;32, Trey McBride 42.2857-&gt;35, Puka Nacua 68-&gt;61, Jaxon Smith-Njigba 63-&gt;56, DeVonta Smith 27-&gt;20, Rashee Rice 26-&gt;19, Garrett Wilson 26-&gt;19, Ja'Marr Chase 60-&gt;54</t>
+          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 61-&gt;53, Chris Olave 40-&gt;32, Trey McBride 42.2857-&gt;35, Puka Nacua 68-&gt;61, DeVonta Smith 27-&gt;20, Rashee Rice 26-&gt;19, Garrett Wilson 25-&gt;18, Ja'Marr Chase 59-&gt;53</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -618,7 +618,7 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B7" s="7" t="n"/>
       <c r="C7" s="7" t="n"/>
@@ -666,7 +666,7 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
@@ -732,13 +732,13 @@
       <c r="A12" s="6" t="n">
         <v>53</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+      <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="n"/>
@@ -752,7 +752,7 @@
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E13" s="7" t="n"/>
@@ -762,15 +762,15 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="B14" s="7" t="n"/>
+        <v>52</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D14" s="7" t="n"/>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
@@ -778,7 +778,7 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
@@ -826,15 +826,15 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="B18" s="7" t="n"/>
+        <v>41</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
@@ -842,15 +842,15 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
@@ -858,13 +858,13 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Justin Jefferson</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E20" s="7" t="n"/>
@@ -876,13 +876,13 @@
       <c r="A21" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="B21" s="7" t="n"/>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
@@ -894,7 +894,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C22" s="7" t="n"/>
@@ -906,15 +906,15 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
@@ -922,23 +922,23 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
@@ -946,7 +946,7 @@
       <c r="E25" s="7" t="n"/>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>Trey McBride</t>
+          <t>Brock Bowers</t>
         </is>
       </c>
       <c r="G25" s="7" t="n"/>
@@ -954,7 +954,7 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
@@ -970,13 +970,13 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Chris Olave</t>
         </is>
       </c>
       <c r="E27" s="7" t="n"/>
@@ -992,7 +992,7 @@
       <c r="C28" s="7" t="n"/>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E28" s="7" t="n"/>
@@ -1002,23 +1002,23 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B29" s="7" t="n"/>
+        <v>31</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C29" s="7" t="n"/>
       <c r="D29" s="7" t="n"/>
       <c r="E29" s="7" t="n"/>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F29" s="7" t="n"/>
       <c r="G29" s="7" t="n"/>
       <c r="H29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
@@ -1054,31 +1054,31 @@
       </c>
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
-      <c r="H32" s="7" t="n"/>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="n"/>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
@@ -1088,7 +1088,7 @@
       <c r="C34" s="7" t="n"/>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E34" s="7" t="n"/>
@@ -1104,7 +1104,7 @@
       <c r="C35" s="7" t="n"/>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E35" s="7" t="n"/>
@@ -1130,13 +1130,13 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E37" s="7" t="n"/>
@@ -1146,13 +1146,13 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E38" s="7" t="n"/>
@@ -1162,15 +1162,15 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B39" s="7" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C39" s="7" t="n"/>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D39" s="7" t="n"/>
       <c r="E39" s="7" t="n"/>
       <c r="F39" s="7" t="n"/>
       <c r="G39" s="7" t="n"/>
@@ -1178,15 +1178,15 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="B40" s="7" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D40" s="7" t="n"/>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
@@ -1196,13 +1196,13 @@
       <c r="A41" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+      <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="n"/>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="7" t="n"/>
@@ -1210,11 +1210,11 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C42" s="7" t="n"/>
@@ -1228,13 +1228,13 @@
       <c r="A43" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+      <c r="B43" s="7" t="n"/>
       <c r="C43" s="7" t="n"/>
-      <c r="D43" s="7" t="n"/>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E43" s="7" t="n"/>
       <c r="F43" s="7" t="n"/>
       <c r="G43" s="7" t="n"/>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C44" s="7" t="n"/>
@@ -1260,13 +1260,13 @@
       <c r="A45" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+      <c r="B45" s="7" t="n"/>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="n"/>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E45" s="7" t="n"/>
       <c r="F45" s="7" t="n"/>
       <c r="G45" s="7" t="n"/>
@@ -1276,13 +1276,13 @@
       <c r="A46" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="n"/>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="7" t="n"/>
@@ -1296,7 +1296,7 @@
       <c r="C47" s="7" t="n"/>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E47" s="7" t="n"/>
@@ -1306,15 +1306,15 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B48" s="7" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D48" s="7" t="n"/>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
@@ -1322,15 +1322,15 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B49" s="7" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D49" s="7" t="n"/>
       <c r="E49" s="7" t="n"/>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n"/>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr.</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="C50" s="7" t="n"/>
@@ -1354,33 +1354,33 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B51" s="7" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C51" s="7" t="n"/>
       <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
       <c r="F51" s="7" t="n"/>
       <c r="G51" s="7" t="n"/>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B52" s="7" t="n"/>
       <c r="C52" s="7" t="n"/>
       <c r="D52" s="7" t="n"/>
       <c r="E52" s="7" t="n"/>
-      <c r="F52" s="7" t="n"/>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G52" s="7" t="n"/>
       <c r="H52" s="7" t="n"/>
     </row>
@@ -1394,7 +1394,7 @@
       <c r="E53" s="7" t="n"/>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>Tyler Warren</t>
+          <t>Colston Loveland</t>
         </is>
       </c>
       <c r="G53" s="7" t="n"/>
@@ -1410,7 +1410,7 @@
       <c r="E54" s="7" t="n"/>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>Colston Loveland</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G54" s="7" t="n"/>
@@ -1426,7 +1426,7 @@
       <c r="E55" s="7" t="n"/>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>Isaiah Likely</t>
+          <t>George Kittle</t>
         </is>
       </c>
       <c r="G55" s="7" t="n"/>
@@ -1440,25 +1440,25 @@
       <c r="C56" s="7" t="n"/>
       <c r="D56" s="7" t="n"/>
       <c r="E56" s="7" t="n"/>
-      <c r="F56" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="n"/>
-      <c r="H56" s="7" t="n"/>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+      <c r="B57" s="7" t="n"/>
       <c r="C57" s="7" t="n"/>
-      <c r="D57" s="7" t="n"/>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E57" s="7" t="n"/>
       <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
@@ -1468,13 +1468,13 @@
       <c r="A58" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+      <c r="B58" s="7" t="n"/>
       <c r="C58" s="7" t="n"/>
-      <c r="D58" s="7" t="n"/>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E58" s="7" t="n"/>
       <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n"/>
@@ -1488,7 +1488,7 @@
       <c r="C59" s="7" t="n"/>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E59" s="7" t="n"/>
@@ -1498,15 +1498,15 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B60" s="7" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C60" s="7" t="n"/>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D60" s="7" t="n"/>
       <c r="E60" s="7" t="n"/>
       <c r="F60" s="7" t="n"/>
       <c r="G60" s="7" t="n"/>
@@ -1514,15 +1514,15 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B61" s="7" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
       <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C62" s="7" t="n"/>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B65" s="7" t="n"/>
       <c r="C65" s="7" t="n"/>
@@ -1600,7 +1600,7 @@
       <c r="C66" s="7" t="n"/>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E66" s="7" t="n"/>
@@ -1728,7 +1728,7 @@
       <c r="C74" s="7" t="n"/>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="E74" s="7" t="n"/>
@@ -1776,7 +1776,7 @@
       <c r="C77" s="7" t="n"/>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E77" s="7" t="n"/>
@@ -1792,7 +1792,7 @@
       <c r="C78" s="7" t="n"/>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E78" s="7" t="n"/>
@@ -1802,15 +1802,15 @@
     </row>
     <row r="79">
       <c r="A79" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B79" s="7" t="n"/>
       <c r="C79" s="7" t="n"/>
-      <c r="D79" s="7" t="n"/>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>Quentin Johnston</t>
+        </is>
+      </c>
       <c r="E79" s="7" t="n"/>
       <c r="F79" s="7" t="n"/>
       <c r="G79" s="7" t="n"/>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C80" s="7" t="n"/>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C81" s="7" t="n"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C82" s="7" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C83" s="7" t="n"/>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>Blake Corum</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C84" s="7" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="C85" s="7" t="n"/>
@@ -1916,13 +1916,13 @@
       <c r="A86" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B86" s="7" t="n"/>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C86" s="7" t="n"/>
-      <c r="D86" s="7" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D86" s="7" t="n"/>
       <c r="E86" s="7" t="n"/>
       <c r="F86" s="7" t="n"/>
       <c r="G86" s="7" t="n"/>
@@ -1936,7 +1936,7 @@
       <c r="C87" s="7" t="n"/>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E87" s="7" t="n"/>
@@ -1968,7 +1968,7 @@
       <c r="C89" s="7" t="n"/>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E89" s="7" t="n"/>
@@ -1984,7 +1984,7 @@
       <c r="C90" s="7" t="n"/>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E90" s="7" t="n"/>
@@ -1998,13 +1998,13 @@
       </c>
       <c r="B91" s="7" t="n"/>
       <c r="C91" s="7" t="n"/>
-      <c r="D91" s="7" t="inlineStr">
-        <is>
-          <t>Chris Godwin Jr.</t>
-        </is>
-      </c>
+      <c r="D91" s="7" t="n"/>
       <c r="E91" s="7" t="n"/>
-      <c r="F91" s="7" t="n"/>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G91" s="7" t="n"/>
       <c r="H91" s="7" t="n"/>
     </row>
@@ -2016,13 +2016,13 @@
       <c r="C92" s="7" t="n"/>
       <c r="D92" s="7" t="n"/>
       <c r="E92" s="7" t="n"/>
-      <c r="F92" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F92" s="7" t="n"/>
       <c r="G92" s="7" t="n"/>
-      <c r="H92" s="7" t="n"/>
+      <c r="H92" s="7" t="inlineStr">
+        <is>
+          <t>Jalen Hurts</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
@@ -2036,7 +2036,7 @@
       <c r="G93" s="7" t="n"/>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
@@ -2052,25 +2052,25 @@
       <c r="G94" s="7" t="n"/>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B95" s="7" t="n"/>
       <c r="C95" s="7" t="n"/>
-      <c r="D95" s="7" t="n"/>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E95" s="7" t="n"/>
       <c r="F95" s="7" t="n"/>
       <c r="G95" s="7" t="n"/>
-      <c r="H95" s="7" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H95" s="7" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
@@ -2170,13 +2170,13 @@
     </row>
     <row r="102">
       <c r="A102" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B102" s="7" t="n"/>
       <c r="C102" s="7" t="n"/>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E102" s="7" t="n"/>
@@ -2192,7 +2192,7 @@
       <c r="C103" s="7" t="n"/>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E103" s="7" t="n"/>
@@ -2208,7 +2208,7 @@
       <c r="C104" s="7" t="n"/>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E104" s="7" t="n"/>
@@ -2224,7 +2224,7 @@
       <c r="C105" s="7" t="n"/>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E105" s="7" t="n"/>
@@ -2295,7 +2295,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 74.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 75.</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 6; 18 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 7; 16 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 70 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 72 players moved.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 61-&gt;53, Chris Olave 40-&gt;32, Trey McBride 42.2857-&gt;35, Puka Nacua 68-&gt;61, DeVonta Smith 27-&gt;20, Rashee Rice 26-&gt;19, Garrett Wilson 25-&gt;18, Ja'Marr Chase 59-&gt;53</t>
+          <t>Largest moves vs. the baseline in this file: Puka Nacua 68-&gt;60, Jaxon Smith-Njigba 61-&gt;53, Chris Olave 40-&gt;32, Trey McBride 42.8571-&gt;35, Ja'Marr Chase 60-&gt;53, Amon-Ra St. Brown 63-&gt;56, Justin Jefferson 46-&gt;39, CeeDee Lamb 48-&gt;41</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -634,7 +634,7 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
@@ -650,15 +650,15 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="B7" s="7" t="n"/>
+        <v>59</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Jonathan Taylor</t>
+        </is>
+      </c>
       <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="7" t="n"/>
@@ -668,13 +668,13 @@
       <c r="A8" s="6" t="n">
         <v>59</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Jonathan Taylor</t>
-        </is>
-      </c>
+      <c r="B8" s="7" t="n"/>
       <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="7" t="n"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>James Cook III</t>
         </is>
       </c>
       <c r="C9" s="7" t="n"/>
@@ -698,11 +698,11 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>James Cook III</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C10" s="7" t="n"/>
@@ -714,7 +714,7 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
@@ -730,7 +730,7 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
@@ -746,7 +746,7 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
@@ -762,11 +762,11 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="C14" s="7" t="n"/>
@@ -782,7 +782,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Saquon Barkley</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="C15" s="7" t="n"/>
@@ -794,7 +794,7 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
@@ -828,13 +828,13 @@
       <c r="A18" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+      <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
@@ -842,15 +842,15 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="B19" s="7" t="n"/>
+        <v>40</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
@@ -858,13 +858,13 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="E20" s="7" t="n"/>
@@ -874,11 +874,11 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C21" s="7" t="n"/>
@@ -894,7 +894,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Ashton Jeanty</t>
         </is>
       </c>
       <c r="C22" s="7" t="n"/>
@@ -922,7 +922,7 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
@@ -976,7 +976,7 @@
       <c r="C27" s="7" t="n"/>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E27" s="7" t="n"/>
@@ -986,15 +986,15 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B28" s="7" t="n"/>
+        <v>31</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
+      <c r="D28" s="7" t="n"/>
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="7" t="n"/>
@@ -1004,13 +1004,13 @@
       <c r="A29" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+      <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="7" t="n"/>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
@@ -1050,35 +1050,35 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D33" s="7" t="n"/>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
-      <c r="H33" s="7" t="n"/>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
@@ -1130,13 +1130,13 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E37" s="7" t="n"/>
@@ -1146,13 +1146,13 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E38" s="7" t="n"/>
@@ -1212,13 +1212,13 @@
       <c r="A42" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+      <c r="B42" s="7" t="n"/>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="n"/>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="7" t="n"/>
@@ -1226,13 +1226,13 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B43" s="7" t="n"/>
       <c r="C43" s="7" t="n"/>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E43" s="7" t="n"/>
@@ -1242,11 +1242,11 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C44" s="7" t="n"/>
@@ -1258,15 +1258,15 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B45" s="7" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D45" s="7" t="n"/>
       <c r="E45" s="7" t="n"/>
       <c r="F45" s="7" t="n"/>
       <c r="G45" s="7" t="n"/>
@@ -1274,15 +1274,15 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B46" s="7" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D46" s="7" t="n"/>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="7" t="n"/>
@@ -1290,15 +1290,15 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B47" s="7" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D47" s="7" t="n"/>
       <c r="E47" s="7" t="n"/>
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="7" t="n"/>
@@ -1308,13 +1308,13 @@
       <c r="A48" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+      <c r="B48" s="7" t="n"/>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="n"/>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
@@ -1324,13 +1324,13 @@
       <c r="A49" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B49" s="7" t="n"/>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="n"/>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E49" s="7" t="n"/>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n"/>
@@ -1340,15 +1340,15 @@
       <c r="A50" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B50" s="7" t="n"/>
       <c r="C50" s="7" t="n"/>
       <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
-      <c r="F50" s="7" t="n"/>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G50" s="7" t="n"/>
       <c r="H50" s="7" t="n"/>
     </row>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C51" s="7" t="n"/>
@@ -1372,15 +1372,15 @@
       <c r="A52" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B52" s="7" t="n"/>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C52" s="7" t="n"/>
       <c r="D52" s="7" t="n"/>
       <c r="E52" s="7" t="n"/>
-      <c r="F52" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F52" s="7" t="n"/>
       <c r="G52" s="7" t="n"/>
       <c r="H52" s="7" t="n"/>
     </row>
@@ -1408,45 +1408,45 @@
       <c r="C54" s="7" t="n"/>
       <c r="D54" s="7" t="n"/>
       <c r="E54" s="7" t="n"/>
-      <c r="F54" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F54" s="7" t="n"/>
       <c r="G54" s="7" t="n"/>
-      <c r="H54" s="7" t="n"/>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B55" s="7" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C55" s="7" t="n"/>
       <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F55" s="7" t="n"/>
       <c r="G55" s="7" t="n"/>
       <c r="H55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B56" s="7" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C56" s="7" t="n"/>
       <c r="D56" s="7" t="n"/>
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="n"/>
-      <c r="H56" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
@@ -1498,33 +1498,33 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B60" s="7" t="n"/>
       <c r="C60" s="7" t="n"/>
       <c r="D60" s="7" t="n"/>
       <c r="E60" s="7" t="n"/>
-      <c r="F60" s="7" t="n"/>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G60" s="7" t="n"/>
       <c r="H60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
       <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
-      <c r="F61" s="7" t="n"/>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G61" s="7" t="n"/>
       <c r="H61" s="7" t="n"/>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C70" s="7" t="n"/>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C71" s="7" t="n"/>
@@ -1692,13 +1692,13 @@
       <c r="A72" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+      <c r="B72" s="7" t="n"/>
       <c r="C72" s="7" t="n"/>
-      <c r="D72" s="7" t="n"/>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E72" s="7" t="n"/>
       <c r="F72" s="7" t="n"/>
       <c r="G72" s="7" t="n"/>
@@ -1708,13 +1708,13 @@
       <c r="A73" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+      <c r="B73" s="7" t="n"/>
       <c r="C73" s="7" t="n"/>
-      <c r="D73" s="7" t="n"/>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E73" s="7" t="n"/>
       <c r="F73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
@@ -1726,27 +1726,27 @@
       </c>
       <c r="B74" s="7" t="n"/>
       <c r="C74" s="7" t="n"/>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
-      <c r="F74" s="7" t="n"/>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G74" s="7" t="n"/>
       <c r="H74" s="7" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B75" s="7" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C75" s="7" t="n"/>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>Brian Thomas Jr.</t>
-        </is>
-      </c>
+      <c r="D75" s="7" t="n"/>
       <c r="E75" s="7" t="n"/>
       <c r="F75" s="7" t="n"/>
       <c r="G75" s="7" t="n"/>
@@ -1754,17 +1754,17 @@
     </row>
     <row r="76">
       <c r="A76" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B76" s="7" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C76" s="7" t="n"/>
       <c r="D76" s="7" t="n"/>
       <c r="E76" s="7" t="n"/>
-      <c r="F76" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F76" s="7" t="n"/>
       <c r="G76" s="7" t="n"/>
       <c r="H76" s="7" t="n"/>
     </row>
@@ -1802,15 +1802,15 @@
     </row>
     <row r="79">
       <c r="A79" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B79" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>Jonathon Brooks</t>
+        </is>
+      </c>
       <c r="C79" s="7" t="n"/>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>Quentin Johnston</t>
-        </is>
-      </c>
+      <c r="D79" s="7" t="n"/>
       <c r="E79" s="7" t="n"/>
       <c r="F79" s="7" t="n"/>
       <c r="G79" s="7" t="n"/>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C80" s="7" t="n"/>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="C81" s="7" t="n"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C82" s="7" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C83" s="7" t="n"/>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="C84" s="7" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>Blake Corum</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="C85" s="7" t="n"/>
@@ -1916,13 +1916,13 @@
       <c r="A86" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+      <c r="B86" s="7" t="n"/>
       <c r="C86" s="7" t="n"/>
-      <c r="D86" s="7" t="n"/>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E86" s="7" t="n"/>
       <c r="F86" s="7" t="n"/>
       <c r="G86" s="7" t="n"/>
@@ -1936,7 +1936,7 @@
       <c r="C87" s="7" t="n"/>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E87" s="7" t="n"/>
@@ -1984,7 +1984,7 @@
       <c r="C90" s="7" t="n"/>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr.</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E90" s="7" t="n"/>
@@ -1998,13 +1998,13 @@
       </c>
       <c r="B91" s="7" t="n"/>
       <c r="C91" s="7" t="n"/>
-      <c r="D91" s="7" t="n"/>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>Chris Godwin Jr.</t>
+        </is>
+      </c>
       <c r="E91" s="7" t="n"/>
-      <c r="F91" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F91" s="7" t="n"/>
       <c r="G91" s="7" t="n"/>
       <c r="H91" s="7" t="n"/>
     </row>
@@ -2016,13 +2016,13 @@
       <c r="C92" s="7" t="n"/>
       <c r="D92" s="7" t="n"/>
       <c r="E92" s="7" t="n"/>
-      <c r="F92" s="7" t="n"/>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G92" s="7" t="n"/>
-      <c r="H92" s="7" t="inlineStr">
-        <is>
-          <t>Jalen Hurts</t>
-        </is>
-      </c>
+      <c r="H92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
@@ -2036,7 +2036,7 @@
       <c r="G93" s="7" t="n"/>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
     </row>
@@ -2052,25 +2052,25 @@
       <c r="G94" s="7" t="n"/>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B95" s="7" t="n"/>
       <c r="C95" s="7" t="n"/>
-      <c r="D95" s="7" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D95" s="7" t="n"/>
       <c r="E95" s="7" t="n"/>
       <c r="F95" s="7" t="n"/>
       <c r="G95" s="7" t="n"/>
-      <c r="H95" s="7" t="n"/>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
@@ -2295,7 +2295,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 75.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 76.</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 7; 16 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 8; 15 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,14 +2333,14 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 72 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 73 players moved.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   No projection this week (value kept): Saquon Barkley, A.J. Brown, Breece Hall, DeVonta Smith, Rashee Rice, Lamar Jackson, Travis Etienne Jr., Jadarian Price, Josh Jacobs, De'Zhaun Stribling, Jordan Mason, Alec Pierce, Brian Thomas Jr., Quentin Johnston, Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Jaxson Dart, Ja'Kobi Lane.</t>
+          <t xml:space="preserve">   No projection this week (value kept): Saquon Barkley, A.J. Brown, Breece Hall, DeVonta Smith, Rashee Rice, Lamar Jackson, Travis Etienne Jr., Jadarian Price, Josh Jacobs, De'Zhaun Stribling, Jordan Mason, Alec Pierce, Brian Thomas Jr., Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Jaxson Dart, Ja'Kobi Lane.</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.7, WR 2.8, TE 4.5, QB 0.0.</t>
+          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.6, WR 2.8, TE 4.5, QB 0.0.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Puka Nacua 68-&gt;60, Jaxon Smith-Njigba 61-&gt;53, Chris Olave 40-&gt;32, Trey McBride 42.8571-&gt;35, Ja'Marr Chase 60-&gt;53, Amon-Ra St. Brown 63-&gt;56, Justin Jefferson 46-&gt;39, CeeDee Lamb 48-&gt;41</t>
+          <t>Largest moves vs. the baseline in this file: Puka Nacua 68-&gt;59, Jaxon Smith-Njigba 61-&gt;52, Chris Olave 40-&gt;31, Ja'Marr Chase 60-&gt;52, Amon-Ra St. Brown 63-&gt;55, Trey McBride 43.4286-&gt;36, Justin Jefferson 46-&gt;39, CeeDee Lamb 47-&gt;40</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -618,7 +618,7 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C6" s="7" t="n"/>
@@ -650,15 +650,15 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Jonathan Taylor</t>
-        </is>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="B7" s="7" t="n"/>
       <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="7" t="n"/>
@@ -666,15 +666,15 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="B8" s="7" t="n"/>
+        <v>60</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D8" s="7" t="n"/>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="7" t="n"/>
@@ -714,7 +714,7 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
@@ -730,15 +730,15 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>52</v>
-      </c>
-      <c r="B12" s="7" t="n"/>
+        <v>53</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Jaxon Smith-Njigba</t>
-        </is>
-      </c>
+      <c r="D12" s="7" t="n"/>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="n"/>
@@ -746,13 +746,13 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="E13" s="7" t="n"/>
@@ -762,15 +762,15 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
@@ -782,7 +782,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="C15" s="7" t="n"/>
@@ -794,7 +794,7 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="E18" s="7" t="n"/>
@@ -842,15 +842,15 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
@@ -858,15 +858,15 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="B20" s="7" t="n"/>
+        <v>39</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
@@ -876,13 +876,13 @@
       <c r="A21" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+      <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
@@ -890,11 +890,11 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C22" s="7" t="n"/>
@@ -906,33 +906,33 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G23" s="7" t="n"/>
       <c r="H23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="B24" s="7" t="n"/>
+        <v>35</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
     </row>
@@ -976,7 +976,7 @@
       <c r="C27" s="7" t="n"/>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Chris Olave</t>
         </is>
       </c>
       <c r="E27" s="7" t="n"/>
@@ -1002,13 +1002,13 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>Nico Collins</t>
         </is>
       </c>
       <c r="E29" s="7" t="n"/>
@@ -1018,13 +1018,13 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Nico Collins</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E30" s="7" t="n"/>
@@ -1082,13 +1082,13 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E34" s="7" t="n"/>
@@ -1098,13 +1098,13 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E35" s="7" t="n"/>
@@ -1120,7 +1120,7 @@
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E36" s="7" t="n"/>
@@ -1162,15 +1162,15 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
-      <c r="D39" s="7" t="n"/>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E39" s="7" t="n"/>
       <c r="F39" s="7" t="n"/>
       <c r="G39" s="7" t="n"/>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="C40" s="7" t="n"/>
@@ -1196,13 +1196,13 @@
       <c r="A41" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B41" s="7" t="n"/>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D41" s="7" t="n"/>
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="7" t="n"/>
@@ -1226,13 +1226,13 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B43" s="7" t="n"/>
       <c r="C43" s="7" t="n"/>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E43" s="7" t="n"/>
@@ -1242,15 +1242,15 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="n"/>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="7" t="n"/>
@@ -1258,15 +1258,15 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B45" s="7" t="n"/>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="n"/>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E45" s="7" t="n"/>
       <c r="F45" s="7" t="n"/>
       <c r="G45" s="7" t="n"/>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C46" s="7" t="n"/>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C47" s="7" t="n"/>
@@ -1308,13 +1308,13 @@
       <c r="A48" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B48" s="7" t="n"/>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D48" s="7" t="n"/>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
@@ -1324,13 +1324,13 @@
       <c r="A49" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B49" s="7" t="n"/>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D49" s="7" t="n"/>
       <c r="E49" s="7" t="n"/>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n"/>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="C52" s="7" t="n"/>
@@ -1420,13 +1420,13 @@
       <c r="A55" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+      <c r="B55" s="7" t="n"/>
       <c r="C55" s="7" t="n"/>
-      <c r="D55" s="7" t="n"/>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E55" s="7" t="n"/>
       <c r="F55" s="7" t="n"/>
       <c r="G55" s="7" t="n"/>
@@ -1436,13 +1436,13 @@
       <c r="A56" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B56" s="7" t="n"/>
       <c r="C56" s="7" t="n"/>
-      <c r="D56" s="7" t="n"/>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="n"/>
@@ -1454,13 +1454,13 @@
       </c>
       <c r="B57" s="7" t="n"/>
       <c r="C57" s="7" t="n"/>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
-      <c r="F57" s="7" t="n"/>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G57" s="7" t="n"/>
       <c r="H57" s="7" t="n"/>
     </row>
@@ -1470,27 +1470,27 @@
       </c>
       <c r="B58" s="7" t="n"/>
       <c r="C58" s="7" t="n"/>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
-      <c r="F58" s="7" t="n"/>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B59" s="7" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
       <c r="F59" s="7" t="n"/>
       <c r="G59" s="7" t="n"/>
@@ -1498,33 +1498,33 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B60" s="7" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C60" s="7" t="n"/>
       <c r="D60" s="7" t="n"/>
       <c r="E60" s="7" t="n"/>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F60" s="7" t="n"/>
       <c r="G60" s="7" t="n"/>
       <c r="H60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B61" s="7" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C61" s="7" t="n"/>
       <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
       <c r="H61" s="7" t="n"/>
     </row>
@@ -1548,13 +1548,13 @@
       <c r="A63" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+      <c r="B63" s="7" t="n"/>
       <c r="C63" s="7" t="n"/>
-      <c r="D63" s="7" t="n"/>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E63" s="7" t="n"/>
       <c r="F63" s="7" t="n"/>
       <c r="G63" s="7" t="n"/>
@@ -1564,13 +1564,13 @@
       <c r="A64" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B64" s="7" t="n"/>
       <c r="C64" s="7" t="n"/>
-      <c r="D64" s="7" t="n"/>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E64" s="7" t="n"/>
       <c r="F64" s="7" t="n"/>
       <c r="G64" s="7" t="n"/>
@@ -1578,15 +1578,15 @@
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B65" s="7" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C65" s="7" t="n"/>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D65" s="7" t="n"/>
       <c r="E65" s="7" t="n"/>
       <c r="F65" s="7" t="n"/>
       <c r="G65" s="7" t="n"/>
@@ -1596,13 +1596,13 @@
       <c r="A66" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B66" s="7" t="n"/>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C66" s="7" t="n"/>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D66" s="7" t="n"/>
       <c r="E66" s="7" t="n"/>
       <c r="F66" s="7" t="n"/>
       <c r="G66" s="7" t="n"/>
@@ -1614,15 +1614,15 @@
       </c>
       <c r="B67" s="7" t="n"/>
       <c r="C67" s="7" t="n"/>
-      <c r="D67" s="7" t="n"/>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E67" s="7" t="n"/>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
-      <c r="H67" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
@@ -1630,15 +1630,15 @@
       </c>
       <c r="B68" s="7" t="n"/>
       <c r="C68" s="7" t="n"/>
-      <c r="D68" s="7" t="n"/>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E68" s="7" t="n"/>
       <c r="F68" s="7" t="n"/>
       <c r="G68" s="7" t="n"/>
-      <c r="H68" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
@@ -1652,53 +1652,53 @@
       <c r="G69" s="7" t="n"/>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Drake Maye</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B70" s="7" t="n"/>
       <c r="C70" s="7" t="n"/>
       <c r="D70" s="7" t="n"/>
       <c r="E70" s="7" t="n"/>
       <c r="F70" s="7" t="n"/>
       <c r="G70" s="7" t="n"/>
-      <c r="H70" s="7" t="n"/>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B71" s="7" t="n"/>
       <c r="C71" s="7" t="n"/>
       <c r="D71" s="7" t="n"/>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
-      <c r="H71" s="7" t="n"/>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B72" s="7" t="n"/>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
       <c r="C72" s="7" t="n"/>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D72" s="7" t="n"/>
       <c r="E72" s="7" t="n"/>
       <c r="F72" s="7" t="n"/>
       <c r="G72" s="7" t="n"/>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C75" s="7" t="n"/>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="C76" s="7" t="n"/>
@@ -1776,7 +1776,7 @@
       <c r="C77" s="7" t="n"/>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E77" s="7" t="n"/>
@@ -1792,7 +1792,7 @@
       <c r="C78" s="7" t="n"/>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E78" s="7" t="n"/>
@@ -1802,15 +1802,15 @@
     </row>
     <row r="79">
       <c r="A79" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>Jonathon Brooks</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B79" s="7" t="n"/>
       <c r="C79" s="7" t="n"/>
-      <c r="D79" s="7" t="n"/>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E79" s="7" t="n"/>
       <c r="F79" s="7" t="n"/>
       <c r="G79" s="7" t="n"/>
@@ -1818,15 +1818,15 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>Mike Washington Jr.</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B80" s="7" t="n"/>
       <c r="C80" s="7" t="n"/>
-      <c r="D80" s="7" t="n"/>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E80" s="7" t="n"/>
       <c r="F80" s="7" t="n"/>
       <c r="G80" s="7" t="n"/>
@@ -1834,15 +1834,15 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B81" s="7" t="n"/>
       <c r="C81" s="7" t="n"/>
-      <c r="D81" s="7" t="n"/>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>Marvin Harrison Jr.</t>
+        </is>
+      </c>
       <c r="E81" s="7" t="n"/>
       <c r="F81" s="7" t="n"/>
       <c r="G81" s="7" t="n"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C82" s="7" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C83" s="7" t="n"/>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>Blake Corum</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C84" s="7" t="n"/>
@@ -1900,13 +1900,13 @@
       <c r="A85" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+      <c r="B85" s="7" t="n"/>
       <c r="C85" s="7" t="n"/>
-      <c r="D85" s="7" t="n"/>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>De'Zhaun Stribling</t>
+        </is>
+      </c>
       <c r="E85" s="7" t="n"/>
       <c r="F85" s="7" t="n"/>
       <c r="G85" s="7" t="n"/>
@@ -1920,7 +1920,7 @@
       <c r="C86" s="7" t="n"/>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E86" s="7" t="n"/>
@@ -1930,15 +1930,15 @@
     </row>
     <row r="87">
       <c r="A87" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B87" s="7" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>J.K. Dobbins</t>
+        </is>
+      </c>
       <c r="C87" s="7" t="n"/>
-      <c r="D87" s="7" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D87" s="7" t="n"/>
       <c r="E87" s="7" t="n"/>
       <c r="F87" s="7" t="n"/>
       <c r="G87" s="7" t="n"/>
@@ -1946,15 +1946,15 @@
     </row>
     <row r="88">
       <c r="A88" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B88" s="7" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>Rico Dowdle</t>
+        </is>
+      </c>
       <c r="C88" s="7" t="n"/>
-      <c r="D88" s="7" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D88" s="7" t="n"/>
       <c r="E88" s="7" t="n"/>
       <c r="F88" s="7" t="n"/>
       <c r="G88" s="7" t="n"/>
@@ -1962,15 +1962,15 @@
     </row>
     <row r="89">
       <c r="A89" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B89" s="7" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C89" s="7" t="n"/>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>De'Zhaun Stribling</t>
-        </is>
-      </c>
+      <c r="D89" s="7" t="n"/>
       <c r="E89" s="7" t="n"/>
       <c r="F89" s="7" t="n"/>
       <c r="G89" s="7" t="n"/>
@@ -1978,15 +1978,15 @@
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B90" s="7" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C90" s="7" t="n"/>
-      <c r="D90" s="7" t="inlineStr">
-        <is>
-          <t>Quentin Johnston</t>
-        </is>
-      </c>
+      <c r="D90" s="7" t="n"/>
       <c r="E90" s="7" t="n"/>
       <c r="F90" s="7" t="n"/>
       <c r="G90" s="7" t="n"/>
@@ -1994,13 +1994,13 @@
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B91" s="7" t="n"/>
       <c r="C91" s="7" t="n"/>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr.</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E91" s="7" t="n"/>
@@ -2010,67 +2010,67 @@
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B92" s="7" t="n"/>
       <c r="C92" s="7" t="n"/>
-      <c r="D92" s="7" t="n"/>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E92" s="7" t="n"/>
-      <c r="F92" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F92" s="7" t="n"/>
       <c r="G92" s="7" t="n"/>
       <c r="H92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B93" s="7" t="n"/>
       <c r="C93" s="7" t="n"/>
-      <c r="D93" s="7" t="n"/>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>Chris Godwin Jr.</t>
+        </is>
+      </c>
       <c r="E93" s="7" t="n"/>
       <c r="F93" s="7" t="n"/>
       <c r="G93" s="7" t="n"/>
-      <c r="H93" s="7" t="inlineStr">
-        <is>
-          <t>Jalen Hurts</t>
-        </is>
-      </c>
+      <c r="H93" s="7" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B94" s="7" t="n"/>
       <c r="C94" s="7" t="n"/>
-      <c r="D94" s="7" t="n"/>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="7" t="n"/>
       <c r="G94" s="7" t="n"/>
-      <c r="H94" s="7" t="inlineStr">
-        <is>
-          <t>Justin Herbert</t>
-        </is>
-      </c>
+      <c r="H94" s="7" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B95" s="7" t="n"/>
       <c r="C95" s="7" t="n"/>
       <c r="D95" s="7" t="n"/>
       <c r="E95" s="7" t="n"/>
-      <c r="F95" s="7" t="n"/>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G95" s="7" t="n"/>
-      <c r="H95" s="7" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H95" s="7" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
@@ -2078,15 +2078,15 @@
       </c>
       <c r="B96" s="7" t="n"/>
       <c r="C96" s="7" t="n"/>
-      <c r="D96" s="7" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
+      <c r="D96" s="7" t="n"/>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="7" t="n"/>
       <c r="G96" s="7" t="n"/>
-      <c r="H96" s="7" t="n"/>
+      <c r="H96" s="7" t="inlineStr">
+        <is>
+          <t>Jalen Hurts</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
@@ -2094,15 +2094,15 @@
       </c>
       <c r="B97" s="7" t="n"/>
       <c r="C97" s="7" t="n"/>
-      <c r="D97" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
+      <c r="D97" s="7" t="n"/>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="7" t="n"/>
       <c r="G97" s="7" t="n"/>
-      <c r="H97" s="7" t="n"/>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>Justin Herbert</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
@@ -2116,25 +2116,25 @@
       <c r="G98" s="7" t="n"/>
       <c r="H98" s="7" t="inlineStr">
         <is>
-          <t>Jaxson Dart</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B99" s="7" t="n"/>
       <c r="C99" s="7" t="n"/>
-      <c r="D99" s="7" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D99" s="7" t="n"/>
       <c r="E99" s="7" t="n"/>
       <c r="F99" s="7" t="n"/>
       <c r="G99" s="7" t="n"/>
-      <c r="H99" s="7" t="n"/>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
@@ -2154,13 +2154,13 @@
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B101" s="7" t="n"/>
       <c r="C101" s="7" t="n"/>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E101" s="7" t="n"/>
@@ -2176,7 +2176,7 @@
       <c r="C102" s="7" t="n"/>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E102" s="7" t="n"/>
@@ -2192,7 +2192,7 @@
       <c r="C103" s="7" t="n"/>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E103" s="7" t="n"/>
@@ -2208,7 +2208,7 @@
       <c r="C104" s="7" t="n"/>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E104" s="7" t="n"/>
@@ -2218,15 +2218,15 @@
     </row>
     <row r="105">
       <c r="A105" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B105" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>Rachaad White</t>
+        </is>
+      </c>
       <c r="C105" s="7" t="n"/>
-      <c r="D105" s="7" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D105" s="7" t="n"/>
       <c r="E105" s="7" t="n"/>
       <c r="F105" s="7" t="n"/>
       <c r="G105" s="7" t="n"/>
@@ -2252,13 +2252,13 @@
       <c r="A107" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B107" s="7" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
+      <c r="B107" s="7" t="n"/>
       <c r="C107" s="7" t="n"/>
-      <c r="D107" s="7" t="n"/>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
       <c r="E107" s="7" t="n"/>
       <c r="F107" s="7" t="n"/>
       <c r="G107" s="7" t="n"/>
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 8; 15 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 9; 13 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,14 +2333,14 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 73 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 74 players moved.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   No projection this week (value kept): Saquon Barkley, A.J. Brown, Breece Hall, DeVonta Smith, Rashee Rice, Lamar Jackson, Travis Etienne Jr., Jadarian Price, Josh Jacobs, De'Zhaun Stribling, Jordan Mason, Alec Pierce, Brian Thomas Jr., Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Jaxson Dart, Ja'Kobi Lane.</t>
+          <t xml:space="preserve">   No projection this week (value kept): Saquon Barkley, Breece Hall, DeVonta Smith, Rashee Rice, Lamar Jackson, Travis Etienne Jr., Jadarian Price, Josh Jacobs, De'Zhaun Stribling, Jordan Mason, Alec Pierce, Brian Thomas Jr., Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Jaxson Dart, Ja'Kobi Lane.</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.6, WR 2.8, TE 4.5, QB 0.0.</t>
+          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.6, WR 3.0, TE 4.5, QB 0.0.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Puka Nacua 68-&gt;59, Jaxon Smith-Njigba 61-&gt;52, Chris Olave 40-&gt;31, Ja'Marr Chase 60-&gt;52, Amon-Ra St. Brown 63-&gt;55, Trey McBride 43.4286-&gt;36, Justin Jefferson 46-&gt;39, CeeDee Lamb 47-&gt;40</t>
+          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 62-&gt;53, Chris Olave 41-&gt;32, Puka Nacua 69-&gt;61, Ja'Marr Chase 60-&gt;52, Trey McBride 43.4286-&gt;36, Amon-Ra St. Brown 63-&gt;56, Justin Jefferson 46-&gt;39, CeeDee Lamb 48-&gt;41</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -618,7 +618,7 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
@@ -634,11 +634,11 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C6" s="7" t="n"/>
@@ -670,7 +670,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>James Cook III</t>
         </is>
       </c>
       <c r="C8" s="7" t="n"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>James Cook III</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C9" s="7" t="n"/>
@@ -730,7 +730,7 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
@@ -828,13 +828,13 @@
       <c r="A18" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="B18" s="7" t="n"/>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
@@ -848,7 +848,7 @@
       <c r="C19" s="7" t="n"/>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="E19" s="7" t="n"/>
@@ -858,15 +858,15 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
@@ -874,15 +874,15 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="B21" s="7" t="n"/>
+        <v>40</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
@@ -890,15 +890,15 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
@@ -906,33 +906,33 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="B23" s="7" t="n"/>
+        <v>38</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C23" s="7" t="n"/>
       <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
       <c r="H23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
     </row>
@@ -940,31 +940,31 @@
       <c r="A25" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="B25" s="7" t="n"/>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
       <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="7" t="n"/>
     </row>
@@ -972,13 +972,13 @@
       <c r="A27" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="B27" s="7" t="n"/>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D27" s="7" t="n"/>
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
@@ -986,15 +986,15 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="7" t="n"/>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
@@ -1034,15 +1034,15 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="7" t="n"/>
       <c r="G31" s="7" t="n"/>
@@ -1052,13 +1052,13 @@
       <c r="A32" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="B32" s="7" t="n"/>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
@@ -1162,7 +1162,7 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>Jadarian Price</t>
         </is>
       </c>
       <c r="C40" s="7" t="n"/>
@@ -1194,15 +1194,15 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="n"/>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="7" t="n"/>
@@ -1214,27 +1214,27 @@
       </c>
       <c r="B42" s="7" t="n"/>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D42" s="7" t="n"/>
       <c r="E42" s="7" t="n"/>
-      <c r="F42" s="7" t="n"/>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G42" s="7" t="n"/>
       <c r="H42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B43" s="7" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C43" s="7" t="n"/>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D43" s="7" t="n"/>
       <c r="E43" s="7" t="n"/>
       <c r="F43" s="7" t="n"/>
       <c r="G43" s="7" t="n"/>
@@ -1242,13 +1242,13 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="n"/>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E44" s="7" t="n"/>
@@ -1264,7 +1264,7 @@
       <c r="C45" s="7" t="n"/>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E45" s="7" t="n"/>
@@ -1274,15 +1274,15 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="n"/>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="7" t="n"/>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C47" s="7" t="n"/>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C48" s="7" t="n"/>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C49" s="7" t="n"/>
@@ -1340,31 +1340,31 @@
       <c r="A50" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B50" s="7" t="n"/>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C50" s="7" t="n"/>
       <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F50" s="7" t="n"/>
       <c r="G50" s="7" t="n"/>
       <c r="H50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B51" s="7" t="n"/>
       <c r="C51" s="7" t="n"/>
       <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
-      <c r="F51" s="7" t="n"/>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G51" s="7" t="n"/>
       <c r="H51" s="7" t="n"/>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C52" s="7" t="n"/>
@@ -1388,15 +1388,15 @@
       <c r="A53" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B53" s="7" t="n"/>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C53" s="7" t="n"/>
       <c r="D53" s="7" t="n"/>
       <c r="E53" s="7" t="n"/>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F53" s="7" t="n"/>
       <c r="G53" s="7" t="n"/>
       <c r="H53" s="7" t="n"/>
     </row>
@@ -1406,47 +1406,47 @@
       </c>
       <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
-      <c r="D54" s="7" t="n"/>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E54" s="7" t="n"/>
       <c r="F54" s="7" t="n"/>
       <c r="G54" s="7" t="n"/>
-      <c r="H54" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B55" s="7" t="n"/>
       <c r="C55" s="7" t="n"/>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7" t="n"/>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G55" s="7" t="n"/>
       <c r="H55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B56" s="7" t="n"/>
       <c r="C56" s="7" t="n"/>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D56" s="7" t="n"/>
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="n"/>
-      <c r="H56" s="7" t="n"/>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
@@ -1454,13 +1454,13 @@
       </c>
       <c r="B57" s="7" t="n"/>
       <c r="C57" s="7" t="n"/>
-      <c r="D57" s="7" t="n"/>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E57" s="7" t="n"/>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
       <c r="H57" s="7" t="n"/>
     </row>
@@ -1470,13 +1470,13 @@
       </c>
       <c r="B58" s="7" t="n"/>
       <c r="C58" s="7" t="n"/>
-      <c r="D58" s="7" t="n"/>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E58" s="7" t="n"/>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C59" s="7" t="n"/>
@@ -1500,13 +1500,13 @@
       <c r="A60" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+      <c r="B60" s="7" t="n"/>
       <c r="C60" s="7" t="n"/>
-      <c r="D60" s="7" t="n"/>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E60" s="7" t="n"/>
       <c r="F60" s="7" t="n"/>
       <c r="G60" s="7" t="n"/>
@@ -1516,25 +1516,25 @@
       <c r="A61" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
       <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
-      <c r="F61" s="7" t="n"/>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G61" s="7" t="n"/>
       <c r="H61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C62" s="7" t="n"/>
@@ -1546,15 +1546,15 @@
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B63" s="7" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C63" s="7" t="n"/>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D63" s="7" t="n"/>
       <c r="E63" s="7" t="n"/>
       <c r="F63" s="7" t="n"/>
       <c r="G63" s="7" t="n"/>
@@ -1562,13 +1562,13 @@
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B64" s="7" t="n"/>
       <c r="C64" s="7" t="n"/>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E64" s="7" t="n"/>
@@ -1580,13 +1580,13 @@
       <c r="A65" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+      <c r="B65" s="7" t="n"/>
       <c r="C65" s="7" t="n"/>
-      <c r="D65" s="7" t="n"/>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E65" s="7" t="n"/>
       <c r="F65" s="7" t="n"/>
       <c r="G65" s="7" t="n"/>
@@ -1596,17 +1596,17 @@
       <c r="A66" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B66" s="7" t="n"/>
       <c r="C66" s="7" t="n"/>
       <c r="D66" s="7" t="n"/>
       <c r="E66" s="7" t="n"/>
       <c r="F66" s="7" t="n"/>
       <c r="G66" s="7" t="n"/>
-      <c r="H66" s="7" t="n"/>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
@@ -1614,15 +1614,15 @@
       </c>
       <c r="B67" s="7" t="n"/>
       <c r="C67" s="7" t="n"/>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D67" s="7" t="n"/>
       <c r="E67" s="7" t="n"/>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
-      <c r="H67" s="7" t="n"/>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
@@ -1630,63 +1630,63 @@
       </c>
       <c r="B68" s="7" t="n"/>
       <c r="C68" s="7" t="n"/>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D68" s="7" t="n"/>
       <c r="E68" s="7" t="n"/>
       <c r="F68" s="7" t="n"/>
       <c r="G68" s="7" t="n"/>
-      <c r="H68" s="7" t="n"/>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B69" s="7" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C69" s="7" t="n"/>
       <c r="D69" s="7" t="n"/>
       <c r="E69" s="7" t="n"/>
       <c r="F69" s="7" t="n"/>
       <c r="G69" s="7" t="n"/>
-      <c r="H69" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B70" s="7" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C70" s="7" t="n"/>
       <c r="D70" s="7" t="n"/>
       <c r="E70" s="7" t="n"/>
       <c r="F70" s="7" t="n"/>
       <c r="G70" s="7" t="n"/>
-      <c r="H70" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B71" s="7" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
       <c r="C71" s="7" t="n"/>
       <c r="D71" s="7" t="n"/>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
-      <c r="H71" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H71" s="7" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C72" s="7" t="n"/>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C75" s="7" t="n"/>
@@ -1756,13 +1756,13 @@
       <c r="A76" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+      <c r="B76" s="7" t="n"/>
       <c r="C76" s="7" t="n"/>
-      <c r="D76" s="7" t="n"/>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E76" s="7" t="n"/>
       <c r="F76" s="7" t="n"/>
       <c r="G76" s="7" t="n"/>
@@ -1776,7 +1776,7 @@
       <c r="C77" s="7" t="n"/>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E77" s="7" t="n"/>
@@ -1792,7 +1792,7 @@
       <c r="C78" s="7" t="n"/>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E78" s="7" t="n"/>
@@ -1808,7 +1808,7 @@
       <c r="C79" s="7" t="n"/>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E79" s="7" t="n"/>
@@ -1818,15 +1818,15 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B80" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C80" s="7" t="n"/>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>Jameson Williams</t>
-        </is>
-      </c>
+      <c r="D80" s="7" t="n"/>
       <c r="E80" s="7" t="n"/>
       <c r="F80" s="7" t="n"/>
       <c r="G80" s="7" t="n"/>
@@ -1834,15 +1834,15 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B81" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>Jonathon Brooks</t>
+        </is>
+      </c>
       <c r="C81" s="7" t="n"/>
-      <c r="D81" s="7" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D81" s="7" t="n"/>
       <c r="E81" s="7" t="n"/>
       <c r="F81" s="7" t="n"/>
       <c r="G81" s="7" t="n"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C82" s="7" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="C83" s="7" t="n"/>
@@ -1884,13 +1884,13 @@
       <c r="A84" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>Mike Washington Jr.</t>
-        </is>
-      </c>
+      <c r="B84" s="7" t="n"/>
       <c r="C84" s="7" t="n"/>
-      <c r="D84" s="7" t="n"/>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E84" s="7" t="n"/>
       <c r="F84" s="7" t="n"/>
       <c r="G84" s="7" t="n"/>
@@ -2154,13 +2154,13 @@
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B101" s="7" t="n"/>
       <c r="C101" s="7" t="n"/>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E101" s="7" t="n"/>
@@ -2172,13 +2172,13 @@
       <c r="A102" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B102" s="7" t="n"/>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>Rachaad White</t>
+        </is>
+      </c>
       <c r="C102" s="7" t="n"/>
-      <c r="D102" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Reed</t>
-        </is>
-      </c>
+      <c r="D102" s="7" t="n"/>
       <c r="E102" s="7" t="n"/>
       <c r="F102" s="7" t="n"/>
       <c r="G102" s="7" t="n"/>
@@ -2192,7 +2192,7 @@
       <c r="C103" s="7" t="n"/>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E103" s="7" t="n"/>
@@ -2208,7 +2208,7 @@
       <c r="C104" s="7" t="n"/>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E104" s="7" t="n"/>
@@ -2218,15 +2218,15 @@
     </row>
     <row r="105">
       <c r="A105" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B105" s="7" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B105" s="7" t="n"/>
       <c r="C105" s="7" t="n"/>
-      <c r="D105" s="7" t="n"/>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>Jordyn Tyson</t>
+        </is>
+      </c>
       <c r="E105" s="7" t="n"/>
       <c r="F105" s="7" t="n"/>
       <c r="G105" s="7" t="n"/>
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 9; 13 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 10; 11 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 74 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 75 players moved.</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -618,7 +618,7 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
@@ -636,13 +636,13 @@
       <c r="A6" s="6" t="n">
         <v>62</v>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+      <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="7" t="n"/>
       <c r="G6" s="7" t="n"/>
@@ -652,13 +652,13 @@
       <c r="A7" s="6" t="n">
         <v>61</v>
       </c>
-      <c r="B7" s="7" t="n"/>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="7" t="n"/>
@@ -714,7 +714,7 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
@@ -778,7 +778,7 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
@@ -876,13 +876,13 @@
       <c r="A21" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+      <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
@@ -892,13 +892,13 @@
       <c r="A22" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="B22" s="7" t="n"/>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
@@ -1034,15 +1034,15 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="B31" s="7" t="n"/>
+        <v>24</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D31" s="7" t="n"/>
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="7" t="n"/>
       <c r="G31" s="7" t="n"/>
@@ -1052,13 +1052,13 @@
       <c r="A32" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+      <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
@@ -1114,13 +1114,13 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E36" s="7" t="n"/>
@@ -1136,7 +1136,7 @@
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E37" s="7" t="n"/>
@@ -1162,7 +1162,7 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
@@ -1210,17 +1210,17 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B42" s="7" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C42" s="7" t="n"/>
       <c r="D42" s="7" t="n"/>
       <c r="E42" s="7" t="n"/>
-      <c r="F42" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F42" s="7" t="n"/>
       <c r="G42" s="7" t="n"/>
       <c r="H42" s="7" t="n"/>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="C43" s="7" t="n"/>
@@ -1324,25 +1324,25 @@
       <c r="A49" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+      <c r="B49" s="7" t="n"/>
       <c r="C49" s="7" t="n"/>
       <c r="D49" s="7" t="n"/>
       <c r="E49" s="7" t="n"/>
-      <c r="F49" s="7" t="n"/>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G49" s="7" t="n"/>
       <c r="H49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C50" s="7" t="n"/>
@@ -1354,17 +1354,17 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B51" s="7" t="n"/>
       <c r="C51" s="7" t="n"/>
-      <c r="D51" s="7" t="n"/>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E51" s="7" t="n"/>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F51" s="7" t="n"/>
       <c r="G51" s="7" t="n"/>
       <c r="H51" s="7" t="n"/>
     </row>
@@ -1372,15 +1372,15 @@
       <c r="A52" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B52" s="7" t="n"/>
       <c r="C52" s="7" t="n"/>
       <c r="D52" s="7" t="n"/>
       <c r="E52" s="7" t="n"/>
-      <c r="F52" s="7" t="n"/>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G52" s="7" t="n"/>
       <c r="H52" s="7" t="n"/>
     </row>
@@ -1388,29 +1388,29 @@
       <c r="A53" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+      <c r="B53" s="7" t="n"/>
       <c r="C53" s="7" t="n"/>
       <c r="D53" s="7" t="n"/>
       <c r="E53" s="7" t="n"/>
       <c r="F53" s="7" t="n"/>
       <c r="G53" s="7" t="n"/>
-      <c r="H53" s="7" t="n"/>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B54" s="7" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C54" s="7" t="n"/>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D54" s="7" t="n"/>
       <c r="E54" s="7" t="n"/>
       <c r="F54" s="7" t="n"/>
       <c r="G54" s="7" t="n"/>
@@ -1418,35 +1418,35 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B55" s="7" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C55" s="7" t="n"/>
       <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F55" s="7" t="n"/>
       <c r="G55" s="7" t="n"/>
       <c r="H55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B56" s="7" t="n"/>
       <c r="C56" s="7" t="n"/>
-      <c r="D56" s="7" t="n"/>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="n"/>
-      <c r="H56" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
@@ -1456,7 +1456,7 @@
       <c r="C57" s="7" t="n"/>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E57" s="7" t="n"/>
@@ -1470,13 +1470,13 @@
       </c>
       <c r="B58" s="7" t="n"/>
       <c r="C58" s="7" t="n"/>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
-      <c r="F58" s="7" t="n"/>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C59" s="7" t="n"/>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C62" s="7" t="n"/>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C63" s="7" t="n"/>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C70" s="7" t="n"/>
@@ -1676,13 +1676,13 @@
       <c r="A71" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+      <c r="B71" s="7" t="n"/>
       <c r="C71" s="7" t="n"/>
-      <c r="D71" s="7" t="n"/>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
@@ -1692,29 +1692,29 @@
       <c r="A72" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+      <c r="B72" s="7" t="n"/>
       <c r="C72" s="7" t="n"/>
       <c r="D72" s="7" t="n"/>
       <c r="E72" s="7" t="n"/>
-      <c r="F72" s="7" t="n"/>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G72" s="7" t="n"/>
       <c r="H72" s="7" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B73" s="7" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C73" s="7" t="n"/>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>Brian Thomas Jr.</t>
-        </is>
-      </c>
+      <c r="D73" s="7" t="n"/>
       <c r="E73" s="7" t="n"/>
       <c r="F73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
@@ -1722,17 +1722,17 @@
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B74" s="7" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C74" s="7" t="n"/>
       <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
-      <c r="F74" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
       <c r="H74" s="7" t="n"/>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="C75" s="7" t="n"/>
@@ -1760,7 +1760,7 @@
       <c r="C76" s="7" t="n"/>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E76" s="7" t="n"/>
@@ -1776,7 +1776,7 @@
       <c r="C77" s="7" t="n"/>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E77" s="7" t="n"/>
@@ -1792,7 +1792,7 @@
       <c r="C78" s="7" t="n"/>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E78" s="7" t="n"/>
@@ -1808,7 +1808,7 @@
       <c r="C79" s="7" t="n"/>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E79" s="7" t="n"/>
@@ -1818,15 +1818,15 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B80" s="7" t="n"/>
       <c r="C80" s="7" t="n"/>
-      <c r="D80" s="7" t="n"/>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>Marvin Harrison Jr.</t>
+        </is>
+      </c>
       <c r="E80" s="7" t="n"/>
       <c r="F80" s="7" t="n"/>
       <c r="G80" s="7" t="n"/>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C81" s="7" t="n"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C82" s="7" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Woody Marks</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C83" s="7" t="n"/>
@@ -1884,13 +1884,13 @@
       <c r="A84" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B84" s="7" t="n"/>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>Mike Washington Jr.</t>
+        </is>
+      </c>
       <c r="C84" s="7" t="n"/>
-      <c r="D84" s="7" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D84" s="7" t="n"/>
       <c r="E84" s="7" t="n"/>
       <c r="F84" s="7" t="n"/>
       <c r="G84" s="7" t="n"/>
@@ -2140,13 +2140,13 @@
       <c r="A100" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B100" s="7" t="n"/>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>Rachaad White</t>
+        </is>
+      </c>
       <c r="C100" s="7" t="n"/>
-      <c r="D100" s="7" t="inlineStr">
-        <is>
-          <t>Carnell Tate</t>
-        </is>
-      </c>
+      <c r="D100" s="7" t="n"/>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="7" t="n"/>
       <c r="G100" s="7" t="n"/>
@@ -2160,7 +2160,7 @@
       <c r="C101" s="7" t="n"/>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E101" s="7" t="n"/>
@@ -2172,13 +2172,13 @@
       <c r="A102" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B102" s="7" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
+      <c r="B102" s="7" t="n"/>
       <c r="C102" s="7" t="n"/>
-      <c r="D102" s="7" t="n"/>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>KC Concepcion</t>
+        </is>
+      </c>
       <c r="E102" s="7" t="n"/>
       <c r="F102" s="7" t="n"/>
       <c r="G102" s="7" t="n"/>
@@ -2192,7 +2192,7 @@
       <c r="C103" s="7" t="n"/>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E103" s="7" t="n"/>
@@ -2208,7 +2208,7 @@
       <c r="C104" s="7" t="n"/>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E104" s="7" t="n"/>
@@ -2224,7 +2224,7 @@
       <c r="C105" s="7" t="n"/>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E105" s="7" t="n"/>
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 10; 11 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 11; 11 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 75 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 74 players moved.</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.6, WR 3.0, TE 4.5, QB 0.0.</t>
+          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.5, WR 3.0, TE 4.5, QB 0.0.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 62-&gt;53, Chris Olave 41-&gt;32, Puka Nacua 69-&gt;61, Ja'Marr Chase 60-&gt;52, Trey McBride 43.4286-&gt;36, Amon-Ra St. Brown 63-&gt;56, Justin Jefferson 46-&gt;39, CeeDee Lamb 48-&gt;41</t>
+          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 62-&gt;53, Chris Olave 41-&gt;32, Puka Nacua 70-&gt;62, Ja'Marr Chase 60-&gt;52, Trey McBride 43.4286-&gt;36, Amon-Ra St. Brown 64-&gt;57, Justin Jefferson 47-&gt;40, Chase Brown 46-&gt;39</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -634,7 +634,7 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
@@ -666,11 +666,11 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>James Cook III</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C8" s="7" t="n"/>
@@ -682,11 +682,11 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>James Cook III</t>
         </is>
       </c>
       <c r="C9" s="7" t="n"/>
@@ -698,7 +698,7 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
@@ -732,13 +732,13 @@
       <c r="A12" s="6" t="n">
         <v>54</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+      <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Jaxon Smith-Njigba</t>
+        </is>
+      </c>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="n"/>
@@ -752,7 +752,7 @@
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E13" s="7" t="n"/>
@@ -764,13 +764,13 @@
       <c r="A14" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="B14" s="7" t="n"/>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D14" s="7" t="n"/>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
@@ -778,7 +778,7 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
@@ -826,15 +826,15 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
@@ -842,13 +842,13 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>CeeDee Lamb</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E19" s="7" t="n"/>
@@ -860,13 +860,13 @@
       <c r="A20" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="B20" s="7" t="n"/>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
@@ -876,13 +876,13 @@
       <c r="A21" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="B21" s="7" t="n"/>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
@@ -890,15 +890,15 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
@@ -906,11 +906,11 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C23" s="7" t="n"/>
@@ -922,7 +922,7 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
@@ -940,13 +940,13 @@
       <c r="A25" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+      <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E25" s="7" t="n"/>
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
@@ -986,15 +986,15 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B28" s="7" t="n"/>
+        <v>31</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D28" s="7" t="n"/>
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="7" t="n"/>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
@@ -1050,19 +1050,19 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
-      <c r="H32" s="7" t="n"/>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
@@ -1070,19 +1070,19 @@
       </c>
       <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="n"/>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
@@ -1114,13 +1114,13 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E36" s="7" t="n"/>
@@ -1136,7 +1136,7 @@
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E37" s="7" t="n"/>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
@@ -1226,17 +1226,17 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B43" s="7" t="n"/>
       <c r="C43" s="7" t="n"/>
       <c r="D43" s="7" t="n"/>
       <c r="E43" s="7" t="n"/>
-      <c r="F43" s="7" t="n"/>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G43" s="7" t="n"/>
       <c r="H43" s="7" t="n"/>
     </row>
@@ -1244,13 +1244,13 @@
       <c r="A44" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B44" s="7" t="n"/>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D44" s="7" t="n"/>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="7" t="n"/>
@@ -1260,13 +1260,13 @@
       <c r="A45" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B45" s="7" t="n"/>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D45" s="7" t="n"/>
       <c r="E45" s="7" t="n"/>
       <c r="F45" s="7" t="n"/>
       <c r="G45" s="7" t="n"/>
@@ -1276,13 +1276,13 @@
       <c r="A46" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B46" s="7" t="n"/>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D46" s="7" t="n"/>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="7" t="n"/>
@@ -1290,15 +1290,15 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="n"/>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E47" s="7" t="n"/>
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="7" t="n"/>
@@ -1306,15 +1306,15 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B48" s="7" t="n"/>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="n"/>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
@@ -1322,47 +1322,47 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B49" s="7" t="n"/>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="n"/>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E49" s="7" t="n"/>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n"/>
       <c r="H49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B50" s="7" t="n"/>
       <c r="C50" s="7" t="n"/>
       <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
-      <c r="F50" s="7" t="n"/>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G50" s="7" t="n"/>
       <c r="H50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B51" s="7" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C51" s="7" t="n"/>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
       <c r="F51" s="7" t="n"/>
       <c r="G51" s="7" t="n"/>
@@ -1372,15 +1372,15 @@
       <c r="A52" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B52" s="7" t="n"/>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C52" s="7" t="n"/>
       <c r="D52" s="7" t="n"/>
       <c r="E52" s="7" t="n"/>
-      <c r="F52" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F52" s="7" t="n"/>
       <c r="G52" s="7" t="n"/>
       <c r="H52" s="7" t="n"/>
     </row>
@@ -1388,29 +1388,29 @@
       <c r="A53" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B53" s="7" t="n"/>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C53" s="7" t="n"/>
       <c r="D53" s="7" t="n"/>
       <c r="E53" s="7" t="n"/>
       <c r="F53" s="7" t="n"/>
       <c r="G53" s="7" t="n"/>
-      <c r="H53" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
-      <c r="D54" s="7" t="n"/>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E54" s="7" t="n"/>
       <c r="F54" s="7" t="n"/>
       <c r="G54" s="7" t="n"/>
@@ -1418,47 +1418,47 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B55" s="7" t="n"/>
       <c r="C55" s="7" t="n"/>
       <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7" t="n"/>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G55" s="7" t="n"/>
       <c r="H55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B56" s="7" t="n"/>
       <c r="C56" s="7" t="n"/>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D56" s="7" t="n"/>
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="n"/>
-      <c r="H56" s="7" t="n"/>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B57" s="7" t="n"/>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C57" s="7" t="n"/>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
       <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
@@ -1470,27 +1470,27 @@
       </c>
       <c r="B58" s="7" t="n"/>
       <c r="C58" s="7" t="n"/>
-      <c r="D58" s="7" t="n"/>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E58" s="7" t="n"/>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B59" s="7" t="n"/>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="7" t="n"/>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E59" s="7" t="n"/>
       <c r="F59" s="7" t="n"/>
       <c r="G59" s="7" t="n"/>
@@ -1498,7 +1498,7 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B60" s="7" t="n"/>
       <c r="C60" s="7" t="n"/>
@@ -1676,13 +1676,13 @@
       <c r="A71" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B71" s="7" t="n"/>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C71" s="7" t="n"/>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>Brian Thomas Jr.</t>
-        </is>
-      </c>
+      <c r="D71" s="7" t="n"/>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
@@ -1694,29 +1694,29 @@
       </c>
       <c r="B72" s="7" t="n"/>
       <c r="C72" s="7" t="n"/>
-      <c r="D72" s="7" t="n"/>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E72" s="7" t="n"/>
-      <c r="F72" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F72" s="7" t="n"/>
       <c r="G72" s="7" t="n"/>
       <c r="H72" s="7" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B73" s="7" t="n"/>
       <c r="C73" s="7" t="n"/>
       <c r="D73" s="7" t="n"/>
       <c r="E73" s="7" t="n"/>
-      <c r="F73" s="7" t="n"/>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G73" s="7" t="n"/>
       <c r="H73" s="7" t="n"/>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>Woody Marks</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C75" s="7" t="n"/>
@@ -1776,7 +1776,7 @@
       <c r="C77" s="7" t="n"/>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E77" s="7" t="n"/>
@@ -1792,7 +1792,7 @@
       <c r="C78" s="7" t="n"/>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E78" s="7" t="n"/>
@@ -1808,7 +1808,7 @@
       <c r="C79" s="7" t="n"/>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E79" s="7" t="n"/>
@@ -1818,15 +1818,15 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B80" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C80" s="7" t="n"/>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D80" s="7" t="n"/>
       <c r="E80" s="7" t="n"/>
       <c r="F80" s="7" t="n"/>
       <c r="G80" s="7" t="n"/>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C81" s="7" t="n"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C82" s="7" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C83" s="7" t="n"/>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C84" s="7" t="n"/>
@@ -1900,13 +1900,13 @@
       <c r="A85" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B85" s="7" t="n"/>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>J.K. Dobbins</t>
+        </is>
+      </c>
       <c r="C85" s="7" t="n"/>
-      <c r="D85" s="7" t="inlineStr">
-        <is>
-          <t>De'Zhaun Stribling</t>
-        </is>
-      </c>
+      <c r="D85" s="7" t="n"/>
       <c r="E85" s="7" t="n"/>
       <c r="F85" s="7" t="n"/>
       <c r="G85" s="7" t="n"/>
@@ -1916,13 +1916,13 @@
       <c r="A86" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B86" s="7" t="n"/>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C86" s="7" t="n"/>
-      <c r="D86" s="7" t="inlineStr">
-        <is>
-          <t>Quentin Johnston</t>
-        </is>
-      </c>
+      <c r="D86" s="7" t="n"/>
       <c r="E86" s="7" t="n"/>
       <c r="F86" s="7" t="n"/>
       <c r="G86" s="7" t="n"/>
@@ -1930,11 +1930,11 @@
     </row>
     <row r="87">
       <c r="A87" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="C87" s="7" t="n"/>
@@ -1946,15 +1946,15 @@
     </row>
     <row r="88">
       <c r="A88" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B88" s="7" t="inlineStr">
-        <is>
-          <t>Rico Dowdle</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B88" s="7" t="n"/>
       <c r="C88" s="7" t="n"/>
-      <c r="D88" s="7" t="n"/>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E88" s="7" t="n"/>
       <c r="F88" s="7" t="n"/>
       <c r="G88" s="7" t="n"/>
@@ -1962,15 +1962,15 @@
     </row>
     <row r="89">
       <c r="A89" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B89" s="7" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B89" s="7" t="n"/>
       <c r="C89" s="7" t="n"/>
-      <c r="D89" s="7" t="n"/>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>De'Zhaun Stribling</t>
+        </is>
+      </c>
       <c r="E89" s="7" t="n"/>
       <c r="F89" s="7" t="n"/>
       <c r="G89" s="7" t="n"/>
@@ -1978,15 +1978,15 @@
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B90" s="7" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B90" s="7" t="n"/>
       <c r="C90" s="7" t="n"/>
-      <c r="D90" s="7" t="n"/>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>Quentin Johnston</t>
+        </is>
+      </c>
       <c r="E90" s="7" t="n"/>
       <c r="F90" s="7" t="n"/>
       <c r="G90" s="7" t="n"/>
@@ -1994,13 +1994,13 @@
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B91" s="7" t="n"/>
       <c r="C91" s="7" t="n"/>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E91" s="7" t="n"/>
@@ -2010,67 +2010,67 @@
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B92" s="7" t="n"/>
       <c r="C92" s="7" t="n"/>
-      <c r="D92" s="7" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D92" s="7" t="n"/>
       <c r="E92" s="7" t="n"/>
-      <c r="F92" s="7" t="n"/>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G92" s="7" t="n"/>
       <c r="H92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B93" s="7" t="n"/>
       <c r="C93" s="7" t="n"/>
-      <c r="D93" s="7" t="inlineStr">
-        <is>
-          <t>Chris Godwin Jr.</t>
-        </is>
-      </c>
+      <c r="D93" s="7" t="n"/>
       <c r="E93" s="7" t="n"/>
       <c r="F93" s="7" t="n"/>
       <c r="G93" s="7" t="n"/>
-      <c r="H93" s="7" t="n"/>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>Jalen Hurts</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B94" s="7" t="n"/>
       <c r="C94" s="7" t="n"/>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
+      <c r="D94" s="7" t="n"/>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="7" t="n"/>
       <c r="G94" s="7" t="n"/>
-      <c r="H94" s="7" t="n"/>
+      <c r="H94" s="7" t="inlineStr">
+        <is>
+          <t>Justin Herbert</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B95" s="7" t="n"/>
       <c r="C95" s="7" t="n"/>
       <c r="D95" s="7" t="n"/>
       <c r="E95" s="7" t="n"/>
-      <c r="F95" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F95" s="7" t="n"/>
       <c r="G95" s="7" t="n"/>
-      <c r="H95" s="7" t="n"/>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
@@ -2078,15 +2078,15 @@
       </c>
       <c r="B96" s="7" t="n"/>
       <c r="C96" s="7" t="n"/>
-      <c r="D96" s="7" t="n"/>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>Terry McLaurin</t>
+        </is>
+      </c>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="7" t="n"/>
       <c r="G96" s="7" t="n"/>
-      <c r="H96" s="7" t="inlineStr">
-        <is>
-          <t>Jalen Hurts</t>
-        </is>
-      </c>
+      <c r="H96" s="7" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
@@ -2094,15 +2094,15 @@
       </c>
       <c r="B97" s="7" t="n"/>
       <c r="C97" s="7" t="n"/>
-      <c r="D97" s="7" t="n"/>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="7" t="n"/>
       <c r="G97" s="7" t="n"/>
-      <c r="H97" s="7" t="inlineStr">
-        <is>
-          <t>Justin Herbert</t>
-        </is>
-      </c>
+      <c r="H97" s="7" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
@@ -2110,15 +2110,15 @@
       </c>
       <c r="B98" s="7" t="n"/>
       <c r="C98" s="7" t="n"/>
-      <c r="D98" s="7" t="n"/>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E98" s="7" t="n"/>
       <c r="F98" s="7" t="n"/>
       <c r="G98" s="7" t="n"/>
-      <c r="H98" s="7" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H98" s="7" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
@@ -2295,7 +2295,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 76.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 75.</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 11; 11 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 12; 11 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,14 +2333,14 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 74 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 71 players moved.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   No projection this week (value kept): Saquon Barkley, Breece Hall, DeVonta Smith, Rashee Rice, Lamar Jackson, Travis Etienne Jr., Jadarian Price, Josh Jacobs, De'Zhaun Stribling, Jordan Mason, Alec Pierce, Brian Thomas Jr., Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Jaxson Dart, Ja'Kobi Lane.</t>
+          <t xml:space="preserve">   No projection this week (value kept): Saquon Barkley, Breece Hall, DeVonta Smith, Rashee Rice, Lamar Jackson, Travis Etienne Jr., Jadarian Price, Josh Jacobs, De'Zhaun Stribling, Jordan Mason, Alec Pierce, Brian Thomas Jr., Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Jaxson Dart, Ja'Kobi Lane.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 62-&gt;53, Chris Olave 41-&gt;32, Puka Nacua 70-&gt;62, Ja'Marr Chase 60-&gt;52, Trey McBride 43.4286-&gt;36, Amon-Ra St. Brown 64-&gt;57, Justin Jefferson 47-&gt;40, Chase Brown 46-&gt;39</t>
+          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 62-&gt;54, Chris Olave 41-&gt;33, Trey McBride 42.8571-&gt;35, Puka Nacua 70-&gt;63, Ja'Marr Chase 60-&gt;53, Justin Jefferson 47-&gt;40, DeVonta Smith 27-&gt;20, Rashee Rice 26-&gt;19</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -938,7 +938,7 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
@@ -1082,13 +1082,13 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E34" s="7" t="n"/>
@@ -1104,7 +1104,7 @@
       <c r="C35" s="7" t="n"/>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E35" s="7" t="n"/>
@@ -1120,7 +1120,7 @@
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E36" s="7" t="n"/>
@@ -1338,17 +1338,17 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B50" s="7" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C50" s="7" t="n"/>
       <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F50" s="7" t="n"/>
       <c r="G50" s="7" t="n"/>
       <c r="H50" s="7" t="n"/>
     </row>
@@ -1356,15 +1356,15 @@
       <c r="A51" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+      <c r="B51" s="7" t="n"/>
       <c r="C51" s="7" t="n"/>
       <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
-      <c r="F51" s="7" t="n"/>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G51" s="7" t="n"/>
       <c r="H51" s="7" t="n"/>
     </row>
@@ -1932,13 +1932,13 @@
       <c r="A87" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B87" s="7" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+      <c r="B87" s="7" t="n"/>
       <c r="C87" s="7" t="n"/>
-      <c r="D87" s="7" t="n"/>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>Terry McLaurin</t>
+        </is>
+      </c>
       <c r="E87" s="7" t="n"/>
       <c r="F87" s="7" t="n"/>
       <c r="G87" s="7" t="n"/>
@@ -2076,13 +2076,13 @@
       <c r="A96" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B96" s="7" t="n"/>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C96" s="7" t="n"/>
-      <c r="D96" s="7" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D96" s="7" t="n"/>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="7" t="n"/>
       <c r="G96" s="7" t="n"/>
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 12; 11 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 13; 11 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 71 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 73 players moved.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 62-&gt;54, Chris Olave 41-&gt;33, Trey McBride 42.8571-&gt;35, Puka Nacua 70-&gt;63, Ja'Marr Chase 60-&gt;53, Justin Jefferson 47-&gt;40, DeVonta Smith 27-&gt;20, Rashee Rice 26-&gt;19</t>
+          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 62-&gt;54, Chris Olave 42-&gt;34, Trey McBride 42.8571-&gt;35, Puka Nacua 70-&gt;63, Ja'Marr Chase 60-&gt;53, Justin Jefferson 47-&gt;40, DeVonta Smith 27-&gt;20, Rashee Rice 26-&gt;19</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Jahmyr Gibbs</t>
+          <t>Bijan Robinson</t>
         </is>
       </c>
       <c r="C4" s="7" t="n"/>
@@ -618,11 +618,11 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Bijan Robinson</t>
+          <t>Jahmyr Gibbs</t>
         </is>
       </c>
       <c r="C5" s="7" t="n"/>
@@ -634,15 +634,15 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>63</v>
-      </c>
-      <c r="B6" s="7" t="n"/>
+        <v>65</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="7" t="n"/>
       <c r="G6" s="7" t="n"/>
@@ -650,15 +650,15 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>62</v>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="B7" s="7" t="n"/>
       <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="7" t="n"/>
@@ -666,7 +666,7 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
@@ -682,11 +682,11 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>James Cook III</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C9" s="7" t="n"/>
@@ -698,11 +698,11 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>James Cook III</t>
         </is>
       </c>
       <c r="C10" s="7" t="n"/>
@@ -714,13 +714,13 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -730,13 +730,13 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E12" s="7" t="n"/>
@@ -746,13 +746,13 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="E13" s="7" t="n"/>
@@ -762,11 +762,11 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="C14" s="7" t="n"/>
@@ -778,11 +778,11 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Saquon Barkley</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="C15" s="7" t="n"/>
@@ -794,15 +794,15 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
@@ -810,31 +810,31 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="B17" s="7" t="n"/>
+        <v>47</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C17" s="7" t="n"/>
       <c r="D17" s="7" t="n"/>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>43</v>
-      </c>
-      <c r="B18" s="7" t="n"/>
+        <v>46</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
@@ -842,15 +842,15 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="B19" s="7" t="n"/>
+        <v>44</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
@@ -858,11 +858,11 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C20" s="7" t="n"/>
@@ -874,29 +874,29 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
       <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Justin Jefferson</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="E22" s="7" t="n"/>
@@ -908,13 +908,13 @@
       <c r="A23" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+      <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
@@ -922,31 +922,31 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="B24" s="7" t="n"/>
+        <v>36</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="B25" s="7" t="n"/>
+        <v>35</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
@@ -954,7 +954,7 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
@@ -962,7 +962,7 @@
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>Brock Bowers</t>
+          <t>Trey McBride</t>
         </is>
       </c>
       <c r="G26" s="7" t="n"/>
@@ -970,15 +970,15 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
@@ -986,23 +986,23 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
       <c r="D28" s="7" t="n"/>
       <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G28" s="7" t="n"/>
       <c r="H28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
@@ -1034,15 +1034,15 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="7" t="n"/>
       <c r="G31" s="7" t="n"/>
@@ -1052,43 +1052,43 @@
       <c r="A32" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="B32" s="7" t="n"/>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C32" s="7" t="n"/>
       <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D33" s="7" t="n"/>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
-      <c r="H33" s="7" t="n"/>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E34" s="7" t="n"/>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
@@ -1114,13 +1114,13 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E36" s="7" t="n"/>
@@ -1130,13 +1130,13 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E37" s="7" t="n"/>
@@ -1146,13 +1146,13 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E38" s="7" t="n"/>
@@ -1162,7 +1162,7 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
@@ -1178,15 +1178,15 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="n"/>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
@@ -1210,11 +1210,11 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C42" s="7" t="n"/>
@@ -1226,27 +1226,27 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B43" s="7" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C43" s="7" t="n"/>
       <c r="D43" s="7" t="n"/>
       <c r="E43" s="7" t="n"/>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F43" s="7" t="n"/>
       <c r="G43" s="7" t="n"/>
       <c r="H43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C44" s="7" t="n"/>
@@ -1258,11 +1258,11 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="C45" s="7" t="n"/>
@@ -1274,11 +1274,11 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="C46" s="7" t="n"/>
@@ -1290,15 +1290,15 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B47" s="7" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D47" s="7" t="n"/>
       <c r="E47" s="7" t="n"/>
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="7" t="n"/>
@@ -1306,15 +1306,15 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B48" s="7" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D48" s="7" t="n"/>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
@@ -1322,13 +1322,13 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B49" s="7" t="n"/>
       <c r="C49" s="7" t="n"/>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E49" s="7" t="n"/>
@@ -1338,15 +1338,15 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B50" s="7" t="n"/>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="n"/>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E50" s="7" t="n"/>
       <c r="F50" s="7" t="n"/>
       <c r="G50" s="7" t="n"/>
@@ -1354,81 +1354,81 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B51" s="7" t="n"/>
       <c r="C51" s="7" t="n"/>
-      <c r="D51" s="7" t="n"/>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E51" s="7" t="n"/>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F51" s="7" t="n"/>
       <c r="G51" s="7" t="n"/>
       <c r="H51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B52" s="7" t="n"/>
       <c r="C52" s="7" t="n"/>
       <c r="D52" s="7" t="n"/>
       <c r="E52" s="7" t="n"/>
-      <c r="F52" s="7" t="n"/>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G52" s="7" t="n"/>
       <c r="H52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B53" s="7" t="n"/>
       <c r="C53" s="7" t="n"/>
       <c r="D53" s="7" t="n"/>
       <c r="E53" s="7" t="n"/>
-      <c r="F53" s="7" t="n"/>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G53" s="7" t="n"/>
       <c r="H53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D54" s="7" t="n"/>
       <c r="E54" s="7" t="n"/>
       <c r="F54" s="7" t="n"/>
       <c r="G54" s="7" t="n"/>
-      <c r="H54" s="7" t="n"/>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B55" s="7" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C55" s="7" t="n"/>
       <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F55" s="7" t="n"/>
       <c r="G55" s="7" t="n"/>
       <c r="H55" s="7" t="n"/>
     </row>
@@ -1438,27 +1438,27 @@
       </c>
       <c r="B56" s="7" t="n"/>
       <c r="C56" s="7" t="n"/>
-      <c r="D56" s="7" t="n"/>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="n"/>
-      <c r="H56" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B57" s="7" t="n"/>
       <c r="C57" s="7" t="n"/>
-      <c r="D57" s="7" t="n"/>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E57" s="7" t="n"/>
       <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
@@ -1466,13 +1466,13 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B58" s="7" t="n"/>
       <c r="C58" s="7" t="n"/>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="E58" s="7" t="n"/>
@@ -1482,17 +1482,17 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B59" s="7" t="n"/>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
-      <c r="F59" s="7" t="n"/>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G59" s="7" t="n"/>
       <c r="H59" s="7" t="n"/>
     </row>
@@ -1500,13 +1500,13 @@
       <c r="A60" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B60" s="7" t="n"/>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C60" s="7" t="n"/>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D60" s="7" t="n"/>
       <c r="E60" s="7" t="n"/>
       <c r="F60" s="7" t="n"/>
       <c r="G60" s="7" t="n"/>
@@ -1516,29 +1516,29 @@
       <c r="A61" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B61" s="7" t="n"/>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C61" s="7" t="n"/>
       <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
       <c r="H61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B62" s="7" t="n"/>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="n"/>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="7" t="n"/>
@@ -1546,15 +1546,15 @@
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B63" s="7" t="n"/>
       <c r="C63" s="7" t="n"/>
-      <c r="D63" s="7" t="n"/>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E63" s="7" t="n"/>
       <c r="F63" s="7" t="n"/>
       <c r="G63" s="7" t="n"/>
@@ -1562,13 +1562,13 @@
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B64" s="7" t="n"/>
       <c r="C64" s="7" t="n"/>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E64" s="7" t="n"/>
@@ -1578,13 +1578,13 @@
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B65" s="7" t="n"/>
       <c r="C65" s="7" t="n"/>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E65" s="7" t="n"/>
@@ -1594,59 +1594,59 @@
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B66" s="7" t="n"/>
       <c r="C66" s="7" t="n"/>
       <c r="D66" s="7" t="n"/>
       <c r="E66" s="7" t="n"/>
-      <c r="F66" s="7" t="n"/>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G66" s="7" t="n"/>
-      <c r="H66" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B67" s="7" t="n"/>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C67" s="7" t="n"/>
       <c r="D67" s="7" t="n"/>
       <c r="E67" s="7" t="n"/>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
-      <c r="H67" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B68" s="7" t="n"/>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C68" s="7" t="n"/>
       <c r="D68" s="7" t="n"/>
       <c r="E68" s="7" t="n"/>
       <c r="F68" s="7" t="n"/>
       <c r="G68" s="7" t="n"/>
-      <c r="H68" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C69" s="7" t="n"/>
@@ -1658,15 +1658,15 @@
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B70" s="7" t="n"/>
       <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="n"/>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>De'Zhaun Stribling</t>
+        </is>
+      </c>
       <c r="E70" s="7" t="n"/>
       <c r="F70" s="7" t="n"/>
       <c r="G70" s="7" t="n"/>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>Woody Marks</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C71" s="7" t="n"/>
@@ -1692,13 +1692,13 @@
       <c r="A72" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B72" s="7" t="n"/>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C72" s="7" t="n"/>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>Brian Thomas Jr.</t>
-        </is>
-      </c>
+      <c r="D72" s="7" t="n"/>
       <c r="E72" s="7" t="n"/>
       <c r="F72" s="7" t="n"/>
       <c r="G72" s="7" t="n"/>
@@ -1710,59 +1710,59 @@
       </c>
       <c r="B73" s="7" t="n"/>
       <c r="C73" s="7" t="n"/>
-      <c r="D73" s="7" t="n"/>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E73" s="7" t="n"/>
-      <c r="F73" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
       <c r="H73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B74" s="7" t="n"/>
       <c r="C74" s="7" t="n"/>
       <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
       <c r="F74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
-      <c r="H74" s="7" t="n"/>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B75" s="7" t="n"/>
       <c r="C75" s="7" t="n"/>
       <c r="D75" s="7" t="n"/>
       <c r="E75" s="7" t="n"/>
       <c r="F75" s="7" t="n"/>
       <c r="G75" s="7" t="n"/>
-      <c r="H75" s="7" t="n"/>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B76" s="7" t="n"/>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C76" s="7" t="n"/>
-      <c r="D76" s="7" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D76" s="7" t="n"/>
       <c r="E76" s="7" t="n"/>
       <c r="F76" s="7" t="n"/>
       <c r="G76" s="7" t="n"/>
@@ -1772,13 +1772,13 @@
       <c r="A77" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B77" s="7" t="n"/>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
       <c r="C77" s="7" t="n"/>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D77" s="7" t="n"/>
       <c r="E77" s="7" t="n"/>
       <c r="F77" s="7" t="n"/>
       <c r="G77" s="7" t="n"/>
@@ -1792,7 +1792,7 @@
       <c r="C78" s="7" t="n"/>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E78" s="7" t="n"/>
@@ -1808,7 +1808,7 @@
       <c r="C79" s="7" t="n"/>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E79" s="7" t="n"/>
@@ -1818,15 +1818,15 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B80" s="7" t="n"/>
       <c r="C80" s="7" t="n"/>
-      <c r="D80" s="7" t="n"/>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>Marvin Harrison Jr.</t>
+        </is>
+      </c>
       <c r="E80" s="7" t="n"/>
       <c r="F80" s="7" t="n"/>
       <c r="G80" s="7" t="n"/>
@@ -1834,35 +1834,35 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B81" s="7" t="n"/>
       <c r="C81" s="7" t="n"/>
       <c r="D81" s="7" t="n"/>
       <c r="E81" s="7" t="n"/>
-      <c r="F81" s="7" t="n"/>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G81" s="7" t="n"/>
       <c r="H81" s="7" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>Jonathon Brooks</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B82" s="7" t="n"/>
       <c r="C82" s="7" t="n"/>
       <c r="D82" s="7" t="n"/>
       <c r="E82" s="7" t="n"/>
       <c r="F82" s="7" t="n"/>
       <c r="G82" s="7" t="n"/>
-      <c r="H82" s="7" t="n"/>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="n">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Rachaad White</t>
         </is>
       </c>
       <c r="C83" s="7" t="n"/>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C84" s="7" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C85" s="7" t="n"/>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>Blake Corum</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C86" s="7" t="n"/>
@@ -1968,7 +1968,7 @@
       <c r="C89" s="7" t="n"/>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E89" s="7" t="n"/>
@@ -1984,7 +1984,7 @@
       <c r="C90" s="7" t="n"/>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E90" s="7" t="n"/>
@@ -2000,7 +2000,7 @@
       <c r="C91" s="7" t="n"/>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr.</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E91" s="7" t="n"/>
@@ -2014,13 +2014,13 @@
       </c>
       <c r="B92" s="7" t="n"/>
       <c r="C92" s="7" t="n"/>
-      <c r="D92" s="7" t="n"/>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Reed</t>
+        </is>
+      </c>
       <c r="E92" s="7" t="n"/>
-      <c r="F92" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F92" s="7" t="n"/>
       <c r="G92" s="7" t="n"/>
       <c r="H92" s="7" t="n"/>
     </row>
@@ -2030,47 +2030,47 @@
       </c>
       <c r="B93" s="7" t="n"/>
       <c r="C93" s="7" t="n"/>
-      <c r="D93" s="7" t="n"/>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>Jordyn Tyson</t>
+        </is>
+      </c>
       <c r="E93" s="7" t="n"/>
       <c r="F93" s="7" t="n"/>
       <c r="G93" s="7" t="n"/>
-      <c r="H93" s="7" t="inlineStr">
-        <is>
-          <t>Jalen Hurts</t>
-        </is>
-      </c>
+      <c r="H93" s="7" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B94" s="7" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>J.K. Dobbins</t>
+        </is>
+      </c>
       <c r="C94" s="7" t="n"/>
       <c r="D94" s="7" t="n"/>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="7" t="n"/>
       <c r="G94" s="7" t="n"/>
-      <c r="H94" s="7" t="inlineStr">
-        <is>
-          <t>Justin Herbert</t>
-        </is>
-      </c>
+      <c r="H94" s="7" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B95" s="7" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C95" s="7" t="n"/>
       <c r="D95" s="7" t="n"/>
       <c r="E95" s="7" t="n"/>
       <c r="F95" s="7" t="n"/>
       <c r="G95" s="7" t="n"/>
-      <c r="H95" s="7" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H95" s="7" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
@@ -2096,7 +2096,7 @@
       <c r="C97" s="7" t="n"/>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E97" s="7" t="n"/>
@@ -2112,7 +2112,7 @@
       <c r="C98" s="7" t="n"/>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E98" s="7" t="n"/>
@@ -2128,71 +2128,71 @@
       <c r="C99" s="7" t="n"/>
       <c r="D99" s="7" t="n"/>
       <c r="E99" s="7" t="n"/>
-      <c r="F99" s="7" t="n"/>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G99" s="7" t="n"/>
-      <c r="H99" s="7" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B100" s="7" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B100" s="7" t="n"/>
       <c r="C100" s="7" t="n"/>
       <c r="D100" s="7" t="n"/>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="7" t="n"/>
       <c r="G100" s="7" t="n"/>
-      <c r="H100" s="7" t="n"/>
+      <c r="H100" s="7" t="inlineStr">
+        <is>
+          <t>Jalen Hurts</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B101" s="7" t="n"/>
       <c r="C101" s="7" t="n"/>
-      <c r="D101" s="7" t="inlineStr">
-        <is>
-          <t>Carnell Tate</t>
-        </is>
-      </c>
+      <c r="D101" s="7" t="n"/>
       <c r="E101" s="7" t="n"/>
       <c r="F101" s="7" t="n"/>
       <c r="G101" s="7" t="n"/>
-      <c r="H101" s="7" t="n"/>
+      <c r="H101" s="7" t="inlineStr">
+        <is>
+          <t>Justin Herbert</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B102" s="7" t="n"/>
       <c r="C102" s="7" t="n"/>
-      <c r="D102" s="7" t="inlineStr">
-        <is>
-          <t>KC Concepcion</t>
-        </is>
-      </c>
+      <c r="D102" s="7" t="n"/>
       <c r="E102" s="7" t="n"/>
       <c r="F102" s="7" t="n"/>
       <c r="G102" s="7" t="n"/>
-      <c r="H102" s="7" t="n"/>
+      <c r="H102" s="7" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B103" s="7" t="n"/>
       <c r="C103" s="7" t="n"/>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Ja'Kobi Lane</t>
         </is>
       </c>
       <c r="E103" s="7" t="n"/>
@@ -2202,31 +2202,31 @@
     </row>
     <row r="104">
       <c r="A104" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B104" s="7" t="n"/>
       <c r="C104" s="7" t="n"/>
-      <c r="D104" s="7" t="inlineStr">
-        <is>
-          <t>Jordyn Tyson</t>
-        </is>
-      </c>
+      <c r="D104" s="7" t="n"/>
       <c r="E104" s="7" t="n"/>
       <c r="F104" s="7" t="n"/>
       <c r="G104" s="7" t="n"/>
-      <c r="H104" s="7" t="n"/>
+      <c r="H104" s="7" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B105" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C105" s="7" t="n"/>
-      <c r="D105" s="7" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D105" s="7" t="n"/>
       <c r="E105" s="7" t="n"/>
       <c r="F105" s="7" t="n"/>
       <c r="G105" s="7" t="n"/>
@@ -2295,7 +2295,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 75.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 71.</t>
         </is>
       </c>
     </row>
@@ -2312,14 +2312,14 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>0) Weekly re-seed. The sheet values were first moved toward the 2026 week 6 Half PPR medians</t>
+          <t>0) Weekly re-seed. The sheet values were first moved toward the 2026 week 7 Half PPR medians</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 13; 11 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 0; 4 players used week 6 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,14 +2333,14 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 73 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 63 players moved.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   No projection this week (value kept): Saquon Barkley, Breece Hall, DeVonta Smith, Rashee Rice, Lamar Jackson, Travis Etienne Jr., Jadarian Price, Josh Jacobs, De'Zhaun Stribling, Jordan Mason, Alec Pierce, Brian Thomas Jr., Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Jaxson Dart, Ja'Kobi Lane.</t>
+          <t xml:space="preserve">   No projection this week (value kept): Jahmyr Gibbs, Ja'Marr Chase, Amon-Ra St. Brown, Saquon Barkley, Justin Jefferson, Chase Brown, Breece Hall, DeVonta Smith, Rashee Rice, Tee Higgins, Lamar Jackson, Travis Etienne Jr., Jadarian Price, Joe Burrow, David Montgomery, Jameson Williams, Josh Jacobs, De'Zhaun Stribling, Jordan Mason, Alec Pierce, Brian Thomas Jr., Marvin Harrison Jr., Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Aaron Jones Sr., Jaxson Dart, Ja'Kobi Lane.</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.5, WR 3.0, TE 4.5, QB 0.0.</t>
+          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.8, WR 3.1, TE 4.5, QB 0.0.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 62-&gt;54, Chris Olave 42-&gt;34, Trey McBride 42.8571-&gt;35, Puka Nacua 70-&gt;63, Ja'Marr Chase 60-&gt;53, Justin Jefferson 47-&gt;40, DeVonta Smith 27-&gt;20, Rashee Rice 26-&gt;19</t>
+          <t>Largest moves vs. the baseline in this file: Chris Olave 40-&gt;34, Rashee Rice 26-&gt;20, Garrett Wilson 24-&gt;18, Davante Adams 20-&gt;14, Trey McBride 40.5714-&gt;35, Jaxon Smith-Njigba 61-&gt;56, DeVonta Smith 27-&gt;22, Travis Etienne Jr. 17-&gt;12</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Bijan Robinson</t>
+          <t>Jahmyr Gibbs</t>
         </is>
       </c>
       <c r="C4" s="7" t="n"/>
@@ -618,11 +618,11 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Jahmyr Gibbs</t>
+          <t>Bijan Robinson</t>
         </is>
       </c>
       <c r="C5" s="7" t="n"/>
@@ -634,15 +634,15 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>65</v>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="7" t="n"/>
       <c r="G6" s="7" t="n"/>
@@ -650,15 +650,15 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>64</v>
-      </c>
-      <c r="B7" s="7" t="n"/>
+        <v>62</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Christian McCaffrey</t>
+        </is>
+      </c>
       <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="7" t="n"/>
@@ -666,7 +666,7 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
@@ -682,11 +682,11 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>James Cook III</t>
         </is>
       </c>
       <c r="C9" s="7" t="n"/>
@@ -698,11 +698,11 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>James Cook III</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C10" s="7" t="n"/>
@@ -714,13 +714,13 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -730,13 +730,13 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="E12" s="7" t="n"/>
@@ -746,13 +746,13 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E13" s="7" t="n"/>
@@ -762,11 +762,11 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Saquon Barkley</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="C14" s="7" t="n"/>
@@ -778,11 +778,11 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="C15" s="7" t="n"/>
@@ -794,15 +794,15 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="B16" s="7" t="n"/>
+        <v>45</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D16" s="7" t="n"/>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
@@ -810,31 +810,31 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="n"/>
       <c r="D17" s="7" t="n"/>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="n"/>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
@@ -842,15 +842,15 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
@@ -858,11 +858,11 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Ashton Jeanty</t>
         </is>
       </c>
       <c r="C20" s="7" t="n"/>
@@ -874,29 +874,29 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>43</v>
-      </c>
-      <c r="B21" s="7" t="n"/>
+        <v>40</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C21" s="7" t="n"/>
       <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>CeeDee Lamb</t>
+          <t>Justin Jefferson</t>
         </is>
       </c>
       <c r="E22" s="7" t="n"/>
@@ -908,13 +908,13 @@
       <c r="A23" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="B23" s="7" t="n"/>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
@@ -922,31 +922,31 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E25" s="7" t="n"/>
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
@@ -954,7 +954,7 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
@@ -962,7 +962,7 @@
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>Trey McBride</t>
+          <t>Brock Bowers</t>
         </is>
       </c>
       <c r="G26" s="7" t="n"/>
@@ -970,15 +970,15 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="B27" s="7" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D27" s="7" t="n"/>
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
@@ -986,23 +986,23 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B28" s="7" t="n"/>
+        <v>31</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C28" s="7" t="n"/>
       <c r="D28" s="7" t="n"/>
       <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F28" s="7" t="n"/>
       <c r="G28" s="7" t="n"/>
       <c r="H28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
@@ -1034,15 +1034,15 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="B31" s="7" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D31" s="7" t="n"/>
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="7" t="n"/>
       <c r="G31" s="7" t="n"/>
@@ -1052,43 +1052,43 @@
       <c r="A32" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+      <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
       <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
-      <c r="H32" s="7" t="n"/>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="n"/>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E34" s="7" t="n"/>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
@@ -1114,13 +1114,13 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E36" s="7" t="n"/>
@@ -1130,13 +1130,13 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E37" s="7" t="n"/>
@@ -1146,13 +1146,13 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E38" s="7" t="n"/>
@@ -1162,7 +1162,7 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
@@ -1178,15 +1178,15 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B40" s="7" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D40" s="7" t="n"/>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
@@ -1210,11 +1210,11 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C42" s="7" t="n"/>
@@ -1226,27 +1226,27 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B43" s="7" t="n"/>
       <c r="C43" s="7" t="n"/>
       <c r="D43" s="7" t="n"/>
       <c r="E43" s="7" t="n"/>
-      <c r="F43" s="7" t="n"/>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G43" s="7" t="n"/>
       <c r="H43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C44" s="7" t="n"/>
@@ -1258,11 +1258,11 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C45" s="7" t="n"/>
@@ -1274,11 +1274,11 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="C46" s="7" t="n"/>
@@ -1290,15 +1290,15 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="n"/>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E47" s="7" t="n"/>
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="7" t="n"/>
@@ -1306,15 +1306,15 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B48" s="7" t="n"/>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="n"/>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
@@ -1322,13 +1322,13 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B49" s="7" t="n"/>
       <c r="C49" s="7" t="n"/>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E49" s="7" t="n"/>
@@ -1338,15 +1338,15 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B50" s="7" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
       <c r="F50" s="7" t="n"/>
       <c r="G50" s="7" t="n"/>
@@ -1354,81 +1354,81 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B51" s="7" t="n"/>
       <c r="C51" s="7" t="n"/>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
-      <c r="F51" s="7" t="n"/>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G51" s="7" t="n"/>
       <c r="H51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B52" s="7" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C52" s="7" t="n"/>
       <c r="D52" s="7" t="n"/>
       <c r="E52" s="7" t="n"/>
-      <c r="F52" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F52" s="7" t="n"/>
       <c r="G52" s="7" t="n"/>
       <c r="H52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B53" s="7" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C53" s="7" t="n"/>
       <c r="D53" s="7" t="n"/>
       <c r="E53" s="7" t="n"/>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F53" s="7" t="n"/>
       <c r="G53" s="7" t="n"/>
       <c r="H53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
-      <c r="D54" s="7" t="n"/>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E54" s="7" t="n"/>
       <c r="F54" s="7" t="n"/>
       <c r="G54" s="7" t="n"/>
-      <c r="H54" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B55" s="7" t="n"/>
       <c r="C55" s="7" t="n"/>
       <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7" t="n"/>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G55" s="7" t="n"/>
       <c r="H55" s="7" t="n"/>
     </row>
@@ -1438,27 +1438,27 @@
       </c>
       <c r="B56" s="7" t="n"/>
       <c r="C56" s="7" t="n"/>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D56" s="7" t="n"/>
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="n"/>
-      <c r="H56" s="7" t="n"/>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B57" s="7" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C57" s="7" t="n"/>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
       <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
@@ -1466,13 +1466,13 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B58" s="7" t="n"/>
       <c r="C58" s="7" t="n"/>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E58" s="7" t="n"/>
@@ -1482,17 +1482,17 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B59" s="7" t="n"/>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="7" t="n"/>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E59" s="7" t="n"/>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F59" s="7" t="n"/>
       <c r="G59" s="7" t="n"/>
       <c r="H59" s="7" t="n"/>
     </row>
@@ -1500,13 +1500,13 @@
       <c r="A60" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+      <c r="B60" s="7" t="n"/>
       <c r="C60" s="7" t="n"/>
-      <c r="D60" s="7" t="n"/>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E60" s="7" t="n"/>
       <c r="F60" s="7" t="n"/>
       <c r="G60" s="7" t="n"/>
@@ -1516,29 +1516,29 @@
       <c r="A61" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+      <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
       <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
-      <c r="F61" s="7" t="n"/>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G61" s="7" t="n"/>
       <c r="H61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B62" s="7" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D62" s="7" t="n"/>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="7" t="n"/>
@@ -1546,15 +1546,15 @@
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B63" s="7" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C63" s="7" t="n"/>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D63" s="7" t="n"/>
       <c r="E63" s="7" t="n"/>
       <c r="F63" s="7" t="n"/>
       <c r="G63" s="7" t="n"/>
@@ -1562,13 +1562,13 @@
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B64" s="7" t="n"/>
       <c r="C64" s="7" t="n"/>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>DJ Moore</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E64" s="7" t="n"/>
@@ -1578,13 +1578,13 @@
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B65" s="7" t="n"/>
       <c r="C65" s="7" t="n"/>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="E65" s="7" t="n"/>
@@ -1594,59 +1594,59 @@
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B66" s="7" t="n"/>
       <c r="C66" s="7" t="n"/>
       <c r="D66" s="7" t="n"/>
       <c r="E66" s="7" t="n"/>
-      <c r="F66" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F66" s="7" t="n"/>
       <c r="G66" s="7" t="n"/>
-      <c r="H66" s="7" t="n"/>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+      <c r="B67" s="7" t="n"/>
       <c r="C67" s="7" t="n"/>
       <c r="D67" s="7" t="n"/>
       <c r="E67" s="7" t="n"/>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
-      <c r="H67" s="7" t="n"/>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B68" s="7" t="n"/>
       <c r="C68" s="7" t="n"/>
       <c r="D68" s="7" t="n"/>
       <c r="E68" s="7" t="n"/>
       <c r="F68" s="7" t="n"/>
       <c r="G68" s="7" t="n"/>
-      <c r="H68" s="7" t="n"/>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="C69" s="7" t="n"/>
@@ -1658,15 +1658,15 @@
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B70" s="7" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
       <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="inlineStr">
-        <is>
-          <t>De'Zhaun Stribling</t>
-        </is>
-      </c>
+      <c r="D70" s="7" t="n"/>
       <c r="E70" s="7" t="n"/>
       <c r="F70" s="7" t="n"/>
       <c r="G70" s="7" t="n"/>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="C71" s="7" t="n"/>
@@ -1692,13 +1692,13 @@
       <c r="A72" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+      <c r="B72" s="7" t="n"/>
       <c r="C72" s="7" t="n"/>
-      <c r="D72" s="7" t="n"/>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E72" s="7" t="n"/>
       <c r="F72" s="7" t="n"/>
       <c r="G72" s="7" t="n"/>
@@ -1710,59 +1710,59 @@
       </c>
       <c r="B73" s="7" t="n"/>
       <c r="C73" s="7" t="n"/>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D73" s="7" t="n"/>
       <c r="E73" s="7" t="n"/>
-      <c r="F73" s="7" t="n"/>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G73" s="7" t="n"/>
       <c r="H73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B74" s="7" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C74" s="7" t="n"/>
       <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
       <c r="F74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
-      <c r="H74" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H74" s="7" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B75" s="7" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C75" s="7" t="n"/>
       <c r="D75" s="7" t="n"/>
       <c r="E75" s="7" t="n"/>
       <c r="F75" s="7" t="n"/>
       <c r="G75" s="7" t="n"/>
-      <c r="H75" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H75" s="7" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+      <c r="B76" s="7" t="n"/>
       <c r="C76" s="7" t="n"/>
-      <c r="D76" s="7" t="n"/>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E76" s="7" t="n"/>
       <c r="F76" s="7" t="n"/>
       <c r="G76" s="7" t="n"/>
@@ -1772,13 +1772,13 @@
       <c r="A77" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+      <c r="B77" s="7" t="n"/>
       <c r="C77" s="7" t="n"/>
-      <c r="D77" s="7" t="n"/>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E77" s="7" t="n"/>
       <c r="F77" s="7" t="n"/>
       <c r="G77" s="7" t="n"/>
@@ -1792,7 +1792,7 @@
       <c r="C78" s="7" t="n"/>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E78" s="7" t="n"/>
@@ -1808,7 +1808,7 @@
       <c r="C79" s="7" t="n"/>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E79" s="7" t="n"/>
@@ -1818,15 +1818,15 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B80" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C80" s="7" t="n"/>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D80" s="7" t="n"/>
       <c r="E80" s="7" t="n"/>
       <c r="F80" s="7" t="n"/>
       <c r="G80" s="7" t="n"/>
@@ -1834,35 +1834,35 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B81" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C81" s="7" t="n"/>
       <c r="D81" s="7" t="n"/>
       <c r="E81" s="7" t="n"/>
-      <c r="F81" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F81" s="7" t="n"/>
       <c r="G81" s="7" t="n"/>
       <c r="H81" s="7" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B82" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>Jonathon Brooks</t>
+        </is>
+      </c>
       <c r="C82" s="7" t="n"/>
       <c r="D82" s="7" t="n"/>
       <c r="E82" s="7" t="n"/>
       <c r="F82" s="7" t="n"/>
       <c r="G82" s="7" t="n"/>
-      <c r="H82" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H82" s="7" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="n">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Rachaad White</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C83" s="7" t="n"/>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C84" s="7" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C85" s="7" t="n"/>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="C86" s="7" t="n"/>
@@ -1968,7 +1968,7 @@
       <c r="C89" s="7" t="n"/>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E89" s="7" t="n"/>
@@ -1984,7 +1984,7 @@
       <c r="C90" s="7" t="n"/>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E90" s="7" t="n"/>
@@ -2000,7 +2000,7 @@
       <c r="C91" s="7" t="n"/>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="E91" s="7" t="n"/>
@@ -2014,13 +2014,13 @@
       </c>
       <c r="B92" s="7" t="n"/>
       <c r="C92" s="7" t="n"/>
-      <c r="D92" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Reed</t>
-        </is>
-      </c>
+      <c r="D92" s="7" t="n"/>
       <c r="E92" s="7" t="n"/>
-      <c r="F92" s="7" t="n"/>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G92" s="7" t="n"/>
       <c r="H92" s="7" t="n"/>
     </row>
@@ -2030,47 +2030,47 @@
       </c>
       <c r="B93" s="7" t="n"/>
       <c r="C93" s="7" t="n"/>
-      <c r="D93" s="7" t="inlineStr">
-        <is>
-          <t>Jordyn Tyson</t>
-        </is>
-      </c>
+      <c r="D93" s="7" t="n"/>
       <c r="E93" s="7" t="n"/>
       <c r="F93" s="7" t="n"/>
       <c r="G93" s="7" t="n"/>
-      <c r="H93" s="7" t="n"/>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>Jalen Hurts</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B94" s="7" t="n"/>
       <c r="C94" s="7" t="n"/>
       <c r="D94" s="7" t="n"/>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="7" t="n"/>
       <c r="G94" s="7" t="n"/>
-      <c r="H94" s="7" t="n"/>
+      <c r="H94" s="7" t="inlineStr">
+        <is>
+          <t>Justin Herbert</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B95" s="7" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B95" s="7" t="n"/>
       <c r="C95" s="7" t="n"/>
       <c r="D95" s="7" t="n"/>
       <c r="E95" s="7" t="n"/>
       <c r="F95" s="7" t="n"/>
       <c r="G95" s="7" t="n"/>
-      <c r="H95" s="7" t="n"/>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
@@ -2096,7 +2096,7 @@
       <c r="C97" s="7" t="n"/>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E97" s="7" t="n"/>
@@ -2112,7 +2112,7 @@
       <c r="C98" s="7" t="n"/>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr.</t>
+          <t>Ja'Kobi Lane</t>
         </is>
       </c>
       <c r="E98" s="7" t="n"/>
@@ -2128,71 +2128,71 @@
       <c r="C99" s="7" t="n"/>
       <c r="D99" s="7" t="n"/>
       <c r="E99" s="7" t="n"/>
-      <c r="F99" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F99" s="7" t="n"/>
       <c r="G99" s="7" t="n"/>
-      <c r="H99" s="7" t="n"/>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B100" s="7" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>Rachaad White</t>
+        </is>
+      </c>
       <c r="C100" s="7" t="n"/>
       <c r="D100" s="7" t="n"/>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="7" t="n"/>
       <c r="G100" s="7" t="n"/>
-      <c r="H100" s="7" t="inlineStr">
-        <is>
-          <t>Jalen Hurts</t>
-        </is>
-      </c>
+      <c r="H100" s="7" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B101" s="7" t="n"/>
       <c r="C101" s="7" t="n"/>
-      <c r="D101" s="7" t="n"/>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>Carnell Tate</t>
+        </is>
+      </c>
       <c r="E101" s="7" t="n"/>
       <c r="F101" s="7" t="n"/>
       <c r="G101" s="7" t="n"/>
-      <c r="H101" s="7" t="inlineStr">
-        <is>
-          <t>Justin Herbert</t>
-        </is>
-      </c>
+      <c r="H101" s="7" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B102" s="7" t="n"/>
       <c r="C102" s="7" t="n"/>
-      <c r="D102" s="7" t="n"/>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>KC Concepcion</t>
+        </is>
+      </c>
       <c r="E102" s="7" t="n"/>
       <c r="F102" s="7" t="n"/>
       <c r="G102" s="7" t="n"/>
-      <c r="H102" s="7" t="inlineStr">
-        <is>
-          <t>Trevor Lawrence</t>
-        </is>
-      </c>
+      <c r="H102" s="7" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B103" s="7" t="n"/>
       <c r="C103" s="7" t="n"/>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E103" s="7" t="n"/>
@@ -2202,31 +2202,31 @@
     </row>
     <row r="104">
       <c r="A104" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B104" s="7" t="n"/>
       <c r="C104" s="7" t="n"/>
-      <c r="D104" s="7" t="n"/>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>Jordyn Tyson</t>
+        </is>
+      </c>
       <c r="E104" s="7" t="n"/>
       <c r="F104" s="7" t="n"/>
       <c r="G104" s="7" t="n"/>
-      <c r="H104" s="7" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H104" s="7" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B105" s="7" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B105" s="7" t="n"/>
       <c r="C105" s="7" t="n"/>
-      <c r="D105" s="7" t="n"/>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E105" s="7" t="n"/>
       <c r="F105" s="7" t="n"/>
       <c r="G105" s="7" t="n"/>
@@ -2295,7 +2295,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 71.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 75.</t>
         </is>
       </c>
     </row>
@@ -2312,14 +2312,14 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>0) Weekly re-seed. The sheet values were first moved toward the 2026 week 7 Half PPR medians</t>
+          <t>0) Weekly re-seed. The sheet values were first moved toward the 2026 week 6 Half PPR medians</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 0; 4 players used week 6 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 13; 11 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,14 +2333,14 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 63 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 73 players moved.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   No projection this week (value kept): Jahmyr Gibbs, Ja'Marr Chase, Amon-Ra St. Brown, Saquon Barkley, Justin Jefferson, Chase Brown, Breece Hall, DeVonta Smith, Rashee Rice, Tee Higgins, Lamar Jackson, Travis Etienne Jr., Jadarian Price, Joe Burrow, David Montgomery, Jameson Williams, Josh Jacobs, De'Zhaun Stribling, Jordan Mason, Alec Pierce, Brian Thomas Jr., Marvin Harrison Jr., Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Aaron Jones Sr., Jaxson Dart, Ja'Kobi Lane.</t>
+          <t xml:space="preserve">   No projection this week (value kept): Saquon Barkley, Breece Hall, DeVonta Smith, Rashee Rice, Lamar Jackson, Travis Etienne Jr., Jadarian Price, Josh Jacobs, De'Zhaun Stribling, Jordan Mason, Alec Pierce, Brian Thomas Jr., Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Jaxson Dart, Ja'Kobi Lane.</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.8, WR 3.1, TE 4.5, QB 0.0.</t>
+          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.5, WR 3.0, TE 4.5, QB 0.0.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Chris Olave 40-&gt;34, Rashee Rice 26-&gt;20, Garrett Wilson 24-&gt;18, Davante Adams 20-&gt;14, Trey McBride 40.5714-&gt;35, Jaxon Smith-Njigba 61-&gt;56, DeVonta Smith 27-&gt;22, Travis Etienne Jr. 17-&gt;12</t>
+          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 62-&gt;54, Chris Olave 42-&gt;34, Trey McBride 42.8571-&gt;35, Puka Nacua 70-&gt;63, Ja'Marr Chase 60-&gt;53, Justin Jefferson 47-&gt;40, DeVonta Smith 27-&gt;20, Rashee Rice 26-&gt;19</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -938,7 +938,7 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
@@ -1082,13 +1082,13 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E34" s="7" t="n"/>
@@ -1104,7 +1104,7 @@
       <c r="C35" s="7" t="n"/>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E35" s="7" t="n"/>
@@ -1120,7 +1120,7 @@
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E36" s="7" t="n"/>
@@ -1338,17 +1338,17 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B50" s="7" t="n"/>
       <c r="C50" s="7" t="n"/>
       <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
-      <c r="F50" s="7" t="n"/>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G50" s="7" t="n"/>
       <c r="H50" s="7" t="n"/>
     </row>
@@ -1356,15 +1356,15 @@
       <c r="A51" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B51" s="7" t="n"/>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C51" s="7" t="n"/>
       <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F51" s="7" t="n"/>
       <c r="G51" s="7" t="n"/>
       <c r="H51" s="7" t="n"/>
     </row>
@@ -1932,13 +1932,13 @@
       <c r="A87" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B87" s="7" t="n"/>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C87" s="7" t="n"/>
-      <c r="D87" s="7" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D87" s="7" t="n"/>
       <c r="E87" s="7" t="n"/>
       <c r="F87" s="7" t="n"/>
       <c r="G87" s="7" t="n"/>
@@ -2076,13 +2076,13 @@
       <c r="A96" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B96" s="7" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+      <c r="B96" s="7" t="n"/>
       <c r="C96" s="7" t="n"/>
-      <c r="D96" s="7" t="n"/>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>Terry McLaurin</t>
+        </is>
+      </c>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="7" t="n"/>
       <c r="G96" s="7" t="n"/>
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 13; 11 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 12; 11 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 73 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 71 players moved.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 62-&gt;54, Chris Olave 42-&gt;34, Trey McBride 42.8571-&gt;35, Puka Nacua 70-&gt;63, Ja'Marr Chase 60-&gt;53, Justin Jefferson 47-&gt;40, DeVonta Smith 27-&gt;20, Rashee Rice 26-&gt;19</t>
+          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 62-&gt;54, Chris Olave 41-&gt;33, Trey McBride 42.8571-&gt;35, Puka Nacua 70-&gt;63, Ja'Marr Chase 60-&gt;53, Justin Jefferson 47-&gt;40, DeVonta Smith 27-&gt;20, Rashee Rice 26-&gt;19</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -618,7 +618,7 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
@@ -666,11 +666,11 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>James Cook III</t>
         </is>
       </c>
       <c r="C8" s="7" t="n"/>
@@ -682,11 +682,11 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>James Cook III</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C9" s="7" t="n"/>
@@ -698,15 +698,15 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Kenneth Walker III</t>
-        </is>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Marr Chase</t>
+        </is>
+      </c>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="n"/>
@@ -714,15 +714,15 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="B11" s="7" t="n"/>
+        <v>55</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Amon-Ra St. Brown</t>
-        </is>
-      </c>
+      <c r="D11" s="7" t="n"/>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
@@ -746,13 +746,13 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E13" s="7" t="n"/>
@@ -762,11 +762,11 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="C14" s="7" t="n"/>
@@ -778,11 +778,11 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Saquon Barkley</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="C15" s="7" t="n"/>
@@ -798,7 +798,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C16" s="7" t="n"/>
@@ -810,23 +810,23 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="B17" s="7" t="n"/>
+        <v>45</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C17" s="7" t="n"/>
       <c r="D17" s="7" t="n"/>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
@@ -842,19 +842,19 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
@@ -862,7 +862,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C20" s="7" t="n"/>
@@ -874,15 +874,15 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
@@ -890,27 +890,27 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C23" s="7" t="n"/>
@@ -922,17 +922,17 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
     </row>
@@ -942,43 +942,43 @@
       </c>
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="B26" s="7" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C26" s="7" t="n"/>
       <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
@@ -986,7 +986,7 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
@@ -1002,13 +1002,13 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Nico Collins</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E29" s="7" t="n"/>
@@ -1018,13 +1018,13 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Chris Olave</t>
         </is>
       </c>
       <c r="E30" s="7" t="n"/>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
@@ -1066,15 +1066,15 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="B33" s="7" t="n"/>
+        <v>23</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D33" s="7" t="n"/>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
@@ -1088,7 +1088,7 @@
       <c r="C34" s="7" t="n"/>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E34" s="7" t="n"/>
@@ -1098,13 +1098,13 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E35" s="7" t="n"/>
@@ -1114,13 +1114,13 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E36" s="7" t="n"/>
@@ -1130,13 +1130,13 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E37" s="7" t="n"/>
@@ -1146,13 +1146,13 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E38" s="7" t="n"/>
@@ -1162,13 +1162,13 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E39" s="7" t="n"/>
@@ -1178,15 +1178,15 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="n"/>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
@@ -1194,13 +1194,13 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E41" s="7" t="n"/>
@@ -1210,15 +1210,15 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B42" s="7" t="n"/>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="n"/>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="7" t="n"/>
@@ -1226,43 +1226,43 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B43" s="7" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C43" s="7" t="n"/>
       <c r="D43" s="7" t="n"/>
       <c r="E43" s="7" t="n"/>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F43" s="7" t="n"/>
       <c r="G43" s="7" t="n"/>
       <c r="H43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="n"/>
       <c r="D44" s="7" t="n"/>
       <c r="E44" s="7" t="n"/>
-      <c r="F44" s="7" t="n"/>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G44" s="7" t="n"/>
       <c r="H44" s="7" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C45" s="7" t="n"/>
@@ -1274,15 +1274,15 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="n"/>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="7" t="n"/>
@@ -1292,13 +1292,13 @@
       <c r="A47" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B47" s="7" t="n"/>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D47" s="7" t="n"/>
       <c r="E47" s="7" t="n"/>
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="7" t="n"/>
@@ -1308,13 +1308,13 @@
       <c r="A48" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B48" s="7" t="n"/>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D48" s="7" t="n"/>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
@@ -1324,13 +1324,13 @@
       <c r="A49" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B49" s="7" t="n"/>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D49" s="7" t="n"/>
       <c r="E49" s="7" t="n"/>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n"/>
@@ -1342,13 +1342,13 @@
       </c>
       <c r="B50" s="7" t="n"/>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="n"/>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E50" s="7" t="n"/>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F50" s="7" t="n"/>
       <c r="G50" s="7" t="n"/>
       <c r="H50" s="7" t="n"/>
     </row>
@@ -1370,11 +1370,11 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr.</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C52" s="7" t="n"/>
@@ -1386,15 +1386,15 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B53" s="7" t="n"/>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="7" t="n"/>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E53" s="7" t="n"/>
       <c r="F53" s="7" t="n"/>
       <c r="G53" s="7" t="n"/>
@@ -1402,23 +1402,23 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D54" s="7" t="n"/>
       <c r="E54" s="7" t="n"/>
-      <c r="F54" s="7" t="n"/>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G54" s="7" t="n"/>
       <c r="H54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B55" s="7" t="n"/>
       <c r="C55" s="7" t="n"/>
@@ -1426,7 +1426,7 @@
       <c r="E55" s="7" t="n"/>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>Colston Loveland</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G55" s="7" t="n"/>
@@ -1436,33 +1436,33 @@
       <c r="A56" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B56" s="7" t="n"/>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C56" s="7" t="n"/>
       <c r="D56" s="7" t="n"/>
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="n"/>
-      <c r="H56" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B57" s="7" t="n"/>
       <c r="C57" s="7" t="n"/>
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
       <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
-      <c r="H57" s="7" t="n"/>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
@@ -1472,7 +1472,7 @@
       <c r="C58" s="7" t="n"/>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E58" s="7" t="n"/>
@@ -1482,15 +1482,15 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B59" s="7" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
       <c r="F59" s="7" t="n"/>
       <c r="G59" s="7" t="n"/>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B60" s="7" t="n"/>
       <c r="C60" s="7" t="n"/>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E60" s="7" t="n"/>
@@ -1518,31 +1518,31 @@
       </c>
       <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="n"/>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E61" s="7" t="n"/>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
       <c r="H61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B62" s="7" t="n"/>
       <c r="C62" s="7" t="n"/>
       <c r="D62" s="7" t="n"/>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="7" t="n"/>
-      <c r="H62" s="7" t="n"/>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C63" s="7" t="n"/>
@@ -1568,7 +1568,7 @@
       <c r="C64" s="7" t="n"/>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E64" s="7" t="n"/>
@@ -1610,35 +1610,35 @@
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B67" s="7" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C67" s="7" t="n"/>
       <c r="D67" s="7" t="n"/>
       <c r="E67" s="7" t="n"/>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
-      <c r="H67" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B68" s="7" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C68" s="7" t="n"/>
       <c r="D68" s="7" t="n"/>
       <c r="E68" s="7" t="n"/>
       <c r="F68" s="7" t="n"/>
       <c r="G68" s="7" t="n"/>
-      <c r="H68" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C69" s="7" t="n"/>
@@ -1676,13 +1676,13 @@
       <c r="A71" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+      <c r="B71" s="7" t="n"/>
       <c r="C71" s="7" t="n"/>
-      <c r="D71" s="7" t="n"/>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
@@ -1710,29 +1710,29 @@
       </c>
       <c r="B73" s="7" t="n"/>
       <c r="C73" s="7" t="n"/>
-      <c r="D73" s="7" t="n"/>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Marvin Harrison Jr.</t>
+        </is>
+      </c>
       <c r="E73" s="7" t="n"/>
-      <c r="F73" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
       <c r="H73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B74" s="7" t="n"/>
       <c r="C74" s="7" t="n"/>
       <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
-      <c r="F74" s="7" t="n"/>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G74" s="7" t="n"/>
       <c r="H74" s="7" t="n"/>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="C75" s="7" t="n"/>
@@ -1756,13 +1756,13 @@
       <c r="A76" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B76" s="7" t="n"/>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>J.K. Dobbins</t>
+        </is>
+      </c>
       <c r="C76" s="7" t="n"/>
-      <c r="D76" s="7" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D76" s="7" t="n"/>
       <c r="E76" s="7" t="n"/>
       <c r="F76" s="7" t="n"/>
       <c r="G76" s="7" t="n"/>
@@ -1772,13 +1772,13 @@
       <c r="A77" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B77" s="7" t="n"/>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C77" s="7" t="n"/>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D77" s="7" t="n"/>
       <c r="E77" s="7" t="n"/>
       <c r="F77" s="7" t="n"/>
       <c r="G77" s="7" t="n"/>
@@ -1790,27 +1790,27 @@
       </c>
       <c r="B78" s="7" t="n"/>
       <c r="C78" s="7" t="n"/>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>Jameson Williams</t>
-        </is>
-      </c>
+      <c r="D78" s="7" t="n"/>
       <c r="E78" s="7" t="n"/>
-      <c r="F78" s="7" t="n"/>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G78" s="7" t="n"/>
       <c r="H78" s="7" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B79" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>Jonathon Brooks</t>
+        </is>
+      </c>
       <c r="C79" s="7" t="n"/>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D79" s="7" t="n"/>
       <c r="E79" s="7" t="n"/>
       <c r="F79" s="7" t="n"/>
       <c r="G79" s="7" t="n"/>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C80" s="7" t="n"/>
@@ -1836,13 +1836,13 @@
       <c r="A81" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B81" s="7" t="n"/>
       <c r="C81" s="7" t="n"/>
-      <c r="D81" s="7" t="n"/>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E81" s="7" t="n"/>
       <c r="F81" s="7" t="n"/>
       <c r="G81" s="7" t="n"/>
@@ -1852,13 +1852,13 @@
       <c r="A82" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>Jonathon Brooks</t>
-        </is>
-      </c>
+      <c r="B82" s="7" t="n"/>
       <c r="C82" s="7" t="n"/>
-      <c r="D82" s="7" t="n"/>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E82" s="7" t="n"/>
       <c r="F82" s="7" t="n"/>
       <c r="G82" s="7" t="n"/>
@@ -1868,13 +1868,13 @@
       <c r="A83" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>Mike Washington Jr.</t>
-        </is>
-      </c>
+      <c r="B83" s="7" t="n"/>
       <c r="C83" s="7" t="n"/>
-      <c r="D83" s="7" t="n"/>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>De'Zhaun Stribling</t>
+        </is>
+      </c>
       <c r="E83" s="7" t="n"/>
       <c r="F83" s="7" t="n"/>
       <c r="G83" s="7" t="n"/>
@@ -1884,13 +1884,13 @@
       <c r="A84" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>Rico Dowdle</t>
-        </is>
-      </c>
+      <c r="B84" s="7" t="n"/>
       <c r="C84" s="7" t="n"/>
-      <c r="D84" s="7" t="n"/>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>Quentin Johnston</t>
+        </is>
+      </c>
       <c r="E84" s="7" t="n"/>
       <c r="F84" s="7" t="n"/>
       <c r="G84" s="7" t="n"/>
@@ -1900,25 +1900,25 @@
       <c r="A85" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
+      <c r="B85" s="7" t="n"/>
       <c r="C85" s="7" t="n"/>
       <c r="D85" s="7" t="n"/>
       <c r="E85" s="7" t="n"/>
       <c r="F85" s="7" t="n"/>
       <c r="G85" s="7" t="n"/>
-      <c r="H85" s="7" t="n"/>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>Blake Corum</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C86" s="7" t="n"/>
@@ -1930,11 +1930,11 @@
     </row>
     <row r="87">
       <c r="A87" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="C87" s="7" t="n"/>
@@ -1946,13 +1946,13 @@
     </row>
     <row r="88">
       <c r="A88" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B88" s="7" t="n"/>
       <c r="C88" s="7" t="n"/>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E88" s="7" t="n"/>
@@ -1962,13 +1962,13 @@
     </row>
     <row r="89">
       <c r="A89" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B89" s="7" t="n"/>
       <c r="C89" s="7" t="n"/>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E89" s="7" t="n"/>
@@ -1978,13 +1978,13 @@
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B90" s="7" t="n"/>
       <c r="C90" s="7" t="n"/>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E90" s="7" t="n"/>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B91" s="7" t="n"/>
       <c r="C91" s="7" t="n"/>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B92" s="7" t="n"/>
       <c r="C92" s="7" t="n"/>
@@ -2026,7 +2026,7 @@
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B93" s="7" t="n"/>
       <c r="C93" s="7" t="n"/>
@@ -2042,7 +2042,7 @@
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B94" s="7" t="n"/>
       <c r="C94" s="7" t="n"/>
@@ -2058,7 +2058,7 @@
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B95" s="7" t="n"/>
       <c r="C95" s="7" t="n"/>
@@ -2074,15 +2074,15 @@
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B96" s="7" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>Rachaad White</t>
+        </is>
+      </c>
       <c r="C96" s="7" t="n"/>
-      <c r="D96" s="7" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D96" s="7" t="n"/>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="7" t="n"/>
       <c r="G96" s="7" t="n"/>
@@ -2090,15 +2090,15 @@
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B97" s="7" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C97" s="7" t="n"/>
-      <c r="D97" s="7" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D97" s="7" t="n"/>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="7" t="n"/>
       <c r="G97" s="7" t="n"/>
@@ -2106,13 +2106,13 @@
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B98" s="7" t="n"/>
       <c r="C98" s="7" t="n"/>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E98" s="7" t="n"/>
@@ -2122,31 +2122,31 @@
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B99" s="7" t="n"/>
       <c r="C99" s="7" t="n"/>
-      <c r="D99" s="7" t="n"/>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>Michael Wilson</t>
+        </is>
+      </c>
       <c r="E99" s="7" t="n"/>
       <c r="F99" s="7" t="n"/>
       <c r="G99" s="7" t="n"/>
-      <c r="H99" s="7" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B100" s="7" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
+      <c r="B100" s="7" t="n"/>
       <c r="C100" s="7" t="n"/>
-      <c r="D100" s="7" t="n"/>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="7" t="n"/>
       <c r="G100" s="7" t="n"/>
@@ -2158,15 +2158,15 @@
       </c>
       <c r="B101" s="7" t="n"/>
       <c r="C101" s="7" t="n"/>
-      <c r="D101" s="7" t="inlineStr">
-        <is>
-          <t>Carnell Tate</t>
-        </is>
-      </c>
+      <c r="D101" s="7" t="n"/>
       <c r="E101" s="7" t="n"/>
       <c r="F101" s="7" t="n"/>
       <c r="G101" s="7" t="n"/>
-      <c r="H101" s="7" t="n"/>
+      <c r="H101" s="7" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="n">
@@ -2218,15 +2218,15 @@
     </row>
     <row r="105">
       <c r="A105" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B105" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C105" s="7" t="n"/>
-      <c r="D105" s="7" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D105" s="7" t="n"/>
       <c r="E105" s="7" t="n"/>
       <c r="F105" s="7" t="n"/>
       <c r="G105" s="7" t="n"/>
@@ -2295,7 +2295,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 75.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 76.</t>
         </is>
       </c>
     </row>
@@ -2312,14 +2312,14 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>0) Weekly re-seed. The sheet values were first moved toward the 2026 week 6 Half PPR medians</t>
+          <t>0) Weekly re-seed. The sheet values were first moved toward the 2026 week 7 Half PPR medians</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 12; 11 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 0; 32 players used week 6 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,14 +2333,14 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 71 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 69 players moved.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   No projection this week (value kept): Saquon Barkley, Breece Hall, DeVonta Smith, Rashee Rice, Lamar Jackson, Travis Etienne Jr., Jadarian Price, Josh Jacobs, De'Zhaun Stribling, Jordan Mason, Alec Pierce, Brian Thomas Jr., Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Jaxson Dart, Ja'Kobi Lane.</t>
+          <t xml:space="preserve">   No projection this week (value kept): Amon-Ra St. Brown, Saquon Barkley, Chase Brown, Breece Hall, DeVonta Smith, Rashee Rice, Lamar Jackson, Travis Etienne Jr., Jadarian Price, David Montgomery, Josh Jacobs, De'Zhaun Stribling, Jordan Mason, Alec Pierce, Brian Thomas Jr., Marvin Harrison Jr., Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Aaron Jones Sr., Jaxson Dart, Ja'Kobi Lane.</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.5, WR 3.0, TE 4.5, QB 0.0.</t>
+          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.8, WR 3.0, TE 4.5, QB 0.0.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 62-&gt;54, Chris Olave 41-&gt;33, Trey McBride 42.8571-&gt;35, Puka Nacua 70-&gt;63, Ja'Marr Chase 60-&gt;53, Justin Jefferson 47-&gt;40, DeVonta Smith 27-&gt;20, Rashee Rice 26-&gt;19</t>
+          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 63-&gt;54, Chris Olave 34-&gt;25, Puka Nacua 69-&gt;61, Amon-Ra St. Brown 60-&gt;52, Trey McBride 43.4286-&gt;36, Ja'Marr Chase 63-&gt;56, Justin Jefferson 43-&gt;36, CeeDee Lamb 51-&gt;44</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -618,7 +618,7 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
@@ -666,11 +666,11 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>James Cook III</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C8" s="7" t="n"/>
@@ -682,11 +682,11 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>James Cook III</t>
         </is>
       </c>
       <c r="C9" s="7" t="n"/>
@@ -698,15 +698,15 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>56</v>
-      </c>
-      <c r="B10" s="7" t="n"/>
+        <v>58</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="n"/>
@@ -714,15 +714,15 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
@@ -746,13 +746,13 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E13" s="7" t="n"/>
@@ -762,11 +762,11 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Saquon Barkley</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="C14" s="7" t="n"/>
@@ -778,11 +778,11 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="C15" s="7" t="n"/>
@@ -798,7 +798,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="C16" s="7" t="n"/>
@@ -810,23 +810,23 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="n"/>
       <c r="D17" s="7" t="n"/>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="n"/>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
@@ -842,19 +842,19 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
@@ -862,7 +862,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Ashton Jeanty</t>
         </is>
       </c>
       <c r="C20" s="7" t="n"/>
@@ -874,15 +874,15 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="B21" s="7" t="n"/>
+        <v>40</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
@@ -890,27 +890,27 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C23" s="7" t="n"/>
@@ -922,17 +922,17 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
     </row>
@@ -942,43 +942,43 @@
       </c>
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
       <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="B27" s="7" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D27" s="7" t="n"/>
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
@@ -986,7 +986,7 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
@@ -1002,13 +1002,13 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Nico Collins</t>
         </is>
       </c>
       <c r="E29" s="7" t="n"/>
@@ -1018,13 +1018,13 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E30" s="7" t="n"/>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
@@ -1066,15 +1066,15 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="n"/>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>George Pickens</t>
+        </is>
+      </c>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
@@ -1088,7 +1088,7 @@
       <c r="C34" s="7" t="n"/>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E34" s="7" t="n"/>
@@ -1098,13 +1098,13 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E35" s="7" t="n"/>
@@ -1114,13 +1114,13 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E36" s="7" t="n"/>
@@ -1130,13 +1130,13 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E37" s="7" t="n"/>
@@ -1146,13 +1146,13 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E38" s="7" t="n"/>
@@ -1162,13 +1162,13 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E39" s="7" t="n"/>
@@ -1178,15 +1178,15 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="B40" s="7" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D40" s="7" t="n"/>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
@@ -1194,13 +1194,13 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E41" s="7" t="n"/>
@@ -1210,15 +1210,15 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="B42" s="7" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D42" s="7" t="n"/>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="7" t="n"/>
@@ -1226,43 +1226,43 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B43" s="7" t="n"/>
       <c r="C43" s="7" t="n"/>
       <c r="D43" s="7" t="n"/>
       <c r="E43" s="7" t="n"/>
-      <c r="F43" s="7" t="n"/>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G43" s="7" t="n"/>
       <c r="H43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B44" s="7" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C44" s="7" t="n"/>
       <c r="D44" s="7" t="n"/>
       <c r="E44" s="7" t="n"/>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F44" s="7" t="n"/>
       <c r="G44" s="7" t="n"/>
       <c r="H44" s="7" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C45" s="7" t="n"/>
@@ -1274,15 +1274,15 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B46" s="7" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D46" s="7" t="n"/>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="7" t="n"/>
@@ -1292,13 +1292,13 @@
       <c r="A47" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+      <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="n"/>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E47" s="7" t="n"/>
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="7" t="n"/>
@@ -1308,13 +1308,13 @@
       <c r="A48" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+      <c r="B48" s="7" t="n"/>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="n"/>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
@@ -1324,13 +1324,13 @@
       <c r="A49" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B49" s="7" t="n"/>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="n"/>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Tetairoa McMillan</t>
+        </is>
+      </c>
       <c r="E49" s="7" t="n"/>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n"/>
@@ -1342,13 +1342,13 @@
       </c>
       <c r="B50" s="7" t="n"/>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
-      <c r="F50" s="7" t="n"/>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G50" s="7" t="n"/>
       <c r="H50" s="7" t="n"/>
     </row>
@@ -1370,11 +1370,11 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C52" s="7" t="n"/>
@@ -1386,15 +1386,15 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B53" s="7" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D53" s="7" t="n"/>
       <c r="E53" s="7" t="n"/>
       <c r="F53" s="7" t="n"/>
       <c r="G53" s="7" t="n"/>
@@ -1402,23 +1402,23 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
-      <c r="D54" s="7" t="n"/>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E54" s="7" t="n"/>
-      <c r="F54" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F54" s="7" t="n"/>
       <c r="G54" s="7" t="n"/>
       <c r="H54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B55" s="7" t="n"/>
       <c r="C55" s="7" t="n"/>
@@ -1426,7 +1426,7 @@
       <c r="E55" s="7" t="n"/>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>Isaiah Likely</t>
+          <t>Colston Loveland</t>
         </is>
       </c>
       <c r="G55" s="7" t="n"/>
@@ -1436,33 +1436,33 @@
       <c r="A56" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B56" s="7" t="n"/>
       <c r="C56" s="7" t="n"/>
       <c r="D56" s="7" t="n"/>
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="n"/>
-      <c r="H56" s="7" t="n"/>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B57" s="7" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C57" s="7" t="n"/>
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
       <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
-      <c r="H57" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
@@ -1472,7 +1472,7 @@
       <c r="C58" s="7" t="n"/>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E58" s="7" t="n"/>
@@ -1482,15 +1482,15 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B59" s="7" t="n"/>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="7" t="n"/>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E59" s="7" t="n"/>
       <c r="F59" s="7" t="n"/>
       <c r="G59" s="7" t="n"/>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B60" s="7" t="n"/>
       <c r="C60" s="7" t="n"/>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E60" s="7" t="n"/>
@@ -1518,31 +1518,31 @@
       </c>
       <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
-      <c r="F61" s="7" t="n"/>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G61" s="7" t="n"/>
       <c r="H61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B62" s="7" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C62" s="7" t="n"/>
       <c r="D62" s="7" t="n"/>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="7" t="n"/>
-      <c r="H62" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C63" s="7" t="n"/>
@@ -1568,7 +1568,7 @@
       <c r="C64" s="7" t="n"/>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="E64" s="7" t="n"/>
@@ -1610,35 +1610,35 @@
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B67" s="7" t="n"/>
       <c r="C67" s="7" t="n"/>
       <c r="D67" s="7" t="n"/>
       <c r="E67" s="7" t="n"/>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
-      <c r="H67" s="7" t="n"/>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B68" s="7" t="n"/>
       <c r="C68" s="7" t="n"/>
       <c r="D68" s="7" t="n"/>
       <c r="E68" s="7" t="n"/>
       <c r="F68" s="7" t="n"/>
       <c r="G68" s="7" t="n"/>
-      <c r="H68" s="7" t="n"/>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="C69" s="7" t="n"/>
@@ -1676,13 +1676,13 @@
       <c r="A71" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B71" s="7" t="n"/>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C71" s="7" t="n"/>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D71" s="7" t="n"/>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
@@ -1710,29 +1710,29 @@
       </c>
       <c r="B73" s="7" t="n"/>
       <c r="C73" s="7" t="n"/>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D73" s="7" t="n"/>
       <c r="E73" s="7" t="n"/>
-      <c r="F73" s="7" t="n"/>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G73" s="7" t="n"/>
       <c r="H73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B74" s="7" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C74" s="7" t="n"/>
       <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
-      <c r="F74" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
       <c r="H74" s="7" t="n"/>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C75" s="7" t="n"/>
@@ -1756,13 +1756,13 @@
       <c r="A76" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
+      <c r="B76" s="7" t="n"/>
       <c r="C76" s="7" t="n"/>
-      <c r="D76" s="7" t="n"/>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E76" s="7" t="n"/>
       <c r="F76" s="7" t="n"/>
       <c r="G76" s="7" t="n"/>
@@ -1772,13 +1772,13 @@
       <c r="A77" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+      <c r="B77" s="7" t="n"/>
       <c r="C77" s="7" t="n"/>
-      <c r="D77" s="7" t="n"/>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E77" s="7" t="n"/>
       <c r="F77" s="7" t="n"/>
       <c r="G77" s="7" t="n"/>
@@ -1790,27 +1790,27 @@
       </c>
       <c r="B78" s="7" t="n"/>
       <c r="C78" s="7" t="n"/>
-      <c r="D78" s="7" t="n"/>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E78" s="7" t="n"/>
-      <c r="F78" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F78" s="7" t="n"/>
       <c r="G78" s="7" t="n"/>
       <c r="H78" s="7" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>Jonathon Brooks</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B79" s="7" t="n"/>
       <c r="C79" s="7" t="n"/>
-      <c r="D79" s="7" t="n"/>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>Marvin Harrison Jr.</t>
+        </is>
+      </c>
       <c r="E79" s="7" t="n"/>
       <c r="F79" s="7" t="n"/>
       <c r="G79" s="7" t="n"/>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C80" s="7" t="n"/>
@@ -1836,13 +1836,13 @@
       <c r="A81" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B81" s="7" t="n"/>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C81" s="7" t="n"/>
-      <c r="D81" s="7" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D81" s="7" t="n"/>
       <c r="E81" s="7" t="n"/>
       <c r="F81" s="7" t="n"/>
       <c r="G81" s="7" t="n"/>
@@ -1852,13 +1852,13 @@
       <c r="A82" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B82" s="7" t="n"/>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>Jonathon Brooks</t>
+        </is>
+      </c>
       <c r="C82" s="7" t="n"/>
-      <c r="D82" s="7" t="inlineStr">
-        <is>
-          <t>Jameson Williams</t>
-        </is>
-      </c>
+      <c r="D82" s="7" t="n"/>
       <c r="E82" s="7" t="n"/>
       <c r="F82" s="7" t="n"/>
       <c r="G82" s="7" t="n"/>
@@ -1868,13 +1868,13 @@
       <c r="A83" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B83" s="7" t="n"/>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>Mike Washington Jr.</t>
+        </is>
+      </c>
       <c r="C83" s="7" t="n"/>
-      <c r="D83" s="7" t="inlineStr">
-        <is>
-          <t>De'Zhaun Stribling</t>
-        </is>
-      </c>
+      <c r="D83" s="7" t="n"/>
       <c r="E83" s="7" t="n"/>
       <c r="F83" s="7" t="n"/>
       <c r="G83" s="7" t="n"/>
@@ -1884,13 +1884,13 @@
       <c r="A84" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B84" s="7" t="n"/>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>Rico Dowdle</t>
+        </is>
+      </c>
       <c r="C84" s="7" t="n"/>
-      <c r="D84" s="7" t="inlineStr">
-        <is>
-          <t>Quentin Johnston</t>
-        </is>
-      </c>
+      <c r="D84" s="7" t="n"/>
       <c r="E84" s="7" t="n"/>
       <c r="F84" s="7" t="n"/>
       <c r="G84" s="7" t="n"/>
@@ -1900,25 +1900,25 @@
       <c r="A85" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B85" s="7" t="n"/>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>J.K. Dobbins</t>
+        </is>
+      </c>
       <c r="C85" s="7" t="n"/>
       <c r="D85" s="7" t="n"/>
       <c r="E85" s="7" t="n"/>
       <c r="F85" s="7" t="n"/>
       <c r="G85" s="7" t="n"/>
-      <c r="H85" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H85" s="7" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="C86" s="7" t="n"/>
@@ -1930,11 +1930,11 @@
     </row>
     <row r="87">
       <c r="A87" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>Blake Corum</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="C87" s="7" t="n"/>
@@ -1946,13 +1946,13 @@
     </row>
     <row r="88">
       <c r="A88" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B88" s="7" t="n"/>
       <c r="C88" s="7" t="n"/>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Terry McLaurin</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E88" s="7" t="n"/>
@@ -1962,13 +1962,13 @@
     </row>
     <row r="89">
       <c r="A89" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B89" s="7" t="n"/>
       <c r="C89" s="7" t="n"/>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E89" s="7" t="n"/>
@@ -1978,13 +1978,13 @@
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B90" s="7" t="n"/>
       <c r="C90" s="7" t="n"/>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E90" s="7" t="n"/>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B91" s="7" t="n"/>
       <c r="C91" s="7" t="n"/>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B92" s="7" t="n"/>
       <c r="C92" s="7" t="n"/>
@@ -2026,7 +2026,7 @@
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B93" s="7" t="n"/>
       <c r="C93" s="7" t="n"/>
@@ -2042,7 +2042,7 @@
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B94" s="7" t="n"/>
       <c r="C94" s="7" t="n"/>
@@ -2058,7 +2058,7 @@
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B95" s="7" t="n"/>
       <c r="C95" s="7" t="n"/>
@@ -2074,15 +2074,15 @@
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B96" s="7" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B96" s="7" t="n"/>
       <c r="C96" s="7" t="n"/>
-      <c r="D96" s="7" t="n"/>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>Terry McLaurin</t>
+        </is>
+      </c>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="7" t="n"/>
       <c r="G96" s="7" t="n"/>
@@ -2090,15 +2090,15 @@
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B97" s="7" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B97" s="7" t="n"/>
       <c r="C97" s="7" t="n"/>
-      <c r="D97" s="7" t="n"/>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>Alec Pierce</t>
+        </is>
+      </c>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="7" t="n"/>
       <c r="G97" s="7" t="n"/>
@@ -2106,13 +2106,13 @@
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B98" s="7" t="n"/>
       <c r="C98" s="7" t="n"/>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Ja'Kobi Lane</t>
         </is>
       </c>
       <c r="E98" s="7" t="n"/>
@@ -2122,31 +2122,31 @@
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B99" s="7" t="n"/>
       <c r="C99" s="7" t="n"/>
-      <c r="D99" s="7" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D99" s="7" t="n"/>
       <c r="E99" s="7" t="n"/>
       <c r="F99" s="7" t="n"/>
       <c r="G99" s="7" t="n"/>
-      <c r="H99" s="7" t="n"/>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B100" s="7" t="n"/>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>Rachaad White</t>
+        </is>
+      </c>
       <c r="C100" s="7" t="n"/>
-      <c r="D100" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
+      <c r="D100" s="7" t="n"/>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="7" t="n"/>
       <c r="G100" s="7" t="n"/>
@@ -2158,15 +2158,15 @@
       </c>
       <c r="B101" s="7" t="n"/>
       <c r="C101" s="7" t="n"/>
-      <c r="D101" s="7" t="n"/>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>Carnell Tate</t>
+        </is>
+      </c>
       <c r="E101" s="7" t="n"/>
       <c r="F101" s="7" t="n"/>
       <c r="G101" s="7" t="n"/>
-      <c r="H101" s="7" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H101" s="7" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="n">
@@ -2218,15 +2218,15 @@
     </row>
     <row r="105">
       <c r="A105" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B105" s="7" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B105" s="7" t="n"/>
       <c r="C105" s="7" t="n"/>
-      <c r="D105" s="7" t="n"/>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E105" s="7" t="n"/>
       <c r="F105" s="7" t="n"/>
       <c r="G105" s="7" t="n"/>
@@ -2295,7 +2295,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 76.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 75.</t>
         </is>
       </c>
     </row>
@@ -2312,14 +2312,14 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>0) Weekly re-seed. The sheet values were first moved toward the 2026 week 7 Half PPR medians</t>
+          <t>0) Weekly re-seed. The sheet values were first moved toward the 2026 week 6 Half PPR medians</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 0; 32 players used week 6 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 12; 11 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,14 +2333,14 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 69 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 71 players moved.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   No projection this week (value kept): Amon-Ra St. Brown, Saquon Barkley, Chase Brown, Breece Hall, DeVonta Smith, Rashee Rice, Lamar Jackson, Travis Etienne Jr., Jadarian Price, David Montgomery, Josh Jacobs, De'Zhaun Stribling, Jordan Mason, Alec Pierce, Brian Thomas Jr., Marvin Harrison Jr., Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Aaron Jones Sr., Jaxson Dart, Ja'Kobi Lane.</t>
+          <t xml:space="preserve">   No projection this week (value kept): Saquon Barkley, Breece Hall, DeVonta Smith, Rashee Rice, Lamar Jackson, Travis Etienne Jr., Jadarian Price, Josh Jacobs, De'Zhaun Stribling, Jordan Mason, Alec Pierce, Brian Thomas Jr., Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Jaxson Dart, Ja'Kobi Lane.</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.8, WR 3.0, TE 4.5, QB 0.0.</t>
+          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.5, WR 3.0, TE 4.5, QB 0.0.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 63-&gt;54, Chris Olave 34-&gt;25, Puka Nacua 69-&gt;61, Amon-Ra St. Brown 60-&gt;52, Trey McBride 43.4286-&gt;36, Ja'Marr Chase 63-&gt;56, Justin Jefferson 43-&gt;36, CeeDee Lamb 51-&gt;44</t>
+          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 62-&gt;54, Chris Olave 41-&gt;33, Trey McBride 42.8571-&gt;35, Puka Nacua 70-&gt;63, Ja'Marr Chase 60-&gt;53, Justin Jefferson 47-&gt;40, DeVonta Smith 27-&gt;20, Rashee Rice 26-&gt;19</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -634,15 +634,15 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>63</v>
-      </c>
-      <c r="B6" s="7" t="n"/>
+        <v>64</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="7" t="n"/>
       <c r="G6" s="7" t="n"/>
@@ -650,15 +650,15 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>62</v>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="B7" s="7" t="n"/>
       <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="7" t="n"/>
@@ -666,11 +666,11 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C8" s="7" t="n"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>James Cook III</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C9" s="7" t="n"/>
@@ -698,11 +698,11 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>James Cook III</t>
         </is>
       </c>
       <c r="C10" s="7" t="n"/>
@@ -778,11 +778,11 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Saquon Barkley</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="C15" s="7" t="n"/>
@@ -794,47 +794,47 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Kyren Williams</t>
-        </is>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
       <c r="D16" s="7" t="n"/>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>43</v>
-      </c>
-      <c r="B18" s="7" t="n"/>
+        <v>41</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
@@ -842,7 +842,7 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
@@ -858,11 +858,11 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C20" s="7" t="n"/>
@@ -876,13 +876,13 @@
       <c r="A21" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+      <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
@@ -890,15 +890,15 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="B22" s="7" t="n"/>
+        <v>39</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
@@ -906,19 +906,19 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
       <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
@@ -940,13 +940,13 @@
       <c r="A25" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="B25" s="7" t="n"/>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
@@ -958,39 +958,39 @@
       </c>
       <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Breece Hall</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
       <c r="D27" s="7" t="n"/>
       <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G27" s="7" t="n"/>
       <c r="H27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C28" s="7" t="n"/>
@@ -1002,15 +1002,15 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="7" t="n"/>
+        <v>31</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>D'Andre Swift</t>
+        </is>
+      </c>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D29" s="7" t="n"/>
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="7" t="n"/>
@@ -1018,15 +1018,15 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="7" t="n"/>
+        <v>30</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D30" s="7" t="n"/>
       <c r="E30" s="7" t="n"/>
       <c r="F30" s="7" t="n"/>
       <c r="G30" s="7" t="n"/>
@@ -1034,15 +1034,15 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="7" t="n"/>
       <c r="G31" s="7" t="n"/>
@@ -1050,31 +1050,31 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="B33" s="7" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
+      <c r="D33" s="7" t="n"/>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
@@ -1082,29 +1082,29 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D34" s="7" t="n"/>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="n"/>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E35" s="7" t="n"/>
@@ -1114,13 +1114,13 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="E36" s="7" t="n"/>
@@ -1130,13 +1130,13 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E37" s="7" t="n"/>
@@ -1146,29 +1146,29 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Garrett Wilson</t>
-        </is>
-      </c>
+      <c r="D38" s="7" t="n"/>
       <c r="E38" s="7" t="n"/>
-      <c r="F38" s="7" t="n"/>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G38" s="7" t="n"/>
       <c r="H38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E39" s="7" t="n"/>
@@ -1178,15 +1178,15 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="n"/>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Mike Evans</t>
+        </is>
+      </c>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
@@ -1194,13 +1194,13 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E41" s="7" t="n"/>
@@ -1210,15 +1210,15 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B42" s="7" t="n"/>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="n"/>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>A.J. Brown</t>
+        </is>
+      </c>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="7" t="n"/>
@@ -1226,31 +1226,31 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B43" s="7" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Omarion Hampton</t>
+        </is>
+      </c>
       <c r="C43" s="7" t="n"/>
       <c r="D43" s="7" t="n"/>
       <c r="E43" s="7" t="n"/>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F43" s="7" t="n"/>
       <c r="G43" s="7" t="n"/>
       <c r="H43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="n"/>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Rashee Rice</t>
+        </is>
+      </c>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="7" t="n"/>
@@ -1258,11 +1258,11 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C45" s="7" t="n"/>
@@ -1274,15 +1274,15 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="n"/>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="7" t="n"/>
@@ -1290,13 +1290,13 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="n"/>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E47" s="7" t="n"/>
@@ -1306,15 +1306,15 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B48" s="7" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D48" s="7" t="n"/>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
@@ -1322,15 +1322,15 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B49" s="7" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D49" s="7" t="n"/>
       <c r="E49" s="7" t="n"/>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n"/>
@@ -1338,27 +1338,27 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B50" s="7" t="n"/>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="n"/>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E50" s="7" t="n"/>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F50" s="7" t="n"/>
       <c r="G50" s="7" t="n"/>
       <c r="H50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C51" s="7" t="n"/>
@@ -1370,11 +1370,11 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr.</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C52" s="7" t="n"/>
@@ -1386,15 +1386,15 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B53" s="7" t="n"/>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="7" t="n"/>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E53" s="7" t="n"/>
       <c r="F53" s="7" t="n"/>
       <c r="G53" s="7" t="n"/>
@@ -1402,33 +1402,33 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D54" s="7" t="n"/>
       <c r="E54" s="7" t="n"/>
-      <c r="F54" s="7" t="n"/>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G54" s="7" t="n"/>
       <c r="H54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B55" s="7" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C55" s="7" t="n"/>
       <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F55" s="7" t="n"/>
       <c r="G55" s="7" t="n"/>
       <c r="H55" s="7" t="n"/>
     </row>
@@ -1436,25 +1436,25 @@
       <c r="A56" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B56" s="7" t="n"/>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C56" s="7" t="n"/>
       <c r="D56" s="7" t="n"/>
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="n"/>
-      <c r="H56" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C57" s="7" t="n"/>
@@ -1466,47 +1466,47 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B58" s="7" t="n"/>
       <c r="C58" s="7" t="n"/>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
-      <c r="F58" s="7" t="n"/>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B59" s="7" t="n"/>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
       <c r="F59" s="7" t="n"/>
       <c r="G59" s="7" t="n"/>
-      <c r="H59" s="7" t="n"/>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B60" s="7" t="n"/>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C60" s="7" t="n"/>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D60" s="7" t="n"/>
       <c r="E60" s="7" t="n"/>
       <c r="F60" s="7" t="n"/>
       <c r="G60" s="7" t="n"/>
@@ -1514,31 +1514,31 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="n"/>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E61" s="7" t="n"/>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
       <c r="H61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B62" s="7" t="n"/>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="n"/>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="7" t="n"/>
@@ -1546,15 +1546,15 @@
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B63" s="7" t="n"/>
       <c r="C63" s="7" t="n"/>
-      <c r="D63" s="7" t="n"/>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E63" s="7" t="n"/>
       <c r="F63" s="7" t="n"/>
       <c r="G63" s="7" t="n"/>
@@ -1562,17 +1562,17 @@
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B64" s="7" t="n"/>
       <c r="C64" s="7" t="n"/>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D64" s="7" t="n"/>
       <c r="E64" s="7" t="n"/>
-      <c r="F64" s="7" t="n"/>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G64" s="7" t="n"/>
       <c r="H64" s="7" t="n"/>
     </row>
@@ -1580,13 +1580,13 @@
       <c r="A65" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B65" s="7" t="n"/>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C65" s="7" t="n"/>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D65" s="7" t="n"/>
       <c r="E65" s="7" t="n"/>
       <c r="F65" s="7" t="n"/>
       <c r="G65" s="7" t="n"/>
@@ -1598,15 +1598,15 @@
       </c>
       <c r="B66" s="7" t="n"/>
       <c r="C66" s="7" t="n"/>
-      <c r="D66" s="7" t="n"/>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E66" s="7" t="n"/>
       <c r="F66" s="7" t="n"/>
       <c r="G66" s="7" t="n"/>
-      <c r="H66" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
@@ -1614,15 +1614,15 @@
       </c>
       <c r="B67" s="7" t="n"/>
       <c r="C67" s="7" t="n"/>
-      <c r="D67" s="7" t="n"/>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E67" s="7" t="n"/>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
-      <c r="H67" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
@@ -1636,25 +1636,25 @@
       <c r="G68" s="7" t="n"/>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B69" s="7" t="n"/>
       <c r="C69" s="7" t="n"/>
       <c r="D69" s="7" t="n"/>
       <c r="E69" s="7" t="n"/>
       <c r="F69" s="7" t="n"/>
       <c r="G69" s="7" t="n"/>
-      <c r="H69" s="7" t="n"/>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="C70" s="7" t="n"/>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>Woody Marks</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C71" s="7" t="n"/>
@@ -1692,13 +1692,13 @@
       <c r="A72" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B72" s="7" t="n"/>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C72" s="7" t="n"/>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>Brian Thomas Jr.</t>
-        </is>
-      </c>
+      <c r="D72" s="7" t="n"/>
       <c r="E72" s="7" t="n"/>
       <c r="F72" s="7" t="n"/>
       <c r="G72" s="7" t="n"/>
@@ -1710,27 +1710,27 @@
       </c>
       <c r="B73" s="7" t="n"/>
       <c r="C73" s="7" t="n"/>
-      <c r="D73" s="7" t="n"/>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E73" s="7" t="n"/>
-      <c r="F73" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
       <c r="H73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B74" s="7" t="n"/>
       <c r="C74" s="7" t="n"/>
-      <c r="D74" s="7" t="n"/>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E74" s="7" t="n"/>
       <c r="F74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
@@ -1738,17 +1738,17 @@
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B75" s="7" t="n"/>
       <c r="C75" s="7" t="n"/>
       <c r="D75" s="7" t="n"/>
       <c r="E75" s="7" t="n"/>
-      <c r="F75" s="7" t="n"/>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G75" s="7" t="n"/>
       <c r="H75" s="7" t="n"/>
     </row>
@@ -1756,13 +1756,13 @@
       <c r="A76" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B76" s="7" t="n"/>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C76" s="7" t="n"/>
-      <c r="D76" s="7" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D76" s="7" t="n"/>
       <c r="E76" s="7" t="n"/>
       <c r="F76" s="7" t="n"/>
       <c r="G76" s="7" t="n"/>
@@ -1772,13 +1772,13 @@
       <c r="A77" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B77" s="7" t="n"/>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Cam Skattebo</t>
+        </is>
+      </c>
       <c r="C77" s="7" t="n"/>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D77" s="7" t="n"/>
       <c r="E77" s="7" t="n"/>
       <c r="F77" s="7" t="n"/>
       <c r="G77" s="7" t="n"/>
@@ -1792,7 +1792,7 @@
       <c r="C78" s="7" t="n"/>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E78" s="7" t="n"/>
@@ -1808,7 +1808,7 @@
       <c r="C79" s="7" t="n"/>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="E79" s="7" t="n"/>
@@ -1818,15 +1818,15 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B80" s="7" t="n"/>
       <c r="C80" s="7" t="n"/>
-      <c r="D80" s="7" t="n"/>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E80" s="7" t="n"/>
       <c r="F80" s="7" t="n"/>
       <c r="G80" s="7" t="n"/>
@@ -1834,15 +1834,15 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B81" s="7" t="n"/>
       <c r="C81" s="7" t="n"/>
-      <c r="D81" s="7" t="n"/>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>Marvin Harrison Jr.</t>
+        </is>
+      </c>
       <c r="E81" s="7" t="n"/>
       <c r="F81" s="7" t="n"/>
       <c r="G81" s="7" t="n"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C82" s="7" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C83" s="7" t="n"/>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C84" s="7" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C85" s="7" t="n"/>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>Blake Corum</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C86" s="7" t="n"/>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="C87" s="7" t="n"/>
@@ -1948,13 +1948,13 @@
       <c r="A88" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B88" s="7" t="n"/>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C88" s="7" t="n"/>
-      <c r="D88" s="7" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D88" s="7" t="n"/>
       <c r="E88" s="7" t="n"/>
       <c r="F88" s="7" t="n"/>
       <c r="G88" s="7" t="n"/>
@@ -1968,7 +1968,7 @@
       <c r="C89" s="7" t="n"/>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E89" s="7" t="n"/>
@@ -1984,7 +1984,7 @@
       <c r="C90" s="7" t="n"/>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E90" s="7" t="n"/>
@@ -2000,7 +2000,7 @@
       <c r="C91" s="7" t="n"/>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr.</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E91" s="7" t="n"/>
@@ -2014,13 +2014,13 @@
       </c>
       <c r="B92" s="7" t="n"/>
       <c r="C92" s="7" t="n"/>
-      <c r="D92" s="7" t="n"/>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>Chris Godwin Jr.</t>
+        </is>
+      </c>
       <c r="E92" s="7" t="n"/>
-      <c r="F92" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F92" s="7" t="n"/>
       <c r="G92" s="7" t="n"/>
       <c r="H92" s="7" t="n"/>
     </row>
@@ -2032,13 +2032,13 @@
       <c r="C93" s="7" t="n"/>
       <c r="D93" s="7" t="n"/>
       <c r="E93" s="7" t="n"/>
-      <c r="F93" s="7" t="n"/>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G93" s="7" t="n"/>
-      <c r="H93" s="7" t="inlineStr">
-        <is>
-          <t>Jalen Hurts</t>
-        </is>
-      </c>
+      <c r="H93" s="7" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
@@ -2052,7 +2052,7 @@
       <c r="G94" s="7" t="n"/>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
     </row>
@@ -2068,25 +2068,25 @@
       <c r="G95" s="7" t="n"/>
       <c r="H95" s="7" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B96" s="7" t="n"/>
       <c r="C96" s="7" t="n"/>
-      <c r="D96" s="7" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D96" s="7" t="n"/>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="7" t="n"/>
       <c r="G96" s="7" t="n"/>
-      <c r="H96" s="7" t="n"/>
+      <c r="H96" s="7" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
@@ -2096,7 +2096,7 @@
       <c r="C97" s="7" t="n"/>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E97" s="7" t="n"/>
@@ -2112,7 +2112,7 @@
       <c r="C98" s="7" t="n"/>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E98" s="7" t="n"/>
@@ -2126,43 +2126,43 @@
       </c>
       <c r="B99" s="7" t="n"/>
       <c r="C99" s="7" t="n"/>
-      <c r="D99" s="7" t="n"/>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E99" s="7" t="n"/>
       <c r="F99" s="7" t="n"/>
       <c r="G99" s="7" t="n"/>
-      <c r="H99" s="7" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B100" s="7" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B100" s="7" t="n"/>
       <c r="C100" s="7" t="n"/>
       <c r="D100" s="7" t="n"/>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="7" t="n"/>
       <c r="G100" s="7" t="n"/>
-      <c r="H100" s="7" t="n"/>
+      <c r="H100" s="7" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B101" s="7" t="n"/>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>Rachaad White</t>
+        </is>
+      </c>
       <c r="C101" s="7" t="n"/>
-      <c r="D101" s="7" t="inlineStr">
-        <is>
-          <t>Carnell Tate</t>
-        </is>
-      </c>
+      <c r="D101" s="7" t="n"/>
       <c r="E101" s="7" t="n"/>
       <c r="F101" s="7" t="n"/>
       <c r="G101" s="7" t="n"/>
@@ -2170,13 +2170,13 @@
     </row>
     <row r="102">
       <c r="A102" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B102" s="7" t="n"/>
       <c r="C102" s="7" t="n"/>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="E102" s="7" t="n"/>
@@ -2192,7 +2192,7 @@
       <c r="C103" s="7" t="n"/>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E103" s="7" t="n"/>
@@ -2208,7 +2208,7 @@
       <c r="C104" s="7" t="n"/>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E104" s="7" t="n"/>
@@ -2224,7 +2224,7 @@
       <c r="C105" s="7" t="n"/>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="E105" s="7" t="n"/>
@@ -2392,7 +2392,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.5, WR 3.0, TE 4.5, QB 0.0.</t>
+          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.5, WR 2.9, TE 4.5, QB 0.0.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 62-&gt;54, Chris Olave 41-&gt;33, Trey McBride 42.8571-&gt;35, Puka Nacua 70-&gt;63, Ja'Marr Chase 60-&gt;53, Justin Jefferson 47-&gt;40, DeVonta Smith 27-&gt;20, Rashee Rice 26-&gt;19</t>
+          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 62-&gt;54, Chris Olave 41-&gt;33, Trey McBride 42.8571-&gt;35, Puka Nacua 70-&gt;63, Ja'Marr Chase 60-&gt;53, Justin Jefferson 47-&gt;40, Drake London 48-&gt;41, DeVonta Smith 27-&gt;20</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -618,7 +618,7 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B7" s="7" t="n"/>
       <c r="C7" s="7" t="n"/>
@@ -666,7 +666,7 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
@@ -682,11 +682,11 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>James Cook III</t>
         </is>
       </c>
       <c r="C9" s="7" t="n"/>
@@ -698,11 +698,11 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>James Cook III</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="C10" s="7" t="n"/>
@@ -714,13 +714,13 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -746,13 +746,13 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E13" s="7" t="n"/>
@@ -762,11 +762,11 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="C14" s="7" t="n"/>
@@ -778,11 +778,11 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C15" s="7" t="n"/>
@@ -794,23 +794,23 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="B16" s="7" t="n"/>
+        <v>45</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Ashton Jeanty</t>
+        </is>
+      </c>
       <c r="C16" s="7" t="n"/>
       <c r="D16" s="7" t="n"/>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>Josh Allen</t>
-        </is>
-      </c>
+      <c r="H16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="n"/>
@@ -826,31 +826,31 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="n"/>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Josh Allen</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="B19" s="7" t="n"/>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
@@ -858,23 +858,23 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
       <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="n"/>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
@@ -890,49 +890,49 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
       <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="B23" s="7" t="n"/>
+        <v>35</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C23" s="7" t="n"/>
       <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
     </row>
@@ -958,39 +958,39 @@
       </c>
       <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="B27" s="7" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Breece Hall</t>
+        </is>
+      </c>
       <c r="C27" s="7" t="n"/>
       <c r="D27" s="7" t="n"/>
       <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
       <c r="H27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="C28" s="7" t="n"/>
@@ -1002,15 +1002,15 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="7" t="n"/>
@@ -1018,11 +1018,11 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C30" s="7" t="n"/>
@@ -1034,13 +1034,13 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Nico Collins</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E31" s="7" t="n"/>
@@ -1050,15 +1050,15 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="B32" s="7" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Malik Nabers</t>
-        </is>
-      </c>
+      <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
@@ -1068,13 +1068,13 @@
       <c r="A33" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+      <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="n"/>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
@@ -1082,19 +1082,19 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="n"/>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Tee Higgins</t>
+        </is>
+      </c>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="inlineStr">
-        <is>
-          <t>Lamar Jackson</t>
-        </is>
-      </c>
+      <c r="H34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
@@ -1104,7 +1104,7 @@
       <c r="C35" s="7" t="n"/>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="E35" s="7" t="n"/>
@@ -1118,13 +1118,13 @@
       </c>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>Tee Higgins</t>
-        </is>
-      </c>
+      <c r="D36" s="7" t="n"/>
       <c r="E36" s="7" t="n"/>
-      <c r="F36" s="7" t="n"/>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
       <c r="G36" s="7" t="n"/>
       <c r="H36" s="7" t="n"/>
     </row>
@@ -1134,29 +1134,29 @@
       </c>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>Tetairoa McMillan</t>
-        </is>
-      </c>
+      <c r="D37" s="7" t="n"/>
       <c r="E37" s="7" t="n"/>
       <c r="F37" s="7" t="n"/>
       <c r="G37" s="7" t="n"/>
-      <c r="H37" s="7" t="n"/>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>Lamar Jackson</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="n"/>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
       <c r="E38" s="7" t="n"/>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
+      <c r="F38" s="7" t="n"/>
       <c r="G38" s="7" t="n"/>
       <c r="H38" s="7" t="n"/>
     </row>
@@ -1168,7 +1168,7 @@
       <c r="C39" s="7" t="n"/>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E39" s="7" t="n"/>
@@ -1180,13 +1180,13 @@
       <c r="A40" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="B40" s="7" t="n"/>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D40" s="7" t="n"/>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
@@ -1194,13 +1194,13 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E41" s="7" t="n"/>
@@ -1210,13 +1210,13 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B42" s="7" t="n"/>
       <c r="C42" s="7" t="n"/>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E42" s="7" t="n"/>
@@ -1226,15 +1226,15 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>Omarion Hampton</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B43" s="7" t="n"/>
       <c r="C43" s="7" t="n"/>
-      <c r="D43" s="7" t="n"/>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>DeVonta Smith</t>
+        </is>
+      </c>
       <c r="E43" s="7" t="n"/>
       <c r="F43" s="7" t="n"/>
       <c r="G43" s="7" t="n"/>
@@ -1242,13 +1242,13 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="n"/>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E44" s="7" t="n"/>
@@ -1258,11 +1258,11 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="C45" s="7" t="n"/>
@@ -1274,13 +1274,13 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="E46" s="7" t="n"/>
@@ -1290,15 +1290,15 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="B47" s="7" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D47" s="7" t="n"/>
       <c r="E47" s="7" t="n"/>
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="7" t="n"/>
@@ -1306,15 +1306,15 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Jadarian Price</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B48" s="7" t="n"/>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="n"/>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
@@ -1322,11 +1322,11 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Jadarian Price</t>
         </is>
       </c>
       <c r="C49" s="7" t="n"/>
@@ -1340,13 +1340,13 @@
       <c r="A50" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B50" s="7" t="n"/>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
       <c r="F50" s="7" t="n"/>
       <c r="G50" s="7" t="n"/>
@@ -1370,15 +1370,15 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B52" s="7" t="n"/>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="7" t="n"/>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="7" t="n"/>
@@ -1388,13 +1388,13 @@
       <c r="A53" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B53" s="7" t="n"/>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Jeremiyah Love</t>
+        </is>
+      </c>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>Davante Adams</t>
-        </is>
-      </c>
+      <c r="D53" s="7" t="n"/>
       <c r="E53" s="7" t="n"/>
       <c r="F53" s="7" t="n"/>
       <c r="G53" s="7" t="n"/>
@@ -1406,13 +1406,13 @@
       </c>
       <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
-      <c r="D54" s="7" t="n"/>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E54" s="7" t="n"/>
-      <c r="F54" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F54" s="7" t="n"/>
       <c r="G54" s="7" t="n"/>
       <c r="H54" s="7" t="n"/>
     </row>
@@ -1420,13 +1420,13 @@
       <c r="A55" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+      <c r="B55" s="7" t="n"/>
       <c r="C55" s="7" t="n"/>
-      <c r="D55" s="7" t="n"/>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Waddle</t>
+        </is>
+      </c>
       <c r="E55" s="7" t="n"/>
       <c r="F55" s="7" t="n"/>
       <c r="G55" s="7" t="n"/>
@@ -1434,33 +1434,33 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B56" s="7" t="n"/>
       <c r="C56" s="7" t="n"/>
       <c r="D56" s="7" t="n"/>
       <c r="E56" s="7" t="n"/>
-      <c r="F56" s="7" t="n"/>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G56" s="7" t="n"/>
       <c r="H56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B57" s="7" t="n"/>
       <c r="C57" s="7" t="n"/>
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
-      <c r="F57" s="7" t="n"/>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G57" s="7" t="n"/>
       <c r="H57" s="7" t="n"/>
     </row>
@@ -1468,15 +1468,15 @@
       <c r="A58" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B58" s="7" t="n"/>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C58" s="7" t="n"/>
       <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
     </row>
@@ -1484,25 +1484,25 @@
       <c r="A59" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B59" s="7" t="n"/>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C59" s="7" t="n"/>
       <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
       <c r="F59" s="7" t="n"/>
       <c r="G59" s="7" t="n"/>
-      <c r="H59" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H59" s="7" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C60" s="7" t="n"/>
@@ -1514,19 +1514,19 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
       <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
-      <c r="H61" s="7" t="n"/>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>Joe Burrow</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
@@ -1546,15 +1546,15 @@
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B63" s="7" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C63" s="7" t="n"/>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D63" s="7" t="n"/>
       <c r="E63" s="7" t="n"/>
       <c r="F63" s="7" t="n"/>
       <c r="G63" s="7" t="n"/>
@@ -1566,27 +1566,27 @@
       </c>
       <c r="B64" s="7" t="n"/>
       <c r="C64" s="7" t="n"/>
-      <c r="D64" s="7" t="n"/>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E64" s="7" t="n"/>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>Tyler Warren</t>
-        </is>
-      </c>
+      <c r="F64" s="7" t="n"/>
       <c r="G64" s="7" t="n"/>
       <c r="H64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B65" s="7" t="n"/>
       <c r="C65" s="7" t="n"/>
-      <c r="D65" s="7" t="n"/>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E65" s="7" t="n"/>
       <c r="F65" s="7" t="n"/>
       <c r="G65" s="7" t="n"/>
@@ -1594,31 +1594,31 @@
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B66" s="7" t="n"/>
       <c r="C66" s="7" t="n"/>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D66" s="7" t="n"/>
       <c r="E66" s="7" t="n"/>
       <c r="F66" s="7" t="n"/>
       <c r="G66" s="7" t="n"/>
-      <c r="H66" s="7" t="n"/>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B67" s="7" t="n"/>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C67" s="7" t="n"/>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D67" s="7" t="n"/>
       <c r="E67" s="7" t="n"/>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
@@ -1630,15 +1630,15 @@
       </c>
       <c r="B68" s="7" t="n"/>
       <c r="C68" s="7" t="n"/>
-      <c r="D68" s="7" t="n"/>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E68" s="7" t="n"/>
       <c r="F68" s="7" t="n"/>
       <c r="G68" s="7" t="n"/>
-      <c r="H68" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
@@ -1648,13 +1648,13 @@
       <c r="C69" s="7" t="n"/>
       <c r="D69" s="7" t="n"/>
       <c r="E69" s="7" t="n"/>
-      <c r="F69" s="7" t="n"/>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G69" s="7" t="n"/>
-      <c r="H69" s="7" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
+      <c r="H69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C70" s="7" t="n"/>
@@ -1676,13 +1676,13 @@
       <c r="A71" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+      <c r="B71" s="7" t="n"/>
       <c r="C71" s="7" t="n"/>
-      <c r="D71" s="7" t="n"/>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>Luther Burden III</t>
+        </is>
+      </c>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
@@ -1692,13 +1692,13 @@
       <c r="A72" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
+      <c r="B72" s="7" t="n"/>
       <c r="C72" s="7" t="n"/>
-      <c r="D72" s="7" t="n"/>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
       <c r="E72" s="7" t="n"/>
       <c r="F72" s="7" t="n"/>
       <c r="G72" s="7" t="n"/>
@@ -1712,7 +1712,7 @@
       <c r="C73" s="7" t="n"/>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="E73" s="7" t="n"/>
@@ -1728,7 +1728,7 @@
       <c r="C74" s="7" t="n"/>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="E74" s="7" t="n"/>
@@ -1738,17 +1738,17 @@
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B75" s="7" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
       <c r="C75" s="7" t="n"/>
       <c r="D75" s="7" t="n"/>
       <c r="E75" s="7" t="n"/>
-      <c r="F75" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F75" s="7" t="n"/>
       <c r="G75" s="7" t="n"/>
       <c r="H75" s="7" t="n"/>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C76" s="7" t="n"/>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C77" s="7" t="n"/>
@@ -1788,13 +1788,13 @@
       <c r="A78" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B78" s="7" t="n"/>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
       <c r="C78" s="7" t="n"/>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D78" s="7" t="n"/>
       <c r="E78" s="7" t="n"/>
       <c r="F78" s="7" t="n"/>
       <c r="G78" s="7" t="n"/>
@@ -1806,27 +1806,27 @@
       </c>
       <c r="B79" s="7" t="n"/>
       <c r="C79" s="7" t="n"/>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
+      <c r="D79" s="7" t="n"/>
       <c r="E79" s="7" t="n"/>
-      <c r="F79" s="7" t="n"/>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>Tyler Warren</t>
+        </is>
+      </c>
       <c r="G79" s="7" t="n"/>
       <c r="H79" s="7" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B80" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C80" s="7" t="n"/>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>Jameson Williams</t>
-        </is>
-      </c>
+      <c r="D80" s="7" t="n"/>
       <c r="E80" s="7" t="n"/>
       <c r="F80" s="7" t="n"/>
       <c r="G80" s="7" t="n"/>
@@ -1834,15 +1834,15 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B81" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>Jonathon Brooks</t>
+        </is>
+      </c>
       <c r="C81" s="7" t="n"/>
-      <c r="D81" s="7" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
+      <c r="D81" s="7" t="n"/>
       <c r="E81" s="7" t="n"/>
       <c r="F81" s="7" t="n"/>
       <c r="G81" s="7" t="n"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C82" s="7" t="n"/>
@@ -1868,13 +1868,13 @@
       <c r="A83" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B83" s="7" t="n"/>
       <c r="C83" s="7" t="n"/>
-      <c r="D83" s="7" t="n"/>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
       <c r="E83" s="7" t="n"/>
       <c r="F83" s="7" t="n"/>
       <c r="G83" s="7" t="n"/>
@@ -1884,13 +1884,13 @@
       <c r="A84" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>Jonathon Brooks</t>
-        </is>
-      </c>
+      <c r="B84" s="7" t="n"/>
       <c r="C84" s="7" t="n"/>
-      <c r="D84" s="7" t="n"/>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>Jameson Williams</t>
+        </is>
+      </c>
       <c r="E84" s="7" t="n"/>
       <c r="F84" s="7" t="n"/>
       <c r="G84" s="7" t="n"/>
@@ -1900,13 +1900,13 @@
       <c r="A85" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>Mike Washington Jr.</t>
-        </is>
-      </c>
+      <c r="B85" s="7" t="n"/>
       <c r="C85" s="7" t="n"/>
-      <c r="D85" s="7" t="n"/>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>De'Zhaun Stribling</t>
+        </is>
+      </c>
       <c r="E85" s="7" t="n"/>
       <c r="F85" s="7" t="n"/>
       <c r="G85" s="7" t="n"/>
@@ -1916,13 +1916,13 @@
       <c r="A86" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>Rico Dowdle</t>
-        </is>
-      </c>
+      <c r="B86" s="7" t="n"/>
       <c r="C86" s="7" t="n"/>
-      <c r="D86" s="7" t="n"/>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>Quentin Johnston</t>
+        </is>
+      </c>
       <c r="E86" s="7" t="n"/>
       <c r="F86" s="7" t="n"/>
       <c r="G86" s="7" t="n"/>
@@ -1932,25 +1932,25 @@
       <c r="A87" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B87" s="7" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
+      <c r="B87" s="7" t="n"/>
       <c r="C87" s="7" t="n"/>
       <c r="D87" s="7" t="n"/>
       <c r="E87" s="7" t="n"/>
       <c r="F87" s="7" t="n"/>
       <c r="G87" s="7" t="n"/>
-      <c r="H87" s="7" t="n"/>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C88" s="7" t="n"/>
@@ -1962,15 +1962,15 @@
     </row>
     <row r="89">
       <c r="A89" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B89" s="7" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
       <c r="C89" s="7" t="n"/>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
+      <c r="D89" s="7" t="n"/>
       <c r="E89" s="7" t="n"/>
       <c r="F89" s="7" t="n"/>
       <c r="G89" s="7" t="n"/>
@@ -1978,15 +1978,15 @@
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B90" s="7" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
       <c r="C90" s="7" t="n"/>
-      <c r="D90" s="7" t="inlineStr">
-        <is>
-          <t>De'Zhaun Stribling</t>
-        </is>
-      </c>
+      <c r="D90" s="7" t="n"/>
       <c r="E90" s="7" t="n"/>
       <c r="F90" s="7" t="n"/>
       <c r="G90" s="7" t="n"/>
@@ -1994,13 +1994,13 @@
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B91" s="7" t="n"/>
       <c r="C91" s="7" t="n"/>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="E91" s="7" t="n"/>
@@ -2010,13 +2010,13 @@
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B92" s="7" t="n"/>
       <c r="C92" s="7" t="n"/>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr.</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E92" s="7" t="n"/>
@@ -2026,55 +2026,55 @@
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B93" s="7" t="n"/>
       <c r="C93" s="7" t="n"/>
-      <c r="D93" s="7" t="n"/>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>Chris Godwin Jr.</t>
+        </is>
+      </c>
       <c r="E93" s="7" t="n"/>
-      <c r="F93" s="7" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
+      <c r="F93" s="7" t="n"/>
       <c r="G93" s="7" t="n"/>
       <c r="H93" s="7" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B94" s="7" t="n"/>
       <c r="C94" s="7" t="n"/>
-      <c r="D94" s="7" t="n"/>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="7" t="n"/>
       <c r="G94" s="7" t="n"/>
-      <c r="H94" s="7" t="inlineStr">
-        <is>
-          <t>Jalen Hurts</t>
-        </is>
-      </c>
+      <c r="H94" s="7" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B95" s="7" t="n"/>
       <c r="C95" s="7" t="n"/>
       <c r="D95" s="7" t="n"/>
       <c r="E95" s="7" t="n"/>
-      <c r="F95" s="7" t="n"/>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>Harold Fannin Jr.</t>
+        </is>
+      </c>
       <c r="G95" s="7" t="n"/>
-      <c r="H95" s="7" t="inlineStr">
-        <is>
-          <t>Justin Herbert</t>
-        </is>
-      </c>
+      <c r="H95" s="7" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B96" s="7" t="n"/>
       <c r="C96" s="7" t="n"/>
@@ -2084,7 +2084,7 @@
       <c r="G96" s="7" t="n"/>
       <c r="H96" s="7" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
     </row>
@@ -2094,15 +2094,15 @@
       </c>
       <c r="B97" s="7" t="n"/>
       <c r="C97" s="7" t="n"/>
-      <c r="D97" s="7" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
+      <c r="D97" s="7" t="n"/>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="7" t="n"/>
       <c r="G97" s="7" t="n"/>
-      <c r="H97" s="7" t="n"/>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>Justin Herbert</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
@@ -2110,15 +2110,15 @@
       </c>
       <c r="B98" s="7" t="n"/>
       <c r="C98" s="7" t="n"/>
-      <c r="D98" s="7" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
+      <c r="D98" s="7" t="n"/>
       <c r="E98" s="7" t="n"/>
       <c r="F98" s="7" t="n"/>
       <c r="G98" s="7" t="n"/>
-      <c r="H98" s="7" t="n"/>
+      <c r="H98" s="7" t="inlineStr">
+        <is>
+          <t>Trevor Lawrence</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
@@ -2126,43 +2126,43 @@
       </c>
       <c r="B99" s="7" t="n"/>
       <c r="C99" s="7" t="n"/>
-      <c r="D99" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
+      <c r="D99" s="7" t="n"/>
       <c r="E99" s="7" t="n"/>
       <c r="F99" s="7" t="n"/>
       <c r="G99" s="7" t="n"/>
-      <c r="H99" s="7" t="n"/>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
+          <t>Jaxson Dart</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B100" s="7" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>Rachaad White</t>
+        </is>
+      </c>
       <c r="C100" s="7" t="n"/>
       <c r="D100" s="7" t="n"/>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="7" t="n"/>
       <c r="G100" s="7" t="n"/>
-      <c r="H100" s="7" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
+      <c r="H100" s="7" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B101" s="7" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
+      <c r="B101" s="7" t="n"/>
       <c r="C101" s="7" t="n"/>
-      <c r="D101" s="7" t="n"/>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>Carnell Tate</t>
+        </is>
+      </c>
       <c r="E101" s="7" t="n"/>
       <c r="F101" s="7" t="n"/>
       <c r="G101" s="7" t="n"/>
@@ -2176,7 +2176,7 @@
       <c r="C102" s="7" t="n"/>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E102" s="7" t="n"/>
@@ -2295,7 +2295,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 75.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 76.</t>
         </is>
       </c>
     </row>
@@ -2312,14 +2312,14 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>0) Weekly re-seed. The sheet values were first moved toward the 2026 week 6 Half PPR medians</t>
+          <t>0) Weekly re-seed. The sheet values were first moved toward the 2026 week 7 Half PPR medians</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 12; 11 players used week 5 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 0; 32 players used week 6 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,14 +2333,14 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 71 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 69 players moved.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   No projection this week (value kept): Saquon Barkley, Breece Hall, DeVonta Smith, Rashee Rice, Lamar Jackson, Travis Etienne Jr., Jadarian Price, Josh Jacobs, De'Zhaun Stribling, Jordan Mason, Alec Pierce, Brian Thomas Jr., Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Rico Dowdle, Jaxson Dart, Ja'Kobi Lane.</t>
+          <t xml:space="preserve">   No projection this week (value kept): Amon-Ra St. Brown, Saquon Barkley, Chase Brown, Breece Hall, DeVonta Smith, Rashee Rice, Lamar Jackson, Travis Etienne Jr., Jadarian Price, David Montgomery, Josh Jacobs, De'Zhaun Stribling, Jordan Mason, Alec Pierce, Brian Thomas Jr., Marvin Harrison Jr., Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Aaron Jones Sr., Jaxson Dart, Ja'Kobi Lane.</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.5, WR 2.9, TE 4.5, QB 0.0.</t>
+          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.5, WR 3.0, TE 4.5, QB 0.0.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 62-&gt;54, Chris Olave 41-&gt;33, Trey McBride 42.8571-&gt;35, Puka Nacua 70-&gt;63, Ja'Marr Chase 60-&gt;53, Justin Jefferson 47-&gt;40, Drake London 48-&gt;41, DeVonta Smith 27-&gt;20</t>
+          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 63-&gt;54, Chris Olave 34-&gt;25, Puka Nacua 69-&gt;61, Amon-Ra St. Brown 60-&gt;52, Trey McBride 43.4286-&gt;36, Parker Washington 30.4-&gt;23, Ja'Marr Chase 63-&gt;56, Justin Jefferson 43-&gt;36</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C6" s="7" t="n"/>
@@ -650,15 +650,15 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>61</v>
-      </c>
-      <c r="B7" s="7" t="n"/>
+        <v>64</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Kenneth Walker III</t>
+        </is>
+      </c>
       <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Puka Nacua</t>
-        </is>
-      </c>
+      <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="7" t="n"/>
@@ -666,15 +666,15 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Christian McCaffrey</t>
-        </is>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="B8" s="7" t="n"/>
       <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="7" t="n"/>
@@ -682,7 +682,7 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
@@ -700,13 +700,13 @@
       <c r="A10" s="6" t="n">
         <v>56</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
+      <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Amon-Ra St. Brown</t>
+        </is>
+      </c>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="n"/>
@@ -714,15 +714,15 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>56</v>
-      </c>
-      <c r="B11" s="7" t="n"/>
+        <v>55</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Derrick Henry</t>
+        </is>
+      </c>
       <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Ja'Marr Chase</t>
-        </is>
-      </c>
+      <c r="D11" s="7" t="n"/>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
@@ -730,13 +730,13 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E12" s="7" t="n"/>
@@ -746,13 +746,13 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="E13" s="7" t="n"/>
@@ -782,7 +782,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Ashton Jeanty</t>
         </is>
       </c>
       <c r="C15" s="7" t="n"/>
@@ -796,13 +796,13 @@
       <c r="A16" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
+      <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
@@ -812,13 +812,13 @@
       <c r="A17" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="B17" s="7" t="n"/>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Jonathan Taylor</t>
+        </is>
+      </c>
       <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D17" s="7" t="n"/>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
@@ -858,49 +858,49 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="B22" s="7" t="n"/>
+        <v>35</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C22" s="7" t="n"/>
       <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
     </row>
@@ -908,15 +908,15 @@
       <c r="A23" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+      <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
       <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G23" s="7" t="n"/>
       <c r="H23" s="7" t="n"/>
     </row>
@@ -986,11 +986,11 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C28" s="7" t="n"/>
@@ -1004,13 +1004,13 @@
       <c r="A29" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="B29" s="7" t="n"/>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D29" s="7" t="n"/>
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="7" t="n"/>
@@ -1018,15 +1018,15 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>D'Andre Swift</t>
-        </is>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="n"/>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Nico Collins</t>
+        </is>
+      </c>
       <c r="E30" s="7" t="n"/>
       <c r="F30" s="7" t="n"/>
       <c r="G30" s="7" t="n"/>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
@@ -1050,15 +1050,15 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
@@ -1068,13 +1068,13 @@
       <c r="A33" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="B33" s="7" t="n"/>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Chuba Hubbard</t>
+        </is>
+      </c>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>Chris Olave</t>
-        </is>
-      </c>
+      <c r="D33" s="7" t="n"/>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
@@ -1148,13 +1148,13 @@
       <c r="A38" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="B38" s="7" t="n"/>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
       <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
+      <c r="D38" s="7" t="n"/>
       <c r="E38" s="7" t="n"/>
       <c r="F38" s="7" t="n"/>
       <c r="G38" s="7" t="n"/>
@@ -1168,7 +1168,7 @@
       <c r="C39" s="7" t="n"/>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="E39" s="7" t="n"/>
@@ -1178,15 +1178,15 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="n"/>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Malik Nabers</t>
+        </is>
+      </c>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
@@ -1194,13 +1194,13 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E41" s="7" t="n"/>
@@ -1216,7 +1216,7 @@
       <c r="C42" s="7" t="n"/>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E42" s="7" t="n"/>
@@ -1242,15 +1242,15 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="B44" s="7" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Aaron Jones Sr.</t>
+        </is>
+      </c>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Mike Evans</t>
-        </is>
-      </c>
+      <c r="D44" s="7" t="n"/>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="7" t="n"/>
@@ -1292,13 +1292,13 @@
       <c r="A47" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>Aaron Jones Sr.</t>
-        </is>
-      </c>
+      <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="n"/>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E47" s="7" t="n"/>
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="7" t="n"/>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C51" s="7" t="n"/>
@@ -1372,13 +1372,13 @@
       <c r="A52" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B52" s="7" t="n"/>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>Zay Flowers</t>
-        </is>
-      </c>
+      <c r="D52" s="7" t="n"/>
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="7" t="n"/>
@@ -1386,15 +1386,15 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>Jeremiyah Love</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B53" s="7" t="n"/>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="7" t="n"/>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Zay Flowers</t>
+        </is>
+      </c>
       <c r="E53" s="7" t="n"/>
       <c r="F53" s="7" t="n"/>
       <c r="G53" s="7" t="n"/>
@@ -1418,7 +1418,7 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B55" s="7" t="n"/>
       <c r="C55" s="7" t="n"/>
@@ -1434,7 +1434,7 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B56" s="7" t="n"/>
       <c r="C56" s="7" t="n"/>
@@ -1442,7 +1442,7 @@
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>Colston Loveland</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="G56" s="7" t="n"/>
@@ -1452,25 +1452,25 @@
       <c r="A57" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B57" s="7" t="n"/>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Travis Etienne Jr.</t>
+        </is>
+      </c>
       <c r="C57" s="7" t="n"/>
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
       <c r="H57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr.</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="C58" s="7" t="n"/>
@@ -1482,17 +1482,17 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B59" s="7" t="n"/>
       <c r="C59" s="7" t="n"/>
       <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
-      <c r="F59" s="7" t="n"/>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G59" s="7" t="n"/>
       <c r="H59" s="7" t="n"/>
     </row>
@@ -1546,31 +1546,31 @@
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>David Montgomery</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B63" s="7" t="n"/>
       <c r="C63" s="7" t="n"/>
       <c r="D63" s="7" t="n"/>
       <c r="E63" s="7" t="n"/>
       <c r="F63" s="7" t="n"/>
       <c r="G63" s="7" t="n"/>
-      <c r="H63" s="7" t="n"/>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B64" s="7" t="n"/>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>David Montgomery</t>
+        </is>
+      </c>
       <c r="C64" s="7" t="n"/>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D64" s="7" t="n"/>
       <c r="E64" s="7" t="n"/>
       <c r="F64" s="7" t="n"/>
       <c r="G64" s="7" t="n"/>
@@ -1580,13 +1580,13 @@
       <c r="A65" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B65" s="7" t="n"/>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C65" s="7" t="n"/>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D65" s="7" t="n"/>
       <c r="E65" s="7" t="n"/>
       <c r="F65" s="7" t="n"/>
       <c r="G65" s="7" t="n"/>
@@ -1598,27 +1598,27 @@
       </c>
       <c r="B66" s="7" t="n"/>
       <c r="C66" s="7" t="n"/>
-      <c r="D66" s="7" t="n"/>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E66" s="7" t="n"/>
       <c r="F66" s="7" t="n"/>
       <c r="G66" s="7" t="n"/>
-      <c r="H66" s="7" t="inlineStr">
-        <is>
-          <t>Jayden Daniels</t>
-        </is>
-      </c>
+      <c r="H66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B67" s="7" t="n"/>
       <c r="C67" s="7" t="n"/>
-      <c r="D67" s="7" t="n"/>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E67" s="7" t="n"/>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
@@ -1628,13 +1628,13 @@
       <c r="A68" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B68" s="7" t="n"/>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>TreVeyon Henderson</t>
+        </is>
+      </c>
       <c r="C68" s="7" t="n"/>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D68" s="7" t="n"/>
       <c r="E68" s="7" t="n"/>
       <c r="F68" s="7" t="n"/>
       <c r="G68" s="7" t="n"/>
@@ -1646,29 +1646,29 @@
       </c>
       <c r="B69" s="7" t="n"/>
       <c r="C69" s="7" t="n"/>
-      <c r="D69" s="7" t="n"/>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E69" s="7" t="n"/>
-      <c r="F69" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F69" s="7" t="n"/>
       <c r="G69" s="7" t="n"/>
       <c r="H69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B70" s="7" t="n"/>
       <c r="C70" s="7" t="n"/>
       <c r="D70" s="7" t="n"/>
       <c r="E70" s="7" t="n"/>
-      <c r="F70" s="7" t="n"/>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G70" s="7" t="n"/>
       <c r="H70" s="7" t="n"/>
     </row>
@@ -1676,13 +1676,13 @@
       <c r="A71" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B71" s="7" t="n"/>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
       <c r="C71" s="7" t="n"/>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
+      <c r="D71" s="7" t="n"/>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
@@ -1692,13 +1692,13 @@
       <c r="A72" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B72" s="7" t="n"/>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
       <c r="C72" s="7" t="n"/>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>DK Metcalf</t>
-        </is>
-      </c>
+      <c r="D72" s="7" t="n"/>
       <c r="E72" s="7" t="n"/>
       <c r="F72" s="7" t="n"/>
       <c r="G72" s="7" t="n"/>
@@ -1712,7 +1712,7 @@
       <c r="C73" s="7" t="n"/>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr.</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="E73" s="7" t="n"/>
@@ -1728,7 +1728,7 @@
       <c r="C74" s="7" t="n"/>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E74" s="7" t="n"/>
@@ -1738,15 +1738,15 @@
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B75" s="7" t="n"/>
       <c r="C75" s="7" t="n"/>
-      <c r="D75" s="7" t="n"/>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>Brian Thomas Jr.</t>
+        </is>
+      </c>
       <c r="E75" s="7" t="n"/>
       <c r="F75" s="7" t="n"/>
       <c r="G75" s="7" t="n"/>
@@ -1754,15 +1754,15 @@
     </row>
     <row r="76">
       <c r="A76" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>Cam Skattebo</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B76" s="7" t="n"/>
       <c r="C76" s="7" t="n"/>
-      <c r="D76" s="7" t="n"/>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>Marvin Harrison Jr.</t>
+        </is>
+      </c>
       <c r="E76" s="7" t="n"/>
       <c r="F76" s="7" t="n"/>
       <c r="G76" s="7" t="n"/>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="C77" s="7" t="n"/>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Woody Marks</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C78" s="7" t="n"/>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C80" s="7" t="n"/>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C81" s="7" t="n"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="C82" s="7" t="n"/>
@@ -2295,7 +2295,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 76.</t>
+          <t>Baseline: the live Trade Values Google Sheet (Half PPR, 10-team), 104 players, top value 75.</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Projections page snapshot 0; 32 players used week 6 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
+          <t xml:space="preserve">   (Projections page snapshot 1; 30 players used week 6 medians): implied = 0.7 x the seed value at the player's projection-rank slot among the projected players at the position + 0.3 x</t>
         </is>
       </c>
     </row>
@@ -2333,14 +2333,14 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 69 players moved.</t>
+          <t xml:space="preserve">   new = sheet + 0.45 x (implied - sheet), then rescaled so the total equals the sheet total. 70 players moved.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   No projection this week (value kept): Amon-Ra St. Brown, Saquon Barkley, Chase Brown, Breece Hall, DeVonta Smith, Rashee Rice, Lamar Jackson, Travis Etienne Jr., Jadarian Price, David Montgomery, Josh Jacobs, De'Zhaun Stribling, Jordan Mason, Alec Pierce, Brian Thomas Jr., Marvin Harrison Jr., Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Aaron Jones Sr., Jaxson Dart, Ja'Kobi Lane.</t>
+          <t xml:space="preserve">   No projection this week (value kept): Saquon Barkley, Chase Brown, Breece Hall, DeVonta Smith, Rashee Rice, Lamar Jackson, Travis Etienne Jr., Jadarian Price, David Montgomery, Josh Jacobs, De'Zhaun Stribling, Jordan Mason, Alec Pierce, Brian Thomas Jr., Marvin Harrison Jr., Jonathon Brooks, Jayden Reed, Mike Washington Jr., Jordyn Tyson, Aaron Jones Sr., Jaxson Dart, Ja'Kobi Lane.</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.5, WR 3.0, TE 4.5, QB 0.0.</t>
+          <t xml:space="preserve">   Replacement level = average line of baseline players valued 5 or less at the position: RB 1.7, WR 3.0, TE 4.5, QB 0.0.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 63-&gt;54, Chris Olave 34-&gt;25, Puka Nacua 69-&gt;61, Amon-Ra St. Brown 60-&gt;52, Trey McBride 43.4286-&gt;36, Parker Washington 30.4-&gt;23, Ja'Marr Chase 63-&gt;56, Justin Jefferson 43-&gt;36</t>
+          <t>Largest moves vs. the baseline in this file: Jaxon Smith-Njigba 61-&gt;53, Chris Olave 34-&gt;26, Trey McBride 42.8571-&gt;35, Puka Nacua 69-&gt;62, Ja'Marr Chase 62-&gt;55, Amon-Ra St. Brown 63-&gt;56, Justin Jefferson 46-&gt;39, Drake London 41-&gt;34</t>
         </is>
       </c>
     </row>

--- a/TradeValueSheets/TradeValues_Standard_12team.xlsx
+++ b/TradeValueSheets/TradeValues_Standard_12team.xlsx
@@ -666,7 +666,7 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B8" s="7" t="n"/>
       <c r="C8" s="7" t="n"/>
@@ -682,7 +682,7 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
       <c r="C10" s="7" t="n"/>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="E10" s="7" t="n"/>
@@ -730,13 +730,13 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="E12" s="7" t="n"/>
@@ -746,13 +746,13 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E13" s="7" t="n"/>
@@ -762,11 +762,11 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C14" s="7" t="n"/>
@@ -778,7 +778,7 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
@@ -794,15 +794,15 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="B16" s="7" t="n"/>
+        <v>46</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Kyren Williams</t>
+        </is>
+      </c>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>CeeDee Lamb</t>
-        </is>
-      </c>
+      <c r="D16" s="7" t="n"/>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
@@ -812,13 +812,13 @@
       <c r="A17" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Jonathan Taylor</t>
-        </is>
-      </c>
+      <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>CeeDee Lamb</t>
+        </is>
+      </c>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
@@ -842,15 +842,15 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Justin Jefferson</t>
+        </is>
+      </c>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
@@ -858,49 +858,49 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Justin Jefferson</t>
-        </is>
-      </c>
+      <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="n"/>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>Drake Maye</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="B21" s="7" t="n"/>
+        <v>36</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Javonte Williams</t>
+        </is>
+      </c>
       <c r="C21" s="7" t="n"/>
       <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>Drake Maye</t>
-        </is>
-      </c>
+      <c r="H21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
       <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Trey McBride</t>
+        </is>
+      </c>
       <c r="G22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
     </row>
@@ -910,27 +910,27 @@
       </c>
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Drake London</t>
+        </is>
+      </c>
       <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
+      <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
       <c r="H23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="B24" s="7" t="n"/>
+        <v>33</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
       <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Drake London</t>
-        </is>
-      </c>
+      <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
@@ -940,31 +940,31 @@
       <c r="A25" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
+      <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Brock Bowers</t>
+        </is>
+      </c>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="B26" s="7" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Chase Brown</t>
+        </is>
+      </c>
       <c r="C26" s="7" t="n"/>
       <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
+      <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="7" t="n"/>
     </row>
@@ -1004,13 +1004,13 @@
       <c r="A29" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
+      <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Chris Olave</t>
+        </is>
+      </c>
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="7" t="n"/>
@@ -1018,15 +1018,15 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="B30" s="7" t="n"/>
+        <v>29</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Bhayshul Tuten</t>
+        </is>
+      </c>
       <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Nico Collins</t>
-        </is>
-      </c>
+      <c r="D30" s="7" t="n"/>
       <c r="E30" s="7" t="n"/>
       <c r="F30" s="7" t="n"/>
       <c r="G30" s="7" t="n"/>
@@ -1034,13 +1034,13 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Nico Collins</t>
         </is>
       </c>
       <c r="E31" s="7" t="n"/>
@@ -1050,13 +1050,13 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E32" s="7" t="n"/>
@@ -1184,7 +1184,7 @@
       <c r="C40" s="7" t="n"/>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E40" s="7" t="n"/>
@@ -1216,7 +1216,7 @@
       <c r="C42" s="7" t="n"/>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="E42" s="7" t="n"/>
@@ -1226,13 +1226,13 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B43" s="7" t="n"/>
       <c r="C43" s="7" t="n"/>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="E43" s="7" t="n"/>
@@ -1296,7 +1296,7 @@
       <c r="C47" s="7" t="n"/>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E47" s="7" t="n"/>
@@ -1306,15 +1306,15 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B48" s="7" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Jadarian Price</t>
+        </is>
+      </c>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
+      <c r="D48" s="7" t="n"/>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
@@ -1322,11 +1322,11 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C49" s="7" t="n"/>
@@ -1338,11 +1338,11 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C50" s="7" t="n"/>
@@ -1354,7 +1354,7 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
@@ -1370,15 +1370,15 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B52" s="7" t="n"/>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="7" t="n"/>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Davante Adams</t>
+        </is>
+      </c>
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="7" t="n"/>
@@ -1386,7 +1386,7 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B53" s="7" t="n"/>
       <c r="C53" s="7" t="n"/>
@@ -1408,7 +1408,7 @@
       <c r="C54" s="7" t="n"/>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="E54" s="7" t="n"/>
@@ -1418,15 +1418,15 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B55" s="7" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Bucky Irving</t>
+        </is>
+      </c>
       <c r="C55" s="7" t="n"/>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
+      <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
       <c r="F55" s="7" t="n"/>
       <c r="G55" s="7" t="n"/>
@@ -1434,17 +1434,17 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B56" s="7" t="n"/>
       <c r="C56" s="7" t="n"/>
-      <c r="D56" s="7" t="n"/>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Garrett Wilson</t>
+        </is>
+      </c>
       <c r="E56" s="7" t="n"/>
-      <c r="F56" s="7" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
+      <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="n"/>
       <c r="H56" s="7" t="n"/>
     </row>
@@ -1452,25 +1452,25 @@
       <c r="A57" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>Travis Etienne Jr.</t>
-        </is>
-      </c>
+      <c r="B57" s="7" t="n"/>
       <c r="C57" s="7" t="n"/>
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
-      <c r="F57" s="7" t="n"/>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>Colston Loveland</t>
+        </is>
+      </c>
       <c r="G57" s="7" t="n"/>
       <c r="H57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C58" s="7" t="n"/>
@@ -1482,17 +1482,17 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B59" s="7" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>J.K. Dobbins</t>
+        </is>
+      </c>
       <c r="C59" s="7" t="n"/>
       <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>Colston Loveland</t>
-        </is>
-      </c>
+      <c r="F59" s="7" t="n"/>
       <c r="G59" s="7" t="n"/>
       <c r="H59" s="7" t="n"/>
     </row>
@@ -1500,13 +1500,13 @@
       <c r="A60" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
+      <c r="B60" s="7" t="n"/>
       <c r="C60" s="7" t="n"/>
-      <c r="D60" s="7" t="n"/>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
       <c r="E60" s="7" t="n"/>
       <c r="F60" s="7" t="n"/>
       <c r="G60" s="7" t="n"/>
@@ -1514,19 +1514,19 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="n"/>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Ladd McConkey</t>
+        </is>
+      </c>
       <c r="E61" s="7" t="n"/>
       <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
+      <c r="H61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
@@ -1534,13 +1534,13 @@
       </c>
       <c r="B62" s="7" t="n"/>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>Ladd McConkey</t>
-        </is>
-      </c>
+      <c r="D62" s="7" t="n"/>
       <c r="E62" s="7" t="n"/>
-      <c r="F62" s="7" t="n"/>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
       <c r="G62" s="7" t="n"/>
       <c r="H62" s="7" t="n"/>
     </row>
@@ -1556,7 +1556,7 @@
       <c r="G63" s="7" t="n"/>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Joe Burrow</t>
         </is>
       </c>
     </row>
@@ -1580,13 +1580,13 @@
       <c r="A65" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>Josh Jacobs</t>
-        </is>
-      </c>
+      <c r="B65" s="7" t="n"/>
       <c r="C65" s="7" t="n"/>
-      <c r="D65" s="7" t="n"/>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>Rome Odunze</t>
+        </is>
+      </c>
       <c r="E65" s="7" t="n"/>
       <c r="F65" s="7" t="n"/>
       <c r="G65" s="7" t="n"/>
@@ -1598,13 +1598,13 @@
       </c>
       <c r="B66" s="7" t="n"/>
       <c r="C66" s="7" t="n"/>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
+      <c r="D66" s="7" t="n"/>
       <c r="E66" s="7" t="n"/>
-      <c r="F66" s="7" t="n"/>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>Tucker Kraft</t>
+        </is>
+      </c>
       <c r="G66" s="7" t="n"/>
       <c r="H66" s="7" t="n"/>
     </row>
@@ -1614,15 +1614,15 @@
       </c>
       <c r="B67" s="7" t="n"/>
       <c r="C67" s="7" t="n"/>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>Rome Odunze</t>
-        </is>
-      </c>
+      <c r="D67" s="7" t="n"/>
       <c r="E67" s="7" t="n"/>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
-      <c r="H67" s="7" t="n"/>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>Jayden Daniels</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
@@ -1644,13 +1644,13 @@
       <c r="A69" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B69" s="7" t="n"/>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
       <c r="C69" s="7" t="n"/>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>Emeka Egbuka</t>
-        </is>
-      </c>
+      <c r="D69" s="7" t="n"/>
       <c r="E69" s="7" t="n"/>
       <c r="F69" s="7" t="n"/>
       <c r="G69" s="7" t="n"/>
@@ -1662,13 +1662,13 @@
       </c>
       <c r="B70" s="7" t="n"/>
       <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="n"/>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Emeka Egbuka</t>
+        </is>
+      </c>
       <c r="E70" s="7" t="n"/>
-      <c r="F70" s="7" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
+      <c r="F70" s="7" t="n"/>
       <c r="G70" s="7" t="n"/>
       <c r="H70" s="7" t="n"/>
     </row>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C71" s="7" t="n"/>
@@ -1692,13 +1692,13 @@
       <c r="A72" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
- 